--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,8 +47,24 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001A6FA8"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00744210"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -75,8 +91,43 @@
         <fgColor rgb="00F0F4F8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6F6D5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF8FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -112,11 +163,25 @@
         <color rgb="00DDDDDD"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00EEEEEE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00EEEEEE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00EEEEEE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00EEEEEE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -137,6 +202,33 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -503,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -600,6 +692,1186 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>91f378388bbb</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Water Engineer/Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>ALDWYCH CONSULTING LTD</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>South East London, London</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K2" s="12" t="inlineStr"/>
+      <c r="L2" s="12" t="inlineStr"/>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N2" s="13" t="inlineStr"/>
+      <c r="O2" s="12" t="inlineStr"/>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>33d1e821e300</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Water Engineer/Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Aldwych Consulting Ltd</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>£40,000 – £48,000</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K3" s="16" t="inlineStr"/>
+      <c r="L3" s="16" t="inlineStr"/>
+      <c r="M3" s="16" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N3" s="17" t="inlineStr"/>
+      <c r="O3" s="16" t="inlineStr"/>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>12d728954ff6</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Water Engineer/Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Aldwych Consulting</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>£40,000 – £48,000</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr"/>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N4" s="13" t="inlineStr"/>
+      <c r="O4" s="12" t="inlineStr"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>0034bed26e43</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Senior Civil Engineer, Water</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>St. Albans, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>£42,509 – £42,509</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="inlineStr"/>
+      <c r="L5" s="16" t="inlineStr"/>
+      <c r="M5" s="16" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N5" s="17" t="inlineStr"/>
+      <c r="O5" s="16" t="inlineStr"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>d0e6c96fa336</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Senior Civil Engineer, Water</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>£43,633 – £43,633</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr"/>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N6" s="13" t="inlineStr"/>
+      <c r="O6" s="12" t="inlineStr"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>ee386e08a3ca</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Thames Water</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Caversham, Reading</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>£42,640 – £55,000</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr"/>
+      <c r="L7" s="16" t="inlineStr"/>
+      <c r="M7" s="16" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N7" s="17" t="inlineStr"/>
+      <c r="O7" s="16" t="inlineStr"/>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>d578bc4c768f</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Recruiter</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>£42,640 – £55,000</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr"/>
+      <c r="L8" s="12" t="inlineStr"/>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N8" s="13" t="inlineStr"/>
+      <c r="O8" s="12" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>9dc5b325f2eb</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>SSA Recruitment</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>West Hampstead, North West London</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>£55,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="J9" s="15" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="inlineStr"/>
+      <c r="L9" s="16" t="inlineStr"/>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N9" s="17" t="inlineStr"/>
+      <c r="O9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>aabe29c643e4</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Senior Water Network Engineer/Modellers</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>£50,253 – £50,253</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr"/>
+      <c r="L10" s="12" t="inlineStr"/>
+      <c r="M10" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N10" s="13" t="inlineStr"/>
+      <c r="O10" s="12" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>c87e01af5979</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>£48,252 – £48,252</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="J11" s="15" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr"/>
+      <c r="L11" s="16" t="inlineStr"/>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N11" s="17" t="inlineStr"/>
+      <c r="O11" s="16" t="inlineStr"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>c43e11ff8ca9</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>£49,369 – £49,369</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K12" s="12" t="inlineStr"/>
+      <c r="L12" s="12" t="inlineStr"/>
+      <c r="M12" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N12" s="13" t="inlineStr"/>
+      <c r="O12" s="12" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>554b6c540a31</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>High Wycombe, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>£50,309 – £50,309</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="J13" s="15" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K13" s="16" t="inlineStr"/>
+      <c r="L13" s="16" t="inlineStr"/>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N13" s="17" t="inlineStr"/>
+      <c r="O13" s="16" t="inlineStr"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>6b5e6cd83ae0</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>£50,558 – £50,558</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr"/>
+      <c r="L14" s="12" t="inlineStr"/>
+      <c r="M14" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N14" s="13" t="inlineStr"/>
+      <c r="O14" s="12" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>1cbc31004a24</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Stantec UK</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Caversham, Reading</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>£44,336 – £44,336</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K15" s="16" t="inlineStr"/>
+      <c r="L15" s="16" t="inlineStr"/>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N15" s="17" t="inlineStr"/>
+      <c r="O15" s="16" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>42be6efe69a3</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Senior Mechanical Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>St. Albans, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>£46,954 – £46,954</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr"/>
+      <c r="L16" s="12" t="inlineStr"/>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N16" s="13" t="inlineStr"/>
+      <c r="O16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>2a82b73d433a</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Senior Mechanical Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>£47,744 – £47,744</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K17" s="16" t="inlineStr"/>
+      <c r="L17" s="16" t="inlineStr"/>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N17" s="17" t="inlineStr"/>
+      <c r="O17" s="16" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>dfe15f60b7a2</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Senior Mechanical Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>£46,355 – £46,355</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr"/>
+      <c r="L18" s="12" t="inlineStr"/>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N18" s="13" t="inlineStr"/>
+      <c r="O18" s="12" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>b296d50b7dce</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Quantity Surveyors THAMES</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Matchtech</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>£45,000 – £75,000</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="J19" s="15" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K19" s="16" t="inlineStr"/>
+      <c r="L19" s="16" t="inlineStr"/>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N19" s="17" t="inlineStr"/>
+      <c r="O19" s="16" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>795cc27c4699</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Electrical Engineer</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Mott MacDonald</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>£51,358 – £51,358</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K20" s="12" t="inlineStr"/>
+      <c r="L20" s="12" t="inlineStr"/>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N20" s="13" t="inlineStr"/>
+      <c r="O20" s="12" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>ec0341cc70f7</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="J21" s="15" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K21" s="16" t="inlineStr"/>
+      <c r="L21" s="16" t="inlineStr"/>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N21" s="17" t="inlineStr"/>
+      <c r="O21" s="16" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -612,6 +1884,28 @@
       <formula1>"Too junior / entry level,Too senior / overqualified,Wrong sector / not water,Wrong location / too far,Salary too low,Contract / not permanent,Missing required licence/cert,Company culture / reputation,Role not interesting,Duplicate / already applied,Other"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" style="18" min="1" max="1"/>
@@ -4792,6 +4792,1304 @@
       </c>
       <c r="N67" s="28" t="inlineStr"/>
       <c r="O67" s="27" t="inlineStr"/>
+    </row>
+    <row r="68" ht="16" customHeight="1" s="18">
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>3cc76a590309</t>
+        </is>
+      </c>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D68" s="20" t="inlineStr">
+        <is>
+          <t>CHARTWELL</t>
+        </is>
+      </c>
+      <c r="E68" s="20" t="inlineStr">
+        <is>
+          <t>Chatham, Kent</t>
+        </is>
+      </c>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G68" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H68" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I68" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J68" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K68" s="23" t="inlineStr"/>
+      <c r="L68" s="23" t="inlineStr"/>
+      <c r="M68" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N68" s="24" t="inlineStr"/>
+      <c r="O68" s="23" t="inlineStr"/>
+    </row>
+    <row r="69" ht="16" customHeight="1" s="18">
+      <c r="A69" s="25" t="inlineStr">
+        <is>
+          <t>e10f2dece6c9</t>
+        </is>
+      </c>
+      <c r="B69" s="25" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C69" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D69" s="25" t="inlineStr">
+        <is>
+          <t>Reed</t>
+        </is>
+      </c>
+      <c r="E69" s="25" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F69" s="25" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G69" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H69" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I69" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J69" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K69" s="27" t="inlineStr"/>
+      <c r="L69" s="27" t="inlineStr"/>
+      <c r="M69" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N69" s="28" t="inlineStr"/>
+      <c r="O69" s="27" t="inlineStr"/>
+    </row>
+    <row r="70" ht="16" customHeight="1" s="18">
+      <c r="A70" s="20" t="inlineStr">
+        <is>
+          <t>a53e7816643f</t>
+        </is>
+      </c>
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="inlineStr">
+        <is>
+          <t>Civil Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="inlineStr">
+        <is>
+          <t>Zodiac Recruitment</t>
+        </is>
+      </c>
+      <c r="E70" s="20" t="inlineStr">
+        <is>
+          <t>Stone Cross, Crowborough</t>
+        </is>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>£32,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G70" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H70" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I70" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J70" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K70" s="23" t="inlineStr"/>
+      <c r="L70" s="23" t="inlineStr"/>
+      <c r="M70" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N70" s="24" t="inlineStr"/>
+      <c r="O70" s="23" t="inlineStr"/>
+    </row>
+    <row r="71" ht="16" customHeight="1" s="18">
+      <c r="A71" s="25" t="inlineStr">
+        <is>
+          <t>5e80718f8434</t>
+        </is>
+      </c>
+      <c r="B71" s="25" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C71" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D71" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E71" s="25" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F71" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G71" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H71" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I71" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J71" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K71" s="27" t="inlineStr"/>
+      <c r="L71" s="27" t="inlineStr"/>
+      <c r="M71" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N71" s="28" t="inlineStr"/>
+      <c r="O71" s="27" t="inlineStr"/>
+    </row>
+    <row r="72" ht="16" customHeight="1" s="18">
+      <c r="A72" s="20" t="inlineStr">
+        <is>
+          <t>b2bb64cff677</t>
+        </is>
+      </c>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D72" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E72" s="20" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F72" s="20" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G72" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H72" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I72" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J72" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K72" s="23" t="inlineStr"/>
+      <c r="L72" s="23" t="inlineStr"/>
+      <c r="M72" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N72" s="24" t="inlineStr"/>
+      <c r="O72" s="23" t="inlineStr"/>
+    </row>
+    <row r="73" ht="16" customHeight="1" s="18">
+      <c r="A73" s="25" t="inlineStr">
+        <is>
+          <t>21e8b262812c</t>
+        </is>
+      </c>
+      <c r="B73" s="25" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C73" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D73" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E73" s="25" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F73" s="25" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G73" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H73" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I73" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J73" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K73" s="27" t="inlineStr"/>
+      <c r="L73" s="27" t="inlineStr"/>
+      <c r="M73" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N73" s="28" t="inlineStr"/>
+      <c r="O73" s="27" t="inlineStr"/>
+    </row>
+    <row r="74" ht="16" customHeight="1" s="18">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>082ff5987df9</t>
+        </is>
+      </c>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D74" s="20" t="inlineStr">
+        <is>
+          <t>SSA Recruitment</t>
+        </is>
+      </c>
+      <c r="E74" s="20" t="inlineStr">
+        <is>
+          <t>West Hampstead, North West London</t>
+        </is>
+      </c>
+      <c r="F74" s="20" t="inlineStr">
+        <is>
+          <t>£55,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G74" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H74" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I74" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="J74" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K74" s="23" t="inlineStr"/>
+      <c r="L74" s="23" t="inlineStr"/>
+      <c r="M74" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N74" s="24" t="inlineStr"/>
+      <c r="O74" s="23" t="inlineStr"/>
+    </row>
+    <row r="75" ht="16" customHeight="1" s="18">
+      <c r="A75" s="25" t="inlineStr">
+        <is>
+          <t>cfb059c12371</t>
+        </is>
+      </c>
+      <c r="B75" s="25" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C75" s="25" t="inlineStr">
+        <is>
+          <t>Senior Water Network Engineer/Modellers</t>
+        </is>
+      </c>
+      <c r="D75" s="25" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E75" s="25" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F75" s="25" t="inlineStr">
+        <is>
+          <t>£50,253 – £50,253</t>
+        </is>
+      </c>
+      <c r="G75" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H75" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I75" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="J75" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K75" s="27" t="inlineStr"/>
+      <c r="L75" s="27" t="inlineStr"/>
+      <c r="M75" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N75" s="28" t="inlineStr"/>
+      <c r="O75" s="27" t="inlineStr"/>
+    </row>
+    <row r="76" ht="16" customHeight="1" s="18">
+      <c r="A76" s="20" t="inlineStr">
+        <is>
+          <t>b20a3074d918</t>
+        </is>
+      </c>
+      <c r="B76" s="20" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D76" s="20" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E76" s="20" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F76" s="20" t="inlineStr">
+        <is>
+          <t>£48,252 – £48,252</t>
+        </is>
+      </c>
+      <c r="G76" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H76" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I76" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="J76" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K76" s="23" t="inlineStr"/>
+      <c r="L76" s="23" t="inlineStr"/>
+      <c r="M76" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N76" s="24" t="inlineStr"/>
+      <c r="O76" s="23" t="inlineStr"/>
+    </row>
+    <row r="77" ht="16" customHeight="1" s="18">
+      <c r="A77" s="25" t="inlineStr">
+        <is>
+          <t>8a98b7dd77e0</t>
+        </is>
+      </c>
+      <c r="B77" s="25" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="25" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D77" s="25" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E77" s="25" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F77" s="25" t="inlineStr">
+        <is>
+          <t>£49,369 – £49,369</t>
+        </is>
+      </c>
+      <c r="G77" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H77" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I77" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="J77" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K77" s="27" t="inlineStr"/>
+      <c r="L77" s="27" t="inlineStr"/>
+      <c r="M77" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N77" s="28" t="inlineStr"/>
+      <c r="O77" s="27" t="inlineStr"/>
+    </row>
+    <row r="78" ht="16" customHeight="1" s="18">
+      <c r="A78" s="20" t="inlineStr">
+        <is>
+          <t>7a3589942e7e</t>
+        </is>
+      </c>
+      <c r="B78" s="20" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="inlineStr">
+        <is>
+          <t>Senior Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D78" s="20" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment</t>
+        </is>
+      </c>
+      <c r="E78" s="20" t="inlineStr">
+        <is>
+          <t>Denner Hill, Great Missenden</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>£38,000 – £60,000</t>
+        </is>
+      </c>
+      <c r="G78" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H78" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I78" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J78" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K78" s="23" t="inlineStr"/>
+      <c r="L78" s="23" t="inlineStr"/>
+      <c r="M78" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N78" s="24" t="inlineStr"/>
+      <c r="O78" s="23" t="inlineStr"/>
+    </row>
+    <row r="79" ht="16" customHeight="1" s="18">
+      <c r="A79" s="25" t="inlineStr">
+        <is>
+          <t>9aac4a1e70a8</t>
+        </is>
+      </c>
+      <c r="B79" s="25" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="25" t="inlineStr">
+        <is>
+          <t>Assistant Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D79" s="25" t="inlineStr">
+        <is>
+          <t>Henley Chase</t>
+        </is>
+      </c>
+      <c r="E79" s="25" t="inlineStr">
+        <is>
+          <t>New Haw, Addlestone</t>
+        </is>
+      </c>
+      <c r="F79" s="25" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G79" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H79" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I79" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J79" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K79" s="27" t="inlineStr"/>
+      <c r="L79" s="27" t="inlineStr"/>
+      <c r="M79" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N79" s="28" t="inlineStr"/>
+      <c r="O79" s="27" t="inlineStr"/>
+    </row>
+    <row r="80" ht="16" customHeight="1" s="18">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>ced6971fdf3b</t>
+        </is>
+      </c>
+      <c r="B80" s="20" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="inlineStr">
+        <is>
+          <t>Junior Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D80" s="20" t="inlineStr">
+        <is>
+          <t>Henley Chase Limited</t>
+        </is>
+      </c>
+      <c r="E80" s="20" t="inlineStr">
+        <is>
+          <t>Addlestone, Surrey</t>
+        </is>
+      </c>
+      <c r="F80" s="20" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G80" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H80" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I80" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J80" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K80" s="23" t="inlineStr"/>
+      <c r="L80" s="23" t="inlineStr"/>
+      <c r="M80" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N80" s="24" t="inlineStr"/>
+      <c r="O80" s="23" t="inlineStr"/>
+    </row>
+    <row r="81" ht="16" customHeight="1" s="18">
+      <c r="A81" s="25" t="inlineStr">
+        <is>
+          <t>5315e7bcce86</t>
+        </is>
+      </c>
+      <c r="B81" s="25" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D81" s="25" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E81" s="25" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F81" s="25" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G81" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H81" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I81" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J81" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K81" s="27" t="inlineStr"/>
+      <c r="L81" s="27" t="inlineStr"/>
+      <c r="M81" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N81" s="28" t="inlineStr"/>
+      <c r="O81" s="27" t="inlineStr"/>
+    </row>
+    <row r="82" ht="16" customHeight="1" s="18">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>f1fd4eec6034</t>
+        </is>
+      </c>
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="inlineStr">
+        <is>
+          <t>Assistant Engineer - Clean Water Modelling</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="inlineStr">
+        <is>
+          <t>WSP</t>
+        </is>
+      </c>
+      <c r="E82" s="20" t="inlineStr">
+        <is>
+          <t>Aldwych, Central London</t>
+        </is>
+      </c>
+      <c r="F82" s="20" t="inlineStr">
+        <is>
+          <t>£45,719 – £45,719</t>
+        </is>
+      </c>
+      <c r="G82" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H82" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I82" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J82" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K82" s="23" t="inlineStr"/>
+      <c r="L82" s="23" t="inlineStr"/>
+      <c r="M82" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N82" s="24" t="inlineStr"/>
+      <c r="O82" s="23" t="inlineStr"/>
+    </row>
+    <row r="83" ht="16" customHeight="1" s="18">
+      <c r="A83" s="25" t="inlineStr">
+        <is>
+          <t>0281ed9ec1ae</t>
+        </is>
+      </c>
+      <c r="B83" s="25" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D83" s="25" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E83" s="25" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F83" s="25" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G83" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H83" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I83" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J83" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K83" s="27" t="inlineStr"/>
+      <c r="L83" s="27" t="inlineStr"/>
+      <c r="M83" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N83" s="28" t="inlineStr"/>
+      <c r="O83" s="27" t="inlineStr"/>
+    </row>
+    <row r="84" ht="16" customHeight="1" s="18">
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>2aa61d5c1bc0</t>
+        </is>
+      </c>
+      <c r="B84" s="20" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C84" s="20" t="inlineStr">
+        <is>
+          <t>Pollution Response Technician</t>
+        </is>
+      </c>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>Lanes Group</t>
+        </is>
+      </c>
+      <c r="E84" s="20" t="inlineStr">
+        <is>
+          <t>Tudeley, Tonbridge</t>
+        </is>
+      </c>
+      <c r="F84" s="20" t="inlineStr">
+        <is>
+          <t>£54,416 – £54,416</t>
+        </is>
+      </c>
+      <c r="G84" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H84" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I84" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J84" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K84" s="23" t="inlineStr"/>
+      <c r="L84" s="23" t="inlineStr"/>
+      <c r="M84" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N84" s="24" t="inlineStr"/>
+      <c r="O84" s="23" t="inlineStr"/>
+    </row>
+    <row r="85" ht="16" customHeight="1" s="18">
+      <c r="A85" s="25" t="inlineStr">
+        <is>
+          <t>aa3b3fa4f83d</t>
+        </is>
+      </c>
+      <c r="B85" s="25" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="25" t="inlineStr">
+        <is>
+          <t>Electrical Project/Design Engineer</t>
+        </is>
+      </c>
+      <c r="D85" s="25" t="inlineStr">
+        <is>
+          <t>Matchtech</t>
+        </is>
+      </c>
+      <c r="E85" s="25" t="inlineStr">
+        <is>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="F85" s="25" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G85" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H85" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I85" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="J85" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K85" s="27" t="inlineStr"/>
+      <c r="L85" s="27" t="inlineStr"/>
+      <c r="M85" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N85" s="28" t="inlineStr"/>
+      <c r="O85" s="27" t="inlineStr"/>
+    </row>
+    <row r="86" ht="16" customHeight="1" s="18">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>8ea18a6807e9</t>
+        </is>
+      </c>
+      <c r="B86" s="20" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="20" t="inlineStr">
+        <is>
+          <t>Civil Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="D86" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E86" s="20" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F86" s="20" t="inlineStr">
+        <is>
+          <t>£55,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G86" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H86" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I86" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="J86" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K86" s="23" t="inlineStr"/>
+      <c r="L86" s="23" t="inlineStr"/>
+      <c r="M86" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N86" s="24" t="inlineStr"/>
+      <c r="O86" s="23" t="inlineStr"/>
+    </row>
+    <row r="87" ht="16" customHeight="1" s="18">
+      <c r="A87" s="25" t="inlineStr">
+        <is>
+          <t>cdd628fe785b</t>
+        </is>
+      </c>
+      <c r="B87" s="25" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="25" t="inlineStr">
+        <is>
+          <t>Civil Engineer Hybrid</t>
+        </is>
+      </c>
+      <c r="D87" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E87" s="25" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F87" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G87" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H87" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I87" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="J87" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K87" s="27" t="inlineStr"/>
+      <c r="L87" s="27" t="inlineStr"/>
+      <c r="M87" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N87" s="28" t="inlineStr"/>
+      <c r="O87" s="27" t="inlineStr"/>
+    </row>
+    <row r="88" ht="16" customHeight="1" s="18">
+      <c r="A88" s="20" t="inlineStr">
+        <is>
+          <t>02e7c1dc067d</t>
+        </is>
+      </c>
+      <c r="B88" s="20" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="20" t="inlineStr">
+        <is>
+          <t>Civil Engineer (Water industry)</t>
+        </is>
+      </c>
+      <c r="D88" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E88" s="20" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F88" s="20" t="inlineStr">
+        <is>
+          <t>£55,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G88" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H88" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I88" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="J88" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K88" s="23" t="inlineStr"/>
+      <c r="L88" s="23" t="inlineStr"/>
+      <c r="M88" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N88" s="24" t="inlineStr"/>
+      <c r="O88" s="23" t="inlineStr"/>
+    </row>
+    <row r="89" ht="16" customHeight="1" s="18">
+      <c r="A89" s="25" t="inlineStr">
+        <is>
+          <t>cd6504ff076a</t>
+        </is>
+      </c>
+      <c r="B89" s="25" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="25" t="inlineStr">
+        <is>
+          <t>Civil Engineer Water industry</t>
+        </is>
+      </c>
+      <c r="D89" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E89" s="25" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F89" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G89" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H89" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I89" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="J89" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K89" s="27" t="inlineStr"/>
+      <c r="L89" s="27" t="inlineStr"/>
+      <c r="M89" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N89" s="28" t="inlineStr"/>
+      <c r="O89" s="27" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -4872,6 +6170,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" style="18" min="1" max="1"/>
@@ -6090,6 +6090,1540 @@
       </c>
       <c r="N89" s="28" t="inlineStr"/>
       <c r="O89" s="27" t="inlineStr"/>
+    </row>
+    <row r="90" ht="16" customHeight="1" s="18">
+      <c r="A90" s="20" t="inlineStr">
+        <is>
+          <t>ad5a339f93f7</t>
+        </is>
+      </c>
+      <c r="B90" s="20" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D90" s="20" t="inlineStr">
+        <is>
+          <t>CHARTWELL</t>
+        </is>
+      </c>
+      <c r="E90" s="20" t="inlineStr">
+        <is>
+          <t>Chatham, Kent</t>
+        </is>
+      </c>
+      <c r="F90" s="20" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G90" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H90" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I90" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J90" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K90" s="23" t="inlineStr"/>
+      <c r="L90" s="23" t="inlineStr"/>
+      <c r="M90" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N90" s="24" t="inlineStr"/>
+      <c r="O90" s="23" t="inlineStr"/>
+    </row>
+    <row r="91" ht="16" customHeight="1" s="18">
+      <c r="A91" s="25" t="inlineStr">
+        <is>
+          <t>b7233cf19e6c</t>
+        </is>
+      </c>
+      <c r="B91" s="25" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D91" s="25" t="inlineStr">
+        <is>
+          <t>Reed</t>
+        </is>
+      </c>
+      <c r="E91" s="25" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F91" s="25" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G91" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H91" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I91" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J91" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K91" s="27" t="inlineStr"/>
+      <c r="L91" s="27" t="inlineStr"/>
+      <c r="M91" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N91" s="28" t="inlineStr"/>
+      <c r="O91" s="27" t="inlineStr"/>
+    </row>
+    <row r="92" ht="16" customHeight="1" s="18">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>67be42e395a2</t>
+        </is>
+      </c>
+      <c r="B92" s="20" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="20" t="inlineStr">
+        <is>
+          <t>Civil Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="D92" s="20" t="inlineStr">
+        <is>
+          <t>Zodiac Recruitment</t>
+        </is>
+      </c>
+      <c r="E92" s="20" t="inlineStr">
+        <is>
+          <t>Stone Cross, Crowborough</t>
+        </is>
+      </c>
+      <c r="F92" s="20" t="inlineStr">
+        <is>
+          <t>£32,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G92" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H92" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I92" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J92" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K92" s="23" t="inlineStr"/>
+      <c r="L92" s="23" t="inlineStr"/>
+      <c r="M92" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N92" s="24" t="inlineStr"/>
+      <c r="O92" s="23" t="inlineStr"/>
+    </row>
+    <row r="93" ht="16" customHeight="1" s="18">
+      <c r="A93" s="25" t="inlineStr">
+        <is>
+          <t>8afc2cf8a5a5</t>
+        </is>
+      </c>
+      <c r="B93" s="25" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D93" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E93" s="25" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F93" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G93" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H93" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I93" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J93" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K93" s="27" t="inlineStr"/>
+      <c r="L93" s="27" t="inlineStr"/>
+      <c r="M93" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N93" s="28" t="inlineStr"/>
+      <c r="O93" s="27" t="inlineStr"/>
+    </row>
+    <row r="94" ht="16" customHeight="1" s="18">
+      <c r="A94" s="20" t="inlineStr">
+        <is>
+          <t>f24c3027be66</t>
+        </is>
+      </c>
+      <c r="B94" s="20" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C94" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D94" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E94" s="20" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F94" s="20" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G94" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H94" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I94" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J94" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K94" s="23" t="inlineStr"/>
+      <c r="L94" s="23" t="inlineStr"/>
+      <c r="M94" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N94" s="24" t="inlineStr"/>
+      <c r="O94" s="23" t="inlineStr"/>
+    </row>
+    <row r="95" ht="16" customHeight="1" s="18">
+      <c r="A95" s="25" t="inlineStr">
+        <is>
+          <t>e3872cb11a63</t>
+        </is>
+      </c>
+      <c r="B95" s="25" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D95" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E95" s="25" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F95" s="25" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G95" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H95" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I95" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J95" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K95" s="27" t="inlineStr"/>
+      <c r="L95" s="27" t="inlineStr"/>
+      <c r="M95" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N95" s="28" t="inlineStr"/>
+      <c r="O95" s="27" t="inlineStr"/>
+    </row>
+    <row r="96" ht="16" customHeight="1" s="18">
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>cee3639a2310</t>
+        </is>
+      </c>
+      <c r="B96" s="20" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C96" s="20" t="inlineStr">
+        <is>
+          <t>Plumber</t>
+        </is>
+      </c>
+      <c r="D96" s="20" t="inlineStr">
+        <is>
+          <t>Wates</t>
+        </is>
+      </c>
+      <c r="E96" s="20" t="inlineStr">
+        <is>
+          <t>Tinsley Green, Crawley</t>
+        </is>
+      </c>
+      <c r="F96" s="20" t="inlineStr">
+        <is>
+          <t>£43,202 – £43,202</t>
+        </is>
+      </c>
+      <c r="G96" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H96" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I96" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J96" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K96" s="23" t="inlineStr"/>
+      <c r="L96" s="23" t="inlineStr"/>
+      <c r="M96" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N96" s="24" t="inlineStr"/>
+      <c r="O96" s="23" t="inlineStr"/>
+    </row>
+    <row r="97" ht="16" customHeight="1" s="18">
+      <c r="A97" s="25" t="inlineStr">
+        <is>
+          <t>70e9cf198ebd</t>
+        </is>
+      </c>
+      <c r="B97" s="25" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="25" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D97" s="25" t="inlineStr">
+        <is>
+          <t>SSA Recruitment</t>
+        </is>
+      </c>
+      <c r="E97" s="25" t="inlineStr">
+        <is>
+          <t>West Hampstead, North West London</t>
+        </is>
+      </c>
+      <c r="F97" s="25" t="inlineStr">
+        <is>
+          <t>£55,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G97" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H97" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I97" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="J97" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K97" s="27" t="inlineStr"/>
+      <c r="L97" s="27" t="inlineStr"/>
+      <c r="M97" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N97" s="28" t="inlineStr"/>
+      <c r="O97" s="27" t="inlineStr"/>
+    </row>
+    <row r="98" ht="16" customHeight="1" s="18">
+      <c r="A98" s="20" t="inlineStr">
+        <is>
+          <t>9f7de7bf8307</t>
+        </is>
+      </c>
+      <c r="B98" s="20" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C98" s="20" t="inlineStr">
+        <is>
+          <t>Senior Water Network Engineer/Modellers</t>
+        </is>
+      </c>
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E98" s="20" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F98" s="20" t="inlineStr">
+        <is>
+          <t>£50,253 – £50,253</t>
+        </is>
+      </c>
+      <c r="G98" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H98" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I98" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="J98" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K98" s="23" t="inlineStr"/>
+      <c r="L98" s="23" t="inlineStr"/>
+      <c r="M98" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N98" s="24" t="inlineStr"/>
+      <c r="O98" s="23" t="inlineStr"/>
+    </row>
+    <row r="99" ht="16" customHeight="1" s="18">
+      <c r="A99" s="25" t="inlineStr">
+        <is>
+          <t>2005366f198b</t>
+        </is>
+      </c>
+      <c r="B99" s="25" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="25" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D99" s="25" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E99" s="25" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F99" s="25" t="inlineStr">
+        <is>
+          <t>£48,252 – £48,252</t>
+        </is>
+      </c>
+      <c r="G99" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H99" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I99" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="J99" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K99" s="27" t="inlineStr"/>
+      <c r="L99" s="27" t="inlineStr"/>
+      <c r="M99" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N99" s="28" t="inlineStr"/>
+      <c r="O99" s="27" t="inlineStr"/>
+    </row>
+    <row r="100" ht="16" customHeight="1" s="18">
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>b73c48b099c2</t>
+        </is>
+      </c>
+      <c r="B100" s="20" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C100" s="20" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D100" s="20" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E100" s="20" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F100" s="20" t="inlineStr">
+        <is>
+          <t>£49,369 – £49,369</t>
+        </is>
+      </c>
+      <c r="G100" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H100" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I100" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="J100" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K100" s="23" t="inlineStr"/>
+      <c r="L100" s="23" t="inlineStr"/>
+      <c r="M100" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N100" s="24" t="inlineStr"/>
+      <c r="O100" s="23" t="inlineStr"/>
+    </row>
+    <row r="101" ht="16" customHeight="1" s="18">
+      <c r="A101" s="25" t="inlineStr">
+        <is>
+          <t>284c1ac9fbb7</t>
+        </is>
+      </c>
+      <c r="B101" s="25" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="25" t="inlineStr">
+        <is>
+          <t>Senior Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D101" s="25" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment</t>
+        </is>
+      </c>
+      <c r="E101" s="25" t="inlineStr">
+        <is>
+          <t>Denner Hill, Great Missenden</t>
+        </is>
+      </c>
+      <c r="F101" s="25" t="inlineStr">
+        <is>
+          <t>£38,000 – £60,000</t>
+        </is>
+      </c>
+      <c r="G101" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H101" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I101" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J101" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K101" s="27" t="inlineStr"/>
+      <c r="L101" s="27" t="inlineStr"/>
+      <c r="M101" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N101" s="28" t="inlineStr"/>
+      <c r="O101" s="27" t="inlineStr"/>
+    </row>
+    <row r="102" ht="16" customHeight="1" s="18">
+      <c r="A102" s="20" t="inlineStr">
+        <is>
+          <t>8a1f7ea66b12</t>
+        </is>
+      </c>
+      <c r="B102" s="20" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="inlineStr">
+        <is>
+          <t>Assistant Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>Henley Chase</t>
+        </is>
+      </c>
+      <c r="E102" s="20" t="inlineStr">
+        <is>
+          <t>New Haw, Addlestone</t>
+        </is>
+      </c>
+      <c r="F102" s="20" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G102" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H102" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I102" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J102" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K102" s="23" t="inlineStr"/>
+      <c r="L102" s="23" t="inlineStr"/>
+      <c r="M102" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N102" s="24" t="inlineStr"/>
+      <c r="O102" s="23" t="inlineStr"/>
+    </row>
+    <row r="103" ht="16" customHeight="1" s="18">
+      <c r="A103" s="25" t="inlineStr">
+        <is>
+          <t>5cbdcd0ea87e</t>
+        </is>
+      </c>
+      <c r="B103" s="25" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="25" t="inlineStr">
+        <is>
+          <t>Junior Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D103" s="25" t="inlineStr">
+        <is>
+          <t>Henley Chase Limited</t>
+        </is>
+      </c>
+      <c r="E103" s="25" t="inlineStr">
+        <is>
+          <t>Addlestone, Surrey</t>
+        </is>
+      </c>
+      <c r="F103" s="25" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G103" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H103" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I103" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J103" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K103" s="27" t="inlineStr"/>
+      <c r="L103" s="27" t="inlineStr"/>
+      <c r="M103" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N103" s="28" t="inlineStr"/>
+      <c r="O103" s="27" t="inlineStr"/>
+    </row>
+    <row r="104" ht="16" customHeight="1" s="18">
+      <c r="A104" s="20" t="inlineStr">
+        <is>
+          <t>93f6bd8d7c80</t>
+        </is>
+      </c>
+      <c r="B104" s="20" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Flood Risk &amp; Drainage</t>
+        </is>
+      </c>
+      <c r="D104" s="20" t="inlineStr">
+        <is>
+          <t>Aztrum</t>
+        </is>
+      </c>
+      <c r="E104" s="20" t="inlineStr">
+        <is>
+          <t>Ash Vale, Aldershot</t>
+        </is>
+      </c>
+      <c r="F104" s="20" t="inlineStr">
+        <is>
+          <t>£45,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G104" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H104" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I104" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J104" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K104" s="23" t="inlineStr"/>
+      <c r="L104" s="23" t="inlineStr"/>
+      <c r="M104" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N104" s="24" t="inlineStr"/>
+      <c r="O104" s="23" t="inlineStr"/>
+    </row>
+    <row r="105" ht="16" customHeight="1" s="18">
+      <c r="A105" s="25" t="inlineStr">
+        <is>
+          <t>10fdb449a05f</t>
+        </is>
+      </c>
+      <c r="B105" s="25" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D105" s="25" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E105" s="25" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F105" s="25" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G105" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H105" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I105" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J105" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K105" s="27" t="inlineStr"/>
+      <c r="L105" s="27" t="inlineStr"/>
+      <c r="M105" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N105" s="28" t="inlineStr"/>
+      <c r="O105" s="27" t="inlineStr"/>
+    </row>
+    <row r="106" ht="16" customHeight="1" s="18">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>53fc0d9a30f8</t>
+        </is>
+      </c>
+      <c r="B106" s="20" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="20" t="inlineStr">
+        <is>
+          <t>Assistant Engineer - Clean Water Modelling</t>
+        </is>
+      </c>
+      <c r="D106" s="20" t="inlineStr">
+        <is>
+          <t>WSP</t>
+        </is>
+      </c>
+      <c r="E106" s="20" t="inlineStr">
+        <is>
+          <t>Aldwych, Central London</t>
+        </is>
+      </c>
+      <c r="F106" s="20" t="inlineStr">
+        <is>
+          <t>£45,719 – £45,719</t>
+        </is>
+      </c>
+      <c r="G106" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H106" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I106" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J106" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K106" s="23" t="inlineStr"/>
+      <c r="L106" s="23" t="inlineStr"/>
+      <c r="M106" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N106" s="24" t="inlineStr"/>
+      <c r="O106" s="23" t="inlineStr"/>
+    </row>
+    <row r="107" ht="16" customHeight="1" s="18">
+      <c r="A107" s="25" t="inlineStr">
+        <is>
+          <t>1315d3fe67d9</t>
+        </is>
+      </c>
+      <c r="B107" s="25" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D107" s="25" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E107" s="25" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F107" s="25" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G107" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H107" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I107" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J107" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K107" s="27" t="inlineStr"/>
+      <c r="L107" s="27" t="inlineStr"/>
+      <c r="M107" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N107" s="28" t="inlineStr"/>
+      <c r="O107" s="27" t="inlineStr"/>
+    </row>
+    <row r="108" ht="16" customHeight="1" s="18">
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>47c380e6fcde</t>
+        </is>
+      </c>
+      <c r="B108" s="20" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="inlineStr">
+        <is>
+          <t>Pollution Response Technician</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>Lanes Group</t>
+        </is>
+      </c>
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>Tudeley, Tonbridge</t>
+        </is>
+      </c>
+      <c r="F108" s="20" t="inlineStr">
+        <is>
+          <t>£54,416 – £54,416</t>
+        </is>
+      </c>
+      <c r="G108" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H108" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I108" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J108" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K108" s="23" t="inlineStr"/>
+      <c r="L108" s="23" t="inlineStr"/>
+      <c r="M108" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N108" s="24" t="inlineStr"/>
+      <c r="O108" s="23" t="inlineStr"/>
+    </row>
+    <row r="109" ht="16" customHeight="1" s="18">
+      <c r="A109" s="25" t="inlineStr">
+        <is>
+          <t>7a727b1cff91</t>
+        </is>
+      </c>
+      <c r="B109" s="25" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="25" t="inlineStr">
+        <is>
+          <t>Electrical Project/Design Engineer</t>
+        </is>
+      </c>
+      <c r="D109" s="25" t="inlineStr">
+        <is>
+          <t>Matchtech</t>
+        </is>
+      </c>
+      <c r="E109" s="25" t="inlineStr">
+        <is>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="F109" s="25" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G109" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H109" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I109" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="J109" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K109" s="27" t="inlineStr"/>
+      <c r="L109" s="27" t="inlineStr"/>
+      <c r="M109" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N109" s="28" t="inlineStr"/>
+      <c r="O109" s="27" t="inlineStr"/>
+    </row>
+    <row r="110" ht="16" customHeight="1" s="18">
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>0021ab6a5949</t>
+        </is>
+      </c>
+      <c r="B110" s="20" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="inlineStr">
+        <is>
+          <t>Civil Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="D110" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E110" s="20" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F110" s="20" t="inlineStr">
+        <is>
+          <t>£55,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G110" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H110" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I110" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="J110" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K110" s="23" t="inlineStr"/>
+      <c r="L110" s="23" t="inlineStr"/>
+      <c r="M110" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N110" s="24" t="inlineStr"/>
+      <c r="O110" s="23" t="inlineStr"/>
+    </row>
+    <row r="111" ht="16" customHeight="1" s="18">
+      <c r="A111" s="25" t="inlineStr">
+        <is>
+          <t>b8512fa7ac5c</t>
+        </is>
+      </c>
+      <c r="B111" s="25" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="25" t="inlineStr">
+        <is>
+          <t>Civil Engineer Hybrid</t>
+        </is>
+      </c>
+      <c r="D111" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E111" s="25" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F111" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G111" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H111" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I111" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="J111" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K111" s="27" t="inlineStr"/>
+      <c r="L111" s="27" t="inlineStr"/>
+      <c r="M111" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N111" s="28" t="inlineStr"/>
+      <c r="O111" s="27" t="inlineStr"/>
+    </row>
+    <row r="112" ht="16" customHeight="1" s="18">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>fbf044dd1647</t>
+        </is>
+      </c>
+      <c r="B112" s="20" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="inlineStr">
+        <is>
+          <t>Civil Engineer (Water industry)</t>
+        </is>
+      </c>
+      <c r="D112" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E112" s="20" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F112" s="20" t="inlineStr">
+        <is>
+          <t>£55,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G112" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H112" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I112" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="J112" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K112" s="23" t="inlineStr"/>
+      <c r="L112" s="23" t="inlineStr"/>
+      <c r="M112" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N112" s="24" t="inlineStr"/>
+      <c r="O112" s="23" t="inlineStr"/>
+    </row>
+    <row r="113" ht="16" customHeight="1" s="18">
+      <c r="A113" s="25" t="inlineStr">
+        <is>
+          <t>bb57f4bf2197</t>
+        </is>
+      </c>
+      <c r="B113" s="25" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="25" t="inlineStr">
+        <is>
+          <t>Civil Engineer Water industry</t>
+        </is>
+      </c>
+      <c r="D113" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E113" s="25" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F113" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G113" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H113" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I113" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="J113" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K113" s="27" t="inlineStr"/>
+      <c r="L113" s="27" t="inlineStr"/>
+      <c r="M113" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N113" s="28" t="inlineStr"/>
+      <c r="O113" s="27" t="inlineStr"/>
+    </row>
+    <row r="114" ht="16" customHeight="1" s="18">
+      <c r="A114" s="20" t="inlineStr">
+        <is>
+          <t>965ea0b9704e</t>
+        </is>
+      </c>
+      <c r="B114" s="20" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="20" t="inlineStr">
+        <is>
+          <t>Civil Engineer (Water industry)</t>
+        </is>
+      </c>
+      <c r="D114" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E114" s="20" t="inlineStr">
+        <is>
+          <t>Chalvey, Slough</t>
+        </is>
+      </c>
+      <c r="F114" s="20" t="inlineStr">
+        <is>
+          <t>£45,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G114" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H114" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I114" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="J114" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K114" s="23" t="inlineStr"/>
+      <c r="L114" s="23" t="inlineStr"/>
+      <c r="M114" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N114" s="24" t="inlineStr"/>
+      <c r="O114" s="23" t="inlineStr"/>
+    </row>
+    <row r="115" ht="16" customHeight="1" s="18">
+      <c r="A115" s="25" t="inlineStr">
+        <is>
+          <t>3f8c59e3dff3</t>
+        </is>
+      </c>
+      <c r="B115" s="25" t="inlineStr">
+        <is>
+          <t>16/02/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="25" t="inlineStr">
+        <is>
+          <t>Senior/Lead, Account Solution Engineer</t>
+        </is>
+      </c>
+      <c r="D115" s="25" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="E115" s="25" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F115" s="25" t="inlineStr">
+        <is>
+          <t>£49,917 – £49,917</t>
+        </is>
+      </c>
+      <c r="G115" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H115" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I115" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="J115" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K115" s="27" t="inlineStr"/>
+      <c r="L115" s="27" t="inlineStr"/>
+      <c r="M115" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N115" s="28" t="inlineStr"/>
+      <c r="O115" s="27" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -6192,6 +7726,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId114"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" style="18" min="1" max="1"/>
@@ -7624,6 +7624,1422 @@
       </c>
       <c r="N115" s="28" t="inlineStr"/>
       <c r="O115" s="27" t="inlineStr"/>
+    </row>
+    <row r="116" ht="16" customHeight="1" s="18">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>97fb0cac3cb8</t>
+        </is>
+      </c>
+      <c r="B116" s="20" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="20" t="inlineStr">
+        <is>
+          <t>Plumber</t>
+        </is>
+      </c>
+      <c r="D116" s="20" t="inlineStr">
+        <is>
+          <t>WATES PROPERTY SERVICES LIMITED</t>
+        </is>
+      </c>
+      <c r="E116" s="20" t="inlineStr">
+        <is>
+          <t>Crawley, West Sussex</t>
+        </is>
+      </c>
+      <c r="F116" s="20" t="inlineStr">
+        <is>
+          <t>£50,654 – £50,654</t>
+        </is>
+      </c>
+      <c r="G116" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H116" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I116" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J116" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K116" s="23" t="inlineStr"/>
+      <c r="L116" s="23" t="inlineStr"/>
+      <c r="M116" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N116" s="24" t="inlineStr"/>
+      <c r="O116" s="23" t="inlineStr"/>
+    </row>
+    <row r="117" ht="16" customHeight="1" s="18">
+      <c r="A117" s="25" t="inlineStr">
+        <is>
+          <t>b9b64834547f</t>
+        </is>
+      </c>
+      <c r="B117" s="25" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D117" s="25" t="inlineStr">
+        <is>
+          <t>CHARTWELL</t>
+        </is>
+      </c>
+      <c r="E117" s="25" t="inlineStr">
+        <is>
+          <t>Chatham, Kent</t>
+        </is>
+      </c>
+      <c r="F117" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G117" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H117" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I117" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J117" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K117" s="27" t="inlineStr"/>
+      <c r="L117" s="27" t="inlineStr"/>
+      <c r="M117" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N117" s="28" t="inlineStr"/>
+      <c r="O117" s="27" t="inlineStr"/>
+    </row>
+    <row r="118" ht="16" customHeight="1" s="18">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>46d1b6a1751d</t>
+        </is>
+      </c>
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D118" s="20" t="inlineStr">
+        <is>
+          <t>Reed</t>
+        </is>
+      </c>
+      <c r="E118" s="20" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F118" s="20" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G118" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H118" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I118" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J118" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K118" s="23" t="inlineStr"/>
+      <c r="L118" s="23" t="inlineStr"/>
+      <c r="M118" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N118" s="24" t="inlineStr"/>
+      <c r="O118" s="23" t="inlineStr"/>
+    </row>
+    <row r="119" ht="16" customHeight="1" s="18">
+      <c r="A119" s="25" t="inlineStr">
+        <is>
+          <t>f52ec3519bf7</t>
+        </is>
+      </c>
+      <c r="B119" s="25" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="25" t="inlineStr">
+        <is>
+          <t>Civil Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="D119" s="25" t="inlineStr">
+        <is>
+          <t>Zodiac Recruitment</t>
+        </is>
+      </c>
+      <c r="E119" s="25" t="inlineStr">
+        <is>
+          <t>Stone Cross, Crowborough</t>
+        </is>
+      </c>
+      <c r="F119" s="25" t="inlineStr">
+        <is>
+          <t>£32,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G119" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H119" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I119" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J119" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K119" s="27" t="inlineStr"/>
+      <c r="L119" s="27" t="inlineStr"/>
+      <c r="M119" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N119" s="28" t="inlineStr"/>
+      <c r="O119" s="27" t="inlineStr"/>
+    </row>
+    <row r="120" ht="16" customHeight="1" s="18">
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>acfc93e16d1a</t>
+        </is>
+      </c>
+      <c r="B120" s="20" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D120" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E120" s="20" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F120" s="20" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G120" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H120" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I120" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J120" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K120" s="23" t="inlineStr"/>
+      <c r="L120" s="23" t="inlineStr"/>
+      <c r="M120" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N120" s="24" t="inlineStr"/>
+      <c r="O120" s="23" t="inlineStr"/>
+    </row>
+    <row r="121" ht="16" customHeight="1" s="18">
+      <c r="A121" s="25" t="inlineStr">
+        <is>
+          <t>315d35cd83ca</t>
+        </is>
+      </c>
+      <c r="B121" s="25" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D121" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E121" s="25" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F121" s="25" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G121" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H121" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I121" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J121" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K121" s="27" t="inlineStr"/>
+      <c r="L121" s="27" t="inlineStr"/>
+      <c r="M121" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N121" s="28" t="inlineStr"/>
+      <c r="O121" s="27" t="inlineStr"/>
+    </row>
+    <row r="122" ht="16" customHeight="1" s="18">
+      <c r="A122" s="20" t="inlineStr">
+        <is>
+          <t>799cef8b927f</t>
+        </is>
+      </c>
+      <c r="B122" s="20" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D122" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E122" s="20" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F122" s="20" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G122" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H122" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I122" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J122" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K122" s="23" t="inlineStr"/>
+      <c r="L122" s="23" t="inlineStr"/>
+      <c r="M122" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N122" s="24" t="inlineStr"/>
+      <c r="O122" s="23" t="inlineStr"/>
+    </row>
+    <row r="123" ht="16" customHeight="1" s="18">
+      <c r="A123" s="25" t="inlineStr">
+        <is>
+          <t>6f949fe2ea72</t>
+        </is>
+      </c>
+      <c r="B123" s="25" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="25" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D123" s="25" t="inlineStr">
+        <is>
+          <t>SSA Recruitment</t>
+        </is>
+      </c>
+      <c r="E123" s="25" t="inlineStr">
+        <is>
+          <t>West Hampstead, North West London</t>
+        </is>
+      </c>
+      <c r="F123" s="25" t="inlineStr">
+        <is>
+          <t>£55,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G123" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H123" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I123" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="J123" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K123" s="27" t="inlineStr"/>
+      <c r="L123" s="27" t="inlineStr"/>
+      <c r="M123" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N123" s="28" t="inlineStr"/>
+      <c r="O123" s="27" t="inlineStr"/>
+    </row>
+    <row r="124" ht="16" customHeight="1" s="18">
+      <c r="A124" s="20" t="inlineStr">
+        <is>
+          <t>2093b8c37eec</t>
+        </is>
+      </c>
+      <c r="B124" s="20" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C124" s="20" t="inlineStr">
+        <is>
+          <t>Senior Water Network Engineer/Modellers</t>
+        </is>
+      </c>
+      <c r="D124" s="20" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E124" s="20" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F124" s="20" t="inlineStr">
+        <is>
+          <t>£50,253 – £50,253</t>
+        </is>
+      </c>
+      <c r="G124" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H124" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I124" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="J124" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K124" s="23" t="inlineStr"/>
+      <c r="L124" s="23" t="inlineStr"/>
+      <c r="M124" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N124" s="24" t="inlineStr"/>
+      <c r="O124" s="23" t="inlineStr"/>
+    </row>
+    <row r="125" ht="16" customHeight="1" s="18">
+      <c r="A125" s="25" t="inlineStr">
+        <is>
+          <t>76cce1012360</t>
+        </is>
+      </c>
+      <c r="B125" s="25" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="25" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D125" s="25" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E125" s="25" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F125" s="25" t="inlineStr">
+        <is>
+          <t>£48,252 – £48,252</t>
+        </is>
+      </c>
+      <c r="G125" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H125" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I125" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="J125" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K125" s="27" t="inlineStr"/>
+      <c r="L125" s="27" t="inlineStr"/>
+      <c r="M125" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N125" s="28" t="inlineStr"/>
+      <c r="O125" s="27" t="inlineStr"/>
+    </row>
+    <row r="126" ht="16" customHeight="1" s="18">
+      <c r="A126" s="20" t="inlineStr">
+        <is>
+          <t>6289d8f3b250</t>
+        </is>
+      </c>
+      <c r="B126" s="20" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C126" s="20" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D126" s="20" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E126" s="20" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F126" s="20" t="inlineStr">
+        <is>
+          <t>£49,369 – £49,369</t>
+        </is>
+      </c>
+      <c r="G126" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H126" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I126" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="J126" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K126" s="23" t="inlineStr"/>
+      <c r="L126" s="23" t="inlineStr"/>
+      <c r="M126" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N126" s="24" t="inlineStr"/>
+      <c r="O126" s="23" t="inlineStr"/>
+    </row>
+    <row r="127" ht="16" customHeight="1" s="18">
+      <c r="A127" s="25" t="inlineStr">
+        <is>
+          <t>bb06f938059b</t>
+        </is>
+      </c>
+      <c r="B127" s="25" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="25" t="inlineStr">
+        <is>
+          <t>Senior Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D127" s="25" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment</t>
+        </is>
+      </c>
+      <c r="E127" s="25" t="inlineStr">
+        <is>
+          <t>Denner Hill, Great Missenden</t>
+        </is>
+      </c>
+      <c r="F127" s="25" t="inlineStr">
+        <is>
+          <t>£38,000 – £60,000</t>
+        </is>
+      </c>
+      <c r="G127" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H127" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I127" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J127" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K127" s="27" t="inlineStr"/>
+      <c r="L127" s="27" t="inlineStr"/>
+      <c r="M127" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N127" s="28" t="inlineStr"/>
+      <c r="O127" s="27" t="inlineStr"/>
+    </row>
+    <row r="128" ht="16" customHeight="1" s="18">
+      <c r="A128" s="20" t="inlineStr">
+        <is>
+          <t>a20577b8c191</t>
+        </is>
+      </c>
+      <c r="B128" s="20" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="20" t="inlineStr">
+        <is>
+          <t>Assistant Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D128" s="20" t="inlineStr">
+        <is>
+          <t>Henley Chase</t>
+        </is>
+      </c>
+      <c r="E128" s="20" t="inlineStr">
+        <is>
+          <t>New Haw, Addlestone</t>
+        </is>
+      </c>
+      <c r="F128" s="20" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G128" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H128" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I128" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J128" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K128" s="23" t="inlineStr"/>
+      <c r="L128" s="23" t="inlineStr"/>
+      <c r="M128" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N128" s="24" t="inlineStr"/>
+      <c r="O128" s="23" t="inlineStr"/>
+    </row>
+    <row r="129" ht="16" customHeight="1" s="18">
+      <c r="A129" s="25" t="inlineStr">
+        <is>
+          <t>d0a0ea2d4f2b</t>
+        </is>
+      </c>
+      <c r="B129" s="25" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="25" t="inlineStr">
+        <is>
+          <t>Junior Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D129" s="25" t="inlineStr">
+        <is>
+          <t>Henley Chase Limited</t>
+        </is>
+      </c>
+      <c r="E129" s="25" t="inlineStr">
+        <is>
+          <t>Addlestone, Surrey</t>
+        </is>
+      </c>
+      <c r="F129" s="25" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G129" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H129" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I129" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J129" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K129" s="27" t="inlineStr"/>
+      <c r="L129" s="27" t="inlineStr"/>
+      <c r="M129" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N129" s="28" t="inlineStr"/>
+      <c r="O129" s="27" t="inlineStr"/>
+    </row>
+    <row r="130" ht="16" customHeight="1" s="18">
+      <c r="A130" s="20" t="inlineStr">
+        <is>
+          <t>f73131fd7fab</t>
+        </is>
+      </c>
+      <c r="B130" s="20" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D130" s="20" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E130" s="20" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F130" s="20" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G130" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H130" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I130" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J130" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K130" s="23" t="inlineStr"/>
+      <c r="L130" s="23" t="inlineStr"/>
+      <c r="M130" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N130" s="24" t="inlineStr"/>
+      <c r="O130" s="23" t="inlineStr"/>
+    </row>
+    <row r="131" ht="16" customHeight="1" s="18">
+      <c r="A131" s="25" t="inlineStr">
+        <is>
+          <t>2147ca886766</t>
+        </is>
+      </c>
+      <c r="B131" s="25" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="25" t="inlineStr">
+        <is>
+          <t>Assistant Engineer - Clean Water Modelling</t>
+        </is>
+      </c>
+      <c r="D131" s="25" t="inlineStr">
+        <is>
+          <t>WSP</t>
+        </is>
+      </c>
+      <c r="E131" s="25" t="inlineStr">
+        <is>
+          <t>Aldwych, Central London</t>
+        </is>
+      </c>
+      <c r="F131" s="25" t="inlineStr">
+        <is>
+          <t>£45,719 – £45,719</t>
+        </is>
+      </c>
+      <c r="G131" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H131" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I131" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J131" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K131" s="27" t="inlineStr"/>
+      <c r="L131" s="27" t="inlineStr"/>
+      <c r="M131" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N131" s="28" t="inlineStr"/>
+      <c r="O131" s="27" t="inlineStr"/>
+    </row>
+    <row r="132" ht="16" customHeight="1" s="18">
+      <c r="A132" s="20" t="inlineStr">
+        <is>
+          <t>c047ce542799</t>
+        </is>
+      </c>
+      <c r="B132" s="20" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="20" t="inlineStr">
+        <is>
+          <t>HGV Class 2 Tanker Driver – Drainage</t>
+        </is>
+      </c>
+      <c r="D132" s="20" t="inlineStr">
+        <is>
+          <t>Excellis Consultancy</t>
+        </is>
+      </c>
+      <c r="E132" s="20" t="inlineStr">
+        <is>
+          <t>Riverhead, Sevenoaks</t>
+        </is>
+      </c>
+      <c r="F132" s="20" t="inlineStr">
+        <is>
+          <t>£45,000 – £48,000</t>
+        </is>
+      </c>
+      <c r="G132" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H132" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I132" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J132" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K132" s="23" t="inlineStr"/>
+      <c r="L132" s="23" t="inlineStr"/>
+      <c r="M132" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N132" s="24" t="inlineStr"/>
+      <c r="O132" s="23" t="inlineStr"/>
+    </row>
+    <row r="133" ht="16" customHeight="1" s="18">
+      <c r="A133" s="25" t="inlineStr">
+        <is>
+          <t>ecedc8c6c270</t>
+        </is>
+      </c>
+      <c r="B133" s="25" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D133" s="25" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E133" s="25" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F133" s="25" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G133" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H133" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I133" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J133" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K133" s="27" t="inlineStr"/>
+      <c r="L133" s="27" t="inlineStr"/>
+      <c r="M133" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N133" s="28" t="inlineStr"/>
+      <c r="O133" s="27" t="inlineStr"/>
+    </row>
+    <row r="134" ht="16" customHeight="1" s="18">
+      <c r="A134" s="20" t="inlineStr">
+        <is>
+          <t>820b34b178cc</t>
+        </is>
+      </c>
+      <c r="B134" s="20" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="20" t="inlineStr">
+        <is>
+          <t>Pollution Response Technician</t>
+        </is>
+      </c>
+      <c r="D134" s="20" t="inlineStr">
+        <is>
+          <t>Lanes Group</t>
+        </is>
+      </c>
+      <c r="E134" s="20" t="inlineStr">
+        <is>
+          <t>Tudeley, Tonbridge</t>
+        </is>
+      </c>
+      <c r="F134" s="20" t="inlineStr">
+        <is>
+          <t>£54,416 – £54,416</t>
+        </is>
+      </c>
+      <c r="G134" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H134" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I134" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J134" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K134" s="23" t="inlineStr"/>
+      <c r="L134" s="23" t="inlineStr"/>
+      <c r="M134" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N134" s="24" t="inlineStr"/>
+      <c r="O134" s="23" t="inlineStr"/>
+    </row>
+    <row r="135" ht="16" customHeight="1" s="18">
+      <c r="A135" s="25" t="inlineStr">
+        <is>
+          <t>4baf7c4c5bbd</t>
+        </is>
+      </c>
+      <c r="B135" s="25" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="25" t="inlineStr">
+        <is>
+          <t>Electrical Project/Design Engineer</t>
+        </is>
+      </c>
+      <c r="D135" s="25" t="inlineStr">
+        <is>
+          <t>Matchtech</t>
+        </is>
+      </c>
+      <c r="E135" s="25" t="inlineStr">
+        <is>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="F135" s="25" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G135" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H135" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I135" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="J135" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K135" s="27" t="inlineStr"/>
+      <c r="L135" s="27" t="inlineStr"/>
+      <c r="M135" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N135" s="28" t="inlineStr"/>
+      <c r="O135" s="27" t="inlineStr"/>
+    </row>
+    <row r="136" ht="16" customHeight="1" s="18">
+      <c r="A136" s="20" t="inlineStr">
+        <is>
+          <t>6e00d0b66737</t>
+        </is>
+      </c>
+      <c r="B136" s="20" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="20" t="inlineStr">
+        <is>
+          <t>Civil Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="D136" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E136" s="20" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F136" s="20" t="inlineStr">
+        <is>
+          <t>£55,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G136" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H136" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I136" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="J136" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K136" s="23" t="inlineStr"/>
+      <c r="L136" s="23" t="inlineStr"/>
+      <c r="M136" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N136" s="24" t="inlineStr"/>
+      <c r="O136" s="23" t="inlineStr"/>
+    </row>
+    <row r="137" ht="16" customHeight="1" s="18">
+      <c r="A137" s="25" t="inlineStr">
+        <is>
+          <t>ccee00df94ed</t>
+        </is>
+      </c>
+      <c r="B137" s="25" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="25" t="inlineStr">
+        <is>
+          <t>Civil Engineer Hybrid</t>
+        </is>
+      </c>
+      <c r="D137" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E137" s="25" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F137" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G137" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H137" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I137" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="J137" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K137" s="27" t="inlineStr"/>
+      <c r="L137" s="27" t="inlineStr"/>
+      <c r="M137" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N137" s="28" t="inlineStr"/>
+      <c r="O137" s="27" t="inlineStr"/>
+    </row>
+    <row r="138" ht="16" customHeight="1" s="18">
+      <c r="A138" s="20" t="inlineStr">
+        <is>
+          <t>9c595afe7c31</t>
+        </is>
+      </c>
+      <c r="B138" s="20" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="20" t="inlineStr">
+        <is>
+          <t>Civil Engineer Water industry</t>
+        </is>
+      </c>
+      <c r="D138" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E138" s="20" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F138" s="20" t="inlineStr">
+        <is>
+          <t>£45,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G138" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H138" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I138" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="J138" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K138" s="23" t="inlineStr"/>
+      <c r="L138" s="23" t="inlineStr"/>
+      <c r="M138" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N138" s="24" t="inlineStr"/>
+      <c r="O138" s="23" t="inlineStr"/>
+    </row>
+    <row r="139" ht="16" customHeight="1" s="18">
+      <c r="A139" s="25" t="inlineStr">
+        <is>
+          <t>701e684e596a</t>
+        </is>
+      </c>
+      <c r="B139" s="25" t="inlineStr">
+        <is>
+          <t>17/02/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="25" t="inlineStr">
+        <is>
+          <t>Civil Engineer (Water industry)</t>
+        </is>
+      </c>
+      <c r="D139" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E139" s="25" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F139" s="25" t="inlineStr">
+        <is>
+          <t>£55,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G139" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H139" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I139" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="J139" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K139" s="27" t="inlineStr"/>
+      <c r="L139" s="27" t="inlineStr"/>
+      <c r="M139" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N139" s="28" t="inlineStr"/>
+      <c r="O139" s="27" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -7752,6 +9168,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O139"/>
+  <dimension ref="A1:O163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" style="18" min="1" max="1"/>
@@ -9040,6 +9040,1422 @@
       </c>
       <c r="N139" s="28" t="inlineStr"/>
       <c r="O139" s="27" t="inlineStr"/>
+    </row>
+    <row r="140" ht="16" customHeight="1" s="18">
+      <c r="A140" s="20" t="inlineStr">
+        <is>
+          <t>f14280a845da</t>
+        </is>
+      </c>
+      <c r="B140" s="20" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="20" t="inlineStr">
+        <is>
+          <t>Plumber</t>
+        </is>
+      </c>
+      <c r="D140" s="20" t="inlineStr">
+        <is>
+          <t>WATES PROPERTY SERVICES LIMITED</t>
+        </is>
+      </c>
+      <c r="E140" s="20" t="inlineStr">
+        <is>
+          <t>Crawley, West Sussex</t>
+        </is>
+      </c>
+      <c r="F140" s="20" t="inlineStr">
+        <is>
+          <t>£50,654 – £50,654</t>
+        </is>
+      </c>
+      <c r="G140" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H140" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I140" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J140" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K140" s="23" t="inlineStr"/>
+      <c r="L140" s="23" t="inlineStr"/>
+      <c r="M140" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N140" s="24" t="inlineStr"/>
+      <c r="O140" s="23" t="inlineStr"/>
+    </row>
+    <row r="141" ht="16" customHeight="1" s="18">
+      <c r="A141" s="25" t="inlineStr">
+        <is>
+          <t>78dd66f6601b</t>
+        </is>
+      </c>
+      <c r="B141" s="25" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D141" s="25" t="inlineStr">
+        <is>
+          <t>CHARTWELL</t>
+        </is>
+      </c>
+      <c r="E141" s="25" t="inlineStr">
+        <is>
+          <t>Chatham, Kent</t>
+        </is>
+      </c>
+      <c r="F141" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G141" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H141" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I141" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J141" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K141" s="27" t="inlineStr"/>
+      <c r="L141" s="27" t="inlineStr"/>
+      <c r="M141" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N141" s="28" t="inlineStr"/>
+      <c r="O141" s="27" t="inlineStr"/>
+    </row>
+    <row r="142" ht="16" customHeight="1" s="18">
+      <c r="A142" s="20" t="inlineStr">
+        <is>
+          <t>0b3ab94ba52b</t>
+        </is>
+      </c>
+      <c r="B142" s="20" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D142" s="20" t="inlineStr">
+        <is>
+          <t>Reed</t>
+        </is>
+      </c>
+      <c r="E142" s="20" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F142" s="20" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G142" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H142" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I142" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J142" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K142" s="23" t="inlineStr"/>
+      <c r="L142" s="23" t="inlineStr"/>
+      <c r="M142" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N142" s="24" t="inlineStr"/>
+      <c r="O142" s="23" t="inlineStr"/>
+    </row>
+    <row r="143" ht="16" customHeight="1" s="18">
+      <c r="A143" s="25" t="inlineStr">
+        <is>
+          <t>364f3b0e4e25</t>
+        </is>
+      </c>
+      <c r="B143" s="25" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="25" t="inlineStr">
+        <is>
+          <t>Civil Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="D143" s="25" t="inlineStr">
+        <is>
+          <t>Zodiac Recruitment</t>
+        </is>
+      </c>
+      <c r="E143" s="25" t="inlineStr">
+        <is>
+          <t>Stone Cross, Crowborough</t>
+        </is>
+      </c>
+      <c r="F143" s="25" t="inlineStr">
+        <is>
+          <t>£32,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G143" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H143" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I143" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J143" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K143" s="27" t="inlineStr"/>
+      <c r="L143" s="27" t="inlineStr"/>
+      <c r="M143" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N143" s="28" t="inlineStr"/>
+      <c r="O143" s="27" t="inlineStr"/>
+    </row>
+    <row r="144" ht="16" customHeight="1" s="18">
+      <c r="A144" s="20" t="inlineStr">
+        <is>
+          <t>512db54969ff</t>
+        </is>
+      </c>
+      <c r="B144" s="20" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D144" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E144" s="20" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F144" s="20" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G144" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H144" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I144" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J144" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K144" s="23" t="inlineStr"/>
+      <c r="L144" s="23" t="inlineStr"/>
+      <c r="M144" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N144" s="24" t="inlineStr"/>
+      <c r="O144" s="23" t="inlineStr"/>
+    </row>
+    <row r="145" ht="16" customHeight="1" s="18">
+      <c r="A145" s="25" t="inlineStr">
+        <is>
+          <t>010c53a0f057</t>
+        </is>
+      </c>
+      <c r="B145" s="25" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D145" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E145" s="25" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F145" s="25" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G145" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H145" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I145" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J145" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K145" s="27" t="inlineStr"/>
+      <c r="L145" s="27" t="inlineStr"/>
+      <c r="M145" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N145" s="28" t="inlineStr"/>
+      <c r="O145" s="27" t="inlineStr"/>
+    </row>
+    <row r="146" ht="16" customHeight="1" s="18">
+      <c r="A146" s="20" t="inlineStr">
+        <is>
+          <t>6beb7a9fb901</t>
+        </is>
+      </c>
+      <c r="B146" s="20" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D146" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E146" s="20" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F146" s="20" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G146" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H146" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I146" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J146" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K146" s="23" t="inlineStr"/>
+      <c r="L146" s="23" t="inlineStr"/>
+      <c r="M146" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N146" s="24" t="inlineStr"/>
+      <c r="O146" s="23" t="inlineStr"/>
+    </row>
+    <row r="147" ht="16" customHeight="1" s="18">
+      <c r="A147" s="25" t="inlineStr">
+        <is>
+          <t>2557e9d8c609</t>
+        </is>
+      </c>
+      <c r="B147" s="25" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="25" t="inlineStr">
+        <is>
+          <t>Senior Water Network Engineer/Modellers</t>
+        </is>
+      </c>
+      <c r="D147" s="25" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E147" s="25" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F147" s="25" t="inlineStr">
+        <is>
+          <t>£50,253 – £50,253</t>
+        </is>
+      </c>
+      <c r="G147" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H147" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I147" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="J147" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K147" s="27" t="inlineStr"/>
+      <c r="L147" s="27" t="inlineStr"/>
+      <c r="M147" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N147" s="28" t="inlineStr"/>
+      <c r="O147" s="27" t="inlineStr"/>
+    </row>
+    <row r="148" ht="16" customHeight="1" s="18">
+      <c r="A148" s="20" t="inlineStr">
+        <is>
+          <t>96e34547a9e5</t>
+        </is>
+      </c>
+      <c r="B148" s="20" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="20" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D148" s="20" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E148" s="20" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F148" s="20" t="inlineStr">
+        <is>
+          <t>£48,252 – £48,252</t>
+        </is>
+      </c>
+      <c r="G148" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H148" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I148" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="J148" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K148" s="23" t="inlineStr"/>
+      <c r="L148" s="23" t="inlineStr"/>
+      <c r="M148" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N148" s="24" t="inlineStr"/>
+      <c r="O148" s="23" t="inlineStr"/>
+    </row>
+    <row r="149" ht="16" customHeight="1" s="18">
+      <c r="A149" s="25" t="inlineStr">
+        <is>
+          <t>361042e68b9e</t>
+        </is>
+      </c>
+      <c r="B149" s="25" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="25" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D149" s="25" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E149" s="25" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F149" s="25" t="inlineStr">
+        <is>
+          <t>£49,369 – £49,369</t>
+        </is>
+      </c>
+      <c r="G149" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H149" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I149" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="J149" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K149" s="27" t="inlineStr"/>
+      <c r="L149" s="27" t="inlineStr"/>
+      <c r="M149" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N149" s="28" t="inlineStr"/>
+      <c r="O149" s="27" t="inlineStr"/>
+    </row>
+    <row r="150" ht="16" customHeight="1" s="18">
+      <c r="A150" s="20" t="inlineStr">
+        <is>
+          <t>07a222444bb4</t>
+        </is>
+      </c>
+      <c r="B150" s="20" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="20" t="inlineStr">
+        <is>
+          <t>Senior Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D150" s="20" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment</t>
+        </is>
+      </c>
+      <c r="E150" s="20" t="inlineStr">
+        <is>
+          <t>Denner Hill, Great Missenden</t>
+        </is>
+      </c>
+      <c r="F150" s="20" t="inlineStr">
+        <is>
+          <t>£38,000 – £60,000</t>
+        </is>
+      </c>
+      <c r="G150" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H150" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I150" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J150" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K150" s="23" t="inlineStr"/>
+      <c r="L150" s="23" t="inlineStr"/>
+      <c r="M150" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N150" s="24" t="inlineStr"/>
+      <c r="O150" s="23" t="inlineStr"/>
+    </row>
+    <row r="151" ht="16" customHeight="1" s="18">
+      <c r="A151" s="25" t="inlineStr">
+        <is>
+          <t>04ece1d79179</t>
+        </is>
+      </c>
+      <c r="B151" s="25" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="25" t="inlineStr">
+        <is>
+          <t>Assistant Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D151" s="25" t="inlineStr">
+        <is>
+          <t>Henley Chase</t>
+        </is>
+      </c>
+      <c r="E151" s="25" t="inlineStr">
+        <is>
+          <t>New Haw, Addlestone</t>
+        </is>
+      </c>
+      <c r="F151" s="25" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G151" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H151" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I151" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J151" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K151" s="27" t="inlineStr"/>
+      <c r="L151" s="27" t="inlineStr"/>
+      <c r="M151" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N151" s="28" t="inlineStr"/>
+      <c r="O151" s="27" t="inlineStr"/>
+    </row>
+    <row r="152" ht="16" customHeight="1" s="18">
+      <c r="A152" s="20" t="inlineStr">
+        <is>
+          <t>b673e5db5235</t>
+        </is>
+      </c>
+      <c r="B152" s="20" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="20" t="inlineStr">
+        <is>
+          <t>Junior Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D152" s="20" t="inlineStr">
+        <is>
+          <t>Henley Chase Limited</t>
+        </is>
+      </c>
+      <c r="E152" s="20" t="inlineStr">
+        <is>
+          <t>Addlestone, Surrey</t>
+        </is>
+      </c>
+      <c r="F152" s="20" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G152" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H152" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I152" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J152" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K152" s="23" t="inlineStr"/>
+      <c r="L152" s="23" t="inlineStr"/>
+      <c r="M152" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N152" s="24" t="inlineStr"/>
+      <c r="O152" s="23" t="inlineStr"/>
+    </row>
+    <row r="153" ht="16" customHeight="1" s="18">
+      <c r="A153" s="25" t="inlineStr">
+        <is>
+          <t>017fd8d32724</t>
+        </is>
+      </c>
+      <c r="B153" s="25" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D153" s="25" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E153" s="25" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F153" s="25" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G153" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H153" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I153" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J153" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K153" s="27" t="inlineStr"/>
+      <c r="L153" s="27" t="inlineStr"/>
+      <c r="M153" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N153" s="28" t="inlineStr"/>
+      <c r="O153" s="27" t="inlineStr"/>
+    </row>
+    <row r="154" ht="16" customHeight="1" s="18">
+      <c r="A154" s="20" t="inlineStr">
+        <is>
+          <t>d8e14bdedc85</t>
+        </is>
+      </c>
+      <c r="B154" s="20" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="20" t="inlineStr">
+        <is>
+          <t>Quality Engineer</t>
+        </is>
+      </c>
+      <c r="D154" s="20" t="inlineStr">
+        <is>
+          <t>Rapiscan Systems</t>
+        </is>
+      </c>
+      <c r="E154" s="20" t="inlineStr">
+        <is>
+          <t>Salfords, Redhill</t>
+        </is>
+      </c>
+      <c r="F154" s="20" t="inlineStr">
+        <is>
+          <t>£46,683 – £46,683</t>
+        </is>
+      </c>
+      <c r="G154" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H154" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I154" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J154" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K154" s="23" t="inlineStr"/>
+      <c r="L154" s="23" t="inlineStr"/>
+      <c r="M154" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N154" s="24" t="inlineStr"/>
+      <c r="O154" s="23" t="inlineStr"/>
+    </row>
+    <row r="155" ht="16" customHeight="1" s="18">
+      <c r="A155" s="25" t="inlineStr">
+        <is>
+          <t>9c1c76c2e8a4</t>
+        </is>
+      </c>
+      <c r="B155" s="25" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="25" t="inlineStr">
+        <is>
+          <t>Quality Engineer</t>
+        </is>
+      </c>
+      <c r="D155" s="25" t="inlineStr">
+        <is>
+          <t>Rapiscan Systems</t>
+        </is>
+      </c>
+      <c r="E155" s="25" t="inlineStr">
+        <is>
+          <t>Redhill, Surrey</t>
+        </is>
+      </c>
+      <c r="F155" s="25" t="inlineStr">
+        <is>
+          <t>£48,879 – £48,879</t>
+        </is>
+      </c>
+      <c r="G155" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H155" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I155" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J155" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K155" s="27" t="inlineStr"/>
+      <c r="L155" s="27" t="inlineStr"/>
+      <c r="M155" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N155" s="28" t="inlineStr"/>
+      <c r="O155" s="27" t="inlineStr"/>
+    </row>
+    <row r="156" ht="16" customHeight="1" s="18">
+      <c r="A156" s="20" t="inlineStr">
+        <is>
+          <t>95a61278166a</t>
+        </is>
+      </c>
+      <c r="B156" s="20" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="20" t="inlineStr">
+        <is>
+          <t>Assistant Engineer - Clean Water Modelling</t>
+        </is>
+      </c>
+      <c r="D156" s="20" t="inlineStr">
+        <is>
+          <t>WSP</t>
+        </is>
+      </c>
+      <c r="E156" s="20" t="inlineStr">
+        <is>
+          <t>Aldwych, Central London</t>
+        </is>
+      </c>
+      <c r="F156" s="20" t="inlineStr">
+        <is>
+          <t>£45,719 – £45,719</t>
+        </is>
+      </c>
+      <c r="G156" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H156" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I156" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J156" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K156" s="23" t="inlineStr"/>
+      <c r="L156" s="23" t="inlineStr"/>
+      <c r="M156" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N156" s="24" t="inlineStr"/>
+      <c r="O156" s="23" t="inlineStr"/>
+    </row>
+    <row r="157" ht="16" customHeight="1" s="18">
+      <c r="A157" s="25" t="inlineStr">
+        <is>
+          <t>3368909f4dd6</t>
+        </is>
+      </c>
+      <c r="B157" s="25" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Operations Manager</t>
+        </is>
+      </c>
+      <c r="D157" s="25" t="inlineStr">
+        <is>
+          <t>Vector Recruitment Solutions</t>
+        </is>
+      </c>
+      <c r="E157" s="25" t="inlineStr">
+        <is>
+          <t>Church Langley, Harlow</t>
+        </is>
+      </c>
+      <c r="F157" s="25" t="inlineStr">
+        <is>
+          <t>£50,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G157" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H157" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I157" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J157" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K157" s="27" t="inlineStr"/>
+      <c r="L157" s="27" t="inlineStr"/>
+      <c r="M157" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N157" s="28" t="inlineStr"/>
+      <c r="O157" s="27" t="inlineStr"/>
+    </row>
+    <row r="158" ht="16" customHeight="1" s="18">
+      <c r="A158" s="20" t="inlineStr">
+        <is>
+          <t>c0b5ead5d703</t>
+        </is>
+      </c>
+      <c r="B158" s="20" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="20" t="inlineStr">
+        <is>
+          <t>HGV Class 2 Tanker Driver – Drainage</t>
+        </is>
+      </c>
+      <c r="D158" s="20" t="inlineStr">
+        <is>
+          <t>Excellis Consultancy</t>
+        </is>
+      </c>
+      <c r="E158" s="20" t="inlineStr">
+        <is>
+          <t>Riverhead, Sevenoaks</t>
+        </is>
+      </c>
+      <c r="F158" s="20" t="inlineStr">
+        <is>
+          <t>£45,000 – £48,000</t>
+        </is>
+      </c>
+      <c r="G158" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H158" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I158" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J158" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K158" s="23" t="inlineStr"/>
+      <c r="L158" s="23" t="inlineStr"/>
+      <c r="M158" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N158" s="24" t="inlineStr"/>
+      <c r="O158" s="23" t="inlineStr"/>
+    </row>
+    <row r="159" ht="16" customHeight="1" s="18">
+      <c r="A159" s="25" t="inlineStr">
+        <is>
+          <t>06f8ddbdfb29</t>
+        </is>
+      </c>
+      <c r="B159" s="25" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D159" s="25" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E159" s="25" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F159" s="25" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G159" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H159" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I159" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J159" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K159" s="27" t="inlineStr"/>
+      <c r="L159" s="27" t="inlineStr"/>
+      <c r="M159" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N159" s="28" t="inlineStr"/>
+      <c r="O159" s="27" t="inlineStr"/>
+    </row>
+    <row r="160" ht="16" customHeight="1" s="18">
+      <c r="A160" s="20" t="inlineStr">
+        <is>
+          <t>5eba76b2be56</t>
+        </is>
+      </c>
+      <c r="B160" s="20" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="20" t="inlineStr">
+        <is>
+          <t>Career Opportunities in the Water Sector - South Central | Expression of Interest</t>
+        </is>
+      </c>
+      <c r="D160" s="20" t="inlineStr">
+        <is>
+          <t>Stantec UK</t>
+        </is>
+      </c>
+      <c r="E160" s="20" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F160" s="20" t="inlineStr">
+        <is>
+          <t>£46,544 – £46,544</t>
+        </is>
+      </c>
+      <c r="G160" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H160" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I160" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J160" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K160" s="23" t="inlineStr"/>
+      <c r="L160" s="23" t="inlineStr"/>
+      <c r="M160" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N160" s="24" t="inlineStr"/>
+      <c r="O160" s="23" t="inlineStr"/>
+    </row>
+    <row r="161" ht="16" customHeight="1" s="18">
+      <c r="A161" s="25" t="inlineStr">
+        <is>
+          <t>ab71cc2367f5</t>
+        </is>
+      </c>
+      <c r="B161" s="25" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="25" t="inlineStr">
+        <is>
+          <t>Pollution Response Technician</t>
+        </is>
+      </c>
+      <c r="D161" s="25" t="inlineStr">
+        <is>
+          <t>Lanes Group</t>
+        </is>
+      </c>
+      <c r="E161" s="25" t="inlineStr">
+        <is>
+          <t>Tudeley, Tonbridge</t>
+        </is>
+      </c>
+      <c r="F161" s="25" t="inlineStr">
+        <is>
+          <t>£54,416 – £54,416</t>
+        </is>
+      </c>
+      <c r="G161" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H161" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I161" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J161" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K161" s="27" t="inlineStr"/>
+      <c r="L161" s="27" t="inlineStr"/>
+      <c r="M161" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N161" s="28" t="inlineStr"/>
+      <c r="O161" s="27" t="inlineStr"/>
+    </row>
+    <row r="162" ht="16" customHeight="1" s="18">
+      <c r="A162" s="20" t="inlineStr">
+        <is>
+          <t>933d53f44cdb</t>
+        </is>
+      </c>
+      <c r="B162" s="20" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="20" t="inlineStr">
+        <is>
+          <t>Electrical Project/Design Engineer</t>
+        </is>
+      </c>
+      <c r="D162" s="20" t="inlineStr">
+        <is>
+          <t>Matchtech</t>
+        </is>
+      </c>
+      <c r="E162" s="20" t="inlineStr">
+        <is>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="F162" s="20" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G162" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H162" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I162" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="J162" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K162" s="23" t="inlineStr"/>
+      <c r="L162" s="23" t="inlineStr"/>
+      <c r="M162" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N162" s="24" t="inlineStr"/>
+      <c r="O162" s="23" t="inlineStr"/>
+    </row>
+    <row r="163" ht="16" customHeight="1" s="18">
+      <c r="A163" s="25" t="inlineStr">
+        <is>
+          <t>218f4d78d772</t>
+        </is>
+      </c>
+      <c r="B163" s="25" t="inlineStr">
+        <is>
+          <t>18/02/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="25" t="inlineStr">
+        <is>
+          <t>Civil Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="D163" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E163" s="25" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F163" s="25" t="inlineStr">
+        <is>
+          <t>£55,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G163" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H163" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I163" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="J163" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K163" s="27" t="inlineStr"/>
+      <c r="L163" s="27" t="inlineStr"/>
+      <c r="M163" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N163" s="28" t="inlineStr"/>
+      <c r="O163" s="27" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -9192,6 +10608,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J138" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J163" r:id="rId162"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O163"/>
+  <dimension ref="A1:O186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" style="18" min="1" max="1"/>
@@ -10456,6 +10456,1363 @@
       </c>
       <c r="N163" s="28" t="inlineStr"/>
       <c r="O163" s="27" t="inlineStr"/>
+    </row>
+    <row r="164" ht="16" customHeight="1" s="18">
+      <c r="A164" s="20" t="inlineStr">
+        <is>
+          <t>51f9f29c4223</t>
+        </is>
+      </c>
+      <c r="B164" s="20" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="20" t="inlineStr">
+        <is>
+          <t>Plumber</t>
+        </is>
+      </c>
+      <c r="D164" s="20" t="inlineStr">
+        <is>
+          <t>WATES PROPERTY SERVICES LIMITED</t>
+        </is>
+      </c>
+      <c r="E164" s="20" t="inlineStr">
+        <is>
+          <t>Crawley, West Sussex</t>
+        </is>
+      </c>
+      <c r="F164" s="20" t="inlineStr">
+        <is>
+          <t>£50,654 – £50,654</t>
+        </is>
+      </c>
+      <c r="G164" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H164" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I164" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J164" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K164" s="23" t="inlineStr"/>
+      <c r="L164" s="23" t="inlineStr"/>
+      <c r="M164" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N164" s="24" t="inlineStr"/>
+      <c r="O164" s="23" t="inlineStr"/>
+    </row>
+    <row r="165" ht="16" customHeight="1" s="18">
+      <c r="A165" s="25" t="inlineStr">
+        <is>
+          <t>4c40fc76ca52</t>
+        </is>
+      </c>
+      <c r="B165" s="25" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D165" s="25" t="inlineStr">
+        <is>
+          <t>CHARTWELL</t>
+        </is>
+      </c>
+      <c r="E165" s="25" t="inlineStr">
+        <is>
+          <t>Chatham, Kent</t>
+        </is>
+      </c>
+      <c r="F165" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G165" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H165" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I165" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J165" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K165" s="27" t="inlineStr"/>
+      <c r="L165" s="27" t="inlineStr"/>
+      <c r="M165" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N165" s="28" t="inlineStr"/>
+      <c r="O165" s="27" t="inlineStr"/>
+    </row>
+    <row r="166" ht="16" customHeight="1" s="18">
+      <c r="A166" s="20" t="inlineStr">
+        <is>
+          <t>e2c2c7b0ace7</t>
+        </is>
+      </c>
+      <c r="B166" s="20" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C166" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D166" s="20" t="inlineStr">
+        <is>
+          <t>Reed</t>
+        </is>
+      </c>
+      <c r="E166" s="20" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F166" s="20" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G166" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H166" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I166" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J166" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K166" s="23" t="inlineStr"/>
+      <c r="L166" s="23" t="inlineStr"/>
+      <c r="M166" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N166" s="24" t="inlineStr"/>
+      <c r="O166" s="23" t="inlineStr"/>
+    </row>
+    <row r="167" ht="16" customHeight="1" s="18">
+      <c r="A167" s="25" t="inlineStr">
+        <is>
+          <t>20ab822ee732</t>
+        </is>
+      </c>
+      <c r="B167" s="25" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="25" t="inlineStr">
+        <is>
+          <t>Civil Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="D167" s="25" t="inlineStr">
+        <is>
+          <t>Zodiac Recruitment</t>
+        </is>
+      </c>
+      <c r="E167" s="25" t="inlineStr">
+        <is>
+          <t>Stone Cross, Crowborough</t>
+        </is>
+      </c>
+      <c r="F167" s="25" t="inlineStr">
+        <is>
+          <t>£32,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G167" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H167" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I167" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J167" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K167" s="27" t="inlineStr"/>
+      <c r="L167" s="27" t="inlineStr"/>
+      <c r="M167" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N167" s="28" t="inlineStr"/>
+      <c r="O167" s="27" t="inlineStr"/>
+    </row>
+    <row r="168" ht="16" customHeight="1" s="18">
+      <c r="A168" s="20" t="inlineStr">
+        <is>
+          <t>87ceadb33ae1</t>
+        </is>
+      </c>
+      <c r="B168" s="20" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C168" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D168" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E168" s="20" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F168" s="20" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G168" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H168" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I168" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J168" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K168" s="23" t="inlineStr"/>
+      <c r="L168" s="23" t="inlineStr"/>
+      <c r="M168" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N168" s="24" t="inlineStr"/>
+      <c r="O168" s="23" t="inlineStr"/>
+    </row>
+    <row r="169" ht="16" customHeight="1" s="18">
+      <c r="A169" s="25" t="inlineStr">
+        <is>
+          <t>699023f27473</t>
+        </is>
+      </c>
+      <c r="B169" s="25" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D169" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E169" s="25" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F169" s="25" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G169" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H169" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I169" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J169" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K169" s="27" t="inlineStr"/>
+      <c r="L169" s="27" t="inlineStr"/>
+      <c r="M169" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N169" s="28" t="inlineStr"/>
+      <c r="O169" s="27" t="inlineStr"/>
+    </row>
+    <row r="170" ht="16" customHeight="1" s="18">
+      <c r="A170" s="20" t="inlineStr">
+        <is>
+          <t>4b2b71c82a9c</t>
+        </is>
+      </c>
+      <c r="B170" s="20" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C170" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D170" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E170" s="20" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F170" s="20" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G170" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H170" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I170" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J170" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K170" s="23" t="inlineStr"/>
+      <c r="L170" s="23" t="inlineStr"/>
+      <c r="M170" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N170" s="24" t="inlineStr"/>
+      <c r="O170" s="23" t="inlineStr"/>
+    </row>
+    <row r="171" ht="16" customHeight="1" s="18">
+      <c r="A171" s="25" t="inlineStr">
+        <is>
+          <t>16c6d8aed40d</t>
+        </is>
+      </c>
+      <c r="B171" s="25" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="25" t="inlineStr">
+        <is>
+          <t>Senior Water Network Engineer/Modellers</t>
+        </is>
+      </c>
+      <c r="D171" s="25" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E171" s="25" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F171" s="25" t="inlineStr">
+        <is>
+          <t>£50,253 – £50,253</t>
+        </is>
+      </c>
+      <c r="G171" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H171" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I171" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="J171" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K171" s="27" t="inlineStr"/>
+      <c r="L171" s="27" t="inlineStr"/>
+      <c r="M171" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N171" s="28" t="inlineStr"/>
+      <c r="O171" s="27" t="inlineStr"/>
+    </row>
+    <row r="172" ht="16" customHeight="1" s="18">
+      <c r="A172" s="20" t="inlineStr">
+        <is>
+          <t>58e2d4977e31</t>
+        </is>
+      </c>
+      <c r="B172" s="20" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C172" s="20" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D172" s="20" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E172" s="20" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F172" s="20" t="inlineStr">
+        <is>
+          <t>£48,252 – £48,252</t>
+        </is>
+      </c>
+      <c r="G172" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H172" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I172" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="J172" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K172" s="23" t="inlineStr"/>
+      <c r="L172" s="23" t="inlineStr"/>
+      <c r="M172" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N172" s="24" t="inlineStr"/>
+      <c r="O172" s="23" t="inlineStr"/>
+    </row>
+    <row r="173" ht="16" customHeight="1" s="18">
+      <c r="A173" s="25" t="inlineStr">
+        <is>
+          <t>0ffe66b77d22</t>
+        </is>
+      </c>
+      <c r="B173" s="25" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="25" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D173" s="25" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E173" s="25" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F173" s="25" t="inlineStr">
+        <is>
+          <t>£49,369 – £49,369</t>
+        </is>
+      </c>
+      <c r="G173" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H173" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I173" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="J173" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K173" s="27" t="inlineStr"/>
+      <c r="L173" s="27" t="inlineStr"/>
+      <c r="M173" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N173" s="28" t="inlineStr"/>
+      <c r="O173" s="27" t="inlineStr"/>
+    </row>
+    <row r="174" ht="16" customHeight="1" s="18">
+      <c r="A174" s="20" t="inlineStr">
+        <is>
+          <t>71b8c7196cec</t>
+        </is>
+      </c>
+      <c r="B174" s="20" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C174" s="20" t="inlineStr">
+        <is>
+          <t>Senior Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D174" s="20" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment</t>
+        </is>
+      </c>
+      <c r="E174" s="20" t="inlineStr">
+        <is>
+          <t>Denner Hill, Great Missenden</t>
+        </is>
+      </c>
+      <c r="F174" s="20" t="inlineStr">
+        <is>
+          <t>£38,000 – £60,000</t>
+        </is>
+      </c>
+      <c r="G174" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H174" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I174" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J174" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K174" s="23" t="inlineStr"/>
+      <c r="L174" s="23" t="inlineStr"/>
+      <c r="M174" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N174" s="24" t="inlineStr"/>
+      <c r="O174" s="23" t="inlineStr"/>
+    </row>
+    <row r="175" ht="16" customHeight="1" s="18">
+      <c r="A175" s="25" t="inlineStr">
+        <is>
+          <t>4f3fee809113</t>
+        </is>
+      </c>
+      <c r="B175" s="25" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="25" t="inlineStr">
+        <is>
+          <t>Assistant Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D175" s="25" t="inlineStr">
+        <is>
+          <t>Henley Chase</t>
+        </is>
+      </c>
+      <c r="E175" s="25" t="inlineStr">
+        <is>
+          <t>New Haw, Addlestone</t>
+        </is>
+      </c>
+      <c r="F175" s="25" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G175" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H175" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I175" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J175" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K175" s="27" t="inlineStr"/>
+      <c r="L175" s="27" t="inlineStr"/>
+      <c r="M175" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N175" s="28" t="inlineStr"/>
+      <c r="O175" s="27" t="inlineStr"/>
+    </row>
+    <row r="176" ht="16" customHeight="1" s="18">
+      <c r="A176" s="20" t="inlineStr">
+        <is>
+          <t>cd35957461e4</t>
+        </is>
+      </c>
+      <c r="B176" s="20" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="20" t="inlineStr">
+        <is>
+          <t>Junior Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D176" s="20" t="inlineStr">
+        <is>
+          <t>Henley Chase Limited</t>
+        </is>
+      </c>
+      <c r="E176" s="20" t="inlineStr">
+        <is>
+          <t>Addlestone, Surrey</t>
+        </is>
+      </c>
+      <c r="F176" s="20" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G176" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H176" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I176" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J176" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K176" s="23" t="inlineStr"/>
+      <c r="L176" s="23" t="inlineStr"/>
+      <c r="M176" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N176" s="24" t="inlineStr"/>
+      <c r="O176" s="23" t="inlineStr"/>
+    </row>
+    <row r="177" ht="16" customHeight="1" s="18">
+      <c r="A177" s="25" t="inlineStr">
+        <is>
+          <t>cd45547cceb7</t>
+        </is>
+      </c>
+      <c r="B177" s="25" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="25" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Flood Risk &amp; Drainage</t>
+        </is>
+      </c>
+      <c r="D177" s="25" t="inlineStr">
+        <is>
+          <t>Aztrum</t>
+        </is>
+      </c>
+      <c r="E177" s="25" t="inlineStr">
+        <is>
+          <t>Ash Vale, Aldershot</t>
+        </is>
+      </c>
+      <c r="F177" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G177" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H177" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I177" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J177" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K177" s="27" t="inlineStr"/>
+      <c r="L177" s="27" t="inlineStr"/>
+      <c r="M177" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N177" s="28" t="inlineStr"/>
+      <c r="O177" s="27" t="inlineStr"/>
+    </row>
+    <row r="178" ht="16" customHeight="1" s="18">
+      <c r="A178" s="20" t="inlineStr">
+        <is>
+          <t>8794def23e7f</t>
+        </is>
+      </c>
+      <c r="B178" s="20" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="20" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D178" s="20" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Recruitment Consultancy</t>
+        </is>
+      </c>
+      <c r="E178" s="20" t="inlineStr">
+        <is>
+          <t>Fleet, Hampshire</t>
+        </is>
+      </c>
+      <c r="F178" s="20" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G178" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H178" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I178" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J178" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K178" s="23" t="inlineStr"/>
+      <c r="L178" s="23" t="inlineStr"/>
+      <c r="M178" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N178" s="24" t="inlineStr"/>
+      <c r="O178" s="23" t="inlineStr"/>
+    </row>
+    <row r="179" ht="16" customHeight="1" s="18">
+      <c r="A179" s="25" t="inlineStr">
+        <is>
+          <t>12db784117dd</t>
+        </is>
+      </c>
+      <c r="B179" s="25" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="25" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D179" s="25" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Associates Ltd</t>
+        </is>
+      </c>
+      <c r="E179" s="25" t="inlineStr">
+        <is>
+          <t>Artington, Guildford</t>
+        </is>
+      </c>
+      <c r="F179" s="25" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G179" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H179" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I179" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J179" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K179" s="27" t="inlineStr"/>
+      <c r="L179" s="27" t="inlineStr"/>
+      <c r="M179" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N179" s="28" t="inlineStr"/>
+      <c r="O179" s="27" t="inlineStr"/>
+    </row>
+    <row r="180" ht="16" customHeight="1" s="18">
+      <c r="A180" s="20" t="inlineStr">
+        <is>
+          <t>cda8ebd585d1</t>
+        </is>
+      </c>
+      <c r="B180" s="20" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C180" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D180" s="20" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E180" s="20" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F180" s="20" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G180" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H180" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I180" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J180" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K180" s="23" t="inlineStr"/>
+      <c r="L180" s="23" t="inlineStr"/>
+      <c r="M180" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N180" s="24" t="inlineStr"/>
+      <c r="O180" s="23" t="inlineStr"/>
+    </row>
+    <row r="181" ht="16" customHeight="1" s="18">
+      <c r="A181" s="25" t="inlineStr">
+        <is>
+          <t>80b9a90c8122</t>
+        </is>
+      </c>
+      <c r="B181" s="25" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="25" t="inlineStr">
+        <is>
+          <t>Quality Engineer</t>
+        </is>
+      </c>
+      <c r="D181" s="25" t="inlineStr">
+        <is>
+          <t>Rapiscan Systems</t>
+        </is>
+      </c>
+      <c r="E181" s="25" t="inlineStr">
+        <is>
+          <t>Salfords, Redhill</t>
+        </is>
+      </c>
+      <c r="F181" s="25" t="inlineStr">
+        <is>
+          <t>£46,683 – £46,683</t>
+        </is>
+      </c>
+      <c r="G181" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H181" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I181" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J181" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K181" s="27" t="inlineStr"/>
+      <c r="L181" s="27" t="inlineStr"/>
+      <c r="M181" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N181" s="28" t="inlineStr"/>
+      <c r="O181" s="27" t="inlineStr"/>
+    </row>
+    <row r="182" ht="16" customHeight="1" s="18">
+      <c r="A182" s="20" t="inlineStr">
+        <is>
+          <t>b1ee2f9b7501</t>
+        </is>
+      </c>
+      <c r="B182" s="20" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C182" s="20" t="inlineStr">
+        <is>
+          <t>Assistant Engineer - Clean Water Modelling</t>
+        </is>
+      </c>
+      <c r="D182" s="20" t="inlineStr">
+        <is>
+          <t>WSP</t>
+        </is>
+      </c>
+      <c r="E182" s="20" t="inlineStr">
+        <is>
+          <t>Aldwych, Central London</t>
+        </is>
+      </c>
+      <c r="F182" s="20" t="inlineStr">
+        <is>
+          <t>£45,719 – £45,719</t>
+        </is>
+      </c>
+      <c r="G182" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H182" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I182" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J182" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K182" s="23" t="inlineStr"/>
+      <c r="L182" s="23" t="inlineStr"/>
+      <c r="M182" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N182" s="24" t="inlineStr"/>
+      <c r="O182" s="23" t="inlineStr"/>
+    </row>
+    <row r="183" ht="16" customHeight="1" s="18">
+      <c r="A183" s="25" t="inlineStr">
+        <is>
+          <t>9143bf653260</t>
+        </is>
+      </c>
+      <c r="B183" s="25" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="25" t="inlineStr">
+        <is>
+          <t>Pump Engineer</t>
+        </is>
+      </c>
+      <c r="D183" s="25" t="inlineStr">
+        <is>
+          <t>Smart Search Technical Ltd</t>
+        </is>
+      </c>
+      <c r="E183" s="25" t="inlineStr">
+        <is>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="F183" s="25" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G183" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H183" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I183" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J183" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K183" s="27" t="inlineStr"/>
+      <c r="L183" s="27" t="inlineStr"/>
+      <c r="M183" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N183" s="28" t="inlineStr"/>
+      <c r="O183" s="27" t="inlineStr"/>
+    </row>
+    <row r="184" ht="16" customHeight="1" s="18">
+      <c r="A184" s="20" t="inlineStr">
+        <is>
+          <t>7457aa6c128f</t>
+        </is>
+      </c>
+      <c r="B184" s="20" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C184" s="20" t="inlineStr">
+        <is>
+          <t>HGV Class 2 Tanker Driver – Drainage</t>
+        </is>
+      </c>
+      <c r="D184" s="20" t="inlineStr">
+        <is>
+          <t>Excellis Consultancy</t>
+        </is>
+      </c>
+      <c r="E184" s="20" t="inlineStr">
+        <is>
+          <t>Riverhead, Sevenoaks</t>
+        </is>
+      </c>
+      <c r="F184" s="20" t="inlineStr">
+        <is>
+          <t>£45,000 – £48,000</t>
+        </is>
+      </c>
+      <c r="G184" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H184" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I184" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J184" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K184" s="23" t="inlineStr"/>
+      <c r="L184" s="23" t="inlineStr"/>
+      <c r="M184" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N184" s="24" t="inlineStr"/>
+      <c r="O184" s="23" t="inlineStr"/>
+    </row>
+    <row r="185" ht="16" customHeight="1" s="18">
+      <c r="A185" s="25" t="inlineStr">
+        <is>
+          <t>03b317594b43</t>
+        </is>
+      </c>
+      <c r="B185" s="25" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C185" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D185" s="25" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E185" s="25" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F185" s="25" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G185" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H185" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I185" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J185" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K185" s="27" t="inlineStr"/>
+      <c r="L185" s="27" t="inlineStr"/>
+      <c r="M185" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N185" s="28" t="inlineStr"/>
+      <c r="O185" s="27" t="inlineStr"/>
+    </row>
+    <row r="186" ht="16" customHeight="1" s="18">
+      <c r="A186" s="20" t="inlineStr">
+        <is>
+          <t>a056e12823ab</t>
+        </is>
+      </c>
+      <c r="B186" s="20" t="inlineStr">
+        <is>
+          <t>19/02/2026</t>
+        </is>
+      </c>
+      <c r="C186" s="20" t="inlineStr">
+        <is>
+          <t>Pollution Response Technician</t>
+        </is>
+      </c>
+      <c r="D186" s="20" t="inlineStr">
+        <is>
+          <t>Lanes Group</t>
+        </is>
+      </c>
+      <c r="E186" s="20" t="inlineStr">
+        <is>
+          <t>Tudeley, Tonbridge</t>
+        </is>
+      </c>
+      <c r="F186" s="20" t="inlineStr">
+        <is>
+          <t>£54,416 – £54,416</t>
+        </is>
+      </c>
+      <c r="G186" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H186" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I186" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J186" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K186" s="23" t="inlineStr"/>
+      <c r="L186" s="23" t="inlineStr"/>
+      <c r="M186" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N186" s="24" t="inlineStr"/>
+      <c r="O186" s="23" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -10632,6 +11989,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J162" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J186" r:id="rId185"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O186"/>
+  <dimension ref="A1:O215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" style="18" min="1" max="1"/>
@@ -11813,6 +11813,1717 @@
       </c>
       <c r="N186" s="24" t="inlineStr"/>
       <c r="O186" s="23" t="inlineStr"/>
+    </row>
+    <row r="187" ht="16" customHeight="1" s="18">
+      <c r="A187" s="25" t="inlineStr">
+        <is>
+          <t>31f7f3b9406f</t>
+        </is>
+      </c>
+      <c r="B187" s="25" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C187" s="25" t="inlineStr">
+        <is>
+          <t>Plumber</t>
+        </is>
+      </c>
+      <c r="D187" s="25" t="inlineStr">
+        <is>
+          <t>WATES PROPERTY SERVICES LIMITED</t>
+        </is>
+      </c>
+      <c r="E187" s="25" t="inlineStr">
+        <is>
+          <t>Crawley, West Sussex</t>
+        </is>
+      </c>
+      <c r="F187" s="25" t="inlineStr">
+        <is>
+          <t>£50,654 – £50,654</t>
+        </is>
+      </c>
+      <c r="G187" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H187" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I187" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J187" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K187" s="27" t="inlineStr"/>
+      <c r="L187" s="27" t="inlineStr"/>
+      <c r="M187" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N187" s="28" t="inlineStr"/>
+      <c r="O187" s="27" t="inlineStr"/>
+    </row>
+    <row r="188" ht="16" customHeight="1" s="18">
+      <c r="A188" s="20" t="inlineStr">
+        <is>
+          <t>6dd4c3e62065</t>
+        </is>
+      </c>
+      <c r="B188" s="20" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C188" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D188" s="20" t="inlineStr">
+        <is>
+          <t>CHARTWELL</t>
+        </is>
+      </c>
+      <c r="E188" s="20" t="inlineStr">
+        <is>
+          <t>Chatham, Kent</t>
+        </is>
+      </c>
+      <c r="F188" s="20" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G188" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H188" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I188" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J188" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K188" s="23" t="inlineStr"/>
+      <c r="L188" s="23" t="inlineStr"/>
+      <c r="M188" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N188" s="24" t="inlineStr"/>
+      <c r="O188" s="23" t="inlineStr"/>
+    </row>
+    <row r="189" ht="16" customHeight="1" s="18">
+      <c r="A189" s="25" t="inlineStr">
+        <is>
+          <t>6c51ad52cabc</t>
+        </is>
+      </c>
+      <c r="B189" s="25" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C189" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D189" s="25" t="inlineStr">
+        <is>
+          <t>Reed</t>
+        </is>
+      </c>
+      <c r="E189" s="25" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F189" s="25" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G189" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H189" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I189" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J189" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K189" s="27" t="inlineStr"/>
+      <c r="L189" s="27" t="inlineStr"/>
+      <c r="M189" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N189" s="28" t="inlineStr"/>
+      <c r="O189" s="27" t="inlineStr"/>
+    </row>
+    <row r="190" ht="16" customHeight="1" s="18">
+      <c r="A190" s="20" t="inlineStr">
+        <is>
+          <t>6905a3f9752c</t>
+        </is>
+      </c>
+      <c r="B190" s="20" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C190" s="20" t="inlineStr">
+        <is>
+          <t>Civil Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="D190" s="20" t="inlineStr">
+        <is>
+          <t>Zodiac Recruitment</t>
+        </is>
+      </c>
+      <c r="E190" s="20" t="inlineStr">
+        <is>
+          <t>Stone Cross, Crowborough</t>
+        </is>
+      </c>
+      <c r="F190" s="20" t="inlineStr">
+        <is>
+          <t>£32,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G190" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H190" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I190" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J190" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K190" s="23" t="inlineStr"/>
+      <c r="L190" s="23" t="inlineStr"/>
+      <c r="M190" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N190" s="24" t="inlineStr"/>
+      <c r="O190" s="23" t="inlineStr"/>
+    </row>
+    <row r="191" ht="16" customHeight="1" s="18">
+      <c r="A191" s="25" t="inlineStr">
+        <is>
+          <t>f512db074604</t>
+        </is>
+      </c>
+      <c r="B191" s="25" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C191" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D191" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E191" s="25" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F191" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G191" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H191" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I191" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J191" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K191" s="27" t="inlineStr"/>
+      <c r="L191" s="27" t="inlineStr"/>
+      <c r="M191" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N191" s="28" t="inlineStr"/>
+      <c r="O191" s="27" t="inlineStr"/>
+    </row>
+    <row r="192" ht="16" customHeight="1" s="18">
+      <c r="A192" s="20" t="inlineStr">
+        <is>
+          <t>c4fa31606365</t>
+        </is>
+      </c>
+      <c r="B192" s="20" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C192" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D192" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E192" s="20" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F192" s="20" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G192" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H192" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I192" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J192" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K192" s="23" t="inlineStr"/>
+      <c r="L192" s="23" t="inlineStr"/>
+      <c r="M192" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N192" s="24" t="inlineStr"/>
+      <c r="O192" s="23" t="inlineStr"/>
+    </row>
+    <row r="193" ht="16" customHeight="1" s="18">
+      <c r="A193" s="25" t="inlineStr">
+        <is>
+          <t>d5352509ed2f</t>
+        </is>
+      </c>
+      <c r="B193" s="25" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C193" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D193" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E193" s="25" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F193" s="25" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G193" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H193" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I193" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J193" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K193" s="27" t="inlineStr"/>
+      <c r="L193" s="27" t="inlineStr"/>
+      <c r="M193" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N193" s="28" t="inlineStr"/>
+      <c r="O193" s="27" t="inlineStr"/>
+    </row>
+    <row r="194" ht="16" customHeight="1" s="18">
+      <c r="A194" s="20" t="inlineStr">
+        <is>
+          <t>a88db1ef1454</t>
+        </is>
+      </c>
+      <c r="B194" s="20" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C194" s="20" t="inlineStr">
+        <is>
+          <t>Senior Water Network Engineer/Modellers</t>
+        </is>
+      </c>
+      <c r="D194" s="20" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E194" s="20" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F194" s="20" t="inlineStr">
+        <is>
+          <t>£50,253 – £50,253</t>
+        </is>
+      </c>
+      <c r="G194" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H194" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I194" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="J194" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K194" s="23" t="inlineStr"/>
+      <c r="L194" s="23" t="inlineStr"/>
+      <c r="M194" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N194" s="24" t="inlineStr"/>
+      <c r="O194" s="23" t="inlineStr"/>
+    </row>
+    <row r="195" ht="16" customHeight="1" s="18">
+      <c r="A195" s="25" t="inlineStr">
+        <is>
+          <t>e93b54ea93b6</t>
+        </is>
+      </c>
+      <c r="B195" s="25" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C195" s="25" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D195" s="25" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E195" s="25" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F195" s="25" t="inlineStr">
+        <is>
+          <t>£48,252 – £48,252</t>
+        </is>
+      </c>
+      <c r="G195" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H195" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I195" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="J195" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K195" s="27" t="inlineStr"/>
+      <c r="L195" s="27" t="inlineStr"/>
+      <c r="M195" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N195" s="28" t="inlineStr"/>
+      <c r="O195" s="27" t="inlineStr"/>
+    </row>
+    <row r="196" ht="16" customHeight="1" s="18">
+      <c r="A196" s="20" t="inlineStr">
+        <is>
+          <t>9d4755cad6f6</t>
+        </is>
+      </c>
+      <c r="B196" s="20" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C196" s="20" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D196" s="20" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E196" s="20" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F196" s="20" t="inlineStr">
+        <is>
+          <t>£49,369 – £49,369</t>
+        </is>
+      </c>
+      <c r="G196" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H196" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I196" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="J196" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K196" s="23" t="inlineStr"/>
+      <c r="L196" s="23" t="inlineStr"/>
+      <c r="M196" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N196" s="24" t="inlineStr"/>
+      <c r="O196" s="23" t="inlineStr"/>
+    </row>
+    <row r="197" ht="16" customHeight="1" s="18">
+      <c r="A197" s="25" t="inlineStr">
+        <is>
+          <t>007e8b5e0aec</t>
+        </is>
+      </c>
+      <c r="B197" s="25" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C197" s="25" t="inlineStr">
+        <is>
+          <t>Senior Electrical Engineer - Water Projects</t>
+        </is>
+      </c>
+      <c r="D197" s="25" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E197" s="25" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F197" s="25" t="inlineStr">
+        <is>
+          <t>£51,555 – £51,555</t>
+        </is>
+      </c>
+      <c r="G197" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H197" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I197" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J197" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K197" s="27" t="inlineStr"/>
+      <c r="L197" s="27" t="inlineStr"/>
+      <c r="M197" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N197" s="28" t="inlineStr"/>
+      <c r="O197" s="27" t="inlineStr"/>
+    </row>
+    <row r="198" ht="16" customHeight="1" s="18">
+      <c r="A198" s="20" t="inlineStr">
+        <is>
+          <t>219d65ccdf91</t>
+        </is>
+      </c>
+      <c r="B198" s="20" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C198" s="20" t="inlineStr">
+        <is>
+          <t>Senior Electrical Engineer - Water Projects</t>
+        </is>
+      </c>
+      <c r="D198" s="20" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E198" s="20" t="inlineStr">
+        <is>
+          <t>St. Albans, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="F198" s="20" t="inlineStr">
+        <is>
+          <t>£52,221 – £52,221</t>
+        </is>
+      </c>
+      <c r="G198" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H198" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I198" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J198" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K198" s="23" t="inlineStr"/>
+      <c r="L198" s="23" t="inlineStr"/>
+      <c r="M198" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N198" s="24" t="inlineStr"/>
+      <c r="O198" s="23" t="inlineStr"/>
+    </row>
+    <row r="199" ht="16" customHeight="1" s="18">
+      <c r="A199" s="25" t="inlineStr">
+        <is>
+          <t>5e7fe1b5a3e8</t>
+        </is>
+      </c>
+      <c r="B199" s="25" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C199" s="25" t="inlineStr">
+        <is>
+          <t>Senior Electrical Engineer - Water Projects</t>
+        </is>
+      </c>
+      <c r="D199" s="25" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E199" s="25" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F199" s="25" t="inlineStr">
+        <is>
+          <t>£53,100 – £53,100</t>
+        </is>
+      </c>
+      <c r="G199" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H199" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I199" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J199" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K199" s="27" t="inlineStr"/>
+      <c r="L199" s="27" t="inlineStr"/>
+      <c r="M199" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N199" s="28" t="inlineStr"/>
+      <c r="O199" s="27" t="inlineStr"/>
+    </row>
+    <row r="200" ht="16" customHeight="1" s="18">
+      <c r="A200" s="20" t="inlineStr">
+        <is>
+          <t>dd2b666dd790</t>
+        </is>
+      </c>
+      <c r="B200" s="20" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C200" s="20" t="inlineStr">
+        <is>
+          <t>Senior Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D200" s="20" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment</t>
+        </is>
+      </c>
+      <c r="E200" s="20" t="inlineStr">
+        <is>
+          <t>Denner Hill, Great Missenden</t>
+        </is>
+      </c>
+      <c r="F200" s="20" t="inlineStr">
+        <is>
+          <t>£38,000 – £60,000</t>
+        </is>
+      </c>
+      <c r="G200" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H200" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I200" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J200" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K200" s="23" t="inlineStr"/>
+      <c r="L200" s="23" t="inlineStr"/>
+      <c r="M200" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N200" s="24" t="inlineStr"/>
+      <c r="O200" s="23" t="inlineStr"/>
+    </row>
+    <row r="201" ht="16" customHeight="1" s="18">
+      <c r="A201" s="25" t="inlineStr">
+        <is>
+          <t>0d14cc1a2fbf</t>
+        </is>
+      </c>
+      <c r="B201" s="25" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C201" s="25" t="inlineStr">
+        <is>
+          <t>Assistant Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D201" s="25" t="inlineStr">
+        <is>
+          <t>Henley Chase</t>
+        </is>
+      </c>
+      <c r="E201" s="25" t="inlineStr">
+        <is>
+          <t>New Haw, Addlestone</t>
+        </is>
+      </c>
+      <c r="F201" s="25" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G201" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H201" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I201" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J201" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K201" s="27" t="inlineStr"/>
+      <c r="L201" s="27" t="inlineStr"/>
+      <c r="M201" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N201" s="28" t="inlineStr"/>
+      <c r="O201" s="27" t="inlineStr"/>
+    </row>
+    <row r="202" ht="16" customHeight="1" s="18">
+      <c r="A202" s="20" t="inlineStr">
+        <is>
+          <t>2d1a4f6cd27f</t>
+        </is>
+      </c>
+      <c r="B202" s="20" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C202" s="20" t="inlineStr">
+        <is>
+          <t>Junior Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D202" s="20" t="inlineStr">
+        <is>
+          <t>Henley Chase Limited</t>
+        </is>
+      </c>
+      <c r="E202" s="20" t="inlineStr">
+        <is>
+          <t>Addlestone, Surrey</t>
+        </is>
+      </c>
+      <c r="F202" s="20" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G202" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H202" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I202" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J202" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K202" s="23" t="inlineStr"/>
+      <c r="L202" s="23" t="inlineStr"/>
+      <c r="M202" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N202" s="24" t="inlineStr"/>
+      <c r="O202" s="23" t="inlineStr"/>
+    </row>
+    <row r="203" ht="16" customHeight="1" s="18">
+      <c r="A203" s="25" t="inlineStr">
+        <is>
+          <t>f3cc713671d2</t>
+        </is>
+      </c>
+      <c r="B203" s="25" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C203" s="25" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Flood Risk &amp; Drainage</t>
+        </is>
+      </c>
+      <c r="D203" s="25" t="inlineStr">
+        <is>
+          <t>Aztrum</t>
+        </is>
+      </c>
+      <c r="E203" s="25" t="inlineStr">
+        <is>
+          <t>Ash Vale, Aldershot</t>
+        </is>
+      </c>
+      <c r="F203" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G203" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H203" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I203" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J203" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K203" s="27" t="inlineStr"/>
+      <c r="L203" s="27" t="inlineStr"/>
+      <c r="M203" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N203" s="28" t="inlineStr"/>
+      <c r="O203" s="27" t="inlineStr"/>
+    </row>
+    <row r="204" ht="16" customHeight="1" s="18">
+      <c r="A204" s="20" t="inlineStr">
+        <is>
+          <t>8156310be7b6</t>
+        </is>
+      </c>
+      <c r="B204" s="20" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C204" s="20" t="inlineStr">
+        <is>
+          <t>Structural Design Engineer</t>
+        </is>
+      </c>
+      <c r="D204" s="20" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Recruitment Consultancy</t>
+        </is>
+      </c>
+      <c r="E204" s="20" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F204" s="20" t="inlineStr">
+        <is>
+          <t>£50,000 – £75,000</t>
+        </is>
+      </c>
+      <c r="G204" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H204" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I204" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J204" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K204" s="23" t="inlineStr"/>
+      <c r="L204" s="23" t="inlineStr"/>
+      <c r="M204" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N204" s="24" t="inlineStr"/>
+      <c r="O204" s="23" t="inlineStr"/>
+    </row>
+    <row r="205" ht="16" customHeight="1" s="18">
+      <c r="A205" s="25" t="inlineStr">
+        <is>
+          <t>6c9b4f501e33</t>
+        </is>
+      </c>
+      <c r="B205" s="25" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C205" s="25" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D205" s="25" t="inlineStr">
+        <is>
+          <t>Murray McIntosh &amp; Associates Limited</t>
+        </is>
+      </c>
+      <c r="E205" s="25" t="inlineStr">
+        <is>
+          <t>Church Crookham, Fleet</t>
+        </is>
+      </c>
+      <c r="F205" s="25" t="inlineStr">
+        <is>
+          <t>£50,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G205" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H205" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I205" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J205" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K205" s="27" t="inlineStr"/>
+      <c r="L205" s="27" t="inlineStr"/>
+      <c r="M205" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N205" s="28" t="inlineStr"/>
+      <c r="O205" s="27" t="inlineStr"/>
+    </row>
+    <row r="206" ht="16" customHeight="1" s="18">
+      <c r="A206" s="20" t="inlineStr">
+        <is>
+          <t>bdf056cde7cf</t>
+        </is>
+      </c>
+      <c r="B206" s="20" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C206" s="20" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D206" s="20" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Recruitment Consultancy</t>
+        </is>
+      </c>
+      <c r="E206" s="20" t="inlineStr">
+        <is>
+          <t>Fleet, Hampshire</t>
+        </is>
+      </c>
+      <c r="F206" s="20" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G206" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H206" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I206" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J206" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K206" s="23" t="inlineStr"/>
+      <c r="L206" s="23" t="inlineStr"/>
+      <c r="M206" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N206" s="24" t="inlineStr"/>
+      <c r="O206" s="23" t="inlineStr"/>
+    </row>
+    <row r="207" ht="16" customHeight="1" s="18">
+      <c r="A207" s="25" t="inlineStr">
+        <is>
+          <t>83f4a5aaa7a8</t>
+        </is>
+      </c>
+      <c r="B207" s="25" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C207" s="25" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D207" s="25" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Associates Ltd</t>
+        </is>
+      </c>
+      <c r="E207" s="25" t="inlineStr">
+        <is>
+          <t>Artington, Guildford</t>
+        </is>
+      </c>
+      <c r="F207" s="25" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G207" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H207" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I207" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J207" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K207" s="27" t="inlineStr"/>
+      <c r="L207" s="27" t="inlineStr"/>
+      <c r="M207" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N207" s="28" t="inlineStr"/>
+      <c r="O207" s="27" t="inlineStr"/>
+    </row>
+    <row r="208" ht="16" customHeight="1" s="18">
+      <c r="A208" s="20" t="inlineStr">
+        <is>
+          <t>f6fdd98a94d4</t>
+        </is>
+      </c>
+      <c r="B208" s="20" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C208" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D208" s="20" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E208" s="20" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F208" s="20" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G208" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H208" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I208" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J208" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K208" s="23" t="inlineStr"/>
+      <c r="L208" s="23" t="inlineStr"/>
+      <c r="M208" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N208" s="24" t="inlineStr"/>
+      <c r="O208" s="23" t="inlineStr"/>
+    </row>
+    <row r="209" ht="16" customHeight="1" s="18">
+      <c r="A209" s="25" t="inlineStr">
+        <is>
+          <t>93371f0888f4</t>
+        </is>
+      </c>
+      <c r="B209" s="25" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C209" s="25" t="inlineStr">
+        <is>
+          <t>Quality Engineer</t>
+        </is>
+      </c>
+      <c r="D209" s="25" t="inlineStr">
+        <is>
+          <t>Rapiscan Systems</t>
+        </is>
+      </c>
+      <c r="E209" s="25" t="inlineStr">
+        <is>
+          <t>Salfords, Redhill</t>
+        </is>
+      </c>
+      <c r="F209" s="25" t="inlineStr">
+        <is>
+          <t>£49,199 – £49,199</t>
+        </is>
+      </c>
+      <c r="G209" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H209" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I209" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J209" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K209" s="27" t="inlineStr"/>
+      <c r="L209" s="27" t="inlineStr"/>
+      <c r="M209" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N209" s="28" t="inlineStr"/>
+      <c r="O209" s="27" t="inlineStr"/>
+    </row>
+    <row r="210" ht="16" customHeight="1" s="18">
+      <c r="A210" s="20" t="inlineStr">
+        <is>
+          <t>2b9ce0da0b95</t>
+        </is>
+      </c>
+      <c r="B210" s="20" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C210" s="20" t="inlineStr">
+        <is>
+          <t>Quality Engineer</t>
+        </is>
+      </c>
+      <c r="D210" s="20" t="inlineStr">
+        <is>
+          <t>Rapiscan Systems</t>
+        </is>
+      </c>
+      <c r="E210" s="20" t="inlineStr">
+        <is>
+          <t>Salfords, Redhill</t>
+        </is>
+      </c>
+      <c r="F210" s="20" t="inlineStr">
+        <is>
+          <t>£46,683 – £46,683</t>
+        </is>
+      </c>
+      <c r="G210" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H210" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I210" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J210" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K210" s="23" t="inlineStr"/>
+      <c r="L210" s="23" t="inlineStr"/>
+      <c r="M210" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N210" s="24" t="inlineStr"/>
+      <c r="O210" s="23" t="inlineStr"/>
+    </row>
+    <row r="211" ht="16" customHeight="1" s="18">
+      <c r="A211" s="25" t="inlineStr">
+        <is>
+          <t>3583b7264ed4</t>
+        </is>
+      </c>
+      <c r="B211" s="25" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C211" s="25" t="inlineStr">
+        <is>
+          <t>Assistant Engineer - Clean Water Modelling</t>
+        </is>
+      </c>
+      <c r="D211" s="25" t="inlineStr">
+        <is>
+          <t>WSP</t>
+        </is>
+      </c>
+      <c r="E211" s="25" t="inlineStr">
+        <is>
+          <t>Aldwych, Central London</t>
+        </is>
+      </c>
+      <c r="F211" s="25" t="inlineStr">
+        <is>
+          <t>£45,209 – £45,209</t>
+        </is>
+      </c>
+      <c r="G211" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H211" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I211" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J211" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K211" s="27" t="inlineStr"/>
+      <c r="L211" s="27" t="inlineStr"/>
+      <c r="M211" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N211" s="28" t="inlineStr"/>
+      <c r="O211" s="27" t="inlineStr"/>
+    </row>
+    <row r="212" ht="16" customHeight="1" s="18">
+      <c r="A212" s="20" t="inlineStr">
+        <is>
+          <t>f059723c790f</t>
+        </is>
+      </c>
+      <c r="B212" s="20" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C212" s="20" t="inlineStr">
+        <is>
+          <t>Pump Engineer</t>
+        </is>
+      </c>
+      <c r="D212" s="20" t="inlineStr">
+        <is>
+          <t>Smart Search Technical Ltd</t>
+        </is>
+      </c>
+      <c r="E212" s="20" t="inlineStr">
+        <is>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="F212" s="20" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G212" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H212" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I212" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J212" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K212" s="23" t="inlineStr"/>
+      <c r="L212" s="23" t="inlineStr"/>
+      <c r="M212" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N212" s="24" t="inlineStr"/>
+      <c r="O212" s="23" t="inlineStr"/>
+    </row>
+    <row r="213" ht="16" customHeight="1" s="18">
+      <c r="A213" s="25" t="inlineStr">
+        <is>
+          <t>c3e2ed210d48</t>
+        </is>
+      </c>
+      <c r="B213" s="25" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C213" s="25" t="inlineStr">
+        <is>
+          <t>HGV Class 2 Tanker Driver – Drainage</t>
+        </is>
+      </c>
+      <c r="D213" s="25" t="inlineStr">
+        <is>
+          <t>Excellis Consultancy</t>
+        </is>
+      </c>
+      <c r="E213" s="25" t="inlineStr">
+        <is>
+          <t>Riverhead, Sevenoaks</t>
+        </is>
+      </c>
+      <c r="F213" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £48,000</t>
+        </is>
+      </c>
+      <c r="G213" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H213" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I213" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J213" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K213" s="27" t="inlineStr"/>
+      <c r="L213" s="27" t="inlineStr"/>
+      <c r="M213" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N213" s="28" t="inlineStr"/>
+      <c r="O213" s="27" t="inlineStr"/>
+    </row>
+    <row r="214" ht="16" customHeight="1" s="18">
+      <c r="A214" s="20" t="inlineStr">
+        <is>
+          <t>5db6b340fd15</t>
+        </is>
+      </c>
+      <c r="B214" s="20" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C214" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D214" s="20" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E214" s="20" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F214" s="20" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G214" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H214" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I214" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J214" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K214" s="23" t="inlineStr"/>
+      <c r="L214" s="23" t="inlineStr"/>
+      <c r="M214" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N214" s="24" t="inlineStr"/>
+      <c r="O214" s="23" t="inlineStr"/>
+    </row>
+    <row r="215" ht="16" customHeight="1" s="18">
+      <c r="A215" s="25" t="inlineStr">
+        <is>
+          <t>219705c85a6b</t>
+        </is>
+      </c>
+      <c r="B215" s="25" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="C215" s="25" t="inlineStr">
+        <is>
+          <t>Pollution Response Technician</t>
+        </is>
+      </c>
+      <c r="D215" s="25" t="inlineStr">
+        <is>
+          <t>Lanes Group</t>
+        </is>
+      </c>
+      <c r="E215" s="25" t="inlineStr">
+        <is>
+          <t>Tudeley, Tonbridge</t>
+        </is>
+      </c>
+      <c r="F215" s="25" t="inlineStr">
+        <is>
+          <t>£54,416 – £54,416</t>
+        </is>
+      </c>
+      <c r="G215" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H215" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I215" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J215" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K215" s="27" t="inlineStr"/>
+      <c r="L215" s="27" t="inlineStr"/>
+      <c r="M215" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N215" s="28" t="inlineStr"/>
+      <c r="O215" s="27" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -12012,6 +13723,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J184" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J185" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J215" r:id="rId214"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O215"/>
+  <dimension ref="A1:O243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" style="18" min="1" max="1"/>
@@ -13524,6 +13524,1658 @@
       </c>
       <c r="N215" s="28" t="inlineStr"/>
       <c r="O215" s="27" t="inlineStr"/>
+    </row>
+    <row r="216" ht="16" customHeight="1" s="18">
+      <c r="A216" s="20" t="inlineStr">
+        <is>
+          <t>214103946cdf</t>
+        </is>
+      </c>
+      <c r="B216" s="20" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C216" s="20" t="inlineStr">
+        <is>
+          <t>Plumber</t>
+        </is>
+      </c>
+      <c r="D216" s="20" t="inlineStr">
+        <is>
+          <t>WATES PROPERTY SERVICES LIMITED</t>
+        </is>
+      </c>
+      <c r="E216" s="20" t="inlineStr">
+        <is>
+          <t>Crawley, West Sussex</t>
+        </is>
+      </c>
+      <c r="F216" s="20" t="inlineStr">
+        <is>
+          <t>£50,654 – £50,654</t>
+        </is>
+      </c>
+      <c r="G216" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H216" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I216" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J216" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K216" s="23" t="inlineStr"/>
+      <c r="L216" s="23" t="inlineStr"/>
+      <c r="M216" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N216" s="24" t="inlineStr"/>
+      <c r="O216" s="23" t="inlineStr"/>
+    </row>
+    <row r="217" ht="16" customHeight="1" s="18">
+      <c r="A217" s="25" t="inlineStr">
+        <is>
+          <t>41df660f858c</t>
+        </is>
+      </c>
+      <c r="B217" s="25" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C217" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D217" s="25" t="inlineStr">
+        <is>
+          <t>CHARTWELL</t>
+        </is>
+      </c>
+      <c r="E217" s="25" t="inlineStr">
+        <is>
+          <t>Chatham, Kent</t>
+        </is>
+      </c>
+      <c r="F217" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G217" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H217" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I217" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J217" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K217" s="27" t="inlineStr"/>
+      <c r="L217" s="27" t="inlineStr"/>
+      <c r="M217" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N217" s="28" t="inlineStr"/>
+      <c r="O217" s="27" t="inlineStr"/>
+    </row>
+    <row r="218" ht="16" customHeight="1" s="18">
+      <c r="A218" s="20" t="inlineStr">
+        <is>
+          <t>9e0395db3cbd</t>
+        </is>
+      </c>
+      <c r="B218" s="20" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C218" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D218" s="20" t="inlineStr">
+        <is>
+          <t>Reed</t>
+        </is>
+      </c>
+      <c r="E218" s="20" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F218" s="20" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G218" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H218" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I218" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J218" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K218" s="23" t="inlineStr"/>
+      <c r="L218" s="23" t="inlineStr"/>
+      <c r="M218" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N218" s="24" t="inlineStr"/>
+      <c r="O218" s="23" t="inlineStr"/>
+    </row>
+    <row r="219" ht="16" customHeight="1" s="18">
+      <c r="A219" s="25" t="inlineStr">
+        <is>
+          <t>8aea820d0004</t>
+        </is>
+      </c>
+      <c r="B219" s="25" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C219" s="25" t="inlineStr">
+        <is>
+          <t>Civil Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="D219" s="25" t="inlineStr">
+        <is>
+          <t>Zodiac Recruitment</t>
+        </is>
+      </c>
+      <c r="E219" s="25" t="inlineStr">
+        <is>
+          <t>Stone Cross, Crowborough</t>
+        </is>
+      </c>
+      <c r="F219" s="25" t="inlineStr">
+        <is>
+          <t>£32,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G219" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H219" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I219" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J219" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K219" s="27" t="inlineStr"/>
+      <c r="L219" s="27" t="inlineStr"/>
+      <c r="M219" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N219" s="28" t="inlineStr"/>
+      <c r="O219" s="27" t="inlineStr"/>
+    </row>
+    <row r="220" ht="16" customHeight="1" s="18">
+      <c r="A220" s="20" t="inlineStr">
+        <is>
+          <t>82bd48219723</t>
+        </is>
+      </c>
+      <c r="B220" s="20" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C220" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D220" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E220" s="20" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F220" s="20" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G220" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H220" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I220" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J220" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K220" s="23" t="inlineStr"/>
+      <c r="L220" s="23" t="inlineStr"/>
+      <c r="M220" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N220" s="24" t="inlineStr"/>
+      <c r="O220" s="23" t="inlineStr"/>
+    </row>
+    <row r="221" ht="16" customHeight="1" s="18">
+      <c r="A221" s="25" t="inlineStr">
+        <is>
+          <t>a38b8da8c96e</t>
+        </is>
+      </c>
+      <c r="B221" s="25" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C221" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D221" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E221" s="25" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F221" s="25" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G221" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H221" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I221" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J221" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K221" s="27" t="inlineStr"/>
+      <c r="L221" s="27" t="inlineStr"/>
+      <c r="M221" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N221" s="28" t="inlineStr"/>
+      <c r="O221" s="27" t="inlineStr"/>
+    </row>
+    <row r="222" ht="16" customHeight="1" s="18">
+      <c r="A222" s="20" t="inlineStr">
+        <is>
+          <t>21a42f91024f</t>
+        </is>
+      </c>
+      <c r="B222" s="20" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C222" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D222" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E222" s="20" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F222" s="20" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G222" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H222" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I222" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J222" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K222" s="23" t="inlineStr"/>
+      <c r="L222" s="23" t="inlineStr"/>
+      <c r="M222" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N222" s="24" t="inlineStr"/>
+      <c r="O222" s="23" t="inlineStr"/>
+    </row>
+    <row r="223" ht="16" customHeight="1" s="18">
+      <c r="A223" s="25" t="inlineStr">
+        <is>
+          <t>41a245309de3</t>
+        </is>
+      </c>
+      <c r="B223" s="25" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C223" s="25" t="inlineStr">
+        <is>
+          <t>Senior Water Network Engineer/Modellers</t>
+        </is>
+      </c>
+      <c r="D223" s="25" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E223" s="25" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F223" s="25" t="inlineStr">
+        <is>
+          <t>£50,253 – £50,253</t>
+        </is>
+      </c>
+      <c r="G223" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H223" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I223" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="J223" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K223" s="27" t="inlineStr"/>
+      <c r="L223" s="27" t="inlineStr"/>
+      <c r="M223" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N223" s="28" t="inlineStr"/>
+      <c r="O223" s="27" t="inlineStr"/>
+    </row>
+    <row r="224" ht="16" customHeight="1" s="18">
+      <c r="A224" s="20" t="inlineStr">
+        <is>
+          <t>b21d3c39a91e</t>
+        </is>
+      </c>
+      <c r="B224" s="20" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C224" s="20" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D224" s="20" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E224" s="20" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F224" s="20" t="inlineStr">
+        <is>
+          <t>£48,252 – £48,252</t>
+        </is>
+      </c>
+      <c r="G224" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H224" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I224" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="J224" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K224" s="23" t="inlineStr"/>
+      <c r="L224" s="23" t="inlineStr"/>
+      <c r="M224" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N224" s="24" t="inlineStr"/>
+      <c r="O224" s="23" t="inlineStr"/>
+    </row>
+    <row r="225" ht="16" customHeight="1" s="18">
+      <c r="A225" s="25" t="inlineStr">
+        <is>
+          <t>3f5d06c4ca65</t>
+        </is>
+      </c>
+      <c r="B225" s="25" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C225" s="25" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D225" s="25" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E225" s="25" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F225" s="25" t="inlineStr">
+        <is>
+          <t>£49,369 – £49,369</t>
+        </is>
+      </c>
+      <c r="G225" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H225" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I225" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="J225" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K225" s="27" t="inlineStr"/>
+      <c r="L225" s="27" t="inlineStr"/>
+      <c r="M225" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N225" s="28" t="inlineStr"/>
+      <c r="O225" s="27" t="inlineStr"/>
+    </row>
+    <row r="226" ht="16" customHeight="1" s="18">
+      <c r="A226" s="20" t="inlineStr">
+        <is>
+          <t>49e8efe40851</t>
+        </is>
+      </c>
+      <c r="B226" s="20" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C226" s="20" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer</t>
+        </is>
+      </c>
+      <c r="D226" s="20" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Recruitment Consultancy</t>
+        </is>
+      </c>
+      <c r="E226" s="20" t="inlineStr">
+        <is>
+          <t>Fleet, Hampshire</t>
+        </is>
+      </c>
+      <c r="F226" s="20" t="inlineStr">
+        <is>
+          <t>£50,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G226" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H226" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I226" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J226" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K226" s="23" t="inlineStr"/>
+      <c r="L226" s="23" t="inlineStr"/>
+      <c r="M226" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N226" s="24" t="inlineStr"/>
+      <c r="O226" s="23" t="inlineStr"/>
+    </row>
+    <row r="227" ht="16" customHeight="1" s="18">
+      <c r="A227" s="25" t="inlineStr">
+        <is>
+          <t>2417c8af27fe</t>
+        </is>
+      </c>
+      <c r="B227" s="25" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C227" s="25" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer</t>
+        </is>
+      </c>
+      <c r="D227" s="25" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Associates Ltd</t>
+        </is>
+      </c>
+      <c r="E227" s="25" t="inlineStr">
+        <is>
+          <t>Artington, Guildford</t>
+        </is>
+      </c>
+      <c r="F227" s="25" t="inlineStr">
+        <is>
+          <t>£50,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G227" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H227" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I227" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J227" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K227" s="27" t="inlineStr"/>
+      <c r="L227" s="27" t="inlineStr"/>
+      <c r="M227" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N227" s="28" t="inlineStr"/>
+      <c r="O227" s="27" t="inlineStr"/>
+    </row>
+    <row r="228" ht="16" customHeight="1" s="18">
+      <c r="A228" s="20" t="inlineStr">
+        <is>
+          <t>13c54a038f0d</t>
+        </is>
+      </c>
+      <c r="B228" s="20" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C228" s="20" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer</t>
+        </is>
+      </c>
+      <c r="D228" s="20" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Recruitment Consultancy</t>
+        </is>
+      </c>
+      <c r="E228" s="20" t="inlineStr">
+        <is>
+          <t>Fleet, Hampshire</t>
+        </is>
+      </c>
+      <c r="F228" s="20" t="inlineStr">
+        <is>
+          <t>£50,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G228" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H228" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I228" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J228" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K228" s="23" t="inlineStr"/>
+      <c r="L228" s="23" t="inlineStr"/>
+      <c r="M228" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N228" s="24" t="inlineStr"/>
+      <c r="O228" s="23" t="inlineStr"/>
+    </row>
+    <row r="229" ht="16" customHeight="1" s="18">
+      <c r="A229" s="25" t="inlineStr">
+        <is>
+          <t>ca08147f9c29</t>
+        </is>
+      </c>
+      <c r="B229" s="25" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C229" s="25" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer</t>
+        </is>
+      </c>
+      <c r="D229" s="25" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Associates Ltd</t>
+        </is>
+      </c>
+      <c r="E229" s="25" t="inlineStr">
+        <is>
+          <t>Artington, Guildford</t>
+        </is>
+      </c>
+      <c r="F229" s="25" t="inlineStr">
+        <is>
+          <t>£50,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G229" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H229" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I229" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J229" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K229" s="27" t="inlineStr"/>
+      <c r="L229" s="27" t="inlineStr"/>
+      <c r="M229" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N229" s="28" t="inlineStr"/>
+      <c r="O229" s="27" t="inlineStr"/>
+    </row>
+    <row r="230" ht="16" customHeight="1" s="18">
+      <c r="A230" s="20" t="inlineStr">
+        <is>
+          <t>30867ccf404b</t>
+        </is>
+      </c>
+      <c r="B230" s="20" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C230" s="20" t="inlineStr">
+        <is>
+          <t>Senior Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D230" s="20" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment</t>
+        </is>
+      </c>
+      <c r="E230" s="20" t="inlineStr">
+        <is>
+          <t>Denner Hill, Great Missenden</t>
+        </is>
+      </c>
+      <c r="F230" s="20" t="inlineStr">
+        <is>
+          <t>£38,000 – £60,000</t>
+        </is>
+      </c>
+      <c r="G230" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H230" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I230" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J230" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K230" s="23" t="inlineStr"/>
+      <c r="L230" s="23" t="inlineStr"/>
+      <c r="M230" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N230" s="24" t="inlineStr"/>
+      <c r="O230" s="23" t="inlineStr"/>
+    </row>
+    <row r="231" ht="16" customHeight="1" s="18">
+      <c r="A231" s="25" t="inlineStr">
+        <is>
+          <t>95c7b53a2cf1</t>
+        </is>
+      </c>
+      <c r="B231" s="25" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C231" s="25" t="inlineStr">
+        <is>
+          <t>Assistant Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D231" s="25" t="inlineStr">
+        <is>
+          <t>Henley Chase</t>
+        </is>
+      </c>
+      <c r="E231" s="25" t="inlineStr">
+        <is>
+          <t>New Haw, Addlestone</t>
+        </is>
+      </c>
+      <c r="F231" s="25" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G231" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H231" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I231" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J231" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K231" s="27" t="inlineStr"/>
+      <c r="L231" s="27" t="inlineStr"/>
+      <c r="M231" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N231" s="28" t="inlineStr"/>
+      <c r="O231" s="27" t="inlineStr"/>
+    </row>
+    <row r="232" ht="16" customHeight="1" s="18">
+      <c r="A232" s="20" t="inlineStr">
+        <is>
+          <t>351547691f70</t>
+        </is>
+      </c>
+      <c r="B232" s="20" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C232" s="20" t="inlineStr">
+        <is>
+          <t>Junior Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D232" s="20" t="inlineStr">
+        <is>
+          <t>Henley Chase Limited</t>
+        </is>
+      </c>
+      <c r="E232" s="20" t="inlineStr">
+        <is>
+          <t>Addlestone, Surrey</t>
+        </is>
+      </c>
+      <c r="F232" s="20" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G232" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H232" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I232" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J232" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K232" s="23" t="inlineStr"/>
+      <c r="L232" s="23" t="inlineStr"/>
+      <c r="M232" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N232" s="24" t="inlineStr"/>
+      <c r="O232" s="23" t="inlineStr"/>
+    </row>
+    <row r="233" ht="16" customHeight="1" s="18">
+      <c r="A233" s="25" t="inlineStr">
+        <is>
+          <t>a3759615d59b</t>
+        </is>
+      </c>
+      <c r="B233" s="25" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C233" s="25" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Flood Risk &amp; Drainage</t>
+        </is>
+      </c>
+      <c r="D233" s="25" t="inlineStr">
+        <is>
+          <t>Aztrum</t>
+        </is>
+      </c>
+      <c r="E233" s="25" t="inlineStr">
+        <is>
+          <t>Ash Vale, Aldershot</t>
+        </is>
+      </c>
+      <c r="F233" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G233" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H233" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I233" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J233" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K233" s="27" t="inlineStr"/>
+      <c r="L233" s="27" t="inlineStr"/>
+      <c r="M233" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N233" s="28" t="inlineStr"/>
+      <c r="O233" s="27" t="inlineStr"/>
+    </row>
+    <row r="234" ht="16" customHeight="1" s="18">
+      <c r="A234" s="20" t="inlineStr">
+        <is>
+          <t>c208b4eddbc2</t>
+        </is>
+      </c>
+      <c r="B234" s="20" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C234" s="20" t="inlineStr">
+        <is>
+          <t>Senior Electrical Engineer - Water Projects</t>
+        </is>
+      </c>
+      <c r="D234" s="20" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E234" s="20" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F234" s="20" t="inlineStr">
+        <is>
+          <t>£47,734 – £47,734</t>
+        </is>
+      </c>
+      <c r="G234" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H234" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I234" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J234" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K234" s="23" t="inlineStr"/>
+      <c r="L234" s="23" t="inlineStr"/>
+      <c r="M234" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N234" s="24" t="inlineStr"/>
+      <c r="O234" s="23" t="inlineStr"/>
+    </row>
+    <row r="235" ht="16" customHeight="1" s="18">
+      <c r="A235" s="25" t="inlineStr">
+        <is>
+          <t>d32df68d5ae6</t>
+        </is>
+      </c>
+      <c r="B235" s="25" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C235" s="25" t="inlineStr">
+        <is>
+          <t>Senior Electrical Engineer - Water Projects</t>
+        </is>
+      </c>
+      <c r="D235" s="25" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E235" s="25" t="inlineStr">
+        <is>
+          <t>St. Albans, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="F235" s="25" t="inlineStr">
+        <is>
+          <t>£48,482 – £48,482</t>
+        </is>
+      </c>
+      <c r="G235" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H235" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I235" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J235" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K235" s="27" t="inlineStr"/>
+      <c r="L235" s="27" t="inlineStr"/>
+      <c r="M235" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N235" s="28" t="inlineStr"/>
+      <c r="O235" s="27" t="inlineStr"/>
+    </row>
+    <row r="236" ht="16" customHeight="1" s="18">
+      <c r="A236" s="20" t="inlineStr">
+        <is>
+          <t>6b4a3dd956ae</t>
+        </is>
+      </c>
+      <c r="B236" s="20" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C236" s="20" t="inlineStr">
+        <is>
+          <t>Senior Electrical Engineer - Water Projects</t>
+        </is>
+      </c>
+      <c r="D236" s="20" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E236" s="20" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F236" s="20" t="inlineStr">
+        <is>
+          <t>£49,911 – £49,911</t>
+        </is>
+      </c>
+      <c r="G236" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H236" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I236" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J236" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K236" s="23" t="inlineStr"/>
+      <c r="L236" s="23" t="inlineStr"/>
+      <c r="M236" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N236" s="24" t="inlineStr"/>
+      <c r="O236" s="23" t="inlineStr"/>
+    </row>
+    <row r="237" ht="16" customHeight="1" s="18">
+      <c r="A237" s="25" t="inlineStr">
+        <is>
+          <t>2f34b28a8274</t>
+        </is>
+      </c>
+      <c r="B237" s="25" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C237" s="25" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D237" s="25" t="inlineStr">
+        <is>
+          <t>Murray McIntosh &amp; Associates Limited</t>
+        </is>
+      </c>
+      <c r="E237" s="25" t="inlineStr">
+        <is>
+          <t>Church Crookham, Fleet</t>
+        </is>
+      </c>
+      <c r="F237" s="25" t="inlineStr">
+        <is>
+          <t>£50,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G237" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H237" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I237" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J237" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K237" s="27" t="inlineStr"/>
+      <c r="L237" s="27" t="inlineStr"/>
+      <c r="M237" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N237" s="28" t="inlineStr"/>
+      <c r="O237" s="27" t="inlineStr"/>
+    </row>
+    <row r="238" ht="16" customHeight="1" s="18">
+      <c r="A238" s="20" t="inlineStr">
+        <is>
+          <t>cd07d08cabc6</t>
+        </is>
+      </c>
+      <c r="B238" s="20" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C238" s="20" t="inlineStr">
+        <is>
+          <t>Structural Design Engineer</t>
+        </is>
+      </c>
+      <c r="D238" s="20" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Recruitment Consultancy</t>
+        </is>
+      </c>
+      <c r="E238" s="20" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F238" s="20" t="inlineStr">
+        <is>
+          <t>£50,000 – £75,000</t>
+        </is>
+      </c>
+      <c r="G238" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H238" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I238" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J238" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K238" s="23" t="inlineStr"/>
+      <c r="L238" s="23" t="inlineStr"/>
+      <c r="M238" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N238" s="24" t="inlineStr"/>
+      <c r="O238" s="23" t="inlineStr"/>
+    </row>
+    <row r="239" ht="16" customHeight="1" s="18">
+      <c r="A239" s="25" t="inlineStr">
+        <is>
+          <t>ed5e36105b42</t>
+        </is>
+      </c>
+      <c r="B239" s="25" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C239" s="25" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D239" s="25" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Recruitment Consultancy</t>
+        </is>
+      </c>
+      <c r="E239" s="25" t="inlineStr">
+        <is>
+          <t>Fleet, Hampshire</t>
+        </is>
+      </c>
+      <c r="F239" s="25" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G239" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H239" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I239" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J239" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K239" s="27" t="inlineStr"/>
+      <c r="L239" s="27" t="inlineStr"/>
+      <c r="M239" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N239" s="28" t="inlineStr"/>
+      <c r="O239" s="27" t="inlineStr"/>
+    </row>
+    <row r="240" ht="16" customHeight="1" s="18">
+      <c r="A240" s="20" t="inlineStr">
+        <is>
+          <t>4725a15896d0</t>
+        </is>
+      </c>
+      <c r="B240" s="20" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C240" s="20" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D240" s="20" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Associates Ltd</t>
+        </is>
+      </c>
+      <c r="E240" s="20" t="inlineStr">
+        <is>
+          <t>Artington, Guildford</t>
+        </is>
+      </c>
+      <c r="F240" s="20" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G240" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H240" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I240" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J240" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K240" s="23" t="inlineStr"/>
+      <c r="L240" s="23" t="inlineStr"/>
+      <c r="M240" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N240" s="24" t="inlineStr"/>
+      <c r="O240" s="23" t="inlineStr"/>
+    </row>
+    <row r="241" ht="16" customHeight="1" s="18">
+      <c r="A241" s="25" t="inlineStr">
+        <is>
+          <t>9b2b64881d68</t>
+        </is>
+      </c>
+      <c r="B241" s="25" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C241" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D241" s="25" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E241" s="25" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F241" s="25" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G241" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H241" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I241" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J241" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K241" s="27" t="inlineStr"/>
+      <c r="L241" s="27" t="inlineStr"/>
+      <c r="M241" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N241" s="28" t="inlineStr"/>
+      <c r="O241" s="27" t="inlineStr"/>
+    </row>
+    <row r="242" ht="16" customHeight="1" s="18">
+      <c r="A242" s="20" t="inlineStr">
+        <is>
+          <t>855bc5671b80</t>
+        </is>
+      </c>
+      <c r="B242" s="20" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C242" s="20" t="inlineStr">
+        <is>
+          <t>Quality Engineer</t>
+        </is>
+      </c>
+      <c r="D242" s="20" t="inlineStr">
+        <is>
+          <t>Rapiscan Systems</t>
+        </is>
+      </c>
+      <c r="E242" s="20" t="inlineStr">
+        <is>
+          <t>Salfords, Redhill</t>
+        </is>
+      </c>
+      <c r="F242" s="20" t="inlineStr">
+        <is>
+          <t>£49,199 – £49,199</t>
+        </is>
+      </c>
+      <c r="G242" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H242" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I242" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J242" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K242" s="23" t="inlineStr"/>
+      <c r="L242" s="23" t="inlineStr"/>
+      <c r="M242" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N242" s="24" t="inlineStr"/>
+      <c r="O242" s="23" t="inlineStr"/>
+    </row>
+    <row r="243" ht="16" customHeight="1" s="18">
+      <c r="A243" s="25" t="inlineStr">
+        <is>
+          <t>11a953f8a77a</t>
+        </is>
+      </c>
+      <c r="B243" s="25" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="C243" s="25" t="inlineStr">
+        <is>
+          <t>Quality Engineer</t>
+        </is>
+      </c>
+      <c r="D243" s="25" t="inlineStr">
+        <is>
+          <t>Rapiscan Systems</t>
+        </is>
+      </c>
+      <c r="E243" s="25" t="inlineStr">
+        <is>
+          <t>Salfords, Redhill</t>
+        </is>
+      </c>
+      <c r="F243" s="25" t="inlineStr">
+        <is>
+          <t>£46,683 – £46,683</t>
+        </is>
+      </c>
+      <c r="G243" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H243" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I243" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J243" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K243" s="27" t="inlineStr"/>
+      <c r="L243" s="27" t="inlineStr"/>
+      <c r="M243" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N243" s="28" t="inlineStr"/>
+      <c r="O243" s="27" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -13752,6 +15404,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J213" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J214" r:id="rId213"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J243" r:id="rId242"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O243"/>
+  <dimension ref="A1:O269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" style="18" min="1" max="1"/>
@@ -15176,6 +15176,1540 @@
       </c>
       <c r="N243" s="28" t="inlineStr"/>
       <c r="O243" s="27" t="inlineStr"/>
+    </row>
+    <row r="244" ht="16" customHeight="1" s="18">
+      <c r="A244" s="20" t="inlineStr">
+        <is>
+          <t>1401977f6364</t>
+        </is>
+      </c>
+      <c r="B244" s="20" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C244" s="20" t="inlineStr">
+        <is>
+          <t>Plumber</t>
+        </is>
+      </c>
+      <c r="D244" s="20" t="inlineStr">
+        <is>
+          <t>WATES PROPERTY SERVICES LIMITED</t>
+        </is>
+      </c>
+      <c r="E244" s="20" t="inlineStr">
+        <is>
+          <t>Crawley, West Sussex</t>
+        </is>
+      </c>
+      <c r="F244" s="20" t="inlineStr">
+        <is>
+          <t>£50,654 – £50,654</t>
+        </is>
+      </c>
+      <c r="G244" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H244" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I244" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J244" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K244" s="23" t="inlineStr"/>
+      <c r="L244" s="23" t="inlineStr"/>
+      <c r="M244" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N244" s="24" t="inlineStr"/>
+      <c r="O244" s="23" t="inlineStr"/>
+    </row>
+    <row r="245" ht="16" customHeight="1" s="18">
+      <c r="A245" s="25" t="inlineStr">
+        <is>
+          <t>789d3251f27d</t>
+        </is>
+      </c>
+      <c r="B245" s="25" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C245" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D245" s="25" t="inlineStr">
+        <is>
+          <t>CHARTWELL</t>
+        </is>
+      </c>
+      <c r="E245" s="25" t="inlineStr">
+        <is>
+          <t>Chatham, Kent</t>
+        </is>
+      </c>
+      <c r="F245" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G245" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H245" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I245" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J245" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K245" s="27" t="inlineStr"/>
+      <c r="L245" s="27" t="inlineStr"/>
+      <c r="M245" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N245" s="28" t="inlineStr"/>
+      <c r="O245" s="27" t="inlineStr"/>
+    </row>
+    <row r="246" ht="16" customHeight="1" s="18">
+      <c r="A246" s="20" t="inlineStr">
+        <is>
+          <t>c616e1c50744</t>
+        </is>
+      </c>
+      <c r="B246" s="20" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C246" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D246" s="20" t="inlineStr">
+        <is>
+          <t>Reed</t>
+        </is>
+      </c>
+      <c r="E246" s="20" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F246" s="20" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G246" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H246" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I246" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J246" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K246" s="23" t="inlineStr"/>
+      <c r="L246" s="23" t="inlineStr"/>
+      <c r="M246" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N246" s="24" t="inlineStr"/>
+      <c r="O246" s="23" t="inlineStr"/>
+    </row>
+    <row r="247" ht="16" customHeight="1" s="18">
+      <c r="A247" s="25" t="inlineStr">
+        <is>
+          <t>e73510d39fc9</t>
+        </is>
+      </c>
+      <c r="B247" s="25" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C247" s="25" t="inlineStr">
+        <is>
+          <t>Civil Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="D247" s="25" t="inlineStr">
+        <is>
+          <t>Zodiac Recruitment</t>
+        </is>
+      </c>
+      <c r="E247" s="25" t="inlineStr">
+        <is>
+          <t>Stone Cross, Crowborough</t>
+        </is>
+      </c>
+      <c r="F247" s="25" t="inlineStr">
+        <is>
+          <t>£32,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G247" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H247" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I247" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J247" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K247" s="27" t="inlineStr"/>
+      <c r="L247" s="27" t="inlineStr"/>
+      <c r="M247" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N247" s="28" t="inlineStr"/>
+      <c r="O247" s="27" t="inlineStr"/>
+    </row>
+    <row r="248" ht="16" customHeight="1" s="18">
+      <c r="A248" s="20" t="inlineStr">
+        <is>
+          <t>9a03b192f1b4</t>
+        </is>
+      </c>
+      <c r="B248" s="20" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C248" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D248" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E248" s="20" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F248" s="20" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G248" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H248" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I248" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J248" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K248" s="23" t="inlineStr"/>
+      <c r="L248" s="23" t="inlineStr"/>
+      <c r="M248" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N248" s="24" t="inlineStr"/>
+      <c r="O248" s="23" t="inlineStr"/>
+    </row>
+    <row r="249" ht="16" customHeight="1" s="18">
+      <c r="A249" s="25" t="inlineStr">
+        <is>
+          <t>c927c4a8f6e4</t>
+        </is>
+      </c>
+      <c r="B249" s="25" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C249" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D249" s="25" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E249" s="25" t="inlineStr">
+        <is>
+          <t>South Croydon, South East London</t>
+        </is>
+      </c>
+      <c r="F249" s="25" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G249" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H249" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I249" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="J249" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K249" s="27" t="inlineStr"/>
+      <c r="L249" s="27" t="inlineStr"/>
+      <c r="M249" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N249" s="28" t="inlineStr"/>
+      <c r="O249" s="27" t="inlineStr"/>
+    </row>
+    <row r="250" ht="16" customHeight="1" s="18">
+      <c r="A250" s="20" t="inlineStr">
+        <is>
+          <t>7267f6a7cef5</t>
+        </is>
+      </c>
+      <c r="B250" s="20" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C250" s="20" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D250" s="20" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E250" s="20" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F250" s="20" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G250" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H250" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I250" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J250" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K250" s="23" t="inlineStr"/>
+      <c r="L250" s="23" t="inlineStr"/>
+      <c r="M250" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N250" s="24" t="inlineStr"/>
+      <c r="O250" s="23" t="inlineStr"/>
+    </row>
+    <row r="251" ht="16" customHeight="1" s="18">
+      <c r="A251" s="25" t="inlineStr">
+        <is>
+          <t>83c438657e84</t>
+        </is>
+      </c>
+      <c r="B251" s="25" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C251" s="25" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D251" s="25" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E251" s="25" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F251" s="25" t="inlineStr">
+        <is>
+          <t>£48,252 – £48,252</t>
+        </is>
+      </c>
+      <c r="G251" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H251" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I251" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="J251" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K251" s="27" t="inlineStr"/>
+      <c r="L251" s="27" t="inlineStr"/>
+      <c r="M251" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N251" s="28" t="inlineStr"/>
+      <c r="O251" s="27" t="inlineStr"/>
+    </row>
+    <row r="252" ht="16" customHeight="1" s="18">
+      <c r="A252" s="20" t="inlineStr">
+        <is>
+          <t>688c82a3c686</t>
+        </is>
+      </c>
+      <c r="B252" s="20" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C252" s="20" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D252" s="20" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E252" s="20" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F252" s="20" t="inlineStr">
+        <is>
+          <t>£49,369 – £49,369</t>
+        </is>
+      </c>
+      <c r="G252" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H252" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I252" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="J252" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K252" s="23" t="inlineStr"/>
+      <c r="L252" s="23" t="inlineStr"/>
+      <c r="M252" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N252" s="24" t="inlineStr"/>
+      <c r="O252" s="23" t="inlineStr"/>
+    </row>
+    <row r="253" ht="16" customHeight="1" s="18">
+      <c r="A253" s="25" t="inlineStr">
+        <is>
+          <t>914f7afe285c</t>
+        </is>
+      </c>
+      <c r="B253" s="25" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C253" s="25" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer</t>
+        </is>
+      </c>
+      <c r="D253" s="25" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Recruitment Consultancy</t>
+        </is>
+      </c>
+      <c r="E253" s="25" t="inlineStr">
+        <is>
+          <t>Fleet, Hampshire</t>
+        </is>
+      </c>
+      <c r="F253" s="25" t="inlineStr">
+        <is>
+          <t>£50,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G253" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H253" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I253" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J253" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K253" s="27" t="inlineStr"/>
+      <c r="L253" s="27" t="inlineStr"/>
+      <c r="M253" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N253" s="28" t="inlineStr"/>
+      <c r="O253" s="27" t="inlineStr"/>
+    </row>
+    <row r="254" ht="16" customHeight="1" s="18">
+      <c r="A254" s="20" t="inlineStr">
+        <is>
+          <t>a347b3891ecd</t>
+        </is>
+      </c>
+      <c r="B254" s="20" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C254" s="20" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer</t>
+        </is>
+      </c>
+      <c r="D254" s="20" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Associates Ltd</t>
+        </is>
+      </c>
+      <c r="E254" s="20" t="inlineStr">
+        <is>
+          <t>Artington, Guildford</t>
+        </is>
+      </c>
+      <c r="F254" s="20" t="inlineStr">
+        <is>
+          <t>£50,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G254" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H254" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I254" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J254" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K254" s="23" t="inlineStr"/>
+      <c r="L254" s="23" t="inlineStr"/>
+      <c r="M254" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N254" s="24" t="inlineStr"/>
+      <c r="O254" s="23" t="inlineStr"/>
+    </row>
+    <row r="255" ht="16" customHeight="1" s="18">
+      <c r="A255" s="25" t="inlineStr">
+        <is>
+          <t>e945ae9de8f5</t>
+        </is>
+      </c>
+      <c r="B255" s="25" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C255" s="25" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer</t>
+        </is>
+      </c>
+      <c r="D255" s="25" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Recruitment Consultancy</t>
+        </is>
+      </c>
+      <c r="E255" s="25" t="inlineStr">
+        <is>
+          <t>Fleet, Hampshire</t>
+        </is>
+      </c>
+      <c r="F255" s="25" t="inlineStr">
+        <is>
+          <t>£50,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G255" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H255" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I255" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J255" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K255" s="27" t="inlineStr"/>
+      <c r="L255" s="27" t="inlineStr"/>
+      <c r="M255" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N255" s="28" t="inlineStr"/>
+      <c r="O255" s="27" t="inlineStr"/>
+    </row>
+    <row r="256" ht="16" customHeight="1" s="18">
+      <c r="A256" s="20" t="inlineStr">
+        <is>
+          <t>73dc16486928</t>
+        </is>
+      </c>
+      <c r="B256" s="20" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C256" s="20" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer</t>
+        </is>
+      </c>
+      <c r="D256" s="20" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Associates Ltd</t>
+        </is>
+      </c>
+      <c r="E256" s="20" t="inlineStr">
+        <is>
+          <t>Artington, Guildford</t>
+        </is>
+      </c>
+      <c r="F256" s="20" t="inlineStr">
+        <is>
+          <t>£50,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G256" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H256" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I256" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J256" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K256" s="23" t="inlineStr"/>
+      <c r="L256" s="23" t="inlineStr"/>
+      <c r="M256" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N256" s="24" t="inlineStr"/>
+      <c r="O256" s="23" t="inlineStr"/>
+    </row>
+    <row r="257" ht="16" customHeight="1" s="18">
+      <c r="A257" s="25" t="inlineStr">
+        <is>
+          <t>44b56711faa4</t>
+        </is>
+      </c>
+      <c r="B257" s="25" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C257" s="25" t="inlineStr">
+        <is>
+          <t>Senior Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D257" s="25" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment</t>
+        </is>
+      </c>
+      <c r="E257" s="25" t="inlineStr">
+        <is>
+          <t>Denner Hill, Great Missenden</t>
+        </is>
+      </c>
+      <c r="F257" s="25" t="inlineStr">
+        <is>
+          <t>£38,000 – £60,000</t>
+        </is>
+      </c>
+      <c r="G257" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H257" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I257" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J257" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K257" s="27" t="inlineStr"/>
+      <c r="L257" s="27" t="inlineStr"/>
+      <c r="M257" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N257" s="28" t="inlineStr"/>
+      <c r="O257" s="27" t="inlineStr"/>
+    </row>
+    <row r="258" ht="16" customHeight="1" s="18">
+      <c r="A258" s="20" t="inlineStr">
+        <is>
+          <t>256d2e97687f</t>
+        </is>
+      </c>
+      <c r="B258" s="20" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C258" s="20" t="inlineStr">
+        <is>
+          <t>Senior Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D258" s="20" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment</t>
+        </is>
+      </c>
+      <c r="E258" s="20" t="inlineStr">
+        <is>
+          <t>Denner Hill, Great Missenden</t>
+        </is>
+      </c>
+      <c r="F258" s="20" t="inlineStr">
+        <is>
+          <t>£38,000 – £60,000</t>
+        </is>
+      </c>
+      <c r="G258" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H258" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I258" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J258" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K258" s="23" t="inlineStr"/>
+      <c r="L258" s="23" t="inlineStr"/>
+      <c r="M258" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N258" s="24" t="inlineStr"/>
+      <c r="O258" s="23" t="inlineStr"/>
+    </row>
+    <row r="259" ht="16" customHeight="1" s="18">
+      <c r="A259" s="25" t="inlineStr">
+        <is>
+          <t>4e7d698282fa</t>
+        </is>
+      </c>
+      <c r="B259" s="25" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C259" s="25" t="inlineStr">
+        <is>
+          <t>Assistant Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D259" s="25" t="inlineStr">
+        <is>
+          <t>Henley Chase</t>
+        </is>
+      </c>
+      <c r="E259" s="25" t="inlineStr">
+        <is>
+          <t>New Haw, Addlestone</t>
+        </is>
+      </c>
+      <c r="F259" s="25" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G259" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H259" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I259" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J259" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K259" s="27" t="inlineStr"/>
+      <c r="L259" s="27" t="inlineStr"/>
+      <c r="M259" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N259" s="28" t="inlineStr"/>
+      <c r="O259" s="27" t="inlineStr"/>
+    </row>
+    <row r="260" ht="16" customHeight="1" s="18">
+      <c r="A260" s="20" t="inlineStr">
+        <is>
+          <t>1b74c42c9785</t>
+        </is>
+      </c>
+      <c r="B260" s="20" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C260" s="20" t="inlineStr">
+        <is>
+          <t>Junior Quantity Surveyor / Estimator - Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D260" s="20" t="inlineStr">
+        <is>
+          <t>Henley Chase Limited</t>
+        </is>
+      </c>
+      <c r="E260" s="20" t="inlineStr">
+        <is>
+          <t>Addlestone, Surrey</t>
+        </is>
+      </c>
+      <c r="F260" s="20" t="inlineStr">
+        <is>
+          <t>£30,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G260" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H260" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I260" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J260" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K260" s="23" t="inlineStr"/>
+      <c r="L260" s="23" t="inlineStr"/>
+      <c r="M260" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N260" s="24" t="inlineStr"/>
+      <c r="O260" s="23" t="inlineStr"/>
+    </row>
+    <row r="261" ht="16" customHeight="1" s="18">
+      <c r="A261" s="25" t="inlineStr">
+        <is>
+          <t>0aa79c24bcd2</t>
+        </is>
+      </c>
+      <c r="B261" s="25" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C261" s="25" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Flood Risk &amp; Drainage</t>
+        </is>
+      </c>
+      <c r="D261" s="25" t="inlineStr">
+        <is>
+          <t>Aztrum</t>
+        </is>
+      </c>
+      <c r="E261" s="25" t="inlineStr">
+        <is>
+          <t>Ash Vale, Aldershot</t>
+        </is>
+      </c>
+      <c r="F261" s="25" t="inlineStr">
+        <is>
+          <t>£45,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G261" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H261" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I261" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="J261" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K261" s="27" t="inlineStr"/>
+      <c r="L261" s="27" t="inlineStr"/>
+      <c r="M261" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N261" s="28" t="inlineStr"/>
+      <c r="O261" s="27" t="inlineStr"/>
+    </row>
+    <row r="262" ht="16" customHeight="1" s="18">
+      <c r="A262" s="20" t="inlineStr">
+        <is>
+          <t>e84e5adb7f21</t>
+        </is>
+      </c>
+      <c r="B262" s="20" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C262" s="20" t="inlineStr">
+        <is>
+          <t>Civil Engineer (Highway / Drainage)</t>
+        </is>
+      </c>
+      <c r="D262" s="20" t="inlineStr">
+        <is>
+          <t>Additional Resources Ltd</t>
+        </is>
+      </c>
+      <c r="E262" s="20" t="inlineStr">
+        <is>
+          <t>Henley-On-Thames, Oxfordshire</t>
+        </is>
+      </c>
+      <c r="F262" s="20" t="inlineStr">
+        <is>
+          <t>£30,000 – £60,000</t>
+        </is>
+      </c>
+      <c r="G262" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H262" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I262" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J262" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K262" s="23" t="inlineStr"/>
+      <c r="L262" s="23" t="inlineStr"/>
+      <c r="M262" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N262" s="24" t="inlineStr"/>
+      <c r="O262" s="23" t="inlineStr"/>
+    </row>
+    <row r="263" ht="16" customHeight="1" s="18">
+      <c r="A263" s="25" t="inlineStr">
+        <is>
+          <t>032f8a8ecf37</t>
+        </is>
+      </c>
+      <c r="B263" s="25" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C263" s="25" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D263" s="25" t="inlineStr">
+        <is>
+          <t>Murray McIntosh &amp; Associates Limited</t>
+        </is>
+      </c>
+      <c r="E263" s="25" t="inlineStr">
+        <is>
+          <t>Church Crookham, Fleet</t>
+        </is>
+      </c>
+      <c r="F263" s="25" t="inlineStr">
+        <is>
+          <t>£50,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G263" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H263" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I263" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J263" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K263" s="27" t="inlineStr"/>
+      <c r="L263" s="27" t="inlineStr"/>
+      <c r="M263" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N263" s="28" t="inlineStr"/>
+      <c r="O263" s="27" t="inlineStr"/>
+    </row>
+    <row r="264" ht="16" customHeight="1" s="18">
+      <c r="A264" s="20" t="inlineStr">
+        <is>
+          <t>bc680b3739a2</t>
+        </is>
+      </c>
+      <c r="B264" s="20" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C264" s="20" t="inlineStr">
+        <is>
+          <t>Structural Design Engineer</t>
+        </is>
+      </c>
+      <c r="D264" s="20" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Recruitment Consultancy</t>
+        </is>
+      </c>
+      <c r="E264" s="20" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F264" s="20" t="inlineStr">
+        <is>
+          <t>£50,000 – £75,000</t>
+        </is>
+      </c>
+      <c r="G264" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H264" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I264" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J264" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K264" s="23" t="inlineStr"/>
+      <c r="L264" s="23" t="inlineStr"/>
+      <c r="M264" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N264" s="24" t="inlineStr"/>
+      <c r="O264" s="23" t="inlineStr"/>
+    </row>
+    <row r="265" ht="16" customHeight="1" s="18">
+      <c r="A265" s="25" t="inlineStr">
+        <is>
+          <t>fb13f3ee86ad</t>
+        </is>
+      </c>
+      <c r="B265" s="25" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C265" s="25" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D265" s="25" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Recruitment Consultancy</t>
+        </is>
+      </c>
+      <c r="E265" s="25" t="inlineStr">
+        <is>
+          <t>Fleet, Hampshire</t>
+        </is>
+      </c>
+      <c r="F265" s="25" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G265" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H265" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I265" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J265" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K265" s="27" t="inlineStr"/>
+      <c r="L265" s="27" t="inlineStr"/>
+      <c r="M265" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N265" s="28" t="inlineStr"/>
+      <c r="O265" s="27" t="inlineStr"/>
+    </row>
+    <row r="266" ht="16" customHeight="1" s="18">
+      <c r="A266" s="20" t="inlineStr">
+        <is>
+          <t>81166ce45dcd</t>
+        </is>
+      </c>
+      <c r="B266" s="20" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C266" s="20" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D266" s="20" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Associates Ltd</t>
+        </is>
+      </c>
+      <c r="E266" s="20" t="inlineStr">
+        <is>
+          <t>Artington, Guildford</t>
+        </is>
+      </c>
+      <c r="F266" s="20" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G266" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H266" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I266" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J266" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K266" s="23" t="inlineStr"/>
+      <c r="L266" s="23" t="inlineStr"/>
+      <c r="M266" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N266" s="24" t="inlineStr"/>
+      <c r="O266" s="23" t="inlineStr"/>
+    </row>
+    <row r="267" ht="16" customHeight="1" s="18">
+      <c r="A267" s="25" t="inlineStr">
+        <is>
+          <t>07eff080e8d0</t>
+        </is>
+      </c>
+      <c r="B267" s="25" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C267" s="25" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D267" s="25" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E267" s="25" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F267" s="25" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G267" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H267" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I267" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J267" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K267" s="27" t="inlineStr"/>
+      <c r="L267" s="27" t="inlineStr"/>
+      <c r="M267" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N267" s="28" t="inlineStr"/>
+      <c r="O267" s="27" t="inlineStr"/>
+    </row>
+    <row r="268" ht="16" customHeight="1" s="18">
+      <c r="A268" s="20" t="inlineStr">
+        <is>
+          <t>5492b74d2c62</t>
+        </is>
+      </c>
+      <c r="B268" s="20" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C268" s="20" t="inlineStr">
+        <is>
+          <t>Quality Engineer</t>
+        </is>
+      </c>
+      <c r="D268" s="20" t="inlineStr">
+        <is>
+          <t>Rapiscan Systems</t>
+        </is>
+      </c>
+      <c r="E268" s="20" t="inlineStr">
+        <is>
+          <t>Salfords, Redhill</t>
+        </is>
+      </c>
+      <c r="F268" s="20" t="inlineStr">
+        <is>
+          <t>£46,683 – £46,683</t>
+        </is>
+      </c>
+      <c r="G268" s="20" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H268" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I268" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J268" s="22" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K268" s="23" t="inlineStr"/>
+      <c r="L268" s="23" t="inlineStr"/>
+      <c r="M268" s="23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N268" s="24" t="inlineStr"/>
+      <c r="O268" s="23" t="inlineStr"/>
+    </row>
+    <row r="269" ht="16" customHeight="1" s="18">
+      <c r="A269" s="25" t="inlineStr">
+        <is>
+          <t>77ba6cefcd2c</t>
+        </is>
+      </c>
+      <c r="B269" s="25" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C269" s="25" t="inlineStr">
+        <is>
+          <t>Assistant Engineer - Clean Water Modelling</t>
+        </is>
+      </c>
+      <c r="D269" s="25" t="inlineStr">
+        <is>
+          <t>WSP</t>
+        </is>
+      </c>
+      <c r="E269" s="25" t="inlineStr">
+        <is>
+          <t>Aldwych, Central London</t>
+        </is>
+      </c>
+      <c r="F269" s="25" t="inlineStr">
+        <is>
+          <t>£45,209 – £45,209</t>
+        </is>
+      </c>
+      <c r="G269" s="25" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H269" s="21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I269" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="J269" s="26" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K269" s="27" t="inlineStr"/>
+      <c r="L269" s="27" t="inlineStr"/>
+      <c r="M269" s="27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N269" s="28" t="inlineStr"/>
+      <c r="O269" s="27" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -15432,6 +16966,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J241" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J242" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J269" r:id="rId268"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,6 +74,12 @@
       <i val="1"/>
       <color rgb="00744210"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001A6FA8"/>
+      <sz val="9"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="20">
@@ -174,7 +180,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -210,11 +216,25 @@
         <color rgb="00DDDDDD"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00EEEEEE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00EEEEEE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00EEEEEE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00EEEEEE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -291,6 +311,33 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -658,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O269"/>
+  <dimension ref="A1:O319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -16681,6 +16728,2956 @@
       <c r="N269" s="27" t="n"/>
       <c r="O269" s="26" t="n"/>
     </row>
+    <row r="270" ht="16" customHeight="1">
+      <c r="A270" s="28" t="inlineStr">
+        <is>
+          <t>6be8a415f3d6</t>
+        </is>
+      </c>
+      <c r="B270" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C270" s="28" t="inlineStr">
+        <is>
+          <t>Senior Water Network Engineer/Modellers</t>
+        </is>
+      </c>
+      <c r="D270" s="28" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E270" s="28" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F270" s="28" t="inlineStr">
+        <is>
+          <t>£50,253 – £50,253</t>
+        </is>
+      </c>
+      <c r="G270" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H270" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I270" s="28" t="n">
+        <v>115</v>
+      </c>
+      <c r="J270" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K270" s="31" t="inlineStr"/>
+      <c r="L270" s="31" t="inlineStr"/>
+      <c r="M270" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N270" s="32" t="inlineStr"/>
+      <c r="O270" s="31" t="inlineStr"/>
+    </row>
+    <row r="271" ht="16" customHeight="1">
+      <c r="A271" s="33" t="inlineStr">
+        <is>
+          <t>a44547004c6e</t>
+        </is>
+      </c>
+      <c r="B271" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C271" s="33" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D271" s="33" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E271" s="33" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F271" s="33" t="inlineStr">
+        <is>
+          <t>£48,252 – £48,252</t>
+        </is>
+      </c>
+      <c r="G271" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H271" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I271" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="J271" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K271" s="35" t="inlineStr"/>
+      <c r="L271" s="35" t="inlineStr"/>
+      <c r="M271" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N271" s="36" t="inlineStr"/>
+      <c r="O271" s="35" t="inlineStr"/>
+    </row>
+    <row r="272" ht="16" customHeight="1">
+      <c r="A272" s="28" t="inlineStr">
+        <is>
+          <t>b533be7869a9</t>
+        </is>
+      </c>
+      <c r="B272" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C272" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulics Engineers - UK Wide</t>
+        </is>
+      </c>
+      <c r="D272" s="28" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E272" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F272" s="28" t="inlineStr">
+        <is>
+          <t>£49,369 – £49,369</t>
+        </is>
+      </c>
+      <c r="G272" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H272" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I272" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J272" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K272" s="31" t="inlineStr"/>
+      <c r="L272" s="31" t="inlineStr"/>
+      <c r="M272" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N272" s="32" t="inlineStr"/>
+      <c r="O272" s="31" t="inlineStr"/>
+    </row>
+    <row r="273" ht="16" customHeight="1">
+      <c r="A273" s="33" t="inlineStr">
+        <is>
+          <t>bdc709b0e510</t>
+        </is>
+      </c>
+      <c r="B273" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C273" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer</t>
+        </is>
+      </c>
+      <c r="D273" s="33" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Recruitment Consultancy</t>
+        </is>
+      </c>
+      <c r="E273" s="33" t="inlineStr">
+        <is>
+          <t>Fleet, Hampshire</t>
+        </is>
+      </c>
+      <c r="F273" s="33" t="inlineStr">
+        <is>
+          <t>£50,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G273" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H273" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I273" s="33" t="n">
+        <v>85</v>
+      </c>
+      <c r="J273" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K273" s="35" t="inlineStr"/>
+      <c r="L273" s="35" t="inlineStr"/>
+      <c r="M273" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N273" s="36" t="inlineStr"/>
+      <c r="O273" s="35" t="inlineStr"/>
+    </row>
+    <row r="274" ht="16" customHeight="1">
+      <c r="A274" s="28" t="inlineStr">
+        <is>
+          <t>c783bc8ff987</t>
+        </is>
+      </c>
+      <c r="B274" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C274" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer</t>
+        </is>
+      </c>
+      <c r="D274" s="28" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Associates Ltd</t>
+        </is>
+      </c>
+      <c r="E274" s="28" t="inlineStr">
+        <is>
+          <t>Artington, Guildford</t>
+        </is>
+      </c>
+      <c r="F274" s="28" t="inlineStr">
+        <is>
+          <t>£50,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G274" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H274" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I274" s="28" t="n">
+        <v>85</v>
+      </c>
+      <c r="J274" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K274" s="31" t="inlineStr"/>
+      <c r="L274" s="31" t="inlineStr"/>
+      <c r="M274" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N274" s="32" t="inlineStr"/>
+      <c r="O274" s="31" t="inlineStr"/>
+    </row>
+    <row r="275" ht="16" customHeight="1">
+      <c r="A275" s="33" t="inlineStr">
+        <is>
+          <t>76de9f084cbc</t>
+        </is>
+      </c>
+      <c r="B275" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C275" s="33" t="inlineStr">
+        <is>
+          <t>Senior Electrical Engineer - Water Projects</t>
+        </is>
+      </c>
+      <c r="D275" s="33" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E275" s="33" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F275" s="33" t="inlineStr">
+        <is>
+          <t>£51,555 – £51,555</t>
+        </is>
+      </c>
+      <c r="G275" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H275" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I275" s="33" t="n">
+        <v>85</v>
+      </c>
+      <c r="J275" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K275" s="35" t="inlineStr"/>
+      <c r="L275" s="35" t="inlineStr"/>
+      <c r="M275" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N275" s="36" t="inlineStr"/>
+      <c r="O275" s="35" t="inlineStr"/>
+    </row>
+    <row r="276" ht="16" customHeight="1">
+      <c r="A276" s="28" t="inlineStr">
+        <is>
+          <t>33a5953210ce</t>
+        </is>
+      </c>
+      <c r="B276" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C276" s="28" t="inlineStr">
+        <is>
+          <t>Senior Electrical Engineer - Water Projects</t>
+        </is>
+      </c>
+      <c r="D276" s="28" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E276" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F276" s="28" t="inlineStr">
+        <is>
+          <t>£53,100 – £53,100</t>
+        </is>
+      </c>
+      <c r="G276" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H276" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I276" s="28" t="n">
+        <v>85</v>
+      </c>
+      <c r="J276" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K276" s="31" t="inlineStr"/>
+      <c r="L276" s="31" t="inlineStr"/>
+      <c r="M276" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N276" s="32" t="inlineStr"/>
+      <c r="O276" s="31" t="inlineStr"/>
+    </row>
+    <row r="277" ht="16" customHeight="1">
+      <c r="A277" s="33" t="inlineStr">
+        <is>
+          <t>de0ec3c61ed2</t>
+        </is>
+      </c>
+      <c r="B277" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C277" s="33" t="inlineStr">
+        <is>
+          <t>Senior Electrical Engineer - Water Projects</t>
+        </is>
+      </c>
+      <c r="D277" s="33" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E277" s="33" t="inlineStr">
+        <is>
+          <t>St. Albans, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="F277" s="33" t="inlineStr">
+        <is>
+          <t>£52,221 – £52,221</t>
+        </is>
+      </c>
+      <c r="G277" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H277" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I277" s="33" t="n">
+        <v>85</v>
+      </c>
+      <c r="J277" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K277" s="35" t="inlineStr"/>
+      <c r="L277" s="35" t="inlineStr"/>
+      <c r="M277" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N277" s="36" t="inlineStr"/>
+      <c r="O277" s="35" t="inlineStr"/>
+    </row>
+    <row r="278" ht="16" customHeight="1">
+      <c r="A278" s="28" t="inlineStr">
+        <is>
+          <t>d7216dba69f0</t>
+        </is>
+      </c>
+      <c r="B278" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C278" s="28" t="inlineStr">
+        <is>
+          <t>Senior Mechanical Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D278" s="28" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E278" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F278" s="28" t="inlineStr">
+        <is>
+          <t>£47,744 – £47,744</t>
+        </is>
+      </c>
+      <c r="G278" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H278" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I278" s="28" t="n">
+        <v>85</v>
+      </c>
+      <c r="J278" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K278" s="31" t="inlineStr"/>
+      <c r="L278" s="31" t="inlineStr"/>
+      <c r="M278" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N278" s="32" t="inlineStr"/>
+      <c r="O278" s="31" t="inlineStr"/>
+    </row>
+    <row r="279" ht="16" customHeight="1">
+      <c r="A279" s="33" t="inlineStr">
+        <is>
+          <t>442a8dc583ae</t>
+        </is>
+      </c>
+      <c r="B279" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C279" s="33" t="inlineStr">
+        <is>
+          <t>Senior Mechanical Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D279" s="33" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E279" s="33" t="inlineStr">
+        <is>
+          <t>St. Albans, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="F279" s="33" t="inlineStr">
+        <is>
+          <t>£46,954 – £46,954</t>
+        </is>
+      </c>
+      <c r="G279" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H279" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I279" s="33" t="n">
+        <v>85</v>
+      </c>
+      <c r="J279" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K279" s="35" t="inlineStr"/>
+      <c r="L279" s="35" t="inlineStr"/>
+      <c r="M279" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N279" s="36" t="inlineStr"/>
+      <c r="O279" s="35" t="inlineStr"/>
+    </row>
+    <row r="280" ht="16" customHeight="1">
+      <c r="A280" s="28" t="inlineStr">
+        <is>
+          <t>47c8dd068ca1</t>
+        </is>
+      </c>
+      <c r="B280" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C280" s="28" t="inlineStr">
+        <is>
+          <t>Senior Mechanical Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D280" s="28" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E280" s="28" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F280" s="28" t="inlineStr">
+        <is>
+          <t>£46,355 – £46,355</t>
+        </is>
+      </c>
+      <c r="G280" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H280" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I280" s="28" t="n">
+        <v>85</v>
+      </c>
+      <c r="J280" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K280" s="31" t="inlineStr"/>
+      <c r="L280" s="31" t="inlineStr"/>
+      <c r="M280" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N280" s="32" t="inlineStr"/>
+      <c r="O280" s="31" t="inlineStr"/>
+    </row>
+    <row r="281" ht="16" customHeight="1">
+      <c r="A281" s="33" t="inlineStr">
+        <is>
+          <t>9d38eeba62b6</t>
+        </is>
+      </c>
+      <c r="B281" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C281" s="33" t="inlineStr">
+        <is>
+          <t>Operations Engineer</t>
+        </is>
+      </c>
+      <c r="D281" s="33" t="inlineStr">
+        <is>
+          <t>ESP Utilities Group Ltd</t>
+        </is>
+      </c>
+      <c r="E281" s="33" t="inlineStr">
+        <is>
+          <t>Leatherhead, Surrey</t>
+        </is>
+      </c>
+      <c r="F281" s="33" t="inlineStr">
+        <is>
+          <t>£54,364 – £54,364</t>
+        </is>
+      </c>
+      <c r="G281" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H281" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I281" s="33" t="n">
+        <v>80</v>
+      </c>
+      <c r="J281" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K281" s="35" t="inlineStr"/>
+      <c r="L281" s="35" t="inlineStr"/>
+      <c r="M281" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N281" s="36" t="inlineStr"/>
+      <c r="O281" s="35" t="inlineStr"/>
+    </row>
+    <row r="282" ht="16" customHeight="1">
+      <c r="A282" s="28" t="inlineStr">
+        <is>
+          <t>a7539bff5c69</t>
+        </is>
+      </c>
+      <c r="B282" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C282" s="28" t="inlineStr">
+        <is>
+          <t>Senior Electrical Engineer - Water Projects</t>
+        </is>
+      </c>
+      <c r="D282" s="28" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E282" s="28" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F282" s="28" t="inlineStr">
+        <is>
+          <t>£47,734 – £47,734</t>
+        </is>
+      </c>
+      <c r="G282" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H282" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I282" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J282" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K282" s="31" t="inlineStr"/>
+      <c r="L282" s="31" t="inlineStr"/>
+      <c r="M282" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N282" s="32" t="inlineStr"/>
+      <c r="O282" s="31" t="inlineStr"/>
+    </row>
+    <row r="283" ht="16" customHeight="1">
+      <c r="A283" s="33" t="inlineStr">
+        <is>
+          <t>ea1e4b2de380</t>
+        </is>
+      </c>
+      <c r="B283" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C283" s="33" t="inlineStr">
+        <is>
+          <t>Senior Electrical Engineer - Water Projects</t>
+        </is>
+      </c>
+      <c r="D283" s="33" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E283" s="33" t="inlineStr">
+        <is>
+          <t>St. Albans, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="F283" s="33" t="inlineStr">
+        <is>
+          <t>£48,482 – £48,482</t>
+        </is>
+      </c>
+      <c r="G283" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H283" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I283" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="J283" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K283" s="35" t="inlineStr"/>
+      <c r="L283" s="35" t="inlineStr"/>
+      <c r="M283" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N283" s="36" t="inlineStr"/>
+      <c r="O283" s="35" t="inlineStr"/>
+    </row>
+    <row r="284" ht="16" customHeight="1">
+      <c r="A284" s="28" t="inlineStr">
+        <is>
+          <t>3465e06e78fd</t>
+        </is>
+      </c>
+      <c r="B284" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C284" s="28" t="inlineStr">
+        <is>
+          <t>Senior Electrical Engineer - Water Projects</t>
+        </is>
+      </c>
+      <c r="D284" s="28" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E284" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F284" s="28" t="inlineStr">
+        <is>
+          <t>£49,911 – £49,911</t>
+        </is>
+      </c>
+      <c r="G284" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H284" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I284" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J284" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K284" s="31" t="inlineStr"/>
+      <c r="L284" s="31" t="inlineStr"/>
+      <c r="M284" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N284" s="32" t="inlineStr"/>
+      <c r="O284" s="31" t="inlineStr"/>
+    </row>
+    <row r="285" ht="16" customHeight="1">
+      <c r="A285" s="33" t="inlineStr">
+        <is>
+          <t>72e94d4ff422</t>
+        </is>
+      </c>
+      <c r="B285" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C285" s="33" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D285" s="33" t="inlineStr">
+        <is>
+          <t>Murray McIntosh &amp; Associates Limited</t>
+        </is>
+      </c>
+      <c r="E285" s="33" t="inlineStr">
+        <is>
+          <t>Church Crookham, Fleet</t>
+        </is>
+      </c>
+      <c r="F285" s="33" t="inlineStr">
+        <is>
+          <t>£50,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G285" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H285" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I285" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="J285" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K285" s="35" t="inlineStr"/>
+      <c r="L285" s="35" t="inlineStr"/>
+      <c r="M285" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N285" s="36" t="inlineStr"/>
+      <c r="O285" s="35" t="inlineStr"/>
+    </row>
+    <row r="286" ht="16" customHeight="1">
+      <c r="A286" s="28" t="inlineStr">
+        <is>
+          <t>60919139560b</t>
+        </is>
+      </c>
+      <c r="B286" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C286" s="28" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D286" s="28" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Recruitment Consultancy</t>
+        </is>
+      </c>
+      <c r="E286" s="28" t="inlineStr">
+        <is>
+          <t>Fleet, Hampshire</t>
+        </is>
+      </c>
+      <c r="F286" s="28" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G286" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H286" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I286" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J286" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K286" s="31" t="inlineStr"/>
+      <c r="L286" s="31" t="inlineStr"/>
+      <c r="M286" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N286" s="32" t="inlineStr"/>
+      <c r="O286" s="31" t="inlineStr"/>
+    </row>
+    <row r="287" ht="16" customHeight="1">
+      <c r="A287" s="33" t="inlineStr">
+        <is>
+          <t>e5c3014a76d0</t>
+        </is>
+      </c>
+      <c r="B287" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C287" s="33" t="inlineStr">
+        <is>
+          <t>Mechanical Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D287" s="33" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Associates Ltd</t>
+        </is>
+      </c>
+      <c r="E287" s="33" t="inlineStr">
+        <is>
+          <t>Artington, Guildford</t>
+        </is>
+      </c>
+      <c r="F287" s="33" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G287" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H287" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I287" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="J287" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K287" s="35" t="inlineStr"/>
+      <c r="L287" s="35" t="inlineStr"/>
+      <c r="M287" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N287" s="36" t="inlineStr"/>
+      <c r="O287" s="35" t="inlineStr"/>
+    </row>
+    <row r="288" ht="16" customHeight="1">
+      <c r="A288" s="28" t="inlineStr">
+        <is>
+          <t>a404e8e9892f</t>
+        </is>
+      </c>
+      <c r="B288" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C288" s="28" t="inlineStr">
+        <is>
+          <t>Drainage Design Engineer</t>
+        </is>
+      </c>
+      <c r="D288" s="28" t="inlineStr">
+        <is>
+          <t>Pave Recruit</t>
+        </is>
+      </c>
+      <c r="E288" s="28" t="inlineStr">
+        <is>
+          <t>Richmond, West London</t>
+        </is>
+      </c>
+      <c r="F288" s="28" t="inlineStr">
+        <is>
+          <t>£38,000 – £44,000</t>
+        </is>
+      </c>
+      <c r="G288" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H288" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I288" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J288" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K288" s="31" t="inlineStr"/>
+      <c r="L288" s="31" t="inlineStr"/>
+      <c r="M288" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N288" s="32" t="inlineStr"/>
+      <c r="O288" s="31" t="inlineStr"/>
+    </row>
+    <row r="289" ht="16" customHeight="1">
+      <c r="A289" s="33" t="inlineStr">
+        <is>
+          <t>1463eee791f7</t>
+        </is>
+      </c>
+      <c r="B289" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C289" s="33" t="inlineStr">
+        <is>
+          <t>Senior Mechanical Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D289" s="33" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E289" s="33" t="inlineStr">
+        <is>
+          <t>St. Albans, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="F289" s="33" t="inlineStr">
+        <is>
+          <t>£45,822 – £45,822</t>
+        </is>
+      </c>
+      <c r="G289" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H289" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I289" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="J289" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K289" s="35" t="inlineStr"/>
+      <c r="L289" s="35" t="inlineStr"/>
+      <c r="M289" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N289" s="36" t="inlineStr"/>
+      <c r="O289" s="35" t="inlineStr"/>
+    </row>
+    <row r="290" ht="16" customHeight="1">
+      <c r="A290" s="28" t="inlineStr">
+        <is>
+          <t>ca7e6262c249</t>
+        </is>
+      </c>
+      <c r="B290" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C290" s="28" t="inlineStr">
+        <is>
+          <t>Senior Mechanical Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D290" s="28" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E290" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F290" s="28" t="inlineStr">
+        <is>
+          <t>£47,172 – £47,172</t>
+        </is>
+      </c>
+      <c r="G290" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H290" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I290" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J290" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K290" s="31" t="inlineStr"/>
+      <c r="L290" s="31" t="inlineStr"/>
+      <c r="M290" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N290" s="32" t="inlineStr"/>
+      <c r="O290" s="31" t="inlineStr"/>
+    </row>
+    <row r="291" ht="16" customHeight="1">
+      <c r="A291" s="33" t="inlineStr">
+        <is>
+          <t>d62bf2bbd601</t>
+        </is>
+      </c>
+      <c r="B291" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C291" s="33" t="inlineStr">
+        <is>
+          <t>Senior Mechanical Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D291" s="33" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E291" s="33" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F291" s="33" t="inlineStr">
+        <is>
+          <t>£45,115 – £45,115</t>
+        </is>
+      </c>
+      <c r="G291" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H291" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I291" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="J291" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K291" s="35" t="inlineStr"/>
+      <c r="L291" s="35" t="inlineStr"/>
+      <c r="M291" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N291" s="36" t="inlineStr"/>
+      <c r="O291" s="35" t="inlineStr"/>
+    </row>
+    <row r="292" ht="16" customHeight="1">
+      <c r="A292" s="28" t="inlineStr">
+        <is>
+          <t>2ed940b1e206</t>
+        </is>
+      </c>
+      <c r="B292" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C292" s="28" t="inlineStr">
+        <is>
+          <t>Grow Your Career In The Water Sector - Expression of Interest</t>
+        </is>
+      </c>
+      <c r="D292" s="28" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E292" s="28" t="inlineStr">
+        <is>
+          <t>St. Albans, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="F292" s="28" t="inlineStr">
+        <is>
+          <t>£45,523 – £45,523</t>
+        </is>
+      </c>
+      <c r="G292" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H292" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I292" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J292" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K292" s="31" t="inlineStr"/>
+      <c r="L292" s="31" t="inlineStr"/>
+      <c r="M292" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N292" s="32" t="inlineStr"/>
+      <c r="O292" s="31" t="inlineStr"/>
+    </row>
+    <row r="293" ht="16" customHeight="1">
+      <c r="A293" s="33" t="inlineStr">
+        <is>
+          <t>f423fafcf7a1</t>
+        </is>
+      </c>
+      <c r="B293" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C293" s="33" t="inlineStr">
+        <is>
+          <t>Grow Your Career In The Water Sector - Expression of Interest</t>
+        </is>
+      </c>
+      <c r="D293" s="33" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E293" s="33" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F293" s="33" t="inlineStr">
+        <is>
+          <t>£46,865 – £46,865</t>
+        </is>
+      </c>
+      <c r="G293" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H293" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I293" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="J293" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K293" s="35" t="inlineStr"/>
+      <c r="L293" s="35" t="inlineStr"/>
+      <c r="M293" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N293" s="36" t="inlineStr"/>
+      <c r="O293" s="35" t="inlineStr"/>
+    </row>
+    <row r="294" ht="16" customHeight="1">
+      <c r="A294" s="28" t="inlineStr">
+        <is>
+          <t>a033c430788b</t>
+        </is>
+      </c>
+      <c r="B294" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C294" s="28" t="inlineStr">
+        <is>
+          <t>Grow Your Career In The Water Sector - Expression of Interest</t>
+        </is>
+      </c>
+      <c r="D294" s="28" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E294" s="28" t="inlineStr">
+        <is>
+          <t>Croydon, London</t>
+        </is>
+      </c>
+      <c r="F294" s="28" t="inlineStr">
+        <is>
+          <t>£44,821 – £44,821</t>
+        </is>
+      </c>
+      <c r="G294" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H294" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I294" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J294" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K294" s="31" t="inlineStr"/>
+      <c r="L294" s="31" t="inlineStr"/>
+      <c r="M294" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N294" s="32" t="inlineStr"/>
+      <c r="O294" s="31" t="inlineStr"/>
+    </row>
+    <row r="295" ht="16" customHeight="1">
+      <c r="A295" s="33" t="inlineStr">
+        <is>
+          <t>23a8608415cc</t>
+        </is>
+      </c>
+      <c r="B295" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C295" s="33" t="inlineStr">
+        <is>
+          <t>Water &amp; Wastewater Sales Engineer - South UK Infrastructure</t>
+        </is>
+      </c>
+      <c r="D295" s="33" t="inlineStr">
+        <is>
+          <t>Victaulic</t>
+        </is>
+      </c>
+      <c r="E295" s="33" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F295" s="33" t="inlineStr">
+        <is>
+          <t>£51,376 – £51,376</t>
+        </is>
+      </c>
+      <c r="G295" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H295" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I295" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="J295" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K295" s="35" t="inlineStr"/>
+      <c r="L295" s="35" t="inlineStr"/>
+      <c r="M295" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N295" s="36" t="inlineStr"/>
+      <c r="O295" s="35" t="inlineStr"/>
+    </row>
+    <row r="296" ht="16" customHeight="1">
+      <c r="A296" s="28" t="inlineStr">
+        <is>
+          <t>cab406157539</t>
+        </is>
+      </c>
+      <c r="B296" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C296" s="28" t="inlineStr">
+        <is>
+          <t>Senior Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D296" s="28" t="inlineStr">
+        <is>
+          <t>Mott MacDonald</t>
+        </is>
+      </c>
+      <c r="E296" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F296" s="28" t="inlineStr">
+        <is>
+          <t>£51,904 – £51,904</t>
+        </is>
+      </c>
+      <c r="G296" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H296" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I296" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J296" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K296" s="31" t="inlineStr"/>
+      <c r="L296" s="31" t="inlineStr"/>
+      <c r="M296" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N296" s="32" t="inlineStr"/>
+      <c r="O296" s="31" t="inlineStr"/>
+    </row>
+    <row r="297" ht="16" customHeight="1">
+      <c r="A297" s="33" t="inlineStr">
+        <is>
+          <t>dacce35cb278</t>
+        </is>
+      </c>
+      <c r="B297" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C297" s="33" t="inlineStr">
+        <is>
+          <t>Civil Engineer Project Leader</t>
+        </is>
+      </c>
+      <c r="D297" s="33" t="inlineStr">
+        <is>
+          <t>Mott MacDonald</t>
+        </is>
+      </c>
+      <c r="E297" s="33" t="inlineStr">
+        <is>
+          <t>Caversham, Reading</t>
+        </is>
+      </c>
+      <c r="F297" s="33" t="inlineStr">
+        <is>
+          <t>£48,165 – £48,165</t>
+        </is>
+      </c>
+      <c r="G297" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H297" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I297" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J297" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K297" s="35" t="inlineStr"/>
+      <c r="L297" s="35" t="inlineStr"/>
+      <c r="M297" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N297" s="36" t="inlineStr"/>
+      <c r="O297" s="35" t="inlineStr"/>
+    </row>
+    <row r="298" ht="16" customHeight="1">
+      <c r="A298" s="28" t="inlineStr">
+        <is>
+          <t>6cbe22bb2262</t>
+        </is>
+      </c>
+      <c r="B298" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C298" s="28" t="inlineStr">
+        <is>
+          <t>Civil Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="D298" s="28" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E298" s="28" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F298" s="28" t="inlineStr">
+        <is>
+          <t>£55,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G298" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H298" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I298" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J298" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K298" s="31" t="inlineStr"/>
+      <c r="L298" s="31" t="inlineStr"/>
+      <c r="M298" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N298" s="32" t="inlineStr"/>
+      <c r="O298" s="31" t="inlineStr"/>
+    </row>
+    <row r="299" ht="16" customHeight="1">
+      <c r="A299" s="33" t="inlineStr">
+        <is>
+          <t>12b2c254203c</t>
+        </is>
+      </c>
+      <c r="B299" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C299" s="33" t="inlineStr">
+        <is>
+          <t>Civil Engineer Hybrid</t>
+        </is>
+      </c>
+      <c r="D299" s="33" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment Limited</t>
+        </is>
+      </c>
+      <c r="E299" s="33" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F299" s="33" t="inlineStr">
+        <is>
+          <t>£45,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G299" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H299" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I299" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J299" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K299" s="35" t="inlineStr"/>
+      <c r="L299" s="35" t="inlineStr"/>
+      <c r="M299" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N299" s="36" t="inlineStr"/>
+      <c r="O299" s="35" t="inlineStr"/>
+    </row>
+    <row r="300" ht="16" customHeight="1">
+      <c r="A300" s="28" t="inlineStr">
+        <is>
+          <t>d7de94d41567</t>
+        </is>
+      </c>
+      <c r="B300" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C300" s="28" t="inlineStr">
+        <is>
+          <t>Civil Engineer (Water industry)</t>
+        </is>
+      </c>
+      <c r="D300" s="28" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E300" s="28" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F300" s="28" t="inlineStr">
+        <is>
+          <t>£55,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G300" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H300" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I300" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J300" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K300" s="31" t="inlineStr"/>
+      <c r="L300" s="31" t="inlineStr"/>
+      <c r="M300" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N300" s="32" t="inlineStr"/>
+      <c r="O300" s="31" t="inlineStr"/>
+    </row>
+    <row r="301" ht="16" customHeight="1">
+      <c r="A301" s="33" t="inlineStr">
+        <is>
+          <t>22978e1eb40b</t>
+        </is>
+      </c>
+      <c r="B301" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C301" s="33" t="inlineStr">
+        <is>
+          <t>Linux Infrastructure Engineer (Automation &amp; Tools) | Large-Scale Distributed Systems | Python, Linux, Automation | London (Hybrid, 3 days) | VP-Level | Total Comp £110-160k+, plus benefits</t>
+        </is>
+      </c>
+      <c r="D301" s="33" t="inlineStr">
+        <is>
+          <t>Owen Thomas | Pending B Corp™</t>
+        </is>
+      </c>
+      <c r="E301" s="33" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F301" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G301" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H301" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I301" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J301" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K301" s="35" t="inlineStr"/>
+      <c r="L301" s="35" t="inlineStr"/>
+      <c r="M301" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N301" s="36" t="inlineStr"/>
+      <c r="O301" s="35" t="inlineStr"/>
+    </row>
+    <row r="302" ht="16" customHeight="1">
+      <c r="A302" s="28" t="inlineStr">
+        <is>
+          <t>469e84536f11</t>
+        </is>
+      </c>
+      <c r="B302" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C302" s="28" t="inlineStr">
+        <is>
+          <t>Infrastructure Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="D302" s="28" t="inlineStr">
+        <is>
+          <t>Cloudflare</t>
+        </is>
+      </c>
+      <c r="E302" s="28" t="inlineStr">
+        <is>
+          <t>Greater London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F302" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G302" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H302" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I302" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J302" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K302" s="31" t="inlineStr"/>
+      <c r="L302" s="31" t="inlineStr"/>
+      <c r="M302" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N302" s="32" t="inlineStr"/>
+      <c r="O302" s="31" t="inlineStr"/>
+    </row>
+    <row r="303" ht="16" customHeight="1">
+      <c r="A303" s="33" t="inlineStr">
+        <is>
+          <t>7e3e4e44a708</t>
+        </is>
+      </c>
+      <c r="B303" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C303" s="33" t="inlineStr">
+        <is>
+          <t>Stairlift Engineer</t>
+        </is>
+      </c>
+      <c r="D303" s="33" t="inlineStr">
+        <is>
+          <t>Stannah Group</t>
+        </is>
+      </c>
+      <c r="E303" s="33" t="inlineStr">
+        <is>
+          <t>Worthing, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F303" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G303" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H303" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I303" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="J303" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K303" s="35" t="inlineStr"/>
+      <c r="L303" s="35" t="inlineStr"/>
+      <c r="M303" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N303" s="36" t="inlineStr"/>
+      <c r="O303" s="35" t="inlineStr"/>
+    </row>
+    <row r="304" ht="16" customHeight="1">
+      <c r="A304" s="28" t="inlineStr">
+        <is>
+          <t>a012b076de10</t>
+        </is>
+      </c>
+      <c r="B304" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C304" s="28" t="inlineStr">
+        <is>
+          <t>Graduate Engineer</t>
+        </is>
+      </c>
+      <c r="D304" s="28" t="inlineStr">
+        <is>
+          <t>Metrology Engineering Services [MES]</t>
+        </is>
+      </c>
+      <c r="E304" s="28" t="inlineStr">
+        <is>
+          <t>Newport, Wales, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F304" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G304" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H304" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I304" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="J304" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K304" s="31" t="inlineStr"/>
+      <c r="L304" s="31" t="inlineStr"/>
+      <c r="M304" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N304" s="32" t="inlineStr"/>
+      <c r="O304" s="31" t="inlineStr"/>
+    </row>
+    <row r="305" ht="16" customHeight="1">
+      <c r="A305" s="33" t="inlineStr">
+        <is>
+          <t>7bdc7af7f828</t>
+        </is>
+      </c>
+      <c r="B305" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C305" s="33" t="inlineStr">
+        <is>
+          <t>Escalator Engineer (Nights)</t>
+        </is>
+      </c>
+      <c r="D305" s="33" t="inlineStr">
+        <is>
+          <t>Stannah Group</t>
+        </is>
+      </c>
+      <c r="E305" s="33" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F305" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G305" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H305" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I305" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="J305" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K305" s="35" t="inlineStr"/>
+      <c r="L305" s="35" t="inlineStr"/>
+      <c r="M305" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N305" s="36" t="inlineStr"/>
+      <c r="O305" s="35" t="inlineStr"/>
+    </row>
+    <row r="306" ht="16" customHeight="1">
+      <c r="A306" s="28" t="inlineStr">
+        <is>
+          <t>5647466123a7</t>
+        </is>
+      </c>
+      <c r="B306" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C306" s="28" t="inlineStr">
+        <is>
+          <t>Composite Designer</t>
+        </is>
+      </c>
+      <c r="D306" s="28" t="inlineStr">
+        <is>
+          <t>Cadillac Formula 1® Team</t>
+        </is>
+      </c>
+      <c r="E306" s="28" t="inlineStr">
+        <is>
+          <t>Silverstone, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F306" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G306" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H306" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I306" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="J306" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K306" s="31" t="inlineStr"/>
+      <c r="L306" s="31" t="inlineStr"/>
+      <c r="M306" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N306" s="32" t="inlineStr"/>
+      <c r="O306" s="31" t="inlineStr"/>
+    </row>
+    <row r="307" ht="16" customHeight="1">
+      <c r="A307" s="33" t="inlineStr">
+        <is>
+          <t>d43dfada7e7b</t>
+        </is>
+      </c>
+      <c r="B307" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C307" s="33" t="inlineStr">
+        <is>
+          <t>Design Engineer</t>
+        </is>
+      </c>
+      <c r="D307" s="33" t="inlineStr">
+        <is>
+          <t>Multiverse</t>
+        </is>
+      </c>
+      <c r="E307" s="33" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F307" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G307" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H307" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I307" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="J307" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K307" s="35" t="inlineStr"/>
+      <c r="L307" s="35" t="inlineStr"/>
+      <c r="M307" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N307" s="36" t="inlineStr"/>
+      <c r="O307" s="35" t="inlineStr"/>
+    </row>
+    <row r="308" ht="16" customHeight="1">
+      <c r="A308" s="28" t="inlineStr">
+        <is>
+          <t>0c44c2386ae8</t>
+        </is>
+      </c>
+      <c r="B308" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C308" s="28" t="inlineStr">
+        <is>
+          <t>Australian Based Dams / Reservoir Engineering Opportunities (Relocation assistance provided)</t>
+        </is>
+      </c>
+      <c r="D308" s="28" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E308" s="28" t="inlineStr">
+        <is>
+          <t>Cardiff, Wales, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F308" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G308" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H308" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I308" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="J308" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K308" s="31" t="inlineStr"/>
+      <c r="L308" s="31" t="inlineStr"/>
+      <c r="M308" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N308" s="32" t="inlineStr"/>
+      <c r="O308" s="31" t="inlineStr"/>
+    </row>
+    <row r="309" ht="16" customHeight="1">
+      <c r="A309" s="33" t="inlineStr">
+        <is>
+          <t>3c3cdf59f9f3</t>
+        </is>
+      </c>
+      <c r="B309" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C309" s="33" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="D309" s="33" t="inlineStr">
+        <is>
+          <t>John Sisk &amp; Son Ltd</t>
+        </is>
+      </c>
+      <c r="E309" s="33" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F309" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G309" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H309" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I309" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="J309" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K309" s="35" t="inlineStr"/>
+      <c r="L309" s="35" t="inlineStr"/>
+      <c r="M309" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N309" s="36" t="inlineStr"/>
+      <c r="O309" s="35" t="inlineStr"/>
+    </row>
+    <row r="310" ht="16" customHeight="1">
+      <c r="A310" s="28" t="inlineStr">
+        <is>
+          <t>f2fdf95c9ccf</t>
+        </is>
+      </c>
+      <c r="B310" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C310" s="28" t="inlineStr">
+        <is>
+          <t>Security Systems CCTV Engineer</t>
+        </is>
+      </c>
+      <c r="D310" s="28" t="inlineStr">
+        <is>
+          <t>Momentum Security Recruitment</t>
+        </is>
+      </c>
+      <c r="E310" s="28" t="inlineStr">
+        <is>
+          <t>Maidstone, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F310" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G310" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H310" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I310" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="J310" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K310" s="31" t="inlineStr"/>
+      <c r="L310" s="31" t="inlineStr"/>
+      <c r="M310" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N310" s="32" t="inlineStr"/>
+      <c r="O310" s="31" t="inlineStr"/>
+    </row>
+    <row r="311" ht="16" customHeight="1">
+      <c r="A311" s="33" t="inlineStr">
+        <is>
+          <t>e108972fc0ed</t>
+        </is>
+      </c>
+      <c r="B311" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C311" s="33" t="inlineStr">
+        <is>
+          <t>Network Engineer V</t>
+        </is>
+      </c>
+      <c r="D311" s="33" t="inlineStr">
+        <is>
+          <t>Keystone Recruitment</t>
+        </is>
+      </c>
+      <c r="E311" s="33" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F311" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G311" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H311" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I311" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="J311" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K311" s="35" t="inlineStr"/>
+      <c r="L311" s="35" t="inlineStr"/>
+      <c r="M311" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N311" s="36" t="inlineStr"/>
+      <c r="O311" s="35" t="inlineStr"/>
+    </row>
+    <row r="312" ht="16" customHeight="1">
+      <c r="A312" s="28" t="inlineStr">
+        <is>
+          <t>843e73e1f904</t>
+        </is>
+      </c>
+      <c r="B312" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C312" s="28" t="inlineStr">
+        <is>
+          <t>Network Engineer x 2 (111254-0126)</t>
+        </is>
+      </c>
+      <c r="D312" s="28" t="inlineStr">
+        <is>
+          <t>University of Warwick</t>
+        </is>
+      </c>
+      <c r="E312" s="28" t="inlineStr">
+        <is>
+          <t>Coventry, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F312" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G312" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H312" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I312" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="J312" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K312" s="31" t="inlineStr"/>
+      <c r="L312" s="31" t="inlineStr"/>
+      <c r="M312" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N312" s="32" t="inlineStr"/>
+      <c r="O312" s="31" t="inlineStr"/>
+    </row>
+    <row r="313" ht="16" customHeight="1">
+      <c r="A313" s="33" t="inlineStr">
+        <is>
+          <t>961d7f95d534</t>
+        </is>
+      </c>
+      <c r="B313" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C313" s="33" t="inlineStr">
+        <is>
+          <t>Senior Cloud Network Engineer - Terraform &amp; Zscaler (FinTech) - £90k</t>
+        </is>
+      </c>
+      <c r="D313" s="33" t="inlineStr">
+        <is>
+          <t>Hawksworth</t>
+        </is>
+      </c>
+      <c r="E313" s="33" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F313" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G313" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H313" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I313" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="J313" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K313" s="35" t="inlineStr"/>
+      <c r="L313" s="35" t="inlineStr"/>
+      <c r="M313" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N313" s="36" t="inlineStr"/>
+      <c r="O313" s="35" t="inlineStr"/>
+    </row>
+    <row r="314" ht="16" customHeight="1">
+      <c r="A314" s="28" t="inlineStr">
+        <is>
+          <t>6f6700168a6f</t>
+        </is>
+      </c>
+      <c r="B314" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C314" s="28" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="D314" s="28" t="inlineStr">
+        <is>
+          <t>hackajob</t>
+        </is>
+      </c>
+      <c r="E314" s="28" t="inlineStr">
+        <is>
+          <t>Erskine, Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F314" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G314" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H314" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I314" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="J314" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K314" s="31" t="inlineStr"/>
+      <c r="L314" s="31" t="inlineStr"/>
+      <c r="M314" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N314" s="32" t="inlineStr"/>
+      <c r="O314" s="31" t="inlineStr"/>
+    </row>
+    <row r="315" ht="16" customHeight="1">
+      <c r="A315" s="33" t="inlineStr">
+        <is>
+          <t>e8e7e5701157</t>
+        </is>
+      </c>
+      <c r="B315" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C315" s="33" t="inlineStr">
+        <is>
+          <t>System Engineer (MBSE)</t>
+        </is>
+      </c>
+      <c r="D315" s="33" t="inlineStr">
+        <is>
+          <t>Apollo Fire Detectors</t>
+        </is>
+      </c>
+      <c r="E315" s="33" t="inlineStr">
+        <is>
+          <t>Havant, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F315" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G315" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H315" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I315" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="J315" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K315" s="35" t="inlineStr"/>
+      <c r="L315" s="35" t="inlineStr"/>
+      <c r="M315" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N315" s="36" t="inlineStr"/>
+      <c r="O315" s="35" t="inlineStr"/>
+    </row>
+    <row r="316" ht="16" customHeight="1">
+      <c r="A316" s="28" t="inlineStr">
+        <is>
+          <t>0d15005ddfd0</t>
+        </is>
+      </c>
+      <c r="B316" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C316" s="28" t="inlineStr">
+        <is>
+          <t>Systems Engineer - Contractor</t>
+        </is>
+      </c>
+      <c r="D316" s="28" t="inlineStr">
+        <is>
+          <t>ESCO Maritime Solutions</t>
+        </is>
+      </c>
+      <c r="E316" s="28" t="inlineStr">
+        <is>
+          <t>Rugeley, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F316" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G316" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H316" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I316" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="J316" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K316" s="31" t="inlineStr"/>
+      <c r="L316" s="31" t="inlineStr"/>
+      <c r="M316" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N316" s="32" t="inlineStr"/>
+      <c r="O316" s="31" t="inlineStr"/>
+    </row>
+    <row r="317" ht="16" customHeight="1">
+      <c r="A317" s="33" t="inlineStr">
+        <is>
+          <t>7a2efcde0bd1</t>
+        </is>
+      </c>
+      <c r="B317" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C317" s="33" t="inlineStr">
+        <is>
+          <t>Senior Associate</t>
+        </is>
+      </c>
+      <c r="D317" s="33" t="inlineStr">
+        <is>
+          <t>Meridian Universal</t>
+        </is>
+      </c>
+      <c r="E317" s="33" t="inlineStr">
+        <is>
+          <t>City Of London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F317" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G317" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H317" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I317" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="J317" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K317" s="35" t="inlineStr"/>
+      <c r="L317" s="35" t="inlineStr"/>
+      <c r="M317" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N317" s="36" t="inlineStr"/>
+      <c r="O317" s="35" t="inlineStr"/>
+    </row>
+    <row r="318" ht="16" customHeight="1">
+      <c r="A318" s="28" t="inlineStr">
+        <is>
+          <t>d8123ec97abc</t>
+        </is>
+      </c>
+      <c r="B318" s="28" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C318" s="28" t="inlineStr">
+        <is>
+          <t>Gas Distribution Senior Modeller</t>
+        </is>
+      </c>
+      <c r="D318" s="28" t="inlineStr">
+        <is>
+          <t>Esyasoft Holding</t>
+        </is>
+      </c>
+      <c r="E318" s="28" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F318" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G318" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H318" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I318" s="28" t="n">
+        <v>45</v>
+      </c>
+      <c r="J318" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K318" s="31" t="inlineStr"/>
+      <c r="L318" s="31" t="inlineStr"/>
+      <c r="M318" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N318" s="32" t="inlineStr"/>
+      <c r="O318" s="31" t="inlineStr"/>
+    </row>
+    <row r="319" ht="16" customHeight="1">
+      <c r="A319" s="33" t="inlineStr">
+        <is>
+          <t>86b8cddc9519</t>
+        </is>
+      </c>
+      <c r="B319" s="33" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="C319" s="33" t="inlineStr">
+        <is>
+          <t>Sound Engineer professionals</t>
+        </is>
+      </c>
+      <c r="D319" s="33" t="inlineStr">
+        <is>
+          <t>BASELINE SOLVING</t>
+        </is>
+      </c>
+      <c r="E319" s="33" t="inlineStr">
+        <is>
+          <t>Greater London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F319" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G319" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H319" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I319" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="J319" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K319" s="35" t="inlineStr"/>
+      <c r="L319" s="35" t="inlineStr"/>
+      <c r="M319" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N319" s="36" t="inlineStr"/>
+      <c r="O319" s="35" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="K2:K5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -16693,6 +19690,58 @@
       <formula1>"Too junior / entry level,Too senior / overqualified,Wrong sector / not water,Wrong location / too far,Salary too low,Contract / not permanent,Missing required licence/cert,Company culture / reputation,Role not interesting,Duplicate / already applied,Other"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J270" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J271" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J272" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J273" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J274" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J275" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J276" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J277" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J278" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J279" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J280" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J281" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J282" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J283" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J284" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J285" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J286" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J287" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J288" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J289" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J290" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J291" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J292" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J293" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J294" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J295" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J296" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J297" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J298" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J299" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J300" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J301" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J302" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J303" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J304" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J305" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J306" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J307" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J308" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J309" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J310" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J311" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J312" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J313" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J314" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J315" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J316" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J317" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J318" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J319" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O319"/>
+  <dimension ref="A1:O326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -19677,6 +19677,419 @@
       </c>
       <c r="N319" s="36" t="inlineStr"/>
       <c r="O319" s="35" t="inlineStr"/>
+    </row>
+    <row r="320" ht="16" customHeight="1">
+      <c r="A320" s="28" t="inlineStr">
+        <is>
+          <t>458e4cb0d9b0</t>
+        </is>
+      </c>
+      <c r="B320" s="28" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="C320" s="28" t="inlineStr">
+        <is>
+          <t>Civil Engineer (Water industry)</t>
+        </is>
+      </c>
+      <c r="D320" s="28" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E320" s="28" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F320" s="28" t="inlineStr">
+        <is>
+          <t>£55,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G320" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H320" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I320" s="28" t="n">
+        <v>43</v>
+      </c>
+      <c r="J320" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K320" s="31" t="inlineStr"/>
+      <c r="L320" s="31" t="inlineStr"/>
+      <c r="M320" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N320" s="32" t="inlineStr"/>
+      <c r="O320" s="31" t="inlineStr"/>
+    </row>
+    <row r="321" ht="16" customHeight="1">
+      <c r="A321" s="33" t="inlineStr">
+        <is>
+          <t>69cb8c6de3b3</t>
+        </is>
+      </c>
+      <c r="B321" s="33" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="C321" s="33" t="inlineStr">
+        <is>
+          <t>Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D321" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E321" s="33" t="inlineStr">
+        <is>
+          <t>High Wycombe, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="F321" s="33" t="inlineStr">
+        <is>
+          <t>£45,172 – £45,172</t>
+        </is>
+      </c>
+      <c r="G321" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H321" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I321" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="J321" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K321" s="35" t="inlineStr"/>
+      <c r="L321" s="35" t="inlineStr"/>
+      <c r="M321" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N321" s="36" t="inlineStr"/>
+      <c r="O321" s="35" t="inlineStr"/>
+    </row>
+    <row r="322" ht="16" customHeight="1">
+      <c r="A322" s="28" t="inlineStr">
+        <is>
+          <t>057a57f00d82</t>
+        </is>
+      </c>
+      <c r="B322" s="28" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="C322" s="28" t="inlineStr">
+        <is>
+          <t>Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D322" s="28" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E322" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F322" s="28" t="inlineStr">
+        <is>
+          <t>£46,447 – £46,447</t>
+        </is>
+      </c>
+      <c r="G322" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H322" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I322" s="28" t="n">
+        <v>40</v>
+      </c>
+      <c r="J322" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K322" s="31" t="inlineStr"/>
+      <c r="L322" s="31" t="inlineStr"/>
+      <c r="M322" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N322" s="32" t="inlineStr"/>
+      <c r="O322" s="31" t="inlineStr"/>
+    </row>
+    <row r="323" ht="16" customHeight="1">
+      <c r="A323" s="33" t="inlineStr">
+        <is>
+          <t>664c621c2d18</t>
+        </is>
+      </c>
+      <c r="B323" s="33" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="C323" s="33" t="inlineStr">
+        <is>
+          <t>Senior Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D323" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E323" s="33" t="inlineStr">
+        <is>
+          <t>High Wycombe, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="F323" s="33" t="inlineStr">
+        <is>
+          <t>£49,539 – £49,539</t>
+        </is>
+      </c>
+      <c r="G323" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H323" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I323" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="J323" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K323" s="35" t="inlineStr"/>
+      <c r="L323" s="35" t="inlineStr"/>
+      <c r="M323" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N323" s="36" t="inlineStr"/>
+      <c r="O323" s="35" t="inlineStr"/>
+    </row>
+    <row r="324" ht="16" customHeight="1">
+      <c r="A324" s="28" t="inlineStr">
+        <is>
+          <t>a0a843314e26</t>
+        </is>
+      </c>
+      <c r="B324" s="28" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="C324" s="28" t="inlineStr">
+        <is>
+          <t>Senior Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D324" s="28" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E324" s="28" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F324" s="28" t="inlineStr">
+        <is>
+          <t>£49,785 – £49,785</t>
+        </is>
+      </c>
+      <c r="G324" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H324" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I324" s="28" t="n">
+        <v>40</v>
+      </c>
+      <c r="J324" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K324" s="31" t="inlineStr"/>
+      <c r="L324" s="31" t="inlineStr"/>
+      <c r="M324" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N324" s="32" t="inlineStr"/>
+      <c r="O324" s="31" t="inlineStr"/>
+    </row>
+    <row r="325" ht="16" customHeight="1">
+      <c r="A325" s="33" t="inlineStr">
+        <is>
+          <t>29e1aa18580e</t>
+        </is>
+      </c>
+      <c r="B325" s="33" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="C325" s="33" t="inlineStr">
+        <is>
+          <t>Senior Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D325" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E325" s="33" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F325" s="33" t="inlineStr">
+        <is>
+          <t>£50,937 – £50,937</t>
+        </is>
+      </c>
+      <c r="G325" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H325" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I325" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="J325" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K325" s="35" t="inlineStr"/>
+      <c r="L325" s="35" t="inlineStr"/>
+      <c r="M325" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N325" s="36" t="inlineStr"/>
+      <c r="O325" s="35" t="inlineStr"/>
+    </row>
+    <row r="326" ht="16" customHeight="1">
+      <c r="A326" s="28" t="inlineStr">
+        <is>
+          <t>d6b88be24890</t>
+        </is>
+      </c>
+      <c r="B326" s="28" t="inlineStr">
+        <is>
+          <t>25/02/2026</t>
+        </is>
+      </c>
+      <c r="C326" s="28" t="inlineStr">
+        <is>
+          <t>Senior Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D326" s="28" t="inlineStr">
+        <is>
+          <t>Stantec UK</t>
+        </is>
+      </c>
+      <c r="E326" s="28" t="inlineStr">
+        <is>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="F326" s="28" t="inlineStr">
+        <is>
+          <t>£52,250 – £52,250</t>
+        </is>
+      </c>
+      <c r="G326" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H326" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I326" s="28" t="n">
+        <v>40</v>
+      </c>
+      <c r="J326" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K326" s="31" t="inlineStr"/>
+      <c r="L326" s="31" t="inlineStr"/>
+      <c r="M326" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N326" s="32" t="inlineStr"/>
+      <c r="O326" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -19741,6 +20154,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J317" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J318" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J319" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J320" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J321" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J322" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J323" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J324" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J325" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J326" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -82,7 +82,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -179,6 +179,11 @@
         <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEFCBF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -234,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -338,6 +343,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="19" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -705,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O326"/>
+  <dimension ref="A1:O327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -20090,6 +20098,65 @@
       </c>
       <c r="N326" s="32" t="inlineStr"/>
       <c r="O326" s="31" t="inlineStr"/>
+    </row>
+    <row r="327" ht="16" customHeight="1">
+      <c r="A327" s="33" t="inlineStr">
+        <is>
+          <t>f5bf082bf4c1</t>
+        </is>
+      </c>
+      <c r="B327" s="33" t="inlineStr">
+        <is>
+          <t>26/02/2026</t>
+        </is>
+      </c>
+      <c r="C327" s="33" t="inlineStr">
+        <is>
+          <t>Assistant Engineer - Clean Water Modelling</t>
+        </is>
+      </c>
+      <c r="D327" s="33" t="inlineStr">
+        <is>
+          <t>WSP in the UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="E327" s="33" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F327" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G327" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H327" s="37" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="I327" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="J327" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K327" s="35" t="inlineStr"/>
+      <c r="L327" s="35" t="inlineStr"/>
+      <c r="M327" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N327" s="36" t="inlineStr"/>
+      <c r="O327" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -20161,6 +20228,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J324" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J325" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J326" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J327" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -713,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O327"/>
+  <dimension ref="A1:O329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -20157,6 +20157,124 @@
       </c>
       <c r="N327" s="36" t="inlineStr"/>
       <c r="O327" s="35" t="inlineStr"/>
+    </row>
+    <row r="328" ht="16" customHeight="1">
+      <c r="A328" s="28" t="inlineStr">
+        <is>
+          <t>27c9af08eff5</t>
+        </is>
+      </c>
+      <c r="B328" s="28" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C328" s="28" t="inlineStr">
+        <is>
+          <t>Water Infrastructure Manager, AWS EMEA Energy &amp; Water Team</t>
+        </is>
+      </c>
+      <c r="D328" s="28" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="E328" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F328" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G328" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H328" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I328" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="J328" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K328" s="31" t="inlineStr"/>
+      <c r="L328" s="31" t="inlineStr"/>
+      <c r="M328" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N328" s="32" t="inlineStr"/>
+      <c r="O328" s="31" t="inlineStr"/>
+    </row>
+    <row r="329" ht="16" customHeight="1">
+      <c r="A329" s="33" t="inlineStr">
+        <is>
+          <t>ead086e9abb7</t>
+        </is>
+      </c>
+      <c r="B329" s="33" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C329" s="33" t="inlineStr">
+        <is>
+          <t>Field Technician - Clean Water</t>
+        </is>
+      </c>
+      <c r="D329" s="33" t="inlineStr">
+        <is>
+          <t>Celnor Group</t>
+        </is>
+      </c>
+      <c r="E329" s="33" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F329" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G329" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H329" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I329" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="J329" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K329" s="35" t="inlineStr"/>
+      <c r="L329" s="35" t="inlineStr"/>
+      <c r="M329" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N329" s="36" t="inlineStr"/>
+      <c r="O329" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -20229,6 +20347,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J325" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J326" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J327" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J328" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J329" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -713,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O329"/>
+  <dimension ref="A1:O331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -20275,6 +20275,124 @@
       </c>
       <c r="N329" s="36" t="inlineStr"/>
       <c r="O329" s="35" t="inlineStr"/>
+    </row>
+    <row r="330" ht="16" customHeight="1">
+      <c r="A330" s="28" t="inlineStr">
+        <is>
+          <t>a44e36c0bad8</t>
+        </is>
+      </c>
+      <c r="B330" s="28" t="inlineStr">
+        <is>
+          <t>28/02/2026</t>
+        </is>
+      </c>
+      <c r="C330" s="28" t="inlineStr">
+        <is>
+          <t>Civil Engineer – UK Water/Wastewater – All Levels – Expression of Interest</t>
+        </is>
+      </c>
+      <c r="D330" s="28" t="inlineStr">
+        <is>
+          <t>Egis</t>
+        </is>
+      </c>
+      <c r="E330" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F330" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G330" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H330" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I330" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="J330" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K330" s="31" t="inlineStr"/>
+      <c r="L330" s="31" t="inlineStr"/>
+      <c r="M330" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N330" s="32" t="inlineStr"/>
+      <c r="O330" s="31" t="inlineStr"/>
+    </row>
+    <row r="331" ht="16" customHeight="1">
+      <c r="A331" s="33" t="inlineStr">
+        <is>
+          <t>19dd79f90989</t>
+        </is>
+      </c>
+      <c r="B331" s="33" t="inlineStr">
+        <is>
+          <t>28/02/2026</t>
+        </is>
+      </c>
+      <c r="C331" s="33" t="inlineStr">
+        <is>
+          <t>Civil Engineering Lead – UK Water/Wastewater (Technical Leadership &amp; Growth)</t>
+        </is>
+      </c>
+      <c r="D331" s="33" t="inlineStr">
+        <is>
+          <t>Egis</t>
+        </is>
+      </c>
+      <c r="E331" s="33" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F331" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G331" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H331" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I331" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="J331" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K331" s="35" t="inlineStr"/>
+      <c r="L331" s="35" t="inlineStr"/>
+      <c r="M331" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N331" s="36" t="inlineStr"/>
+      <c r="O331" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -20349,6 +20467,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J327" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J328" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J329" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J330" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J331" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -713,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O331"/>
+  <dimension ref="A1:O332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -20393,6 +20393,65 @@
       </c>
       <c r="N331" s="36" t="inlineStr"/>
       <c r="O331" s="35" t="inlineStr"/>
+    </row>
+    <row r="332" ht="16" customHeight="1">
+      <c r="A332" s="28" t="inlineStr">
+        <is>
+          <t>32f5f5f9afe1</t>
+        </is>
+      </c>
+      <c r="B332" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C332" s="28" t="inlineStr">
+        <is>
+          <t>Graduate Civil Engineer - Regulated Water (Bristol)</t>
+        </is>
+      </c>
+      <c r="D332" s="28" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E332" s="28" t="inlineStr">
+        <is>
+          <t>Bristol, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F332" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G332" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H332" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I332" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="J332" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K332" s="31" t="inlineStr"/>
+      <c r="L332" s="31" t="inlineStr"/>
+      <c r="M332" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N332" s="32" t="inlineStr"/>
+      <c r="O332" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -20469,6 +20528,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J329" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J330" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J331" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J332" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -713,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O332"/>
+  <dimension ref="A1:O377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -20452,6 +20452,2661 @@
       </c>
       <c r="N332" s="32" t="inlineStr"/>
       <c r="O332" s="31" t="inlineStr"/>
+    </row>
+    <row r="333" ht="16" customHeight="1">
+      <c r="A333" s="33" t="inlineStr">
+        <is>
+          <t>8ccb1d121c5f</t>
+        </is>
+      </c>
+      <c r="B333" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C333" s="33" t="inlineStr">
+        <is>
+          <t>Civil Engineer Water</t>
+        </is>
+      </c>
+      <c r="D333" s="33" t="inlineStr">
+        <is>
+          <t>Binnies UK Ltd</t>
+        </is>
+      </c>
+      <c r="E333" s="33" t="inlineStr">
+        <is>
+          <t>Earlswood, Redhill</t>
+        </is>
+      </c>
+      <c r="F333" s="33" t="inlineStr">
+        <is>
+          <t>£39,746 – £39,746</t>
+        </is>
+      </c>
+      <c r="G333" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H333" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I333" s="33" t="n">
+        <v>120</v>
+      </c>
+      <c r="J333" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K333" s="35" t="inlineStr"/>
+      <c r="L333" s="35" t="inlineStr"/>
+      <c r="M333" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N333" s="36" t="inlineStr"/>
+      <c r="O333" s="35" t="inlineStr"/>
+    </row>
+    <row r="334" ht="16" customHeight="1">
+      <c r="A334" s="28" t="inlineStr">
+        <is>
+          <t>b98dd7d25fd5</t>
+        </is>
+      </c>
+      <c r="B334" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C334" s="28" t="inlineStr">
+        <is>
+          <t>Civil Engineer Water</t>
+        </is>
+      </c>
+      <c r="D334" s="28" t="inlineStr">
+        <is>
+          <t>Binnies UK Ltd</t>
+        </is>
+      </c>
+      <c r="E334" s="28" t="inlineStr">
+        <is>
+          <t>Redhill, Surrey</t>
+        </is>
+      </c>
+      <c r="F334" s="28" t="inlineStr">
+        <is>
+          <t>£41,953 – £41,953</t>
+        </is>
+      </c>
+      <c r="G334" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H334" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I334" s="28" t="n">
+        <v>120</v>
+      </c>
+      <c r="J334" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K334" s="31" t="inlineStr"/>
+      <c r="L334" s="31" t="inlineStr"/>
+      <c r="M334" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N334" s="32" t="inlineStr"/>
+      <c r="O334" s="31" t="inlineStr"/>
+    </row>
+    <row r="335" ht="16" customHeight="1">
+      <c r="A335" s="33" t="inlineStr">
+        <is>
+          <t>988df77e9568</t>
+        </is>
+      </c>
+      <c r="B335" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C335" s="33" t="inlineStr">
+        <is>
+          <t>Irrigation Engineer (Water Systems Engineer)- KSA</t>
+        </is>
+      </c>
+      <c r="D335" s="33" t="inlineStr">
+        <is>
+          <t>Career Land Center</t>
+        </is>
+      </c>
+      <c r="E335" s="33" t="inlineStr">
+        <is>
+          <t>Monument, Central London</t>
+        </is>
+      </c>
+      <c r="F335" s="33" t="inlineStr">
+        <is>
+          <t>£39,363 – £39,363</t>
+        </is>
+      </c>
+      <c r="G335" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H335" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I335" s="33" t="n">
+        <v>105</v>
+      </c>
+      <c r="J335" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K335" s="35" t="inlineStr"/>
+      <c r="L335" s="35" t="inlineStr"/>
+      <c r="M335" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N335" s="36" t="inlineStr"/>
+      <c r="O335" s="35" t="inlineStr"/>
+    </row>
+    <row r="336" ht="16" customHeight="1">
+      <c r="A336" s="28" t="inlineStr">
+        <is>
+          <t>b56fa66dac18</t>
+        </is>
+      </c>
+      <c r="B336" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C336" s="28" t="inlineStr">
+        <is>
+          <t>Assistant Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D336" s="28" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment Ltd</t>
+        </is>
+      </c>
+      <c r="E336" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F336" s="28" t="inlineStr">
+        <is>
+          <t>£36,000 – £40,000</t>
+        </is>
+      </c>
+      <c r="G336" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H336" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I336" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="J336" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K336" s="31" t="inlineStr"/>
+      <c r="L336" s="31" t="inlineStr"/>
+      <c r="M336" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N336" s="32" t="inlineStr"/>
+      <c r="O336" s="31" t="inlineStr"/>
+    </row>
+    <row r="337" ht="16" customHeight="1">
+      <c r="A337" s="33" t="inlineStr">
+        <is>
+          <t>de1e25551388</t>
+        </is>
+      </c>
+      <c r="B337" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C337" s="33" t="inlineStr">
+        <is>
+          <t>Site Agent</t>
+        </is>
+      </c>
+      <c r="D337" s="33" t="inlineStr">
+        <is>
+          <t>Pinnacle Recruitment</t>
+        </is>
+      </c>
+      <c r="E337" s="33" t="inlineStr">
+        <is>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="F337" s="33" t="inlineStr">
+        <is>
+          <t>£55,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G337" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H337" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I337" s="33" t="n">
+        <v>80</v>
+      </c>
+      <c r="J337" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K337" s="35" t="inlineStr"/>
+      <c r="L337" s="35" t="inlineStr"/>
+      <c r="M337" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N337" s="36" t="inlineStr"/>
+      <c r="O337" s="35" t="inlineStr"/>
+    </row>
+    <row r="338" ht="16" customHeight="1">
+      <c r="A338" s="28" t="inlineStr">
+        <is>
+          <t>ff4c5d4ea86c</t>
+        </is>
+      </c>
+      <c r="B338" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C338" s="28" t="inlineStr">
+        <is>
+          <t>Process Design Engineer</t>
+        </is>
+      </c>
+      <c r="D338" s="28" t="inlineStr">
+        <is>
+          <t>J Browne Construction</t>
+        </is>
+      </c>
+      <c r="E338" s="28" t="inlineStr">
+        <is>
+          <t>Shendish, Hemel Hempstead</t>
+        </is>
+      </c>
+      <c r="F338" s="28" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G338" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H338" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I338" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J338" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K338" s="31" t="inlineStr"/>
+      <c r="L338" s="31" t="inlineStr"/>
+      <c r="M338" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N338" s="32" t="inlineStr"/>
+      <c r="O338" s="31" t="inlineStr"/>
+    </row>
+    <row r="339" ht="16" customHeight="1">
+      <c r="A339" s="33" t="inlineStr">
+        <is>
+          <t>f305eb4cb92f</t>
+        </is>
+      </c>
+      <c r="B339" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C339" s="33" t="inlineStr">
+        <is>
+          <t>Process Design Engineer</t>
+        </is>
+      </c>
+      <c r="D339" s="33" t="inlineStr">
+        <is>
+          <t>J Browne Construction Company Ltd</t>
+        </is>
+      </c>
+      <c r="E339" s="33" t="inlineStr">
+        <is>
+          <t>Shendish, Hemel Hempstead</t>
+        </is>
+      </c>
+      <c r="F339" s="33" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G339" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H339" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I339" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="J339" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K339" s="35" t="inlineStr"/>
+      <c r="L339" s="35" t="inlineStr"/>
+      <c r="M339" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N339" s="36" t="inlineStr"/>
+      <c r="O339" s="35" t="inlineStr"/>
+    </row>
+    <row r="340" ht="16" customHeight="1">
+      <c r="A340" s="28" t="inlineStr">
+        <is>
+          <t>48162a467bb3</t>
+        </is>
+      </c>
+      <c r="B340" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C340" s="28" t="inlineStr">
+        <is>
+          <t>Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D340" s="28" t="inlineStr">
+        <is>
+          <t>Dc Solutions Services</t>
+        </is>
+      </c>
+      <c r="E340" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F340" s="28" t="inlineStr">
+        <is>
+          <t>£36,994 – £36,994</t>
+        </is>
+      </c>
+      <c r="G340" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H340" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I340" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J340" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K340" s="31" t="inlineStr"/>
+      <c r="L340" s="31" t="inlineStr"/>
+      <c r="M340" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N340" s="32" t="inlineStr"/>
+      <c r="O340" s="31" t="inlineStr"/>
+    </row>
+    <row r="341" ht="16" customHeight="1">
+      <c r="A341" s="33" t="inlineStr">
+        <is>
+          <t>3a8f91affedc</t>
+        </is>
+      </c>
+      <c r="B341" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C341" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer</t>
+        </is>
+      </c>
+      <c r="D341" s="33" t="inlineStr">
+        <is>
+          <t>Murray McIntosh Recruitment Consultancy</t>
+        </is>
+      </c>
+      <c r="E341" s="33" t="inlineStr">
+        <is>
+          <t>Fleet, Hampshire</t>
+        </is>
+      </c>
+      <c r="F341" s="33" t="inlineStr">
+        <is>
+          <t>£50,000 – £65,000</t>
+        </is>
+      </c>
+      <c r="G341" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H341" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I341" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="J341" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K341" s="35" t="inlineStr"/>
+      <c r="L341" s="35" t="inlineStr"/>
+      <c r="M341" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N341" s="36" t="inlineStr"/>
+      <c r="O341" s="35" t="inlineStr"/>
+    </row>
+    <row r="342" ht="16" customHeight="1">
+      <c r="A342" s="28" t="inlineStr">
+        <is>
+          <t>9afa89f2389c</t>
+        </is>
+      </c>
+      <c r="B342" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C342" s="28" t="inlineStr">
+        <is>
+          <t>Graduate Urban Drainage Modeller - 2026 (Reading)</t>
+        </is>
+      </c>
+      <c r="D342" s="28" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E342" s="28" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F342" s="28" t="inlineStr">
+        <is>
+          <t>£41,041 – £41,041</t>
+        </is>
+      </c>
+      <c r="G342" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H342" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I342" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J342" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K342" s="31" t="inlineStr"/>
+      <c r="L342" s="31" t="inlineStr"/>
+      <c r="M342" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N342" s="32" t="inlineStr"/>
+      <c r="O342" s="31" t="inlineStr"/>
+    </row>
+    <row r="343" ht="16" customHeight="1">
+      <c r="A343" s="33" t="inlineStr">
+        <is>
+          <t>6c41481ea907</t>
+        </is>
+      </c>
+      <c r="B343" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C343" s="33" t="inlineStr">
+        <is>
+          <t>Graduate Urban Drainage Modeller - 2026 (High Wycombe)</t>
+        </is>
+      </c>
+      <c r="D343" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E343" s="33" t="inlineStr">
+        <is>
+          <t>High Wycombe, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="F343" s="33" t="inlineStr">
+        <is>
+          <t>£41,409 – £41,409</t>
+        </is>
+      </c>
+      <c r="G343" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H343" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I343" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="J343" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K343" s="35" t="inlineStr"/>
+      <c r="L343" s="35" t="inlineStr"/>
+      <c r="M343" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N343" s="36" t="inlineStr"/>
+      <c r="O343" s="35" t="inlineStr"/>
+    </row>
+    <row r="344" ht="16" customHeight="1">
+      <c r="A344" s="28" t="inlineStr">
+        <is>
+          <t>25fb668c615b</t>
+        </is>
+      </c>
+      <c r="B344" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C344" s="28" t="inlineStr">
+        <is>
+          <t>Graduate Urban Drainage Modeller - 2026 (High Wycombe)</t>
+        </is>
+      </c>
+      <c r="D344" s="28" t="inlineStr">
+        <is>
+          <t>Stantec UK</t>
+        </is>
+      </c>
+      <c r="E344" s="28" t="inlineStr">
+        <is>
+          <t>Hughenden, High Wycombe</t>
+        </is>
+      </c>
+      <c r="F344" s="28" t="inlineStr">
+        <is>
+          <t>£37,839 – £37,839</t>
+        </is>
+      </c>
+      <c r="G344" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H344" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I344" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J344" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K344" s="31" t="inlineStr"/>
+      <c r="L344" s="31" t="inlineStr"/>
+      <c r="M344" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N344" s="32" t="inlineStr"/>
+      <c r="O344" s="31" t="inlineStr"/>
+    </row>
+    <row r="345" ht="16" customHeight="1">
+      <c r="A345" s="33" t="inlineStr">
+        <is>
+          <t>a3ecf2cde781</t>
+        </is>
+      </c>
+      <c r="B345" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C345" s="33" t="inlineStr">
+        <is>
+          <t>Installation operative</t>
+        </is>
+      </c>
+      <c r="D345" s="33" t="inlineStr">
+        <is>
+          <t>Kiota Recruitment</t>
+        </is>
+      </c>
+      <c r="E345" s="33" t="inlineStr">
+        <is>
+          <t>Binfield, Bracknell</t>
+        </is>
+      </c>
+      <c r="F345" s="33" t="inlineStr">
+        <is>
+          <t>£35,000 – £40,000</t>
+        </is>
+      </c>
+      <c r="G345" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H345" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I345" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="J345" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K345" s="35" t="inlineStr"/>
+      <c r="L345" s="35" t="inlineStr"/>
+      <c r="M345" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N345" s="36" t="inlineStr"/>
+      <c r="O345" s="35" t="inlineStr"/>
+    </row>
+    <row r="346" ht="16" customHeight="1">
+      <c r="A346" s="28" t="inlineStr">
+        <is>
+          <t>5f62d3dfd0a4</t>
+        </is>
+      </c>
+      <c r="B346" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C346" s="28" t="inlineStr">
+        <is>
+          <t>Site Agent</t>
+        </is>
+      </c>
+      <c r="D346" s="28" t="inlineStr">
+        <is>
+          <t>Pinnacle Recruitment</t>
+        </is>
+      </c>
+      <c r="E346" s="28" t="inlineStr">
+        <is>
+          <t>Waltham Forest, East London</t>
+        </is>
+      </c>
+      <c r="F346" s="28" t="inlineStr">
+        <is>
+          <t>£55,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G346" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H346" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I346" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J346" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K346" s="31" t="inlineStr"/>
+      <c r="L346" s="31" t="inlineStr"/>
+      <c r="M346" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N346" s="32" t="inlineStr"/>
+      <c r="O346" s="31" t="inlineStr"/>
+    </row>
+    <row r="347" ht="16" customHeight="1">
+      <c r="A347" s="33" t="inlineStr">
+        <is>
+          <t>286784ca7f2e</t>
+        </is>
+      </c>
+      <c r="B347" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C347" s="33" t="inlineStr">
+        <is>
+          <t>Mains Replacement Agent</t>
+        </is>
+      </c>
+      <c r="D347" s="33" t="inlineStr">
+        <is>
+          <t>J Browne Construction Company Ltd</t>
+        </is>
+      </c>
+      <c r="E347" s="33" t="inlineStr">
+        <is>
+          <t>Clapton, East London</t>
+        </is>
+      </c>
+      <c r="F347" s="33" t="inlineStr">
+        <is>
+          <t>£50,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G347" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H347" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I347" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="J347" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K347" s="35" t="inlineStr"/>
+      <c r="L347" s="35" t="inlineStr"/>
+      <c r="M347" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N347" s="36" t="inlineStr"/>
+      <c r="O347" s="35" t="inlineStr"/>
+    </row>
+    <row r="348" ht="16" customHeight="1">
+      <c r="A348" s="28" t="inlineStr">
+        <is>
+          <t>63c220611019</t>
+        </is>
+      </c>
+      <c r="B348" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C348" s="28" t="inlineStr">
+        <is>
+          <t>Mains Replacement Agent</t>
+        </is>
+      </c>
+      <c r="D348" s="28" t="inlineStr">
+        <is>
+          <t>Browne Construction</t>
+        </is>
+      </c>
+      <c r="E348" s="28" t="inlineStr">
+        <is>
+          <t>Lea Bridge, East London</t>
+        </is>
+      </c>
+      <c r="F348" s="28" t="inlineStr">
+        <is>
+          <t>£50,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G348" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H348" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I348" s="28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J348" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K348" s="31" t="inlineStr"/>
+      <c r="L348" s="31" t="inlineStr"/>
+      <c r="M348" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N348" s="32" t="inlineStr"/>
+      <c r="O348" s="31" t="inlineStr"/>
+    </row>
+    <row r="349" ht="16" customHeight="1">
+      <c r="A349" s="33" t="inlineStr">
+        <is>
+          <t>126917020101</t>
+        </is>
+      </c>
+      <c r="B349" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C349" s="33" t="inlineStr">
+        <is>
+          <t>Career Opportunities in the Water Sector - Brighton &amp; The South East | Expression of Interest</t>
+        </is>
+      </c>
+      <c r="D349" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E349" s="33" t="inlineStr">
+        <is>
+          <t>Kings Hill, West Malling</t>
+        </is>
+      </c>
+      <c r="F349" s="33" t="inlineStr">
+        <is>
+          <t>£48,677 – £48,677</t>
+        </is>
+      </c>
+      <c r="G349" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H349" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I349" s="33" t="n">
+        <v>55</v>
+      </c>
+      <c r="J349" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K349" s="35" t="inlineStr"/>
+      <c r="L349" s="35" t="inlineStr"/>
+      <c r="M349" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N349" s="36" t="inlineStr"/>
+      <c r="O349" s="35" t="inlineStr"/>
+    </row>
+    <row r="350" ht="16" customHeight="1">
+      <c r="A350" s="28" t="inlineStr">
+        <is>
+          <t>14d95f9c23b5</t>
+        </is>
+      </c>
+      <c r="B350" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C350" s="28" t="inlineStr">
+        <is>
+          <t>Drainage Engineer</t>
+        </is>
+      </c>
+      <c r="D350" s="28" t="inlineStr">
+        <is>
+          <t>Clear Rod Drainage Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="E350" s="28" t="inlineStr">
+        <is>
+          <t>Sidcup, Kent</t>
+        </is>
+      </c>
+      <c r="F350" s="28" t="inlineStr">
+        <is>
+          <t>£35,000 – £35,000</t>
+        </is>
+      </c>
+      <c r="G350" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H350" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I350" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J350" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K350" s="31" t="inlineStr"/>
+      <c r="L350" s="31" t="inlineStr"/>
+      <c r="M350" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N350" s="32" t="inlineStr"/>
+      <c r="O350" s="31" t="inlineStr"/>
+    </row>
+    <row r="351" ht="16" customHeight="1">
+      <c r="A351" s="33" t="inlineStr">
+        <is>
+          <t>6708cfa62590</t>
+        </is>
+      </c>
+      <c r="B351" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C351" s="33" t="inlineStr">
+        <is>
+          <t>Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D351" s="33" t="inlineStr">
+        <is>
+          <t>Anglian Water Services</t>
+        </is>
+      </c>
+      <c r="E351" s="33" t="inlineStr">
+        <is>
+          <t>Selby, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F351" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G351" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H351" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I351" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="J351" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K351" s="35" t="inlineStr"/>
+      <c r="L351" s="35" t="inlineStr"/>
+      <c r="M351" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N351" s="36" t="inlineStr"/>
+      <c r="O351" s="35" t="inlineStr"/>
+    </row>
+    <row r="352" ht="16" customHeight="1">
+      <c r="A352" s="28" t="inlineStr">
+        <is>
+          <t>8e3fdf66fb8e</t>
+        </is>
+      </c>
+      <c r="B352" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C352" s="28" t="inlineStr">
+        <is>
+          <t>Health, Safety &amp; Environmental (SHE) Advisor</t>
+        </is>
+      </c>
+      <c r="D352" s="28" t="inlineStr">
+        <is>
+          <t>RSK Group</t>
+        </is>
+      </c>
+      <c r="E352" s="28" t="inlineStr">
+        <is>
+          <t>Earlswood, Redhill</t>
+        </is>
+      </c>
+      <c r="F352" s="28" t="inlineStr">
+        <is>
+          <t>£43,512 – £43,512</t>
+        </is>
+      </c>
+      <c r="G352" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H352" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I352" s="28" t="n">
+        <v>40</v>
+      </c>
+      <c r="J352" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K352" s="31" t="inlineStr"/>
+      <c r="L352" s="31" t="inlineStr"/>
+      <c r="M352" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N352" s="32" t="inlineStr"/>
+      <c r="O352" s="31" t="inlineStr"/>
+    </row>
+    <row r="353" ht="16" customHeight="1">
+      <c r="A353" s="33" t="inlineStr">
+        <is>
+          <t>b1905e913478</t>
+        </is>
+      </c>
+      <c r="B353" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C353" s="33" t="inlineStr">
+        <is>
+          <t>Health and Safety Advisor</t>
+        </is>
+      </c>
+      <c r="D353" s="33" t="inlineStr">
+        <is>
+          <t>THE CLANCY GROUP</t>
+        </is>
+      </c>
+      <c r="E353" s="33" t="inlineStr">
+        <is>
+          <t>Sawbridgeworth, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="F353" s="33" t="inlineStr">
+        <is>
+          <t>£45,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G353" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H353" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I353" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="J353" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K353" s="35" t="inlineStr"/>
+      <c r="L353" s="35" t="inlineStr"/>
+      <c r="M353" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N353" s="36" t="inlineStr"/>
+      <c r="O353" s="35" t="inlineStr"/>
+    </row>
+    <row r="354" ht="16" customHeight="1">
+      <c r="A354" s="28" t="inlineStr">
+        <is>
+          <t>d3991a2404ba</t>
+        </is>
+      </c>
+      <c r="B354" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C354" s="28" t="inlineStr">
+        <is>
+          <t>Advocacy and Parliamentary Affairs Officer</t>
+        </is>
+      </c>
+      <c r="D354" s="28" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E354" s="28" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="F354" s="28" t="inlineStr">
+        <is>
+          <t>See listing</t>
+        </is>
+      </c>
+      <c r="G354" s="28" t="inlineStr">
+        <is>
+          <t>Environment Jobs</t>
+        </is>
+      </c>
+      <c r="H354" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I354" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="J354" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K354" s="31" t="inlineStr"/>
+      <c r="L354" s="31" t="inlineStr"/>
+      <c r="M354" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N354" s="32" t="inlineStr"/>
+      <c r="O354" s="31" t="inlineStr"/>
+    </row>
+    <row r="355" ht="16" customHeight="1">
+      <c r="A355" s="33" t="inlineStr">
+        <is>
+          <t>a703125d5215</t>
+        </is>
+      </c>
+      <c r="B355" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C355" s="33" t="inlineStr">
+        <is>
+          <t>Design Engineer</t>
+        </is>
+      </c>
+      <c r="D355" s="33" t="inlineStr">
+        <is>
+          <t>E-Solutions</t>
+        </is>
+      </c>
+      <c r="E355" s="33" t="inlineStr">
+        <is>
+          <t>Wales, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F355" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G355" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H355" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I355" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="J355" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K355" s="35" t="inlineStr"/>
+      <c r="L355" s="35" t="inlineStr"/>
+      <c r="M355" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N355" s="36" t="inlineStr"/>
+      <c r="O355" s="35" t="inlineStr"/>
+    </row>
+    <row r="356" ht="16" customHeight="1">
+      <c r="A356" s="28" t="inlineStr">
+        <is>
+          <t>e4d8ae43b42f</t>
+        </is>
+      </c>
+      <c r="B356" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C356" s="28" t="inlineStr">
+        <is>
+          <t>Multiskilled Engineer</t>
+        </is>
+      </c>
+      <c r="D356" s="28" t="inlineStr">
+        <is>
+          <t>Styrene Packaging &amp; Insulation Ltd</t>
+        </is>
+      </c>
+      <c r="E356" s="28" t="inlineStr">
+        <is>
+          <t>Bradford, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F356" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G356" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H356" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I356" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="J356" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K356" s="31" t="inlineStr"/>
+      <c r="L356" s="31" t="inlineStr"/>
+      <c r="M356" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N356" s="32" t="inlineStr"/>
+      <c r="O356" s="31" t="inlineStr"/>
+    </row>
+    <row r="357" ht="16" customHeight="1">
+      <c r="A357" s="33" t="inlineStr">
+        <is>
+          <t>c6f56742e13e</t>
+        </is>
+      </c>
+      <c r="B357" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C357" s="33" t="inlineStr">
+        <is>
+          <t>Section Engineer</t>
+        </is>
+      </c>
+      <c r="D357" s="33" t="inlineStr">
+        <is>
+          <t>BAM UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="E357" s="33" t="inlineStr">
+        <is>
+          <t>Plymouth, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F357" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G357" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H357" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I357" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="J357" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K357" s="35" t="inlineStr"/>
+      <c r="L357" s="35" t="inlineStr"/>
+      <c r="M357" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N357" s="36" t="inlineStr"/>
+      <c r="O357" s="35" t="inlineStr"/>
+    </row>
+    <row r="358" ht="16" customHeight="1">
+      <c r="A358" s="28" t="inlineStr">
+        <is>
+          <t>ef306be90e51</t>
+        </is>
+      </c>
+      <c r="B358" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C358" s="28" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="D358" s="28" t="inlineStr">
+        <is>
+          <t>Persimmon Homes</t>
+        </is>
+      </c>
+      <c r="E358" s="28" t="inlineStr">
+        <is>
+          <t>North Yorkshire, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F358" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G358" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H358" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I358" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="J358" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K358" s="31" t="inlineStr"/>
+      <c r="L358" s="31" t="inlineStr"/>
+      <c r="M358" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N358" s="32" t="inlineStr"/>
+      <c r="O358" s="31" t="inlineStr"/>
+    </row>
+    <row r="359" ht="16" customHeight="1">
+      <c r="A359" s="33" t="inlineStr">
+        <is>
+          <t>24bbe4029ad1</t>
+        </is>
+      </c>
+      <c r="B359" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C359" s="33" t="inlineStr">
+        <is>
+          <t>Graduate Maritime Engineer (5647)</t>
+        </is>
+      </c>
+      <c r="D359" s="33" t="inlineStr">
+        <is>
+          <t>Arup</t>
+        </is>
+      </c>
+      <c r="E359" s="33" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F359" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G359" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H359" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I359" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="J359" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K359" s="35" t="inlineStr"/>
+      <c r="L359" s="35" t="inlineStr"/>
+      <c r="M359" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N359" s="36" t="inlineStr"/>
+      <c r="O359" s="35" t="inlineStr"/>
+    </row>
+    <row r="360" ht="16" customHeight="1">
+      <c r="A360" s="28" t="inlineStr">
+        <is>
+          <t>5f1dcec245a1</t>
+        </is>
+      </c>
+      <c r="B360" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C360" s="28" t="inlineStr">
+        <is>
+          <t>Network Engineer - FinTech - £80,000-£120,000 + Bonus</t>
+        </is>
+      </c>
+      <c r="D360" s="28" t="inlineStr">
+        <is>
+          <t>Hunter Bond</t>
+        </is>
+      </c>
+      <c r="E360" s="28" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F360" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G360" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H360" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I360" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="J360" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K360" s="31" t="inlineStr"/>
+      <c r="L360" s="31" t="inlineStr"/>
+      <c r="M360" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N360" s="32" t="inlineStr"/>
+      <c r="O360" s="31" t="inlineStr"/>
+    </row>
+    <row r="361" ht="16" customHeight="1">
+      <c r="A361" s="33" t="inlineStr">
+        <is>
+          <t>71ea56a0cb1f</t>
+        </is>
+      </c>
+      <c r="B361" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C361" s="33" t="inlineStr">
+        <is>
+          <t>Low Voltage Systems Engineer</t>
+        </is>
+      </c>
+      <c r="D361" s="33" t="inlineStr">
+        <is>
+          <t>Advanced Resource Managers</t>
+        </is>
+      </c>
+      <c r="E361" s="33" t="inlineStr">
+        <is>
+          <t>Crewe, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F361" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G361" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H361" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I361" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="J361" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K361" s="35" t="inlineStr"/>
+      <c r="L361" s="35" t="inlineStr"/>
+      <c r="M361" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N361" s="36" t="inlineStr"/>
+      <c r="O361" s="35" t="inlineStr"/>
+    </row>
+    <row r="362" ht="16" customHeight="1">
+      <c r="A362" s="28" t="inlineStr">
+        <is>
+          <t>b01613ee6bb0</t>
+        </is>
+      </c>
+      <c r="B362" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C362" s="28" t="inlineStr">
+        <is>
+          <t>Network Engineer</t>
+        </is>
+      </c>
+      <c r="D362" s="28" t="inlineStr">
+        <is>
+          <t>hackajob</t>
+        </is>
+      </c>
+      <c r="E362" s="28" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F362" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G362" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H362" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I362" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="J362" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K362" s="31" t="inlineStr"/>
+      <c r="L362" s="31" t="inlineStr"/>
+      <c r="M362" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N362" s="32" t="inlineStr"/>
+      <c r="O362" s="31" t="inlineStr"/>
+    </row>
+    <row r="363" ht="16" customHeight="1">
+      <c r="A363" s="33" t="inlineStr">
+        <is>
+          <t>46fea5802e6b</t>
+        </is>
+      </c>
+      <c r="B363" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C363" s="33" t="inlineStr">
+        <is>
+          <t>Senior InfoSec / Network Engineer (NIST / CIS) - £90k</t>
+        </is>
+      </c>
+      <c r="D363" s="33" t="inlineStr">
+        <is>
+          <t>Hawksworth</t>
+        </is>
+      </c>
+      <c r="E363" s="33" t="inlineStr">
+        <is>
+          <t>Surrey, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F363" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G363" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H363" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I363" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="J363" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K363" s="35" t="inlineStr"/>
+      <c r="L363" s="35" t="inlineStr"/>
+      <c r="M363" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N363" s="36" t="inlineStr"/>
+      <c r="O363" s="35" t="inlineStr"/>
+    </row>
+    <row r="364" ht="16" customHeight="1">
+      <c r="A364" s="28" t="inlineStr">
+        <is>
+          <t>862bc6b192d4</t>
+        </is>
+      </c>
+      <c r="B364" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C364" s="28" t="inlineStr">
+        <is>
+          <t>Network Engineer - Trading - £100,000-£180,000 + Bonus</t>
+        </is>
+      </c>
+      <c r="D364" s="28" t="inlineStr">
+        <is>
+          <t>Jobs via eFinancialCareers</t>
+        </is>
+      </c>
+      <c r="E364" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F364" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G364" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H364" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I364" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="J364" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K364" s="31" t="inlineStr"/>
+      <c r="L364" s="31" t="inlineStr"/>
+      <c r="M364" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N364" s="32" t="inlineStr"/>
+      <c r="O364" s="31" t="inlineStr"/>
+    </row>
+    <row r="365" ht="16" customHeight="1">
+      <c r="A365" s="33" t="inlineStr">
+        <is>
+          <t>af86f2e091fa</t>
+        </is>
+      </c>
+      <c r="B365" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C365" s="33" t="inlineStr">
+        <is>
+          <t>Field Manager</t>
+        </is>
+      </c>
+      <c r="D365" s="33" t="inlineStr">
+        <is>
+          <t>Lanes Group</t>
+        </is>
+      </c>
+      <c r="E365" s="33" t="inlineStr">
+        <is>
+          <t>Widford, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F365" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G365" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H365" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I365" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="J365" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K365" s="35" t="inlineStr"/>
+      <c r="L365" s="35" t="inlineStr"/>
+      <c r="M365" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N365" s="36" t="inlineStr"/>
+      <c r="O365" s="35" t="inlineStr"/>
+    </row>
+    <row r="366" ht="16" customHeight="1">
+      <c r="A366" s="28" t="inlineStr">
+        <is>
+          <t>535964c714ff</t>
+        </is>
+      </c>
+      <c r="B366" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C366" s="28" t="inlineStr">
+        <is>
+          <t>Design Manager - Water Sector</t>
+        </is>
+      </c>
+      <c r="D366" s="28" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E366" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F366" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G366" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H366" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I366" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="J366" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K366" s="31" t="inlineStr"/>
+      <c r="L366" s="31" t="inlineStr"/>
+      <c r="M366" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N366" s="32" t="inlineStr"/>
+      <c r="O366" s="31" t="inlineStr"/>
+    </row>
+    <row r="367" ht="16" customHeight="1">
+      <c r="A367" s="33" t="inlineStr">
+        <is>
+          <t>c43a5a9f6da8</t>
+        </is>
+      </c>
+      <c r="B367" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C367" s="33" t="inlineStr">
+        <is>
+          <t>Senior Economics Consultant - Advisory</t>
+        </is>
+      </c>
+      <c r="D367" s="33" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E367" s="33" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F367" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G367" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H367" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I367" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="J367" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K367" s="35" t="inlineStr"/>
+      <c r="L367" s="35" t="inlineStr"/>
+      <c r="M367" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N367" s="36" t="inlineStr"/>
+      <c r="O367" s="35" t="inlineStr"/>
+    </row>
+    <row r="368" ht="16" customHeight="1">
+      <c r="A368" s="28" t="inlineStr">
+        <is>
+          <t>3486e6ec3ddf</t>
+        </is>
+      </c>
+      <c r="B368" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C368" s="28" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="D368" s="28" t="inlineStr">
+        <is>
+          <t>VolkerWessels UK</t>
+        </is>
+      </c>
+      <c r="E368" s="28" t="inlineStr">
+        <is>
+          <t>Brentwood, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F368" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G368" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H368" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I368" s="28" t="n">
+        <v>35</v>
+      </c>
+      <c r="J368" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K368" s="31" t="inlineStr"/>
+      <c r="L368" s="31" t="inlineStr"/>
+      <c r="M368" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N368" s="32" t="inlineStr"/>
+      <c r="O368" s="31" t="inlineStr"/>
+    </row>
+    <row r="369" ht="16" customHeight="1">
+      <c r="A369" s="33" t="inlineStr">
+        <is>
+          <t>6a08705e18d2</t>
+        </is>
+      </c>
+      <c r="B369" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C369" s="33" t="inlineStr">
+        <is>
+          <t>Electrical/ EICA Engineer – UK Water/Wastewater – All Levels – Expression of Interest</t>
+        </is>
+      </c>
+      <c r="D369" s="33" t="inlineStr">
+        <is>
+          <t>Egis Group</t>
+        </is>
+      </c>
+      <c r="E369" s="33" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F369" s="33" t="inlineStr">
+        <is>
+          <t>£52,715 – £52,715</t>
+        </is>
+      </c>
+      <c r="G369" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H369" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I369" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="J369" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K369" s="35" t="inlineStr"/>
+      <c r="L369" s="35" t="inlineStr"/>
+      <c r="M369" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N369" s="36" t="inlineStr"/>
+      <c r="O369" s="35" t="inlineStr"/>
+    </row>
+    <row r="370" ht="16" customHeight="1">
+      <c r="A370" s="28" t="inlineStr">
+        <is>
+          <t>95afd6422474</t>
+        </is>
+      </c>
+      <c r="B370" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C370" s="28" t="inlineStr">
+        <is>
+          <t>Senior Process Design Engineer</t>
+        </is>
+      </c>
+      <c r="D370" s="28" t="inlineStr">
+        <is>
+          <t>J Browne Construction Company Ltd</t>
+        </is>
+      </c>
+      <c r="E370" s="28" t="inlineStr">
+        <is>
+          <t>Shendish, Hemel Hempstead</t>
+        </is>
+      </c>
+      <c r="F370" s="28" t="inlineStr">
+        <is>
+          <t>£50,000 – £60,000</t>
+        </is>
+      </c>
+      <c r="G370" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H370" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I370" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="J370" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K370" s="31" t="inlineStr"/>
+      <c r="L370" s="31" t="inlineStr"/>
+      <c r="M370" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N370" s="32" t="inlineStr"/>
+      <c r="O370" s="31" t="inlineStr"/>
+    </row>
+    <row r="371" ht="16" customHeight="1">
+      <c r="A371" s="33" t="inlineStr">
+        <is>
+          <t>dd0af96b5474</t>
+        </is>
+      </c>
+      <c r="B371" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C371" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer</t>
+        </is>
+      </c>
+      <c r="D371" s="33" t="inlineStr">
+        <is>
+          <t>J Browne Construction Company Ltd</t>
+        </is>
+      </c>
+      <c r="E371" s="33" t="inlineStr">
+        <is>
+          <t>Shendish, Hemel Hempstead</t>
+        </is>
+      </c>
+      <c r="F371" s="33" t="inlineStr">
+        <is>
+          <t>£40,000 – £60,000</t>
+        </is>
+      </c>
+      <c r="G371" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H371" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I371" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="J371" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K371" s="35" t="inlineStr"/>
+      <c r="L371" s="35" t="inlineStr"/>
+      <c r="M371" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N371" s="36" t="inlineStr"/>
+      <c r="O371" s="35" t="inlineStr"/>
+    </row>
+    <row r="372" ht="16" customHeight="1">
+      <c r="A372" s="28" t="inlineStr">
+        <is>
+          <t>6fc94359cdd7</t>
+        </is>
+      </c>
+      <c r="B372" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C372" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer</t>
+        </is>
+      </c>
+      <c r="D372" s="28" t="inlineStr">
+        <is>
+          <t>Browne Construction</t>
+        </is>
+      </c>
+      <c r="E372" s="28" t="inlineStr">
+        <is>
+          <t>Shendish, Hemel Hempstead</t>
+        </is>
+      </c>
+      <c r="F372" s="28" t="inlineStr">
+        <is>
+          <t>£40,000 – £60,000</t>
+        </is>
+      </c>
+      <c r="G372" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H372" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I372" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="J372" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K372" s="31" t="inlineStr"/>
+      <c r="L372" s="31" t="inlineStr"/>
+      <c r="M372" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N372" s="32" t="inlineStr"/>
+      <c r="O372" s="31" t="inlineStr"/>
+    </row>
+    <row r="373" ht="16" customHeight="1">
+      <c r="A373" s="33" t="inlineStr">
+        <is>
+          <t>7b870fae6592</t>
+        </is>
+      </c>
+      <c r="B373" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C373" s="33" t="inlineStr">
+        <is>
+          <t>Project Engineer</t>
+        </is>
+      </c>
+      <c r="D373" s="33" t="inlineStr">
+        <is>
+          <t>Fortis Recruitment Solutions</t>
+        </is>
+      </c>
+      <c r="E373" s="33" t="inlineStr">
+        <is>
+          <t>Artington, Guildford</t>
+        </is>
+      </c>
+      <c r="F373" s="33" t="inlineStr">
+        <is>
+          <t>£45,000 – £70,000</t>
+        </is>
+      </c>
+      <c r="G373" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H373" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I373" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="J373" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K373" s="35" t="inlineStr"/>
+      <c r="L373" s="35" t="inlineStr"/>
+      <c r="M373" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N373" s="36" t="inlineStr"/>
+      <c r="O373" s="35" t="inlineStr"/>
+    </row>
+    <row r="374" ht="16" customHeight="1">
+      <c r="A374" s="28" t="inlineStr">
+        <is>
+          <t>81af3cfdec0c</t>
+        </is>
+      </c>
+      <c r="B374" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C374" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer</t>
+        </is>
+      </c>
+      <c r="D374" s="28" t="inlineStr">
+        <is>
+          <t>Fortis Recruitment Solutions</t>
+        </is>
+      </c>
+      <c r="E374" s="28" t="inlineStr">
+        <is>
+          <t>Artington, Guildford</t>
+        </is>
+      </c>
+      <c r="F374" s="28" t="inlineStr">
+        <is>
+          <t>£45,000 – £60,000</t>
+        </is>
+      </c>
+      <c r="G374" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H374" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I374" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="J374" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K374" s="31" t="inlineStr"/>
+      <c r="L374" s="31" t="inlineStr"/>
+      <c r="M374" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N374" s="32" t="inlineStr"/>
+      <c r="O374" s="31" t="inlineStr"/>
+    </row>
+    <row r="375" ht="16" customHeight="1">
+      <c r="A375" s="33" t="inlineStr">
+        <is>
+          <t>f5a5b0b0aa79</t>
+        </is>
+      </c>
+      <c r="B375" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C375" s="33" t="inlineStr">
+        <is>
+          <t>Water Hygiene Engineer</t>
+        </is>
+      </c>
+      <c r="D375" s="33" t="inlineStr">
+        <is>
+          <t>Example Recruitment</t>
+        </is>
+      </c>
+      <c r="E375" s="33" t="inlineStr">
+        <is>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="F375" s="33" t="inlineStr">
+        <is>
+          <t>£30,000 – £35,000</t>
+        </is>
+      </c>
+      <c r="G375" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H375" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I375" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="J375" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K375" s="35" t="inlineStr"/>
+      <c r="L375" s="35" t="inlineStr"/>
+      <c r="M375" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N375" s="36" t="inlineStr"/>
+      <c r="O375" s="35" t="inlineStr"/>
+    </row>
+    <row r="376" ht="16" customHeight="1">
+      <c r="A376" s="28" t="inlineStr">
+        <is>
+          <t>3f070f26b47e</t>
+        </is>
+      </c>
+      <c r="B376" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C376" s="28" t="inlineStr">
+        <is>
+          <t>Project engineer</t>
+        </is>
+      </c>
+      <c r="D376" s="28" t="inlineStr">
+        <is>
+          <t>Dc Solutions Services</t>
+        </is>
+      </c>
+      <c r="E376" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F376" s="28" t="inlineStr">
+        <is>
+          <t>£40,443 – £40,443</t>
+        </is>
+      </c>
+      <c r="G376" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H376" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I376" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="J376" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K376" s="31" t="inlineStr"/>
+      <c r="L376" s="31" t="inlineStr"/>
+      <c r="M376" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N376" s="32" t="inlineStr"/>
+      <c r="O376" s="31" t="inlineStr"/>
+    </row>
+    <row r="377" ht="16" customHeight="1">
+      <c r="A377" s="33" t="inlineStr">
+        <is>
+          <t>aba4a5afc728</t>
+        </is>
+      </c>
+      <c r="B377" s="33" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C377" s="33" t="inlineStr">
+        <is>
+          <t>Hydrologist / Water Resource Engineer (Mining)</t>
+        </is>
+      </c>
+      <c r="D377" s="33" t="inlineStr">
+        <is>
+          <t>WSP</t>
+        </is>
+      </c>
+      <c r="E377" s="33" t="inlineStr">
+        <is>
+          <t>Aldwych, Central London</t>
+        </is>
+      </c>
+      <c r="F377" s="33" t="inlineStr">
+        <is>
+          <t>£50,365 – £50,365</t>
+        </is>
+      </c>
+      <c r="G377" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H377" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I377" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="J377" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K377" s="35" t="inlineStr"/>
+      <c r="L377" s="35" t="inlineStr"/>
+      <c r="M377" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N377" s="36" t="inlineStr"/>
+      <c r="O377" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -20529,6 +23184,51 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J330" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J331" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J332" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J333" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J334" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J335" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J336" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J337" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J338" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J339" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J340" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J341" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J342" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J343" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J344" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J345" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J346" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J347" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J348" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J349" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J350" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J351" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J352" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J353" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J354" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J355" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J356" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J357" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J358" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J359" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J360" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J361" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J362" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J363" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J364" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J365" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J366" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J367" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J368" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J369" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J370" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J371" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J372" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J373" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J374" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J375" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J376" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J377" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -82,7 +82,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -184,6 +184,11 @@
         <fgColor rgb="00FEFCBF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF5F5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -239,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -346,6 +351,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="20" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -713,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O377"/>
+  <dimension ref="A1:O378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -23107,6 +23115,65 @@
       </c>
       <c r="N377" s="36" t="inlineStr"/>
       <c r="O377" s="35" t="inlineStr"/>
+    </row>
+    <row r="378" ht="16" customHeight="1">
+      <c r="A378" s="28" t="inlineStr">
+        <is>
+          <t>1b088c04ed4b</t>
+        </is>
+      </c>
+      <c r="B378" s="28" t="inlineStr">
+        <is>
+          <t>02/03/2026</t>
+        </is>
+      </c>
+      <c r="C378" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D378" s="28" t="inlineStr">
+        <is>
+          <t>Carrington West</t>
+        </is>
+      </c>
+      <c r="E378" s="28" t="inlineStr">
+        <is>
+          <t>Central London, London</t>
+        </is>
+      </c>
+      <c r="F378" s="28" t="inlineStr">
+        <is>
+          <t>£40,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G378" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H378" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I378" s="28" t="n">
+        <v>110</v>
+      </c>
+      <c r="J378" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K378" s="31" t="inlineStr"/>
+      <c r="L378" s="31" t="inlineStr"/>
+      <c r="M378" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N378" s="32" t="inlineStr"/>
+      <c r="O378" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -23229,6 +23296,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J375" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J376" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J377" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J378" r:id="rId109"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O378"/>
+  <dimension ref="A1:O379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -23174,6 +23174,65 @@
       </c>
       <c r="N378" s="32" t="inlineStr"/>
       <c r="O378" s="31" t="inlineStr"/>
+    </row>
+    <row r="379" ht="16" customHeight="1">
+      <c r="A379" s="33" t="inlineStr">
+        <is>
+          <t>25bbb84083b1</t>
+        </is>
+      </c>
+      <c r="B379" s="33" t="inlineStr">
+        <is>
+          <t>03/03/2026</t>
+        </is>
+      </c>
+      <c r="C379" s="33" t="inlineStr">
+        <is>
+          <t>Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D379" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E379" s="33" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F379" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G379" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H379" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I379" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J379" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K379" s="35" t="inlineStr"/>
+      <c r="L379" s="35" t="inlineStr"/>
+      <c r="M379" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N379" s="36" t="inlineStr"/>
+      <c r="O379" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -23297,6 +23356,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J376" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J377" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J378" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J379" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O379"/>
+  <dimension ref="A1:O380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -23233,6 +23233,65 @@
       </c>
       <c r="N379" s="36" t="inlineStr"/>
       <c r="O379" s="35" t="inlineStr"/>
+    </row>
+    <row r="380" ht="16" customHeight="1">
+      <c r="A380" s="28" t="inlineStr">
+        <is>
+          <t>cb0182f28041</t>
+        </is>
+      </c>
+      <c r="B380" s="28" t="inlineStr">
+        <is>
+          <t>08/03/2026</t>
+        </is>
+      </c>
+      <c r="C380" s="28" t="inlineStr">
+        <is>
+          <t>Water Infrastructure Manager, AWS EMEA Energy &amp; Water Team</t>
+        </is>
+      </c>
+      <c r="D380" s="28" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="E380" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F380" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G380" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H380" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I380" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="J380" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K380" s="31" t="inlineStr"/>
+      <c r="L380" s="31" t="inlineStr"/>
+      <c r="M380" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N380" s="32" t="inlineStr"/>
+      <c r="O380" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -23357,6 +23416,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J377" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J378" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J379" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J380" r:id="rId111"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O380"/>
+  <dimension ref="A1:O381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -23292,6 +23292,65 @@
       </c>
       <c r="N380" s="32" t="inlineStr"/>
       <c r="O380" s="31" t="inlineStr"/>
+    </row>
+    <row r="381" ht="16" customHeight="1">
+      <c r="A381" s="33" t="inlineStr">
+        <is>
+          <t>5d3f407abe23</t>
+        </is>
+      </c>
+      <c r="B381" s="33" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="C381" s="33" t="inlineStr">
+        <is>
+          <t>Clean Water (Hydraulic) Modellers</t>
+        </is>
+      </c>
+      <c r="D381" s="33" t="inlineStr">
+        <is>
+          <t>RPS</t>
+        </is>
+      </c>
+      <c r="E381" s="33" t="inlineStr">
+        <is>
+          <t>Glasgow, Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F381" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G381" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H381" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I381" s="33" t="n">
+        <v>65</v>
+      </c>
+      <c r="J381" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K381" s="35" t="inlineStr"/>
+      <c r="L381" s="35" t="inlineStr"/>
+      <c r="M381" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N381" s="36" t="inlineStr"/>
+      <c r="O381" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -23417,6 +23476,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J378" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J379" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J380" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J381" r:id="rId112"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O381"/>
+  <dimension ref="A1:O382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -23351,6 +23351,65 @@
       </c>
       <c r="N381" s="36" t="inlineStr"/>
       <c r="O381" s="35" t="inlineStr"/>
+    </row>
+    <row r="382" ht="16" customHeight="1">
+      <c r="A382" s="28" t="inlineStr">
+        <is>
+          <t>e706b7e3c84d</t>
+        </is>
+      </c>
+      <c r="B382" s="28" t="inlineStr">
+        <is>
+          <t>11/03/2026</t>
+        </is>
+      </c>
+      <c r="C382" s="28" t="inlineStr">
+        <is>
+          <t>Water Network Engineer</t>
+        </is>
+      </c>
+      <c r="D382" s="28" t="inlineStr">
+        <is>
+          <t>Celnor Group</t>
+        </is>
+      </c>
+      <c r="E382" s="28" t="inlineStr">
+        <is>
+          <t>West Malling, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F382" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G382" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H382" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I382" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J382" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K382" s="31" t="inlineStr"/>
+      <c r="L382" s="31" t="inlineStr"/>
+      <c r="M382" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N382" s="32" t="inlineStr"/>
+      <c r="O382" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -23477,6 +23536,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J379" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J380" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J381" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J382" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O382"/>
+  <dimension ref="A1:O384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -23410,6 +23410,124 @@
       </c>
       <c r="N382" s="32" t="inlineStr"/>
       <c r="O382" s="31" t="inlineStr"/>
+    </row>
+    <row r="383" ht="16" customHeight="1">
+      <c r="A383" s="33" t="inlineStr">
+        <is>
+          <t>29ad73838a39</t>
+        </is>
+      </c>
+      <c r="B383" s="33" t="inlineStr">
+        <is>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="C383" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D383" s="33" t="inlineStr">
+        <is>
+          <t>Alexander Associates Limited</t>
+        </is>
+      </c>
+      <c r="E383" s="33" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F383" s="33" t="inlineStr">
+        <is>
+          <t>£49,656 – £49,656</t>
+        </is>
+      </c>
+      <c r="G383" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H383" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I383" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="J383" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K383" s="35" t="inlineStr"/>
+      <c r="L383" s="35" t="inlineStr"/>
+      <c r="M383" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N383" s="36" t="inlineStr"/>
+      <c r="O383" s="35" t="inlineStr"/>
+    </row>
+    <row r="384" ht="16" customHeight="1">
+      <c r="A384" s="28" t="inlineStr">
+        <is>
+          <t>a21a5a306168</t>
+        </is>
+      </c>
+      <c r="B384" s="28" t="inlineStr">
+        <is>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="C384" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D384" s="28" t="inlineStr">
+        <is>
+          <t>Alexander Associates</t>
+        </is>
+      </c>
+      <c r="E384" s="28" t="inlineStr">
+        <is>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="F384" s="28" t="inlineStr">
+        <is>
+          <t>£48,620 – £48,620</t>
+        </is>
+      </c>
+      <c r="G384" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H384" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I384" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="J384" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K384" s="31" t="inlineStr"/>
+      <c r="L384" s="31" t="inlineStr"/>
+      <c r="M384" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N384" s="32" t="inlineStr"/>
+      <c r="O384" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -23537,6 +23655,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J380" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J381" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J382" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J383" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J384" r:id="rId115"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O384"/>
+  <dimension ref="A1:O385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -23528,6 +23528,65 @@
       </c>
       <c r="N384" s="32" t="inlineStr"/>
       <c r="O384" s="31" t="inlineStr"/>
+    </row>
+    <row r="385" ht="16" customHeight="1">
+      <c r="A385" s="33" t="inlineStr">
+        <is>
+          <t>add811ba595c</t>
+        </is>
+      </c>
+      <c r="B385" s="33" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="C385" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D385" s="33" t="inlineStr">
+        <is>
+          <t>Alexander Associates</t>
+        </is>
+      </c>
+      <c r="E385" s="33" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F385" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G385" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H385" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I385" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J385" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K385" s="35" t="inlineStr"/>
+      <c r="L385" s="35" t="inlineStr"/>
+      <c r="M385" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N385" s="36" t="inlineStr"/>
+      <c r="O385" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -23657,6 +23716,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J382" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J383" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J384" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J385" r:id="rId116"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O385"/>
+  <dimension ref="A1:O386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -23587,6 +23587,65 @@
       </c>
       <c r="N385" s="36" t="inlineStr"/>
       <c r="O385" s="35" t="inlineStr"/>
+    </row>
+    <row r="386" ht="16" customHeight="1">
+      <c r="A386" s="28" t="inlineStr">
+        <is>
+          <t>b26155ff061a</t>
+        </is>
+      </c>
+      <c r="B386" s="28" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="C386" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D386" s="28" t="inlineStr">
+        <is>
+          <t>Flux Consulting</t>
+        </is>
+      </c>
+      <c r="E386" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F386" s="28" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G386" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H386" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I386" s="28" t="n">
+        <v>110</v>
+      </c>
+      <c r="J386" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K386" s="31" t="inlineStr"/>
+      <c r="L386" s="31" t="inlineStr"/>
+      <c r="M386" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N386" s="32" t="inlineStr"/>
+      <c r="O386" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -23717,6 +23776,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J383" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J384" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J385" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J386" r:id="rId117"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O386"/>
+  <dimension ref="A1:O387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -23646,6 +23646,65 @@
       </c>
       <c r="N386" s="32" t="inlineStr"/>
       <c r="O386" s="31" t="inlineStr"/>
+    </row>
+    <row r="387" ht="16" customHeight="1">
+      <c r="A387" s="33" t="inlineStr">
+        <is>
+          <t>fa5433f34389</t>
+        </is>
+      </c>
+      <c r="B387" s="33" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="C387" s="33" t="inlineStr">
+        <is>
+          <t>Outside IR35 Contract | Civil Design Engineer | Water Sector</t>
+        </is>
+      </c>
+      <c r="D387" s="33" t="inlineStr">
+        <is>
+          <t>Alexander Associates Technical Recruitment</t>
+        </is>
+      </c>
+      <c r="E387" s="33" t="inlineStr">
+        <is>
+          <t>Chatham, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F387" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G387" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H387" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I387" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J387" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K387" s="35" t="inlineStr"/>
+      <c r="L387" s="35" t="inlineStr"/>
+      <c r="M387" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N387" s="36" t="inlineStr"/>
+      <c r="O387" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -23777,6 +23836,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J384" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J385" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J386" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J387" r:id="rId118"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O387"/>
+  <dimension ref="A1:O389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -23705,6 +23705,124 @@
       </c>
       <c r="N387" s="36" t="inlineStr"/>
       <c r="O387" s="35" t="inlineStr"/>
+    </row>
+    <row r="388" ht="16" customHeight="1">
+      <c r="A388" s="28" t="inlineStr">
+        <is>
+          <t>4343ece95781</t>
+        </is>
+      </c>
+      <c r="B388" s="28" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="C388" s="28" t="inlineStr">
+        <is>
+          <t>Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D388" s="28" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E388" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F388" s="28" t="inlineStr">
+        <is>
+          <t>£50,479 – £50,479</t>
+        </is>
+      </c>
+      <c r="G388" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H388" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I388" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="J388" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K388" s="31" t="inlineStr"/>
+      <c r="L388" s="31" t="inlineStr"/>
+      <c r="M388" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N388" s="32" t="inlineStr"/>
+      <c r="O388" s="31" t="inlineStr"/>
+    </row>
+    <row r="389" ht="16" customHeight="1">
+      <c r="A389" s="33" t="inlineStr">
+        <is>
+          <t>609d6bb95a56</t>
+        </is>
+      </c>
+      <c r="B389" s="33" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="C389" s="33" t="inlineStr">
+        <is>
+          <t>Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D389" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E389" s="33" t="inlineStr">
+        <is>
+          <t>High Wycombe, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="F389" s="33" t="inlineStr">
+        <is>
+          <t>£49,094 – £49,094</t>
+        </is>
+      </c>
+      <c r="G389" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H389" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I389" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="J389" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K389" s="35" t="inlineStr"/>
+      <c r="L389" s="35" t="inlineStr"/>
+      <c r="M389" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N389" s="36" t="inlineStr"/>
+      <c r="O389" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -23837,6 +23955,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J385" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J386" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J387" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J388" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J389" r:id="rId120"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O389"/>
+  <dimension ref="A1:O391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -23823,6 +23823,124 @@
       </c>
       <c r="N389" s="36" t="inlineStr"/>
       <c r="O389" s="35" t="inlineStr"/>
+    </row>
+    <row r="390" ht="16" customHeight="1">
+      <c r="A390" s="28" t="inlineStr">
+        <is>
+          <t>5601fd256c97</t>
+        </is>
+      </c>
+      <c r="B390" s="28" t="inlineStr">
+        <is>
+          <t>22/03/2026</t>
+        </is>
+      </c>
+      <c r="C390" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Sector</t>
+        </is>
+      </c>
+      <c r="D390" s="28" t="inlineStr">
+        <is>
+          <t>Alexander Associates</t>
+        </is>
+      </c>
+      <c r="E390" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F390" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G390" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H390" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I390" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J390" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K390" s="31" t="inlineStr"/>
+      <c r="L390" s="31" t="inlineStr"/>
+      <c r="M390" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N390" s="32" t="inlineStr"/>
+      <c r="O390" s="31" t="inlineStr"/>
+    </row>
+    <row r="391" ht="16" customHeight="1">
+      <c r="A391" s="33" t="inlineStr">
+        <is>
+          <t>4caa693928dc</t>
+        </is>
+      </c>
+      <c r="B391" s="33" t="inlineStr">
+        <is>
+          <t>22/03/2026</t>
+        </is>
+      </c>
+      <c r="C391" s="33" t="inlineStr">
+        <is>
+          <t>Civil Engineer (Urban Drainage / Wastewater Networks)</t>
+        </is>
+      </c>
+      <c r="D391" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E391" s="33" t="inlineStr">
+        <is>
+          <t>Warrington, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F391" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G391" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H391" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I391" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J391" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K391" s="35" t="inlineStr"/>
+      <c r="L391" s="35" t="inlineStr"/>
+      <c r="M391" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N391" s="36" t="inlineStr"/>
+      <c r="O391" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -23957,6 +24075,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J387" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J388" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J389" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J390" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J391" r:id="rId122"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O391"/>
+  <dimension ref="A1:O392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -23941,6 +23941,65 @@
       </c>
       <c r="N391" s="36" t="inlineStr"/>
       <c r="O391" s="35" t="inlineStr"/>
+    </row>
+    <row r="392" ht="16" customHeight="1">
+      <c r="A392" s="28" t="inlineStr">
+        <is>
+          <t>760c44d2a13b</t>
+        </is>
+      </c>
+      <c r="B392" s="28" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="C392" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulic Design Engineer</t>
+        </is>
+      </c>
+      <c r="D392" s="28" t="inlineStr">
+        <is>
+          <t>Extension Recruitment Ltd</t>
+        </is>
+      </c>
+      <c r="E392" s="28" t="inlineStr">
+        <is>
+          <t>Newcastle Upon Tyne, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F392" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G392" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H392" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I392" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J392" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K392" s="31" t="inlineStr"/>
+      <c r="L392" s="31" t="inlineStr"/>
+      <c r="M392" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N392" s="32" t="inlineStr"/>
+      <c r="O392" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -24077,6 +24136,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J389" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J390" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J391" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J392" r:id="rId123"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O392"/>
+  <dimension ref="A1:O395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -24000,6 +24000,183 @@
       </c>
       <c r="N392" s="32" t="inlineStr"/>
       <c r="O392" s="31" t="inlineStr"/>
+    </row>
+    <row r="393" ht="16" customHeight="1">
+      <c r="A393" s="33" t="inlineStr">
+        <is>
+          <t>468de08a8d3e</t>
+        </is>
+      </c>
+      <c r="B393" s="33" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="C393" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D393" s="33" t="inlineStr">
+        <is>
+          <t>Thames Water</t>
+        </is>
+      </c>
+      <c r="E393" s="33" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F393" s="33" t="inlineStr">
+        <is>
+          <t>£45,940 – £68,000</t>
+        </is>
+      </c>
+      <c r="G393" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H393" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I393" s="33" t="n">
+        <v>110</v>
+      </c>
+      <c r="J393" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K393" s="35" t="inlineStr"/>
+      <c r="L393" s="35" t="inlineStr"/>
+      <c r="M393" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N393" s="36" t="inlineStr"/>
+      <c r="O393" s="35" t="inlineStr"/>
+    </row>
+    <row r="394" ht="16" customHeight="1">
+      <c r="A394" s="28" t="inlineStr">
+        <is>
+          <t>d11ffe09f6f7</t>
+        </is>
+      </c>
+      <c r="B394" s="28" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="C394" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D394" s="28" t="inlineStr">
+        <is>
+          <t>Thames Water</t>
+        </is>
+      </c>
+      <c r="E394" s="28" t="inlineStr">
+        <is>
+          <t>Pingewood, Reading</t>
+        </is>
+      </c>
+      <c r="F394" s="28" t="inlineStr">
+        <is>
+          <t>£45,940 – £68,000</t>
+        </is>
+      </c>
+      <c r="G394" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H394" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I394" s="28" t="n">
+        <v>110</v>
+      </c>
+      <c r="J394" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K394" s="31" t="inlineStr"/>
+      <c r="L394" s="31" t="inlineStr"/>
+      <c r="M394" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N394" s="32" t="inlineStr"/>
+      <c r="O394" s="31" t="inlineStr"/>
+    </row>
+    <row r="395" ht="16" customHeight="1">
+      <c r="A395" s="33" t="inlineStr">
+        <is>
+          <t>3a6c36205356</t>
+        </is>
+      </c>
+      <c r="B395" s="33" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="C395" s="33" t="inlineStr">
+        <is>
+          <t>Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D395" s="33" t="inlineStr">
+        <is>
+          <t>Stantec UK</t>
+        </is>
+      </c>
+      <c r="E395" s="33" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F395" s="33" t="inlineStr">
+        <is>
+          <t>£44,887 – £44,887</t>
+        </is>
+      </c>
+      <c r="G395" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H395" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I395" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="J395" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K395" s="35" t="inlineStr"/>
+      <c r="L395" s="35" t="inlineStr"/>
+      <c r="M395" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N395" s="36" t="inlineStr"/>
+      <c r="O395" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -24137,6 +24314,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J390" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J391" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J392" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J393" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J394" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J395" r:id="rId126"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O395"/>
+  <dimension ref="A1:O396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -24177,6 +24177,65 @@
       </c>
       <c r="N395" s="36" t="inlineStr"/>
       <c r="O395" s="35" t="inlineStr"/>
+    </row>
+    <row r="396" ht="16" customHeight="1">
+      <c r="A396" s="28" t="inlineStr">
+        <is>
+          <t>83742c727c0f</t>
+        </is>
+      </c>
+      <c r="B396" s="28" t="inlineStr">
+        <is>
+          <t>28/03/2026</t>
+        </is>
+      </c>
+      <c r="C396" s="28" t="inlineStr">
+        <is>
+          <t>Design Engineer – Wastewater</t>
+        </is>
+      </c>
+      <c r="D396" s="28" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E396" s="28" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F396" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G396" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H396" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I396" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J396" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K396" s="31" t="inlineStr"/>
+      <c r="L396" s="31" t="inlineStr"/>
+      <c r="M396" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N396" s="32" t="inlineStr"/>
+      <c r="O396" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -24317,6 +24376,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J393" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J394" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J395" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J396" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O396"/>
+  <dimension ref="A1:O398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -24236,6 +24236,124 @@
       </c>
       <c r="N396" s="32" t="inlineStr"/>
       <c r="O396" s="31" t="inlineStr"/>
+    </row>
+    <row r="397" ht="16" customHeight="1">
+      <c r="A397" s="33" t="inlineStr">
+        <is>
+          <t>ad31540f93b4</t>
+        </is>
+      </c>
+      <c r="B397" s="33" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C397" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D397" s="33" t="inlineStr">
+        <is>
+          <t>Ganymede</t>
+        </is>
+      </c>
+      <c r="E397" s="33" t="inlineStr">
+        <is>
+          <t>England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F397" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G397" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H397" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I397" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J397" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K397" s="35" t="inlineStr"/>
+      <c r="L397" s="35" t="inlineStr"/>
+      <c r="M397" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N397" s="36" t="inlineStr"/>
+      <c r="O397" s="35" t="inlineStr"/>
+    </row>
+    <row r="398" ht="16" customHeight="1">
+      <c r="A398" s="28" t="inlineStr">
+        <is>
+          <t>bcba4f39902d</t>
+        </is>
+      </c>
+      <c r="B398" s="28" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C398" s="28" t="inlineStr">
+        <is>
+          <t>Design Engineer – Wastewater</t>
+        </is>
+      </c>
+      <c r="D398" s="28" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E398" s="28" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F398" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G398" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H398" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I398" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J398" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K398" s="31" t="inlineStr"/>
+      <c r="L398" s="31" t="inlineStr"/>
+      <c r="M398" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N398" s="32" t="inlineStr"/>
+      <c r="O398" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -24377,6 +24495,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J394" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J395" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J396" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J397" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J398" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O398"/>
+  <dimension ref="A1:O401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -24354,6 +24354,183 @@
       </c>
       <c r="N398" s="32" t="inlineStr"/>
       <c r="O398" s="31" t="inlineStr"/>
+    </row>
+    <row r="399" ht="16" customHeight="1">
+      <c r="A399" s="33" t="inlineStr">
+        <is>
+          <t>4520a8f8dcfc</t>
+        </is>
+      </c>
+      <c r="B399" s="33" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C399" s="33" t="inlineStr">
+        <is>
+          <t>Water Design Engineer</t>
+        </is>
+      </c>
+      <c r="D399" s="33" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E399" s="33" t="inlineStr">
+        <is>
+          <t>Surrey, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F399" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G399" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H399" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I399" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="J399" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K399" s="35" t="inlineStr"/>
+      <c r="L399" s="35" t="inlineStr"/>
+      <c r="M399" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N399" s="36" t="inlineStr"/>
+      <c r="O399" s="35" t="inlineStr"/>
+    </row>
+    <row r="400" ht="16" customHeight="1">
+      <c r="A400" s="28" t="inlineStr">
+        <is>
+          <t>a0a0a15fa044</t>
+        </is>
+      </c>
+      <c r="B400" s="28" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C400" s="28" t="inlineStr">
+        <is>
+          <t>Design Engineer – Wastewater</t>
+        </is>
+      </c>
+      <c r="D400" s="28" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E400" s="28" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F400" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G400" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H400" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I400" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J400" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K400" s="31" t="inlineStr"/>
+      <c r="L400" s="31" t="inlineStr"/>
+      <c r="M400" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N400" s="32" t="inlineStr"/>
+      <c r="O400" s="31" t="inlineStr"/>
+    </row>
+    <row r="401" ht="16" customHeight="1">
+      <c r="A401" s="33" t="inlineStr">
+        <is>
+          <t>176e709b15a4</t>
+        </is>
+      </c>
+      <c r="B401" s="33" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C401" s="33" t="inlineStr">
+        <is>
+          <t>Design Engineer - Wastewater</t>
+        </is>
+      </c>
+      <c r="D401" s="33" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E401" s="33" t="inlineStr">
+        <is>
+          <t>Guildford, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F401" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G401" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H401" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I401" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J401" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K401" s="35" t="inlineStr"/>
+      <c r="L401" s="35" t="inlineStr"/>
+      <c r="M401" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N401" s="36" t="inlineStr"/>
+      <c r="O401" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -24497,6 +24674,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J396" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J397" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J398" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J399" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J400" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J401" r:id="rId132"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O401"/>
+  <dimension ref="A1:O403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -24531,6 +24531,124 @@
       </c>
       <c r="N401" s="36" t="inlineStr"/>
       <c r="O401" s="35" t="inlineStr"/>
+    </row>
+    <row r="402" ht="16" customHeight="1">
+      <c r="A402" s="28" t="inlineStr">
+        <is>
+          <t>edecf1d4c2e4</t>
+        </is>
+      </c>
+      <c r="B402" s="28" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C402" s="28" t="inlineStr">
+        <is>
+          <t>Design Manager - Water</t>
+        </is>
+      </c>
+      <c r="D402" s="28" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E402" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F402" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G402" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H402" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I402" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J402" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K402" s="31" t="inlineStr"/>
+      <c r="L402" s="31" t="inlineStr"/>
+      <c r="M402" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N402" s="32" t="inlineStr"/>
+      <c r="O402" s="31" t="inlineStr"/>
+    </row>
+    <row r="403" ht="16" customHeight="1">
+      <c r="A403" s="33" t="inlineStr">
+        <is>
+          <t>43f0acfae23e</t>
+        </is>
+      </c>
+      <c r="B403" s="33" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C403" s="33" t="inlineStr">
+        <is>
+          <t>Water Design Engineer</t>
+        </is>
+      </c>
+      <c r="D403" s="33" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E403" s="33" t="inlineStr">
+        <is>
+          <t>Surrey, South East England</t>
+        </is>
+      </c>
+      <c r="F403" s="33" t="inlineStr">
+        <is>
+          <t>£39,730 – £39,730</t>
+        </is>
+      </c>
+      <c r="G403" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H403" s="37" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="I403" s="33" t="n">
+        <v>140</v>
+      </c>
+      <c r="J403" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K403" s="35" t="inlineStr"/>
+      <c r="L403" s="35" t="inlineStr"/>
+      <c r="M403" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N403" s="36" t="inlineStr"/>
+      <c r="O403" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -24677,6 +24795,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J399" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J400" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J401" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J402" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J403" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O403"/>
+  <dimension ref="A1:O406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -24649,6 +24649,183 @@
       </c>
       <c r="N403" s="36" t="inlineStr"/>
       <c r="O403" s="35" t="inlineStr"/>
+    </row>
+    <row r="404" ht="16" customHeight="1">
+      <c r="A404" s="28" t="inlineStr">
+        <is>
+          <t>af09f1c64fd5</t>
+        </is>
+      </c>
+      <c r="B404" s="28" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C404" s="28" t="inlineStr">
+        <is>
+          <t>Water Design Engineer</t>
+        </is>
+      </c>
+      <c r="D404" s="28" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E404" s="28" t="inlineStr">
+        <is>
+          <t>Surrey, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F404" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G404" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H404" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I404" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J404" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K404" s="31" t="inlineStr"/>
+      <c r="L404" s="31" t="inlineStr"/>
+      <c r="M404" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N404" s="32" t="inlineStr"/>
+      <c r="O404" s="31" t="inlineStr"/>
+    </row>
+    <row r="405" ht="16" customHeight="1">
+      <c r="A405" s="33" t="inlineStr">
+        <is>
+          <t>35a6169f718e</t>
+        </is>
+      </c>
+      <c r="B405" s="33" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C405" s="33" t="inlineStr">
+        <is>
+          <t>Design Engineer – Wastewater</t>
+        </is>
+      </c>
+      <c r="D405" s="33" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E405" s="33" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F405" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G405" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H405" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I405" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J405" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K405" s="35" t="inlineStr"/>
+      <c r="L405" s="35" t="inlineStr"/>
+      <c r="M405" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N405" s="36" t="inlineStr"/>
+      <c r="O405" s="35" t="inlineStr"/>
+    </row>
+    <row r="406" ht="16" customHeight="1">
+      <c r="A406" s="28" t="inlineStr">
+        <is>
+          <t>6d8e1780f724</t>
+        </is>
+      </c>
+      <c r="B406" s="28" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C406" s="28" t="inlineStr">
+        <is>
+          <t>Design Engineer - Wastewater</t>
+        </is>
+      </c>
+      <c r="D406" s="28" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E406" s="28" t="inlineStr">
+        <is>
+          <t>Guildford, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F406" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G406" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H406" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I406" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J406" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K406" s="31" t="inlineStr"/>
+      <c r="L406" s="31" t="inlineStr"/>
+      <c r="M406" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N406" s="32" t="inlineStr"/>
+      <c r="O406" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -24797,6 +24974,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J401" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J402" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J403" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J404" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J405" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J406" r:id="rId137"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O406"/>
+  <dimension ref="A1:O407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -24826,6 +24826,65 @@
       </c>
       <c r="N406" s="32" t="inlineStr"/>
       <c r="O406" s="31" t="inlineStr"/>
+    </row>
+    <row r="407" ht="16" customHeight="1">
+      <c r="A407" s="33" t="inlineStr">
+        <is>
+          <t>2fbda069d678</t>
+        </is>
+      </c>
+      <c r="B407" s="33" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C407" s="33" t="inlineStr">
+        <is>
+          <t>Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D407" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E407" s="33" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F407" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G407" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H407" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I407" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J407" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K407" s="35" t="inlineStr"/>
+      <c r="L407" s="35" t="inlineStr"/>
+      <c r="M407" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N407" s="36" t="inlineStr"/>
+      <c r="O407" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -24977,6 +25036,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J404" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J405" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J406" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J407" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O407"/>
+  <dimension ref="A1:O409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -24885,6 +24885,124 @@
       </c>
       <c r="N407" s="36" t="inlineStr"/>
       <c r="O407" s="35" t="inlineStr"/>
+    </row>
+    <row r="408" ht="16" customHeight="1">
+      <c r="A408" s="28" t="inlineStr">
+        <is>
+          <t>fe16ec025ab3</t>
+        </is>
+      </c>
+      <c r="B408" s="28" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C408" s="28" t="inlineStr">
+        <is>
+          <t>Design Engineer (Water Networks)</t>
+        </is>
+      </c>
+      <c r="D408" s="28" t="inlineStr">
+        <is>
+          <t>Severn Trent</t>
+        </is>
+      </c>
+      <c r="E408" s="28" t="inlineStr">
+        <is>
+          <t>South Derbyshire, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F408" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G408" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H408" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I408" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="J408" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K408" s="31" t="inlineStr"/>
+      <c r="L408" s="31" t="inlineStr"/>
+      <c r="M408" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N408" s="32" t="inlineStr"/>
+      <c r="O408" s="31" t="inlineStr"/>
+    </row>
+    <row r="409" ht="16" customHeight="1">
+      <c r="A409" s="33" t="inlineStr">
+        <is>
+          <t>0e0da1fad7fc</t>
+        </is>
+      </c>
+      <c r="B409" s="33" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C409" s="33" t="inlineStr">
+        <is>
+          <t>Water Design Engineer</t>
+        </is>
+      </c>
+      <c r="D409" s="33" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E409" s="33" t="inlineStr">
+        <is>
+          <t>Surrey, South East England</t>
+        </is>
+      </c>
+      <c r="F409" s="33" t="inlineStr">
+        <is>
+          <t>£39,730 – £39,730</t>
+        </is>
+      </c>
+      <c r="G409" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H409" s="37" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="I409" s="33" t="n">
+        <v>140</v>
+      </c>
+      <c r="J409" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K409" s="35" t="inlineStr"/>
+      <c r="L409" s="35" t="inlineStr"/>
+      <c r="M409" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N409" s="36" t="inlineStr"/>
+      <c r="O409" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -25037,6 +25155,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J405" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J406" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J407" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J408" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J409" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O409"/>
+  <dimension ref="A1:O412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -25003,6 +25003,183 @@
       </c>
       <c r="N409" s="36" t="inlineStr"/>
       <c r="O409" s="35" t="inlineStr"/>
+    </row>
+    <row r="410" ht="16" customHeight="1">
+      <c r="A410" s="28" t="inlineStr">
+        <is>
+          <t>46c9075b028a</t>
+        </is>
+      </c>
+      <c r="B410" s="28" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C410" s="28" t="inlineStr">
+        <is>
+          <t>Water Design Engineer</t>
+        </is>
+      </c>
+      <c r="D410" s="28" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E410" s="28" t="inlineStr">
+        <is>
+          <t>Surrey, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F410" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G410" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H410" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I410" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J410" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K410" s="31" t="inlineStr"/>
+      <c r="L410" s="31" t="inlineStr"/>
+      <c r="M410" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N410" s="32" t="inlineStr"/>
+      <c r="O410" s="31" t="inlineStr"/>
+    </row>
+    <row r="411" ht="16" customHeight="1">
+      <c r="A411" s="33" t="inlineStr">
+        <is>
+          <t>213aa3e07fa6</t>
+        </is>
+      </c>
+      <c r="B411" s="33" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C411" s="33" t="inlineStr">
+        <is>
+          <t>Design Engineer – Wastewater</t>
+        </is>
+      </c>
+      <c r="D411" s="33" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E411" s="33" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F411" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G411" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H411" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I411" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J411" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K411" s="35" t="inlineStr"/>
+      <c r="L411" s="35" t="inlineStr"/>
+      <c r="M411" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N411" s="36" t="inlineStr"/>
+      <c r="O411" s="35" t="inlineStr"/>
+    </row>
+    <row r="412" ht="16" customHeight="1">
+      <c r="A412" s="28" t="inlineStr">
+        <is>
+          <t>0b38b4cf407d</t>
+        </is>
+      </c>
+      <c r="B412" s="28" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C412" s="28" t="inlineStr">
+        <is>
+          <t>Design Engineer - Wastewater</t>
+        </is>
+      </c>
+      <c r="D412" s="28" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E412" s="28" t="inlineStr">
+        <is>
+          <t>Guildford, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F412" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G412" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H412" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I412" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J412" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K412" s="31" t="inlineStr"/>
+      <c r="L412" s="31" t="inlineStr"/>
+      <c r="M412" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N412" s="32" t="inlineStr"/>
+      <c r="O412" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -25157,6 +25334,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J407" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J408" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J409" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J410" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J411" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J412" r:id="rId143"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O412"/>
+  <dimension ref="A1:O413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -25180,6 +25180,65 @@
       </c>
       <c r="N412" s="32" t="inlineStr"/>
       <c r="O412" s="31" t="inlineStr"/>
+    </row>
+    <row r="413" ht="16" customHeight="1">
+      <c r="A413" s="33" t="inlineStr">
+        <is>
+          <t>c1ba1b179d20</t>
+        </is>
+      </c>
+      <c r="B413" s="33" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C413" s="33" t="inlineStr">
+        <is>
+          <t>Water Design Engineer</t>
+        </is>
+      </c>
+      <c r="D413" s="33" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E413" s="33" t="inlineStr">
+        <is>
+          <t>Surrey, South East England</t>
+        </is>
+      </c>
+      <c r="F413" s="33" t="inlineStr">
+        <is>
+          <t>£39,730 – £39,730</t>
+        </is>
+      </c>
+      <c r="G413" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H413" s="37" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="I413" s="33" t="n">
+        <v>140</v>
+      </c>
+      <c r="J413" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K413" s="35" t="inlineStr"/>
+      <c r="L413" s="35" t="inlineStr"/>
+      <c r="M413" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N413" s="36" t="inlineStr"/>
+      <c r="O413" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -25337,6 +25396,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J410" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J411" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J412" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J413" r:id="rId144"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O413"/>
+  <dimension ref="A1:O416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -25239,6 +25239,183 @@
       </c>
       <c r="N413" s="36" t="inlineStr"/>
       <c r="O413" s="35" t="inlineStr"/>
+    </row>
+    <row r="414" ht="16" customHeight="1">
+      <c r="A414" s="28" t="inlineStr">
+        <is>
+          <t>884085f73e77</t>
+        </is>
+      </c>
+      <c r="B414" s="28" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C414" s="28" t="inlineStr">
+        <is>
+          <t>Water Design Engineer</t>
+        </is>
+      </c>
+      <c r="D414" s="28" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E414" s="28" t="inlineStr">
+        <is>
+          <t>Surrey, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F414" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G414" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H414" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I414" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J414" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K414" s="31" t="inlineStr"/>
+      <c r="L414" s="31" t="inlineStr"/>
+      <c r="M414" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N414" s="32" t="inlineStr"/>
+      <c r="O414" s="31" t="inlineStr"/>
+    </row>
+    <row r="415" ht="16" customHeight="1">
+      <c r="A415" s="33" t="inlineStr">
+        <is>
+          <t>401eb93bb39e</t>
+        </is>
+      </c>
+      <c r="B415" s="33" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C415" s="33" t="inlineStr">
+        <is>
+          <t>Design Engineer – Wastewater</t>
+        </is>
+      </c>
+      <c r="D415" s="33" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E415" s="33" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F415" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G415" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H415" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I415" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J415" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K415" s="35" t="inlineStr"/>
+      <c r="L415" s="35" t="inlineStr"/>
+      <c r="M415" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N415" s="36" t="inlineStr"/>
+      <c r="O415" s="35" t="inlineStr"/>
+    </row>
+    <row r="416" ht="16" customHeight="1">
+      <c r="A416" s="28" t="inlineStr">
+        <is>
+          <t>2f3c7b7bd5c1</t>
+        </is>
+      </c>
+      <c r="B416" s="28" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C416" s="28" t="inlineStr">
+        <is>
+          <t>Design Engineer - Wastewater</t>
+        </is>
+      </c>
+      <c r="D416" s="28" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E416" s="28" t="inlineStr">
+        <is>
+          <t>Guildford, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F416" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G416" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H416" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I416" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J416" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K416" s="31" t="inlineStr"/>
+      <c r="L416" s="31" t="inlineStr"/>
+      <c r="M416" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N416" s="32" t="inlineStr"/>
+      <c r="O416" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -25397,6 +25574,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J411" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J412" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J413" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J414" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J415" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J416" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O416"/>
+  <dimension ref="A1:O419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -25416,6 +25416,183 @@
       </c>
       <c r="N416" s="32" t="inlineStr"/>
       <c r="O416" s="31" t="inlineStr"/>
+    </row>
+    <row r="417" ht="16" customHeight="1">
+      <c r="A417" s="33" t="inlineStr">
+        <is>
+          <t>7f0fbbda05ff</t>
+        </is>
+      </c>
+      <c r="B417" s="33" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C417" s="33" t="inlineStr">
+        <is>
+          <t>Water Design Engineer</t>
+        </is>
+      </c>
+      <c r="D417" s="33" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E417" s="33" t="inlineStr">
+        <is>
+          <t>Surrey, South East England</t>
+        </is>
+      </c>
+      <c r="F417" s="33" t="inlineStr">
+        <is>
+          <t>£39,730 – £39,730</t>
+        </is>
+      </c>
+      <c r="G417" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H417" s="37" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="I417" s="33" t="n">
+        <v>140</v>
+      </c>
+      <c r="J417" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K417" s="35" t="inlineStr"/>
+      <c r="L417" s="35" t="inlineStr"/>
+      <c r="M417" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N417" s="36" t="inlineStr"/>
+      <c r="O417" s="35" t="inlineStr"/>
+    </row>
+    <row r="418" ht="16" customHeight="1">
+      <c r="A418" s="28" t="inlineStr">
+        <is>
+          <t>75e746290988</t>
+        </is>
+      </c>
+      <c r="B418" s="28" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C418" s="28" t="inlineStr">
+        <is>
+          <t>Water Design Engineer</t>
+        </is>
+      </c>
+      <c r="D418" s="28" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E418" s="28" t="inlineStr">
+        <is>
+          <t>Surrey, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F418" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G418" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H418" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I418" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J418" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K418" s="31" t="inlineStr"/>
+      <c r="L418" s="31" t="inlineStr"/>
+      <c r="M418" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N418" s="32" t="inlineStr"/>
+      <c r="O418" s="31" t="inlineStr"/>
+    </row>
+    <row r="419" ht="16" customHeight="1">
+      <c r="A419" s="33" t="inlineStr">
+        <is>
+          <t>7ce3f0baf0fd</t>
+        </is>
+      </c>
+      <c r="B419" s="33" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C419" s="33" t="inlineStr">
+        <is>
+          <t>Design Engineer - Wastewater</t>
+        </is>
+      </c>
+      <c r="D419" s="33" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E419" s="33" t="inlineStr">
+        <is>
+          <t>Guildford, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F419" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G419" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H419" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I419" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J419" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K419" s="35" t="inlineStr"/>
+      <c r="L419" s="35" t="inlineStr"/>
+      <c r="M419" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N419" s="36" t="inlineStr"/>
+      <c r="O419" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -25577,6 +25754,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J414" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J415" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J416" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J417" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J418" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J419" r:id="rId150"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O419"/>
+  <dimension ref="A1:O420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -25593,6 +25593,65 @@
       </c>
       <c r="N419" s="36" t="inlineStr"/>
       <c r="O419" s="35" t="inlineStr"/>
+    </row>
+    <row r="420" ht="16" customHeight="1">
+      <c r="A420" s="28" t="inlineStr">
+        <is>
+          <t>985a3fcb8e6e</t>
+        </is>
+      </c>
+      <c r="B420" s="28" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C420" s="28" t="inlineStr">
+        <is>
+          <t>Design Engineer – Wastewater</t>
+        </is>
+      </c>
+      <c r="D420" s="28" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E420" s="28" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F420" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G420" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H420" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I420" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J420" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K420" s="31" t="inlineStr"/>
+      <c r="L420" s="31" t="inlineStr"/>
+      <c r="M420" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N420" s="32" t="inlineStr"/>
+      <c r="O420" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -25757,6 +25816,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J417" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J418" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J419" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J420" r:id="rId151"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O420"/>
+  <dimension ref="A1:O422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -25652,6 +25652,124 @@
       </c>
       <c r="N420" s="32" t="inlineStr"/>
       <c r="O420" s="31" t="inlineStr"/>
+    </row>
+    <row r="421" ht="16" customHeight="1">
+      <c r="A421" s="33" t="inlineStr">
+        <is>
+          <t>7ea439573191</t>
+        </is>
+      </c>
+      <c r="B421" s="33" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="C421" s="33" t="inlineStr">
+        <is>
+          <t>Process Design Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D421" s="33" t="inlineStr">
+        <is>
+          <t>Shirley Parsons Ltd</t>
+        </is>
+      </c>
+      <c r="E421" s="33" t="inlineStr">
+        <is>
+          <t>Hemel Hempstead, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="F421" s="33" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G421" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H421" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I421" s="33" t="n">
+        <v>85</v>
+      </c>
+      <c r="J421" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K421" s="35" t="inlineStr"/>
+      <c r="L421" s="35" t="inlineStr"/>
+      <c r="M421" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N421" s="36" t="inlineStr"/>
+      <c r="O421" s="35" t="inlineStr"/>
+    </row>
+    <row r="422" ht="16" customHeight="1">
+      <c r="A422" s="28" t="inlineStr">
+        <is>
+          <t>67c2c1945a5d</t>
+        </is>
+      </c>
+      <c r="B422" s="28" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="C422" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D422" s="28" t="inlineStr">
+        <is>
+          <t>Shirley Parsons</t>
+        </is>
+      </c>
+      <c r="E422" s="28" t="inlineStr">
+        <is>
+          <t>Hemel Hempstead, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F422" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G422" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H422" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I422" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J422" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K422" s="31" t="inlineStr"/>
+      <c r="L422" s="31" t="inlineStr"/>
+      <c r="M422" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N422" s="32" t="inlineStr"/>
+      <c r="O422" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -25817,6 +25935,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J418" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J419" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J420" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J421" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J422" r:id="rId153"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O422"/>
+  <dimension ref="A1:O423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -25770,6 +25770,65 @@
       </c>
       <c r="N422" s="32" t="inlineStr"/>
       <c r="O422" s="31" t="inlineStr"/>
+    </row>
+    <row r="423" ht="16" customHeight="1">
+      <c r="A423" s="33" t="inlineStr">
+        <is>
+          <t>f02641b6fdd7</t>
+        </is>
+      </c>
+      <c r="B423" s="33" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="C423" s="33" t="inlineStr">
+        <is>
+          <t>Water Design Engineer</t>
+        </is>
+      </c>
+      <c r="D423" s="33" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E423" s="33" t="inlineStr">
+        <is>
+          <t>Surrey, South East England</t>
+        </is>
+      </c>
+      <c r="F423" s="33" t="inlineStr">
+        <is>
+          <t>£39,730 – £39,730</t>
+        </is>
+      </c>
+      <c r="G423" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H423" s="37" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="I423" s="33" t="n">
+        <v>140</v>
+      </c>
+      <c r="J423" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K423" s="35" t="inlineStr"/>
+      <c r="L423" s="35" t="inlineStr"/>
+      <c r="M423" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N423" s="36" t="inlineStr"/>
+      <c r="O423" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -25937,6 +25996,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J420" r:id="rId151"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J421" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J422" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J423" r:id="rId154"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O423"/>
+  <dimension ref="A1:O427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -25829,6 +25829,242 @@
       </c>
       <c r="N423" s="36" t="inlineStr"/>
       <c r="O423" s="35" t="inlineStr"/>
+    </row>
+    <row r="424" ht="16" customHeight="1">
+      <c r="A424" s="28" t="inlineStr">
+        <is>
+          <t>616dea57aace</t>
+        </is>
+      </c>
+      <c r="B424" s="28" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="C424" s="28" t="inlineStr">
+        <is>
+          <t>Project Manager - Water Infrastructure</t>
+        </is>
+      </c>
+      <c r="D424" s="28" t="inlineStr">
+        <is>
+          <t>AtkinsRéalis</t>
+        </is>
+      </c>
+      <c r="E424" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F424" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G424" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H424" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I424" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="J424" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K424" s="31" t="inlineStr"/>
+      <c r="L424" s="31" t="inlineStr"/>
+      <c r="M424" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N424" s="32" t="inlineStr"/>
+      <c r="O424" s="31" t="inlineStr"/>
+    </row>
+    <row r="425" ht="16" customHeight="1">
+      <c r="A425" s="33" t="inlineStr">
+        <is>
+          <t>3d813f3f32f5</t>
+        </is>
+      </c>
+      <c r="B425" s="33" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="C425" s="33" t="inlineStr">
+        <is>
+          <t>Water Design Engineer</t>
+        </is>
+      </c>
+      <c r="D425" s="33" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E425" s="33" t="inlineStr">
+        <is>
+          <t>Surrey, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F425" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G425" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H425" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I425" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="J425" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K425" s="35" t="inlineStr"/>
+      <c r="L425" s="35" t="inlineStr"/>
+      <c r="M425" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N425" s="36" t="inlineStr"/>
+      <c r="O425" s="35" t="inlineStr"/>
+    </row>
+    <row r="426" ht="16" customHeight="1">
+      <c r="A426" s="28" t="inlineStr">
+        <is>
+          <t>2f3b77946507</t>
+        </is>
+      </c>
+      <c r="B426" s="28" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="C426" s="28" t="inlineStr">
+        <is>
+          <t>Design Engineer – Wastewater</t>
+        </is>
+      </c>
+      <c r="D426" s="28" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E426" s="28" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F426" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G426" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H426" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I426" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J426" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K426" s="31" t="inlineStr"/>
+      <c r="L426" s="31" t="inlineStr"/>
+      <c r="M426" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N426" s="32" t="inlineStr"/>
+      <c r="O426" s="31" t="inlineStr"/>
+    </row>
+    <row r="427" ht="16" customHeight="1">
+      <c r="A427" s="33" t="inlineStr">
+        <is>
+          <t>20a00e6ec41e</t>
+        </is>
+      </c>
+      <c r="B427" s="33" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="C427" s="33" t="inlineStr">
+        <is>
+          <t>Design Engineer - Wastewater</t>
+        </is>
+      </c>
+      <c r="D427" s="33" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E427" s="33" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F427" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G427" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H427" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I427" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J427" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K427" s="35" t="inlineStr"/>
+      <c r="L427" s="35" t="inlineStr"/>
+      <c r="M427" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N427" s="36" t="inlineStr"/>
+      <c r="O427" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -25997,6 +26233,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J421" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J422" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J423" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J424" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J426" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J427" r:id="rId158"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O427"/>
+  <dimension ref="A1:O429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -26065,6 +26065,124 @@
       </c>
       <c r="N427" s="36" t="inlineStr"/>
       <c r="O427" s="35" t="inlineStr"/>
+    </row>
+    <row r="428" ht="16" customHeight="1">
+      <c r="A428" s="28" t="inlineStr">
+        <is>
+          <t>45198645c5fe</t>
+        </is>
+      </c>
+      <c r="B428" s="28" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="C428" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulic / Flood Modeller</t>
+        </is>
+      </c>
+      <c r="D428" s="28" t="inlineStr">
+        <is>
+          <t>Calibre Search</t>
+        </is>
+      </c>
+      <c r="E428" s="28" t="inlineStr">
+        <is>
+          <t>Bishopsgate, Central London</t>
+        </is>
+      </c>
+      <c r="F428" s="28" t="inlineStr">
+        <is>
+          <t>£28,000 – £40,000</t>
+        </is>
+      </c>
+      <c r="G428" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H428" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I428" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J428" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K428" s="31" t="inlineStr"/>
+      <c r="L428" s="31" t="inlineStr"/>
+      <c r="M428" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N428" s="32" t="inlineStr"/>
+      <c r="O428" s="31" t="inlineStr"/>
+    </row>
+    <row r="429" ht="16" customHeight="1">
+      <c r="A429" s="33" t="inlineStr">
+        <is>
+          <t>3bde9138c749</t>
+        </is>
+      </c>
+      <c r="B429" s="33" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="C429" s="33" t="inlineStr">
+        <is>
+          <t>Hydraulic / Flood Modeller</t>
+        </is>
+      </c>
+      <c r="D429" s="33" t="inlineStr">
+        <is>
+          <t>Calibre Search</t>
+        </is>
+      </c>
+      <c r="E429" s="33" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F429" s="33" t="inlineStr">
+        <is>
+          <t>£28,000 – £40,000</t>
+        </is>
+      </c>
+      <c r="G429" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H429" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I429" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J429" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K429" s="35" t="inlineStr"/>
+      <c r="L429" s="35" t="inlineStr"/>
+      <c r="M429" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N429" s="36" t="inlineStr"/>
+      <c r="O429" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -26237,6 +26355,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J426" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J427" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J428" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J429" r:id="rId160"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O429"/>
+  <dimension ref="A1:O430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -26183,6 +26183,65 @@
       </c>
       <c r="N429" s="36" t="inlineStr"/>
       <c r="O429" s="35" t="inlineStr"/>
+    </row>
+    <row r="430" ht="16" customHeight="1">
+      <c r="A430" s="28" t="inlineStr">
+        <is>
+          <t>6c55ea27b7e0</t>
+        </is>
+      </c>
+      <c r="B430" s="28" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C430" s="28" t="inlineStr">
+        <is>
+          <t>Water Design Engineer</t>
+        </is>
+      </c>
+      <c r="D430" s="28" t="inlineStr">
+        <is>
+          <t>Timely Recruit Ltd</t>
+        </is>
+      </c>
+      <c r="E430" s="28" t="inlineStr">
+        <is>
+          <t>Surrey, South East England</t>
+        </is>
+      </c>
+      <c r="F430" s="28" t="inlineStr">
+        <is>
+          <t>£39,730 – £39,730</t>
+        </is>
+      </c>
+      <c r="G430" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H430" s="37" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="I430" s="28" t="n">
+        <v>140</v>
+      </c>
+      <c r="J430" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K430" s="31" t="inlineStr"/>
+      <c r="L430" s="31" t="inlineStr"/>
+      <c r="M430" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N430" s="32" t="inlineStr"/>
+      <c r="O430" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -26357,6 +26416,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J427" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J428" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J429" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J430" r:id="rId161"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O430"/>
+  <dimension ref="A1:O432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -26242,6 +26242,124 @@
       </c>
       <c r="N430" s="32" t="inlineStr"/>
       <c r="O430" s="31" t="inlineStr"/>
+    </row>
+    <row r="431" ht="16" customHeight="1">
+      <c r="A431" s="33" t="inlineStr">
+        <is>
+          <t>f43b0d3be3bb</t>
+        </is>
+      </c>
+      <c r="B431" s="33" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="C431" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D431" s="33" t="inlineStr">
+        <is>
+          <t>Shirley Parsons</t>
+        </is>
+      </c>
+      <c r="E431" s="33" t="inlineStr">
+        <is>
+          <t>Hemel Hempstead, Hertfordshire</t>
+        </is>
+      </c>
+      <c r="F431" s="33" t="inlineStr">
+        <is>
+          <t>£45,594 – £45,594</t>
+        </is>
+      </c>
+      <c r="G431" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H431" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I431" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="J431" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K431" s="35" t="inlineStr"/>
+      <c r="L431" s="35" t="inlineStr"/>
+      <c r="M431" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N431" s="36" t="inlineStr"/>
+      <c r="O431" s="35" t="inlineStr"/>
+    </row>
+    <row r="432" ht="16" customHeight="1">
+      <c r="A432" s="28" t="inlineStr">
+        <is>
+          <t>65aac2ac2f1e</t>
+        </is>
+      </c>
+      <c r="B432" s="28" t="inlineStr">
+        <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="C432" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D432" s="28" t="inlineStr">
+        <is>
+          <t>Ganymede</t>
+        </is>
+      </c>
+      <c r="E432" s="28" t="inlineStr">
+        <is>
+          <t>England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F432" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G432" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H432" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I432" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J432" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K432" s="31" t="inlineStr"/>
+      <c r="L432" s="31" t="inlineStr"/>
+      <c r="M432" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N432" s="32" t="inlineStr"/>
+      <c r="O432" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -26417,6 +26535,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J428" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J429" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J430" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J431" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J432" r:id="rId163"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O432"/>
+  <dimension ref="A1:O434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -26360,6 +26360,124 @@
       </c>
       <c r="N432" s="32" t="inlineStr"/>
       <c r="O432" s="31" t="inlineStr"/>
+    </row>
+    <row r="433" ht="16" customHeight="1">
+      <c r="A433" s="33" t="inlineStr">
+        <is>
+          <t>ba74981d6755</t>
+        </is>
+      </c>
+      <c r="B433" s="33" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C433" s="33" t="inlineStr">
+        <is>
+          <t>Water Systems Design Engineer, Data Centre Design Engineering</t>
+        </is>
+      </c>
+      <c r="D433" s="33" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E433" s="33" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F433" s="33" t="inlineStr">
+        <is>
+          <t>£49,438 – £49,438</t>
+        </is>
+      </c>
+      <c r="G433" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H433" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I433" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="J433" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K433" s="35" t="inlineStr"/>
+      <c r="L433" s="35" t="inlineStr"/>
+      <c r="M433" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N433" s="36" t="inlineStr"/>
+      <c r="O433" s="35" t="inlineStr"/>
+    </row>
+    <row r="434" ht="16" customHeight="1">
+      <c r="A434" s="28" t="inlineStr">
+        <is>
+          <t>0f038bca8c87</t>
+        </is>
+      </c>
+      <c r="B434" s="28" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="C434" s="28" t="inlineStr">
+        <is>
+          <t>Water Systems Design Engineer, Data Centre Design Engineering</t>
+        </is>
+      </c>
+      <c r="D434" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amazon EU SARL </t>
+        </is>
+      </c>
+      <c r="E434" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F434" s="28" t="inlineStr">
+        <is>
+          <t>£49,135 – £49,135</t>
+        </is>
+      </c>
+      <c r="G434" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H434" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I434" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="J434" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K434" s="31" t="inlineStr"/>
+      <c r="L434" s="31" t="inlineStr"/>
+      <c r="M434" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N434" s="32" t="inlineStr"/>
+      <c r="O434" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -26537,6 +26655,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J430" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J431" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J432" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J433" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J434" r:id="rId165"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O434"/>
+  <dimension ref="A1:O435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -26478,6 +26478,65 @@
       </c>
       <c r="N434" s="32" t="inlineStr"/>
       <c r="O434" s="31" t="inlineStr"/>
+    </row>
+    <row r="435" ht="16" customHeight="1">
+      <c r="A435" s="33" t="inlineStr">
+        <is>
+          <t>2f6e1806d27f</t>
+        </is>
+      </c>
+      <c r="B435" s="33" t="inlineStr">
+        <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="C435" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D435" s="33" t="inlineStr">
+        <is>
+          <t>Recruiter</t>
+        </is>
+      </c>
+      <c r="E435" s="33" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F435" s="33" t="inlineStr">
+        <is>
+          <t>£45,940 – £68,000</t>
+        </is>
+      </c>
+      <c r="G435" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H435" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I435" s="33" t="n">
+        <v>110</v>
+      </c>
+      <c r="J435" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K435" s="35" t="inlineStr"/>
+      <c r="L435" s="35" t="inlineStr"/>
+      <c r="M435" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N435" s="36" t="inlineStr"/>
+      <c r="O435" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -26657,6 +26716,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J432" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J433" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J434" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J435" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O435"/>
+  <dimension ref="A1:O436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -26537,6 +26537,65 @@
       </c>
       <c r="N435" s="36" t="inlineStr"/>
       <c r="O435" s="35" t="inlineStr"/>
+    </row>
+    <row r="436" ht="16" customHeight="1">
+      <c r="A436" s="28" t="inlineStr">
+        <is>
+          <t>779e4855badd</t>
+        </is>
+      </c>
+      <c r="B436" s="28" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="C436" s="28" t="inlineStr">
+        <is>
+          <t>Water Systems Design Engineer, Data Centre Design Engineering</t>
+        </is>
+      </c>
+      <c r="D436" s="28" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="E436" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F436" s="28" t="inlineStr">
+        <is>
+          <t>£51,150 – £51,150</t>
+        </is>
+      </c>
+      <c r="G436" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H436" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I436" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="J436" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K436" s="31" t="inlineStr"/>
+      <c r="L436" s="31" t="inlineStr"/>
+      <c r="M436" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N436" s="32" t="inlineStr"/>
+      <c r="O436" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -26717,6 +26776,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J433" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J434" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J435" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J436" r:id="rId167"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O436"/>
+  <dimension ref="A1:O438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -26596,6 +26596,124 @@
       </c>
       <c r="N436" s="32" t="inlineStr"/>
       <c r="O436" s="31" t="inlineStr"/>
+    </row>
+    <row r="437" ht="16" customHeight="1">
+      <c r="A437" s="33" t="inlineStr">
+        <is>
+          <t>ccd30f1604f1</t>
+        </is>
+      </c>
+      <c r="B437" s="33" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="C437" s="33" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Wastewater Infrastructure</t>
+        </is>
+      </c>
+      <c r="D437" s="33" t="inlineStr">
+        <is>
+          <t>Aldwych Consulting Ltd</t>
+        </is>
+      </c>
+      <c r="E437" s="33" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F437" s="33" t="inlineStr">
+        <is>
+          <t>£40,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G437" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H437" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I437" s="33" t="n">
+        <v>85</v>
+      </c>
+      <c r="J437" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K437" s="35" t="inlineStr"/>
+      <c r="L437" s="35" t="inlineStr"/>
+      <c r="M437" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N437" s="36" t="inlineStr"/>
+      <c r="O437" s="35" t="inlineStr"/>
+    </row>
+    <row r="438" ht="16" customHeight="1">
+      <c r="A438" s="28" t="inlineStr">
+        <is>
+          <t>fbcf3a44cfce</t>
+        </is>
+      </c>
+      <c r="B438" s="28" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="C438" s="28" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Wastewater Infrastructure</t>
+        </is>
+      </c>
+      <c r="D438" s="28" t="inlineStr">
+        <is>
+          <t>Aldwych Consulting</t>
+        </is>
+      </c>
+      <c r="E438" s="28" t="inlineStr">
+        <is>
+          <t>Chalvey, Slough</t>
+        </is>
+      </c>
+      <c r="F438" s="28" t="inlineStr">
+        <is>
+          <t>£40,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G438" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H438" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I438" s="28" t="n">
+        <v>85</v>
+      </c>
+      <c r="J438" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K438" s="31" t="inlineStr"/>
+      <c r="L438" s="31" t="inlineStr"/>
+      <c r="M438" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N438" s="32" t="inlineStr"/>
+      <c r="O438" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -26777,6 +26895,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J434" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J435" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J436" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J437" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J438" r:id="rId169"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O438"/>
+  <dimension ref="A1:O439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -26714,6 +26714,65 @@
       </c>
       <c r="N438" s="32" t="inlineStr"/>
       <c r="O438" s="31" t="inlineStr"/>
+    </row>
+    <row r="439" ht="16" customHeight="1">
+      <c r="A439" s="33" t="inlineStr">
+        <is>
+          <t>26d50fa7ebd2</t>
+        </is>
+      </c>
+      <c r="B439" s="33" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="C439" s="33" t="inlineStr">
+        <is>
+          <t>Water Infrastructure Manager, AWS EMEA Energy &amp; Water Team</t>
+        </is>
+      </c>
+      <c r="D439" s="33" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="E439" s="33" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F439" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G439" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H439" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I439" s="33" t="n">
+        <v>65</v>
+      </c>
+      <c r="J439" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K439" s="35" t="inlineStr"/>
+      <c r="L439" s="35" t="inlineStr"/>
+      <c r="M439" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N439" s="36" t="inlineStr"/>
+      <c r="O439" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -26897,6 +26956,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J436" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J437" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J438" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J439" r:id="rId170"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O439"/>
+  <dimension ref="A1:O443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -26773,6 +26773,242 @@
       </c>
       <c r="N439" s="36" t="inlineStr"/>
       <c r="O439" s="35" t="inlineStr"/>
+    </row>
+    <row r="440" ht="16" customHeight="1">
+      <c r="A440" s="28" t="inlineStr">
+        <is>
+          <t>103f84cb765f</t>
+        </is>
+      </c>
+      <c r="B440" s="28" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="C440" s="28" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Wastewater Infrastructure</t>
+        </is>
+      </c>
+      <c r="D440" s="28" t="inlineStr">
+        <is>
+          <t>Aldwych Consulting Ltd</t>
+        </is>
+      </c>
+      <c r="E440" s="28" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F440" s="28" t="inlineStr">
+        <is>
+          <t>£55,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G440" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H440" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I440" s="28" t="n">
+        <v>85</v>
+      </c>
+      <c r="J440" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K440" s="31" t="inlineStr"/>
+      <c r="L440" s="31" t="inlineStr"/>
+      <c r="M440" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N440" s="32" t="inlineStr"/>
+      <c r="O440" s="31" t="inlineStr"/>
+    </row>
+    <row r="441" ht="16" customHeight="1">
+      <c r="A441" s="33" t="inlineStr">
+        <is>
+          <t>fd895c339a60</t>
+        </is>
+      </c>
+      <c r="B441" s="33" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="C441" s="33" t="inlineStr">
+        <is>
+          <t>Clean Water (Hydraulic) Modeller</t>
+        </is>
+      </c>
+      <c r="D441" s="33" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E441" s="33" t="inlineStr">
+        <is>
+          <t>Brighton, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F441" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G441" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H441" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I441" s="33" t="n">
+        <v>65</v>
+      </c>
+      <c r="J441" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K441" s="35" t="inlineStr"/>
+      <c r="L441" s="35" t="inlineStr"/>
+      <c r="M441" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N441" s="36" t="inlineStr"/>
+      <c r="O441" s="35" t="inlineStr"/>
+    </row>
+    <row r="442" ht="16" customHeight="1">
+      <c r="A442" s="28" t="inlineStr">
+        <is>
+          <t>fb19a9032563</t>
+        </is>
+      </c>
+      <c r="B442" s="28" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="C442" s="28" t="inlineStr">
+        <is>
+          <t>Water Infrastructure Manager, AWS EMEA Energy &amp; Water Team</t>
+        </is>
+      </c>
+      <c r="D442" s="28" t="inlineStr">
+        <is>
+          <t>myGwork - LGBTQ+ Business Community</t>
+        </is>
+      </c>
+      <c r="E442" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F442" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G442" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H442" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I442" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="J442" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K442" s="31" t="inlineStr"/>
+      <c r="L442" s="31" t="inlineStr"/>
+      <c r="M442" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N442" s="32" t="inlineStr"/>
+      <c r="O442" s="31" t="inlineStr"/>
+    </row>
+    <row r="443" ht="16" customHeight="1">
+      <c r="A443" s="33" t="inlineStr">
+        <is>
+          <t>9c8080a790a0</t>
+        </is>
+      </c>
+      <c r="B443" s="33" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="C443" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater (Hydraulic) Modeller</t>
+        </is>
+      </c>
+      <c r="D443" s="33" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E443" s="33" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F443" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G443" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H443" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I443" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J443" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K443" s="35" t="inlineStr"/>
+      <c r="L443" s="35" t="inlineStr"/>
+      <c r="M443" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N443" s="36" t="inlineStr"/>
+      <c r="O443" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -26957,6 +27193,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J437" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J438" r:id="rId169"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J439" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J440" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J441" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J442" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J443" r:id="rId174"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O443"/>
+  <dimension ref="A1:O444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -27009,6 +27009,65 @@
       </c>
       <c r="N443" s="36" t="inlineStr"/>
       <c r="O443" s="35" t="inlineStr"/>
+    </row>
+    <row r="444" ht="16" customHeight="1">
+      <c r="A444" s="28" t="inlineStr">
+        <is>
+          <t>050bb806e93f</t>
+        </is>
+      </c>
+      <c r="B444" s="28" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="C444" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller (Flood Risk Management)</t>
+        </is>
+      </c>
+      <c r="D444" s="28" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E444" s="28" t="inlineStr">
+        <is>
+          <t>Wokingham, Berkshire</t>
+        </is>
+      </c>
+      <c r="F444" s="28" t="inlineStr">
+        <is>
+          <t>£37,427 – £37,427</t>
+        </is>
+      </c>
+      <c r="G444" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H444" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I444" s="28" t="n">
+        <v>125</v>
+      </c>
+      <c r="J444" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K444" s="31" t="inlineStr"/>
+      <c r="L444" s="31" t="inlineStr"/>
+      <c r="M444" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N444" s="32" t="inlineStr"/>
+      <c r="O444" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -27197,6 +27256,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J441" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J442" r:id="rId173"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J443" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J444" r:id="rId175"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O444"/>
+  <dimension ref="A1:O445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -27068,6 +27068,65 @@
       </c>
       <c r="N444" s="32" t="inlineStr"/>
       <c r="O444" s="31" t="inlineStr"/>
+    </row>
+    <row r="445" ht="16" customHeight="1">
+      <c r="A445" s="33" t="inlineStr">
+        <is>
+          <t>e52c63dc6e00</t>
+        </is>
+      </c>
+      <c r="B445" s="33" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="C445" s="33" t="inlineStr">
+        <is>
+          <t>Design Manager - (Water Civil Engineering)</t>
+        </is>
+      </c>
+      <c r="D445" s="33" t="inlineStr">
+        <is>
+          <t>. WSP</t>
+        </is>
+      </c>
+      <c r="E445" s="33" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F445" s="33" t="inlineStr">
+        <is>
+          <t>£50,693 – £50,693</t>
+        </is>
+      </c>
+      <c r="G445" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H445" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I445" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="J445" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K445" s="35" t="inlineStr"/>
+      <c r="L445" s="35" t="inlineStr"/>
+      <c r="M445" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N445" s="36" t="inlineStr"/>
+      <c r="O445" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -27257,6 +27316,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J442" r:id="rId173"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J443" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J444" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J445" r:id="rId176"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O445"/>
+  <dimension ref="A1:O447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -27127,6 +27127,124 @@
       </c>
       <c r="N445" s="36" t="inlineStr"/>
       <c r="O445" s="35" t="inlineStr"/>
+    </row>
+    <row r="446" ht="16" customHeight="1">
+      <c r="A446" s="28" t="inlineStr">
+        <is>
+          <t>d63d7294d356</t>
+        </is>
+      </c>
+      <c r="B446" s="28" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="C446" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller- London</t>
+        </is>
+      </c>
+      <c r="D446" s="28" t="inlineStr">
+        <is>
+          <t>Aztrum</t>
+        </is>
+      </c>
+      <c r="E446" s="28" t="inlineStr">
+        <is>
+          <t>Farringdon, Central London</t>
+        </is>
+      </c>
+      <c r="F446" s="28" t="inlineStr">
+        <is>
+          <t>£35,000 – £45,000</t>
+        </is>
+      </c>
+      <c r="G446" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H446" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I446" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="J446" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K446" s="31" t="inlineStr"/>
+      <c r="L446" s="31" t="inlineStr"/>
+      <c r="M446" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N446" s="32" t="inlineStr"/>
+      <c r="O446" s="31" t="inlineStr"/>
+    </row>
+    <row r="447" ht="16" customHeight="1">
+      <c r="A447" s="33" t="inlineStr">
+        <is>
+          <t>b47f30c431e8</t>
+        </is>
+      </c>
+      <c r="B447" s="33" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="C447" s="33" t="inlineStr">
+        <is>
+          <t>Associate- Water Infrastructure</t>
+        </is>
+      </c>
+      <c r="D447" s="33" t="inlineStr">
+        <is>
+          <t>Arup</t>
+        </is>
+      </c>
+      <c r="E447" s="33" t="inlineStr">
+        <is>
+          <t>Manchester, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F447" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G447" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H447" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I447" s="33" t="n">
+        <v>65</v>
+      </c>
+      <c r="J447" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K447" s="35" t="inlineStr"/>
+      <c r="L447" s="35" t="inlineStr"/>
+      <c r="M447" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N447" s="36" t="inlineStr"/>
+      <c r="O447" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -27317,6 +27435,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J443" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J444" r:id="rId175"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J445" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J446" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J447" r:id="rId178"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O447"/>
+  <dimension ref="A1:O448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -27245,6 +27245,65 @@
       </c>
       <c r="N447" s="36" t="inlineStr"/>
       <c r="O447" s="35" t="inlineStr"/>
+    </row>
+    <row r="448" ht="16" customHeight="1">
+      <c r="A448" s="28" t="inlineStr">
+        <is>
+          <t>7e614d852700</t>
+        </is>
+      </c>
+      <c r="B448" s="28" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="C448" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D448" s="28" t="inlineStr">
+        <is>
+          <t>Pertemps Thames Water</t>
+        </is>
+      </c>
+      <c r="E448" s="28" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F448" s="28" t="inlineStr">
+        <is>
+          <t>£45,940 – £68,000</t>
+        </is>
+      </c>
+      <c r="G448" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H448" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I448" s="28" t="n">
+        <v>110</v>
+      </c>
+      <c r="J448" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K448" s="31" t="inlineStr"/>
+      <c r="L448" s="31" t="inlineStr"/>
+      <c r="M448" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N448" s="32" t="inlineStr"/>
+      <c r="O448" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -27437,6 +27496,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J445" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J446" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J447" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J448" r:id="rId179"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O448"/>
+  <dimension ref="A1:O451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -27304,6 +27304,183 @@
       </c>
       <c r="N448" s="32" t="inlineStr"/>
       <c r="O448" s="31" t="inlineStr"/>
+    </row>
+    <row r="449" ht="16" customHeight="1">
+      <c r="A449" s="33" t="inlineStr">
+        <is>
+          <t>393ede20b127</t>
+        </is>
+      </c>
+      <c r="B449" s="33" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="C449" s="33" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller- London</t>
+        </is>
+      </c>
+      <c r="D449" s="33" t="inlineStr">
+        <is>
+          <t>Aztrum</t>
+        </is>
+      </c>
+      <c r="E449" s="33" t="inlineStr">
+        <is>
+          <t>The City, Central London</t>
+        </is>
+      </c>
+      <c r="F449" s="33" t="inlineStr">
+        <is>
+          <t>£43,674 – £43,674</t>
+        </is>
+      </c>
+      <c r="G449" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H449" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I449" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="J449" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K449" s="35" t="inlineStr"/>
+      <c r="L449" s="35" t="inlineStr"/>
+      <c r="M449" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N449" s="36" t="inlineStr"/>
+      <c r="O449" s="35" t="inlineStr"/>
+    </row>
+    <row r="450" ht="16" customHeight="1">
+      <c r="A450" s="28" t="inlineStr">
+        <is>
+          <t>771dd63ab042</t>
+        </is>
+      </c>
+      <c r="B450" s="28" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="C450" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D450" s="28" t="inlineStr">
+        <is>
+          <t>Recruiter</t>
+        </is>
+      </c>
+      <c r="E450" s="28" t="inlineStr">
+        <is>
+          <t>Reading, Berkshire</t>
+        </is>
+      </c>
+      <c r="F450" s="28" t="inlineStr">
+        <is>
+          <t>£45,940 – £68,000</t>
+        </is>
+      </c>
+      <c r="G450" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H450" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I450" s="28" t="n">
+        <v>110</v>
+      </c>
+      <c r="J450" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K450" s="31" t="inlineStr"/>
+      <c r="L450" s="31" t="inlineStr"/>
+      <c r="M450" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N450" s="32" t="inlineStr"/>
+      <c r="O450" s="31" t="inlineStr"/>
+    </row>
+    <row r="451" ht="16" customHeight="1">
+      <c r="A451" s="33" t="inlineStr">
+        <is>
+          <t>e858138a587a</t>
+        </is>
+      </c>
+      <c r="B451" s="33" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="C451" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D451" s="33" t="inlineStr">
+        <is>
+          <t>Mott MacDonald</t>
+        </is>
+      </c>
+      <c r="E451" s="33" t="inlineStr">
+        <is>
+          <t>Cardiff, Wales, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F451" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G451" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H451" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I451" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J451" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K451" s="35" t="inlineStr"/>
+      <c r="L451" s="35" t="inlineStr"/>
+      <c r="M451" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N451" s="36" t="inlineStr"/>
+      <c r="O451" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -27497,6 +27674,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J446" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J447" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J448" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J449" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J450" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J451" r:id="rId182"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O451"/>
+  <dimension ref="A1:O452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -27481,6 +27481,65 @@
       </c>
       <c r="N451" s="36" t="inlineStr"/>
       <c r="O451" s="35" t="inlineStr"/>
+    </row>
+    <row r="452" ht="16" customHeight="1">
+      <c r="A452" s="28" t="inlineStr">
+        <is>
+          <t>f0da09a65c5b</t>
+        </is>
+      </c>
+      <c r="B452" s="28" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="C452" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D452" s="28" t="inlineStr">
+        <is>
+          <t>Thames Water</t>
+        </is>
+      </c>
+      <c r="E452" s="28" t="inlineStr">
+        <is>
+          <t>Pingewood, Reading</t>
+        </is>
+      </c>
+      <c r="F452" s="28" t="inlineStr">
+        <is>
+          <t>£45,940 – £68,000</t>
+        </is>
+      </c>
+      <c r="G452" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H452" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I452" s="28" t="n">
+        <v>110</v>
+      </c>
+      <c r="J452" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K452" s="31" t="inlineStr"/>
+      <c r="L452" s="31" t="inlineStr"/>
+      <c r="M452" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N452" s="32" t="inlineStr"/>
+      <c r="O452" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -27677,6 +27736,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J449" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J450" r:id="rId181"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J451" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J452" r:id="rId183"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O452"/>
+  <dimension ref="A1:O453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -27540,6 +27540,65 @@
       </c>
       <c r="N452" s="32" t="inlineStr"/>
       <c r="O452" s="31" t="inlineStr"/>
+    </row>
+    <row r="453" ht="16" customHeight="1">
+      <c r="A453" s="33" t="inlineStr">
+        <is>
+          <t>98a55b0735f9</t>
+        </is>
+      </c>
+      <c r="B453" s="33" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="C453" s="33" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D453" s="33" t="inlineStr">
+        <is>
+          <t>Pick Everard</t>
+        </is>
+      </c>
+      <c r="E453" s="33" t="inlineStr">
+        <is>
+          <t>Leicester, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F453" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G453" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H453" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I453" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="J453" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K453" s="35" t="inlineStr"/>
+      <c r="L453" s="35" t="inlineStr"/>
+      <c r="M453" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N453" s="36" t="inlineStr"/>
+      <c r="O453" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -27737,6 +27796,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J450" r:id="rId181"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J451" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J452" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J453" r:id="rId184"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O453"/>
+  <dimension ref="A1:O454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -27599,6 +27599,65 @@
       </c>
       <c r="N453" s="36" t="inlineStr"/>
       <c r="O453" s="35" t="inlineStr"/>
+    </row>
+    <row r="454" ht="16" customHeight="1">
+      <c r="A454" s="28" t="inlineStr">
+        <is>
+          <t>f335486a7fcc</t>
+        </is>
+      </c>
+      <c r="B454" s="28" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="C454" s="28" t="inlineStr">
+        <is>
+          <t>Water Systems Design Engineer, Data Centre Design Engineering</t>
+        </is>
+      </c>
+      <c r="D454" s="28" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="E454" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F454" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G454" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H454" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I454" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J454" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K454" s="31" t="inlineStr"/>
+      <c r="L454" s="31" t="inlineStr"/>
+      <c r="M454" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N454" s="32" t="inlineStr"/>
+      <c r="O454" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -27797,6 +27856,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J451" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J452" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J453" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J454" r:id="rId185"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O454"/>
+  <dimension ref="A1:O458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -27658,6 +27658,242 @@
       </c>
       <c r="N454" s="32" t="inlineStr"/>
       <c r="O454" s="31" t="inlineStr"/>
+    </row>
+    <row r="455" ht="16" customHeight="1">
+      <c r="A455" s="33" t="inlineStr">
+        <is>
+          <t>249f092a2cbf</t>
+        </is>
+      </c>
+      <c r="B455" s="33" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="C455" s="33" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Wastewater Infrastructure</t>
+        </is>
+      </c>
+      <c r="D455" s="33" t="inlineStr">
+        <is>
+          <t>Aldwych Consulting Ltd</t>
+        </is>
+      </c>
+      <c r="E455" s="33" t="inlineStr">
+        <is>
+          <t>Hampshire, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F455" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G455" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H455" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I455" s="33" t="n">
+        <v>65</v>
+      </c>
+      <c r="J455" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K455" s="35" t="inlineStr"/>
+      <c r="L455" s="35" t="inlineStr"/>
+      <c r="M455" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N455" s="36" t="inlineStr"/>
+      <c r="O455" s="35" t="inlineStr"/>
+    </row>
+    <row r="456" ht="16" customHeight="1">
+      <c r="A456" s="28" t="inlineStr">
+        <is>
+          <t>adc294b60d0a</t>
+        </is>
+      </c>
+      <c r="B456" s="28" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="C456" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Industry</t>
+        </is>
+      </c>
+      <c r="D456" s="28" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E456" s="28" t="inlineStr">
+        <is>
+          <t>Brighton, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F456" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G456" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H456" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I456" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J456" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K456" s="31" t="inlineStr"/>
+      <c r="L456" s="31" t="inlineStr"/>
+      <c r="M456" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N456" s="32" t="inlineStr"/>
+      <c r="O456" s="31" t="inlineStr"/>
+    </row>
+    <row r="457" ht="16" customHeight="1">
+      <c r="A457" s="33" t="inlineStr">
+        <is>
+          <t>bdd4cd4c17c3</t>
+        </is>
+      </c>
+      <c r="B457" s="33" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="C457" s="33" t="inlineStr">
+        <is>
+          <t>Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D457" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E457" s="33" t="inlineStr">
+        <is>
+          <t>Leeds, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F457" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G457" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H457" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I457" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J457" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K457" s="35" t="inlineStr"/>
+      <c r="L457" s="35" t="inlineStr"/>
+      <c r="M457" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N457" s="36" t="inlineStr"/>
+      <c r="O457" s="35" t="inlineStr"/>
+    </row>
+    <row r="458" ht="16" customHeight="1">
+      <c r="A458" s="28" t="inlineStr">
+        <is>
+          <t>d319818fcec2</t>
+        </is>
+      </c>
+      <c r="B458" s="28" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="C458" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulic / Flood Modeller</t>
+        </is>
+      </c>
+      <c r="D458" s="28" t="inlineStr">
+        <is>
+          <t>Calibre Search</t>
+        </is>
+      </c>
+      <c r="E458" s="28" t="inlineStr">
+        <is>
+          <t>Bishopsgate, Central London</t>
+        </is>
+      </c>
+      <c r="F458" s="28" t="inlineStr">
+        <is>
+          <t>£28,000 – £40,000</t>
+        </is>
+      </c>
+      <c r="G458" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H458" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I458" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J458" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K458" s="31" t="inlineStr"/>
+      <c r="L458" s="31" t="inlineStr"/>
+      <c r="M458" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N458" s="32" t="inlineStr"/>
+      <c r="O458" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -27857,6 +28093,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J452" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J453" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J454" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J455" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J456" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J457" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J458" r:id="rId189"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O458"/>
+  <dimension ref="A1:O460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -27894,6 +27894,124 @@
       </c>
       <c r="N458" s="32" t="inlineStr"/>
       <c r="O458" s="31" t="inlineStr"/>
+    </row>
+    <row r="459" ht="16" customHeight="1">
+      <c r="A459" s="33" t="inlineStr">
+        <is>
+          <t>a6af65ef7551</t>
+        </is>
+      </c>
+      <c r="B459" s="33" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="C459" s="33" t="inlineStr">
+        <is>
+          <t>Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D459" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E459" s="33" t="inlineStr">
+        <is>
+          <t>High Wycombe, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="F459" s="33" t="inlineStr">
+        <is>
+          <t>£49,205 – £49,205</t>
+        </is>
+      </c>
+      <c r="G459" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H459" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I459" s="33" t="n">
+        <v>70</v>
+      </c>
+      <c r="J459" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K459" s="35" t="inlineStr"/>
+      <c r="L459" s="35" t="inlineStr"/>
+      <c r="M459" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N459" s="36" t="inlineStr"/>
+      <c r="O459" s="35" t="inlineStr"/>
+    </row>
+    <row r="460" ht="16" customHeight="1">
+      <c r="A460" s="28" t="inlineStr">
+        <is>
+          <t>4f277857c788</t>
+        </is>
+      </c>
+      <c r="B460" s="28" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="C460" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulic / Flood Modeller</t>
+        </is>
+      </c>
+      <c r="D460" s="28" t="inlineStr">
+        <is>
+          <t>Calibre Search</t>
+        </is>
+      </c>
+      <c r="E460" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F460" s="28" t="inlineStr">
+        <is>
+          <t>£28,000 – £40,000</t>
+        </is>
+      </c>
+      <c r="G460" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H460" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I460" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J460" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K460" s="31" t="inlineStr"/>
+      <c r="L460" s="31" t="inlineStr"/>
+      <c r="M460" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N460" s="32" t="inlineStr"/>
+      <c r="O460" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -28097,6 +28215,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J456" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J457" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J458" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J459" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J460" r:id="rId191"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O460"/>
+  <dimension ref="A1:O461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -28012,6 +28012,65 @@
       </c>
       <c r="N460" s="32" t="inlineStr"/>
       <c r="O460" s="31" t="inlineStr"/>
+    </row>
+    <row r="461" ht="16" customHeight="1">
+      <c r="A461" s="33" t="inlineStr">
+        <is>
+          <t>bcbd55d11cc3</t>
+        </is>
+      </c>
+      <c r="B461" s="33" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="C461" s="33" t="inlineStr">
+        <is>
+          <t>(Water) Civil Design Engineers / Engineers - North West / Various Locations and Various Levels</t>
+        </is>
+      </c>
+      <c r="D461" s="33" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E461" s="33" t="inlineStr">
+        <is>
+          <t>Manchester, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F461" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G461" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H461" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I461" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J461" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K461" s="35" t="inlineStr"/>
+      <c r="L461" s="35" t="inlineStr"/>
+      <c r="M461" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N461" s="36" t="inlineStr"/>
+      <c r="O461" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -28217,6 +28276,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J458" r:id="rId189"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J459" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J460" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J461" r:id="rId192"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O461"/>
+  <dimension ref="A1:O464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -28071,6 +28071,183 @@
       </c>
       <c r="N461" s="36" t="inlineStr"/>
       <c r="O461" s="35" t="inlineStr"/>
+    </row>
+    <row r="462" ht="16" customHeight="1">
+      <c r="A462" s="28" t="inlineStr">
+        <is>
+          <t>001e77bc2182</t>
+        </is>
+      </c>
+      <c r="B462" s="28" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C462" s="28" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Wastewater Infrastructure</t>
+        </is>
+      </c>
+      <c r="D462" s="28" t="inlineStr">
+        <is>
+          <t>ALDWYCH CONSULTING LTD</t>
+        </is>
+      </c>
+      <c r="E462" s="28" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F462" s="28" t="inlineStr">
+        <is>
+          <t>£55,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G462" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H462" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I462" s="28" t="n">
+        <v>85</v>
+      </c>
+      <c r="J462" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K462" s="31" t="inlineStr"/>
+      <c r="L462" s="31" t="inlineStr"/>
+      <c r="M462" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N462" s="32" t="inlineStr"/>
+      <c r="O462" s="31" t="inlineStr"/>
+    </row>
+    <row r="463" ht="16" customHeight="1">
+      <c r="A463" s="33" t="inlineStr">
+        <is>
+          <t>ff823ff01be3</t>
+        </is>
+      </c>
+      <c r="B463" s="33" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C463" s="33" t="inlineStr">
+        <is>
+          <t>Associate- Water Infrastructure</t>
+        </is>
+      </c>
+      <c r="D463" s="33" t="inlineStr">
+        <is>
+          <t>Arup</t>
+        </is>
+      </c>
+      <c r="E463" s="33" t="inlineStr">
+        <is>
+          <t>Liverpool, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F463" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G463" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H463" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I463" s="33" t="n">
+        <v>65</v>
+      </c>
+      <c r="J463" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K463" s="35" t="inlineStr"/>
+      <c r="L463" s="35" t="inlineStr"/>
+      <c r="M463" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N463" s="36" t="inlineStr"/>
+      <c r="O463" s="35" t="inlineStr"/>
+    </row>
+    <row r="464" ht="16" customHeight="1">
+      <c r="A464" s="28" t="inlineStr">
+        <is>
+          <t>9c506934ea3d</t>
+        </is>
+      </c>
+      <c r="B464" s="28" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C464" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Design Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D464" s="28" t="inlineStr">
+        <is>
+          <t>Finlay Jude Associates Ltd</t>
+        </is>
+      </c>
+      <c r="E464" s="28" t="inlineStr">
+        <is>
+          <t>Batley, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F464" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G464" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H464" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I464" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J464" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K464" s="31" t="inlineStr"/>
+      <c r="L464" s="31" t="inlineStr"/>
+      <c r="M464" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N464" s="32" t="inlineStr"/>
+      <c r="O464" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -28277,6 +28454,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J459" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J460" r:id="rId191"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J461" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J462" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J463" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J464" r:id="rId195"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O464"/>
+  <dimension ref="A1:O467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -28248,6 +28248,183 @@
       </c>
       <c r="N464" s="32" t="inlineStr"/>
       <c r="O464" s="31" t="inlineStr"/>
+    </row>
+    <row r="465" ht="16" customHeight="1">
+      <c r="A465" s="33" t="inlineStr">
+        <is>
+          <t>4be7c51e8a24</t>
+        </is>
+      </c>
+      <c r="B465" s="33" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C465" s="33" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller (Flood Risk Management)</t>
+        </is>
+      </c>
+      <c r="D465" s="33" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E465" s="33" t="inlineStr">
+        <is>
+          <t>Wokingham, Berkshire</t>
+        </is>
+      </c>
+      <c r="F465" s="33" t="inlineStr">
+        <is>
+          <t>£37,445 – £37,445</t>
+        </is>
+      </c>
+      <c r="G465" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H465" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I465" s="33" t="n">
+        <v>125</v>
+      </c>
+      <c r="J465" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K465" s="35" t="inlineStr"/>
+      <c r="L465" s="35" t="inlineStr"/>
+      <c r="M465" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N465" s="36" t="inlineStr"/>
+      <c r="O465" s="35" t="inlineStr"/>
+    </row>
+    <row r="466" ht="16" customHeight="1">
+      <c r="A466" s="28" t="inlineStr">
+        <is>
+          <t>ffda5da6b97f</t>
+        </is>
+      </c>
+      <c r="B466" s="28" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C466" s="28" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Wastewater Infrastructure</t>
+        </is>
+      </c>
+      <c r="D466" s="28" t="inlineStr">
+        <is>
+          <t>Aldwych Consulting Ltd</t>
+        </is>
+      </c>
+      <c r="E466" s="28" t="inlineStr">
+        <is>
+          <t>Hampshire, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F466" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G466" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H466" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I466" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="J466" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K466" s="31" t="inlineStr"/>
+      <c r="L466" s="31" t="inlineStr"/>
+      <c r="M466" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N466" s="32" t="inlineStr"/>
+      <c r="O466" s="31" t="inlineStr"/>
+    </row>
+    <row r="467" ht="16" customHeight="1">
+      <c r="A467" s="33" t="inlineStr">
+        <is>
+          <t>06bfbd1246af</t>
+        </is>
+      </c>
+      <c r="B467" s="33" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="C467" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Industry</t>
+        </is>
+      </c>
+      <c r="D467" s="33" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E467" s="33" t="inlineStr">
+        <is>
+          <t>Glasgow, Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F467" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G467" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H467" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I467" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J467" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K467" s="35" t="inlineStr"/>
+      <c r="L467" s="35" t="inlineStr"/>
+      <c r="M467" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N467" s="36" t="inlineStr"/>
+      <c r="O467" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -28457,6 +28634,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J462" r:id="rId193"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J463" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J464" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J465" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J466" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J467" r:id="rId198"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O467"/>
+  <dimension ref="A1:O469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -28425,6 +28425,124 @@
       </c>
       <c r="N467" s="36" t="inlineStr"/>
       <c r="O467" s="35" t="inlineStr"/>
+    </row>
+    <row r="468" ht="16" customHeight="1">
+      <c r="A468" s="28" t="inlineStr">
+        <is>
+          <t>a05172de2aa4</t>
+        </is>
+      </c>
+      <c r="B468" s="28" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="C468" s="28" t="inlineStr">
+        <is>
+          <t>Hydrologist | Flood Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D468" s="28" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E468" s="28" t="inlineStr">
+        <is>
+          <t>Manchester, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F468" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G468" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H468" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I468" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J468" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K468" s="31" t="inlineStr"/>
+      <c r="L468" s="31" t="inlineStr"/>
+      <c r="M468" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N468" s="32" t="inlineStr"/>
+      <c r="O468" s="31" t="inlineStr"/>
+    </row>
+    <row r="469" ht="16" customHeight="1">
+      <c r="A469" s="33" t="inlineStr">
+        <is>
+          <t>417980a8399a</t>
+        </is>
+      </c>
+      <c r="B469" s="33" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="C469" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Industry</t>
+        </is>
+      </c>
+      <c r="D469" s="33" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E469" s="33" t="inlineStr">
+        <is>
+          <t>Glasgow, Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F469" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G469" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H469" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I469" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J469" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K469" s="35" t="inlineStr"/>
+      <c r="L469" s="35" t="inlineStr"/>
+      <c r="M469" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N469" s="36" t="inlineStr"/>
+      <c r="O469" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -28637,6 +28755,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J465" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J466" r:id="rId197"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J467" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J468" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J469" r:id="rId200"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O469"/>
+  <dimension ref="A1:O471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -28543,6 +28543,124 @@
       </c>
       <c r="N469" s="36" t="inlineStr"/>
       <c r="O469" s="35" t="inlineStr"/>
+    </row>
+    <row r="470" ht="16" customHeight="1">
+      <c r="A470" s="28" t="inlineStr">
+        <is>
+          <t>5a97cb3bb79e</t>
+        </is>
+      </c>
+      <c r="B470" s="28" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C470" s="28" t="inlineStr">
+        <is>
+          <t>Clean Water (Hydraulic) Modeller</t>
+        </is>
+      </c>
+      <c r="D470" s="28" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E470" s="28" t="inlineStr">
+        <is>
+          <t>Abingdon-On-Thames, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F470" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G470" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H470" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I470" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="J470" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K470" s="31" t="inlineStr"/>
+      <c r="L470" s="31" t="inlineStr"/>
+      <c r="M470" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N470" s="32" t="inlineStr"/>
+      <c r="O470" s="31" t="inlineStr"/>
+    </row>
+    <row r="471" ht="16" customHeight="1">
+      <c r="A471" s="33" t="inlineStr">
+        <is>
+          <t>6d74c305065a</t>
+        </is>
+      </c>
+      <c r="B471" s="33" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="C471" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Industry</t>
+        </is>
+      </c>
+      <c r="D471" s="33" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E471" s="33" t="inlineStr">
+        <is>
+          <t>Glasgow, Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F471" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G471" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H471" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I471" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J471" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K471" s="35" t="inlineStr"/>
+      <c r="L471" s="35" t="inlineStr"/>
+      <c r="M471" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N471" s="36" t="inlineStr"/>
+      <c r="O471" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -28757,6 +28875,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J467" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J468" r:id="rId199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J469" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J470" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J471" r:id="rId202"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O471"/>
+  <dimension ref="A1:O472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -28661,6 +28661,65 @@
       </c>
       <c r="N471" s="36" t="inlineStr"/>
       <c r="O471" s="35" t="inlineStr"/>
+    </row>
+    <row r="472" ht="16" customHeight="1">
+      <c r="A472" s="28" t="inlineStr">
+        <is>
+          <t>5b0007aa454f</t>
+        </is>
+      </c>
+      <c r="B472" s="28" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="C472" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Civil Design Engineer</t>
+        </is>
+      </c>
+      <c r="D472" s="28" t="inlineStr">
+        <is>
+          <t>Finlay Jude Associates Ltd</t>
+        </is>
+      </c>
+      <c r="E472" s="28" t="inlineStr">
+        <is>
+          <t>Leeds, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F472" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G472" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H472" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I472" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J472" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K472" s="31" t="inlineStr"/>
+      <c r="L472" s="31" t="inlineStr"/>
+      <c r="M472" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N472" s="32" t="inlineStr"/>
+      <c r="O472" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -28877,6 +28936,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J469" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J470" r:id="rId201"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J471" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J472" r:id="rId203"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O472"/>
+  <dimension ref="A1:O473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -28720,6 +28720,65 @@
       </c>
       <c r="N472" s="32" t="inlineStr"/>
       <c r="O472" s="31" t="inlineStr"/>
+    </row>
+    <row r="473" ht="16" customHeight="1">
+      <c r="A473" s="33" t="inlineStr">
+        <is>
+          <t>10a4e9e5e48f</t>
+        </is>
+      </c>
+      <c r="B473" s="33" t="inlineStr">
+        <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="C473" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Sector AMP8</t>
+        </is>
+      </c>
+      <c r="D473" s="33" t="inlineStr">
+        <is>
+          <t>Arcadis</t>
+        </is>
+      </c>
+      <c r="E473" s="33" t="inlineStr">
+        <is>
+          <t>Manchester, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F473" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G473" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H473" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I473" s="33" t="n">
+        <v>75</v>
+      </c>
+      <c r="J473" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K473" s="35" t="inlineStr"/>
+      <c r="L473" s="35" t="inlineStr"/>
+      <c r="M473" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N473" s="36" t="inlineStr"/>
+      <c r="O473" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -28937,6 +28996,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J470" r:id="rId201"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J471" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J472" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J473" r:id="rId204"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O473"/>
+  <dimension ref="A1:O474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -28779,6 +28779,65 @@
       </c>
       <c r="N473" s="36" t="inlineStr"/>
       <c r="O473" s="35" t="inlineStr"/>
+    </row>
+    <row r="474" ht="16" customHeight="1">
+      <c r="A474" s="28" t="inlineStr">
+        <is>
+          <t>5d97fcf71c50</t>
+        </is>
+      </c>
+      <c r="B474" s="28" t="inlineStr">
+        <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="C474" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Design Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D474" s="28" t="inlineStr">
+        <is>
+          <t>M Group Water</t>
+        </is>
+      </c>
+      <c r="E474" s="28" t="inlineStr">
+        <is>
+          <t>Birstall, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F474" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G474" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H474" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I474" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J474" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K474" s="31" t="inlineStr"/>
+      <c r="L474" s="31" t="inlineStr"/>
+      <c r="M474" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N474" s="32" t="inlineStr"/>
+      <c r="O474" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -28997,6 +29056,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J471" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J472" r:id="rId203"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J473" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J474" r:id="rId205"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O474"/>
+  <dimension ref="A1:O475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -28838,6 +28838,65 @@
       </c>
       <c r="N474" s="32" t="inlineStr"/>
       <c r="O474" s="31" t="inlineStr"/>
+    </row>
+    <row r="475" ht="16" customHeight="1">
+      <c r="A475" s="33" t="inlineStr">
+        <is>
+          <t>6319c548f22b</t>
+        </is>
+      </c>
+      <c r="B475" s="33" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="C475" s="33" t="inlineStr">
+        <is>
+          <t>Design Manager - Water Sector</t>
+        </is>
+      </c>
+      <c r="D475" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E475" s="33" t="inlineStr">
+        <is>
+          <t>Reading, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F475" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G475" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H475" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I475" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J475" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K475" s="35" t="inlineStr"/>
+      <c r="L475" s="35" t="inlineStr"/>
+      <c r="M475" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N475" s="36" t="inlineStr"/>
+      <c r="O475" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -29057,6 +29116,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J472" r:id="rId203"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J473" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J474" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J475" r:id="rId206"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O475"/>
+  <dimension ref="A1:O477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -28897,6 +28897,124 @@
       </c>
       <c r="N475" s="36" t="inlineStr"/>
       <c r="O475" s="35" t="inlineStr"/>
+    </row>
+    <row r="476" ht="16" customHeight="1">
+      <c r="A476" s="28" t="inlineStr">
+        <is>
+          <t>e1f819a4297b</t>
+        </is>
+      </c>
+      <c r="B476" s="28" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="C476" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller (Flood Risk Management)</t>
+        </is>
+      </c>
+      <c r="D476" s="28" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E476" s="28" t="inlineStr">
+        <is>
+          <t>Wokingham, Berkshire</t>
+        </is>
+      </c>
+      <c r="F476" s="28" t="inlineStr">
+        <is>
+          <t>£37,427 – £37,427</t>
+        </is>
+      </c>
+      <c r="G476" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H476" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I476" s="28" t="n">
+        <v>125</v>
+      </c>
+      <c r="J476" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K476" s="31" t="inlineStr"/>
+      <c r="L476" s="31" t="inlineStr"/>
+      <c r="M476" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N476" s="32" t="inlineStr"/>
+      <c r="O476" s="31" t="inlineStr"/>
+    </row>
+    <row r="477" ht="16" customHeight="1">
+      <c r="A477" s="33" t="inlineStr">
+        <is>
+          <t>074d9d8a8a7f</t>
+        </is>
+      </c>
+      <c r="B477" s="33" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="C477" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer (Wastewater Infrastructure)</t>
+        </is>
+      </c>
+      <c r="D477" s="33" t="inlineStr">
+        <is>
+          <t>J&amp;T Business Consulting</t>
+        </is>
+      </c>
+      <c r="E477" s="33" t="inlineStr">
+        <is>
+          <t>Slough, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F477" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G477" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H477" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I477" s="33" t="n">
+        <v>65</v>
+      </c>
+      <c r="J477" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K477" s="35" t="inlineStr"/>
+      <c r="L477" s="35" t="inlineStr"/>
+      <c r="M477" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N477" s="36" t="inlineStr"/>
+      <c r="O477" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -29117,6 +29235,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J473" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J474" r:id="rId205"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J475" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J476" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J477" r:id="rId208"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O477"/>
+  <dimension ref="A1:O478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -29015,6 +29015,65 @@
       </c>
       <c r="N477" s="36" t="inlineStr"/>
       <c r="O477" s="35" t="inlineStr"/>
+    </row>
+    <row r="478" ht="16" customHeight="1">
+      <c r="A478" s="28" t="inlineStr">
+        <is>
+          <t>08ce52d81488</t>
+        </is>
+      </c>
+      <c r="B478" s="28" t="inlineStr">
+        <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="C478" s="28" t="inlineStr">
+        <is>
+          <t>Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D478" s="28" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E478" s="28" t="inlineStr">
+        <is>
+          <t>Newcastle Upon Tyne, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F478" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G478" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H478" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I478" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J478" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K478" s="31" t="inlineStr"/>
+      <c r="L478" s="31" t="inlineStr"/>
+      <c r="M478" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N478" s="32" t="inlineStr"/>
+      <c r="O478" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -29237,6 +29296,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J475" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J476" r:id="rId207"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J477" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J478" r:id="rId209"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O478"/>
+  <dimension ref="A1:O480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -29074,6 +29074,124 @@
       </c>
       <c r="N478" s="32" t="inlineStr"/>
       <c r="O478" s="31" t="inlineStr"/>
+    </row>
+    <row r="479" ht="16" customHeight="1">
+      <c r="A479" s="33" t="inlineStr">
+        <is>
+          <t>40f2545fb8c8</t>
+        </is>
+      </c>
+      <c r="B479" s="33" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="C479" s="33" t="inlineStr">
+        <is>
+          <t>EOI | Project Management Roles | Water Infrastructure Projects</t>
+        </is>
+      </c>
+      <c r="D479" s="33" t="inlineStr">
+        <is>
+          <t>Pershing Consultants</t>
+        </is>
+      </c>
+      <c r="E479" s="33" t="inlineStr">
+        <is>
+          <t>Holborn, Central London</t>
+        </is>
+      </c>
+      <c r="F479" s="33" t="inlineStr">
+        <is>
+          <t>£45,727 – £45,727</t>
+        </is>
+      </c>
+      <c r="G479" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H479" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I479" s="33" t="n">
+        <v>85</v>
+      </c>
+      <c r="J479" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K479" s="35" t="inlineStr"/>
+      <c r="L479" s="35" t="inlineStr"/>
+      <c r="M479" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N479" s="36" t="inlineStr"/>
+      <c r="O479" s="35" t="inlineStr"/>
+    </row>
+    <row r="480" ht="16" customHeight="1">
+      <c r="A480" s="28" t="inlineStr">
+        <is>
+          <t>15e1e6d86cd9</t>
+        </is>
+      </c>
+      <c r="B480" s="28" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="C480" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water</t>
+        </is>
+      </c>
+      <c r="D480" s="28" t="inlineStr">
+        <is>
+          <t>Matchtech</t>
+        </is>
+      </c>
+      <c r="E480" s="28" t="inlineStr">
+        <is>
+          <t>Cardiff, Wales, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F480" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G480" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H480" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I480" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J480" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K480" s="31" t="inlineStr"/>
+      <c r="L480" s="31" t="inlineStr"/>
+      <c r="M480" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N480" s="32" t="inlineStr"/>
+      <c r="O480" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -29297,6 +29415,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J476" r:id="rId207"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J477" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J478" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J479" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J480" r:id="rId211"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O480"/>
+  <dimension ref="A1:O481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -29192,6 +29192,65 @@
       </c>
       <c r="N480" s="32" t="inlineStr"/>
       <c r="O480" s="31" t="inlineStr"/>
+    </row>
+    <row r="481" ht="16" customHeight="1">
+      <c r="A481" s="33" t="inlineStr">
+        <is>
+          <t>f3e1155b548a</t>
+        </is>
+      </c>
+      <c r="B481" s="33" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="C481" s="33" t="inlineStr">
+        <is>
+          <t>EOI | Project Management Roles | Water Infrastructure Projects</t>
+        </is>
+      </c>
+      <c r="D481" s="33" t="inlineStr">
+        <is>
+          <t>Pershing Consultants</t>
+        </is>
+      </c>
+      <c r="E481" s="33" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F481" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G481" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H481" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I481" s="33" t="n">
+        <v>65</v>
+      </c>
+      <c r="J481" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K481" s="35" t="inlineStr"/>
+      <c r="L481" s="35" t="inlineStr"/>
+      <c r="M481" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N481" s="36" t="inlineStr"/>
+      <c r="O481" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -29417,6 +29476,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J478" r:id="rId209"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J479" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J480" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J481" r:id="rId212"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O481"/>
+  <dimension ref="A1:O483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -29251,6 +29251,124 @@
       </c>
       <c r="N481" s="36" t="inlineStr"/>
       <c r="O481" s="35" t="inlineStr"/>
+    </row>
+    <row r="482" ht="16" customHeight="1">
+      <c r="A482" s="28" t="inlineStr">
+        <is>
+          <t>5c73625b1710</t>
+        </is>
+      </c>
+      <c r="B482" s="28" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="C482" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer (Wastewater Infrastructure)</t>
+        </is>
+      </c>
+      <c r="D482" s="28" t="inlineStr">
+        <is>
+          <t>J&amp;T Business Consulting</t>
+        </is>
+      </c>
+      <c r="E482" s="28" t="inlineStr">
+        <is>
+          <t>Chalvey, Slough</t>
+        </is>
+      </c>
+      <c r="F482" s="28" t="inlineStr">
+        <is>
+          <t>£47,723 – £47,723</t>
+        </is>
+      </c>
+      <c r="G482" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H482" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I482" s="28" t="n">
+        <v>85</v>
+      </c>
+      <c r="J482" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K482" s="31" t="inlineStr"/>
+      <c r="L482" s="31" t="inlineStr"/>
+      <c r="M482" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N482" s="32" t="inlineStr"/>
+      <c r="O482" s="31" t="inlineStr"/>
+    </row>
+    <row r="483" ht="16" customHeight="1">
+      <c r="A483" s="33" t="inlineStr">
+        <is>
+          <t>c42f27e7aa88</t>
+        </is>
+      </c>
+      <c r="B483" s="33" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="C483" s="33" t="inlineStr">
+        <is>
+          <t>(Water) Civil Design Engineers / Engineers - North West / Various Locations and Various Levels</t>
+        </is>
+      </c>
+      <c r="D483" s="33" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E483" s="33" t="inlineStr">
+        <is>
+          <t>Birmingham, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F483" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G483" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H483" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I483" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J483" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K483" s="35" t="inlineStr"/>
+      <c r="L483" s="35" t="inlineStr"/>
+      <c r="M483" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N483" s="36" t="inlineStr"/>
+      <c r="O483" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -29477,6 +29595,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J479" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J480" r:id="rId211"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J481" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J482" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J483" r:id="rId214"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O483"/>
+  <dimension ref="A1:O485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -29369,6 +29369,124 @@
       </c>
       <c r="N483" s="36" t="inlineStr"/>
       <c r="O483" s="35" t="inlineStr"/>
+    </row>
+    <row r="484" ht="16" customHeight="1">
+      <c r="A484" s="28" t="inlineStr">
+        <is>
+          <t>c6c9c7e5dbe9</t>
+        </is>
+      </c>
+      <c r="B484" s="28" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="C484" s="28" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Wastewater Infrastructure</t>
+        </is>
+      </c>
+      <c r="D484" s="28" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment Ltd</t>
+        </is>
+      </c>
+      <c r="E484" s="28" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F484" s="28" t="inlineStr">
+        <is>
+          <t>£40,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G484" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H484" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I484" s="28" t="n">
+        <v>85</v>
+      </c>
+      <c r="J484" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K484" s="31" t="inlineStr"/>
+      <c r="L484" s="31" t="inlineStr"/>
+      <c r="M484" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N484" s="32" t="inlineStr"/>
+      <c r="O484" s="31" t="inlineStr"/>
+    </row>
+    <row r="485" ht="16" customHeight="1">
+      <c r="A485" s="33" t="inlineStr">
+        <is>
+          <t>fafa6dd19915</t>
+        </is>
+      </c>
+      <c r="B485" s="33" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="C485" s="33" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Wastewater Infrastructure</t>
+        </is>
+      </c>
+      <c r="D485" s="33" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment</t>
+        </is>
+      </c>
+      <c r="E485" s="33" t="inlineStr">
+        <is>
+          <t>Chalvey, Slough</t>
+        </is>
+      </c>
+      <c r="F485" s="33" t="inlineStr">
+        <is>
+          <t>£40,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G485" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H485" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I485" s="33" t="n">
+        <v>85</v>
+      </c>
+      <c r="J485" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K485" s="35" t="inlineStr"/>
+      <c r="L485" s="35" t="inlineStr"/>
+      <c r="M485" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N485" s="36" t="inlineStr"/>
+      <c r="O485" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -29597,6 +29715,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J481" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J482" r:id="rId213"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J483" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J484" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J485" r:id="rId216"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O485"/>
+  <dimension ref="A1:O486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -29487,6 +29487,65 @@
       </c>
       <c r="N485" s="36" t="inlineStr"/>
       <c r="O485" s="35" t="inlineStr"/>
+    </row>
+    <row r="486" ht="16" customHeight="1">
+      <c r="A486" s="28" t="inlineStr">
+        <is>
+          <t>b1b00f0e1554</t>
+        </is>
+      </c>
+      <c r="B486" s="28" t="inlineStr">
+        <is>
+          <t>28/06/2026</t>
+        </is>
+      </c>
+      <c r="C486" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller (Flood Risk Management)</t>
+        </is>
+      </c>
+      <c r="D486" s="28" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E486" s="28" t="inlineStr">
+        <is>
+          <t>Peterborough, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F486" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G486" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H486" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I486" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J486" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K486" s="31" t="inlineStr"/>
+      <c r="L486" s="31" t="inlineStr"/>
+      <c r="M486" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N486" s="32" t="inlineStr"/>
+      <c r="O486" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -29717,6 +29776,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J483" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J484" r:id="rId215"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J485" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J486" r:id="rId217"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O486"/>
+  <dimension ref="A1:O488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -29546,6 +29546,124 @@
       </c>
       <c r="N486" s="32" t="inlineStr"/>
       <c r="O486" s="31" t="inlineStr"/>
+    </row>
+    <row r="487" ht="16" customHeight="1">
+      <c r="A487" s="33" t="inlineStr">
+        <is>
+          <t>ffd5f559f4df</t>
+        </is>
+      </c>
+      <c r="B487" s="33" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="C487" s="33" t="inlineStr">
+        <is>
+          <t>Water Design Manager</t>
+        </is>
+      </c>
+      <c r="D487" s="33" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="E487" s="33" t="inlineStr">
+        <is>
+          <t>Basingstoke, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F487" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G487" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H487" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I487" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J487" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K487" s="35" t="inlineStr"/>
+      <c r="L487" s="35" t="inlineStr"/>
+      <c r="M487" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N487" s="36" t="inlineStr"/>
+      <c r="O487" s="35" t="inlineStr"/>
+    </row>
+    <row r="488" ht="16" customHeight="1">
+      <c r="A488" s="28" t="inlineStr">
+        <is>
+          <t>56397a65ab3e</t>
+        </is>
+      </c>
+      <c r="B488" s="28" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="C488" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D488" s="28" t="inlineStr">
+        <is>
+          <t>Mott MacDonald</t>
+        </is>
+      </c>
+      <c r="E488" s="28" t="inlineStr">
+        <is>
+          <t>Edinburgh, Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F488" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G488" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H488" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I488" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J488" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K488" s="31" t="inlineStr"/>
+      <c r="L488" s="31" t="inlineStr"/>
+      <c r="M488" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N488" s="32" t="inlineStr"/>
+      <c r="O488" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -29777,6 +29895,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J484" r:id="rId215"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J485" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J486" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J487" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J488" r:id="rId219"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O488"/>
+  <dimension ref="A1:O490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -29664,6 +29664,124 @@
       </c>
       <c r="N488" s="32" t="inlineStr"/>
       <c r="O488" s="31" t="inlineStr"/>
+    </row>
+    <row r="489" ht="16" customHeight="1">
+      <c r="A489" s="33" t="inlineStr">
+        <is>
+          <t>19a06ab5e592</t>
+        </is>
+      </c>
+      <c r="B489" s="33" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="C489" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater Design Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D489" s="33" t="inlineStr">
+        <is>
+          <t>Finlay Jude Associates Ltd</t>
+        </is>
+      </c>
+      <c r="E489" s="33" t="inlineStr">
+        <is>
+          <t>Batley, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F489" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G489" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H489" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I489" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J489" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K489" s="35" t="inlineStr"/>
+      <c r="L489" s="35" t="inlineStr"/>
+      <c r="M489" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N489" s="36" t="inlineStr"/>
+      <c r="O489" s="35" t="inlineStr"/>
+    </row>
+    <row r="490" ht="16" customHeight="1">
+      <c r="A490" s="28" t="inlineStr">
+        <is>
+          <t>f30458081f12</t>
+        </is>
+      </c>
+      <c r="B490" s="28" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="C490" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D490" s="28" t="inlineStr">
+        <is>
+          <t>Mott MacDonald</t>
+        </is>
+      </c>
+      <c r="E490" s="28" t="inlineStr">
+        <is>
+          <t>Derby, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F490" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G490" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H490" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I490" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J490" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K490" s="31" t="inlineStr"/>
+      <c r="L490" s="31" t="inlineStr"/>
+      <c r="M490" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N490" s="32" t="inlineStr"/>
+      <c r="O490" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -29897,6 +30015,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J486" r:id="rId217"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J487" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J488" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J489" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J490" r:id="rId221"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O490"/>
+  <dimension ref="A1:O492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -29782,6 +29782,124 @@
       </c>
       <c r="N490" s="32" t="inlineStr"/>
       <c r="O490" s="31" t="inlineStr"/>
+    </row>
+    <row r="491" ht="16" customHeight="1">
+      <c r="A491" s="33" t="inlineStr">
+        <is>
+          <t>3a8fee0a2f7c</t>
+        </is>
+      </c>
+      <c r="B491" s="33" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="C491" s="33" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Wastewater Infrastructure</t>
+        </is>
+      </c>
+      <c r="D491" s="33" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment Ltd</t>
+        </is>
+      </c>
+      <c r="E491" s="33" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F491" s="33" t="inlineStr">
+        <is>
+          <t>£40,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G491" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H491" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I491" s="33" t="n">
+        <v>85</v>
+      </c>
+      <c r="J491" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K491" s="35" t="inlineStr"/>
+      <c r="L491" s="35" t="inlineStr"/>
+      <c r="M491" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N491" s="36" t="inlineStr"/>
+      <c r="O491" s="35" t="inlineStr"/>
+    </row>
+    <row r="492" ht="16" customHeight="1">
+      <c r="A492" s="28" t="inlineStr">
+        <is>
+          <t>2fde8e93579c</t>
+        </is>
+      </c>
+      <c r="B492" s="28" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="C492" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D492" s="28" t="inlineStr">
+        <is>
+          <t>WSP in the UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="E492" s="28" t="inlineStr">
+        <is>
+          <t>England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F492" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G492" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H492" s="37" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="I492" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J492" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K492" s="31" t="inlineStr"/>
+      <c r="L492" s="31" t="inlineStr"/>
+      <c r="M492" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N492" s="32" t="inlineStr"/>
+      <c r="O492" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -30017,6 +30135,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J488" r:id="rId219"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J489" r:id="rId220"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J490" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J491" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J492" r:id="rId223"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O492"/>
+  <dimension ref="A1:O493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -29900,6 +29900,65 @@
       </c>
       <c r="N492" s="32" t="inlineStr"/>
       <c r="O492" s="31" t="inlineStr"/>
+    </row>
+    <row r="493" ht="16" customHeight="1">
+      <c r="A493" s="33" t="inlineStr">
+        <is>
+          <t>334823e2e1e5</t>
+        </is>
+      </c>
+      <c r="B493" s="33" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="C493" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Sector AMP8</t>
+        </is>
+      </c>
+      <c r="D493" s="33" t="inlineStr">
+        <is>
+          <t>Arcadis</t>
+        </is>
+      </c>
+      <c r="E493" s="33" t="inlineStr">
+        <is>
+          <t>Cardiff, Wales, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F493" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G493" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H493" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I493" s="33" t="n">
+        <v>75</v>
+      </c>
+      <c r="J493" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K493" s="35" t="inlineStr"/>
+      <c r="L493" s="35" t="inlineStr"/>
+      <c r="M493" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N493" s="36" t="inlineStr"/>
+      <c r="O493" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -30137,6 +30196,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J490" r:id="rId221"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J491" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J492" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J493" r:id="rId224"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O493"/>
+  <dimension ref="A1:O495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -29959,6 +29959,124 @@
       </c>
       <c r="N493" s="36" t="inlineStr"/>
       <c r="O493" s="35" t="inlineStr"/>
+    </row>
+    <row r="494" ht="16" customHeight="1">
+      <c r="A494" s="28" t="inlineStr">
+        <is>
+          <t>f3edaaafaece</t>
+        </is>
+      </c>
+      <c r="B494" s="28" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C494" s="28" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Wastewater Infrastructure</t>
+        </is>
+      </c>
+      <c r="D494" s="28" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment Ltd</t>
+        </is>
+      </c>
+      <c r="E494" s="28" t="inlineStr">
+        <is>
+          <t>Slough, Berkshire</t>
+        </is>
+      </c>
+      <c r="F494" s="28" t="inlineStr">
+        <is>
+          <t>£40,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G494" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H494" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I494" s="28" t="n">
+        <v>85</v>
+      </c>
+      <c r="J494" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K494" s="31" t="inlineStr"/>
+      <c r="L494" s="31" t="inlineStr"/>
+      <c r="M494" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N494" s="32" t="inlineStr"/>
+      <c r="O494" s="31" t="inlineStr"/>
+    </row>
+    <row r="495" ht="16" customHeight="1">
+      <c r="A495" s="33" t="inlineStr">
+        <is>
+          <t>905a8766d25a</t>
+        </is>
+      </c>
+      <c r="B495" s="33" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C495" s="33" t="inlineStr">
+        <is>
+          <t>Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D495" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E495" s="33" t="inlineStr">
+        <is>
+          <t>Leeds, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F495" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G495" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H495" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I495" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J495" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K495" s="35" t="inlineStr"/>
+      <c r="L495" s="35" t="inlineStr"/>
+      <c r="M495" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N495" s="36" t="inlineStr"/>
+      <c r="O495" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -30197,6 +30315,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J491" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J492" r:id="rId223"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J493" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J494" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J495" r:id="rId226"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O495"/>
+  <dimension ref="A1:O497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -30077,6 +30077,124 @@
       </c>
       <c r="N495" s="36" t="inlineStr"/>
       <c r="O495" s="35" t="inlineStr"/>
+    </row>
+    <row r="496" ht="16" customHeight="1">
+      <c r="A496" s="28" t="inlineStr">
+        <is>
+          <t>6b9542f0d2e6</t>
+        </is>
+      </c>
+      <c r="B496" s="28" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="C496" s="28" t="inlineStr">
+        <is>
+          <t>Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D496" s="28" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E496" s="28" t="inlineStr">
+        <is>
+          <t>High Wycombe, Buckinghamshire</t>
+        </is>
+      </c>
+      <c r="F496" s="28" t="inlineStr">
+        <is>
+          <t>£49,101 – £49,101</t>
+        </is>
+      </c>
+      <c r="G496" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H496" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I496" s="28" t="n">
+        <v>85</v>
+      </c>
+      <c r="J496" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K496" s="31" t="inlineStr"/>
+      <c r="L496" s="31" t="inlineStr"/>
+      <c r="M496" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N496" s="32" t="inlineStr"/>
+      <c r="O496" s="31" t="inlineStr"/>
+    </row>
+    <row r="497" ht="16" customHeight="1">
+      <c r="A497" s="33" t="inlineStr">
+        <is>
+          <t>fcf562437f39</t>
+        </is>
+      </c>
+      <c r="B497" s="33" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="C497" s="33" t="inlineStr">
+        <is>
+          <t>Clean Water Network Modellers/ Engineers  (All Grades)</t>
+        </is>
+      </c>
+      <c r="D497" s="33" t="inlineStr">
+        <is>
+          <t>AtkinsRéalis</t>
+        </is>
+      </c>
+      <c r="E497" s="33" t="inlineStr">
+        <is>
+          <t>Liverpool, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F497" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G497" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H497" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I497" s="33" t="n">
+        <v>65</v>
+      </c>
+      <c r="J497" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K497" s="35" t="inlineStr"/>
+      <c r="L497" s="35" t="inlineStr"/>
+      <c r="M497" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N497" s="36" t="inlineStr"/>
+      <c r="O497" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -30317,6 +30435,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J493" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J494" r:id="rId225"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J495" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J496" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J497" r:id="rId228"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O497"/>
+  <dimension ref="A1:O499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -30195,6 +30195,124 @@
       </c>
       <c r="N497" s="36" t="inlineStr"/>
       <c r="O497" s="35" t="inlineStr"/>
+    </row>
+    <row r="498" ht="16" customHeight="1">
+      <c r="A498" s="28" t="inlineStr">
+        <is>
+          <t>20fdcf4e3634</t>
+        </is>
+      </c>
+      <c r="B498" s="28" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="C498" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Hydraulic Modeller – Modeller to Associate</t>
+        </is>
+      </c>
+      <c r="D498" s="28" t="inlineStr">
+        <is>
+          <t>AtkinsRéalis</t>
+        </is>
+      </c>
+      <c r="E498" s="28" t="inlineStr">
+        <is>
+          <t>Stockton-On-Tees, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F498" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G498" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H498" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I498" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J498" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K498" s="31" t="inlineStr"/>
+      <c r="L498" s="31" t="inlineStr"/>
+      <c r="M498" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N498" s="32" t="inlineStr"/>
+      <c r="O498" s="31" t="inlineStr"/>
+    </row>
+    <row r="499" ht="16" customHeight="1">
+      <c r="A499" s="33" t="inlineStr">
+        <is>
+          <t>3b2cdcf02c13</t>
+        </is>
+      </c>
+      <c r="B499" s="33" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="C499" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater (Hydraulic) Modeller</t>
+        </is>
+      </c>
+      <c r="D499" s="33" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E499" s="33" t="inlineStr">
+        <is>
+          <t>Warrington, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F499" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G499" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H499" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I499" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J499" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K499" s="35" t="inlineStr"/>
+      <c r="L499" s="35" t="inlineStr"/>
+      <c r="M499" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N499" s="36" t="inlineStr"/>
+      <c r="O499" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -30437,6 +30555,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J495" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J496" r:id="rId227"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J497" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J498" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J499" r:id="rId230"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O499"/>
+  <dimension ref="A1:O501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -30313,6 +30313,124 @@
       </c>
       <c r="N499" s="36" t="inlineStr"/>
       <c r="O499" s="35" t="inlineStr"/>
+    </row>
+    <row r="500" ht="16" customHeight="1">
+      <c r="A500" s="28" t="inlineStr">
+        <is>
+          <t>f39fdcad9831</t>
+        </is>
+      </c>
+      <c r="B500" s="28" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="C500" s="28" t="inlineStr">
+        <is>
+          <t>Design Manager (Wastewater Infrastructure)</t>
+        </is>
+      </c>
+      <c r="D500" s="28" t="inlineStr">
+        <is>
+          <t>COWI</t>
+        </is>
+      </c>
+      <c r="E500" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F500" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G500" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H500" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I500" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="J500" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K500" s="31" t="inlineStr"/>
+      <c r="L500" s="31" t="inlineStr"/>
+      <c r="M500" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N500" s="32" t="inlineStr"/>
+      <c r="O500" s="31" t="inlineStr"/>
+    </row>
+    <row r="501" ht="16" customHeight="1">
+      <c r="A501" s="33" t="inlineStr">
+        <is>
+          <t>9cafd590cacc</t>
+        </is>
+      </c>
+      <c r="B501" s="33" t="inlineStr">
+        <is>
+          <t>12/07/2026</t>
+        </is>
+      </c>
+      <c r="C501" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer (Water/Wastewater)</t>
+        </is>
+      </c>
+      <c r="D501" s="33" t="inlineStr">
+        <is>
+          <t>COWI</t>
+        </is>
+      </c>
+      <c r="E501" s="33" t="inlineStr">
+        <is>
+          <t>York, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F501" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G501" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H501" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I501" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J501" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K501" s="35" t="inlineStr"/>
+      <c r="L501" s="35" t="inlineStr"/>
+      <c r="M501" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N501" s="36" t="inlineStr"/>
+      <c r="O501" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -30557,6 +30675,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J497" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J498" r:id="rId229"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J499" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J500" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J501" r:id="rId232"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O501"/>
+  <dimension ref="A1:O502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -30431,6 +30431,65 @@
       </c>
       <c r="N501" s="36" t="inlineStr"/>
       <c r="O501" s="35" t="inlineStr"/>
+    </row>
+    <row r="502" ht="16" customHeight="1">
+      <c r="A502" s="28" t="inlineStr">
+        <is>
+          <t>b057a813b7a3</t>
+        </is>
+      </c>
+      <c r="B502" s="28" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="C502" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer (Water/Wastewater)</t>
+        </is>
+      </c>
+      <c r="D502" s="28" t="inlineStr">
+        <is>
+          <t>COWI</t>
+        </is>
+      </c>
+      <c r="E502" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F502" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G502" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H502" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I502" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J502" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K502" s="31" t="inlineStr"/>
+      <c r="L502" s="31" t="inlineStr"/>
+      <c r="M502" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N502" s="32" t="inlineStr"/>
+      <c r="O502" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -30677,6 +30736,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J499" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J500" r:id="rId231"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J501" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J502" r:id="rId233"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O502"/>
+  <dimension ref="A1:O504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -30490,6 +30490,124 @@
       </c>
       <c r="N502" s="32" t="inlineStr"/>
       <c r="O502" s="31" t="inlineStr"/>
+    </row>
+    <row r="503" ht="16" customHeight="1">
+      <c r="A503" s="33" t="inlineStr">
+        <is>
+          <t>7f2df345a7e8</t>
+        </is>
+      </c>
+      <c r="B503" s="33" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="C503" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D503" s="33" t="inlineStr">
+        <is>
+          <t>AtkinsRéalis</t>
+        </is>
+      </c>
+      <c r="E503" s="33" t="inlineStr">
+        <is>
+          <t>Derby, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F503" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G503" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H503" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I503" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="J503" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K503" s="35" t="inlineStr"/>
+      <c r="L503" s="35" t="inlineStr"/>
+      <c r="M503" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N503" s="36" t="inlineStr"/>
+      <c r="O503" s="35" t="inlineStr"/>
+    </row>
+    <row r="504" ht="16" customHeight="1">
+      <c r="A504" s="28" t="inlineStr">
+        <is>
+          <t>1cb232e77254</t>
+        </is>
+      </c>
+      <c r="B504" s="28" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="C504" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Hydraulic Modeller – Modeller to Associate</t>
+        </is>
+      </c>
+      <c r="D504" s="28" t="inlineStr">
+        <is>
+          <t>AtkinsRéalis</t>
+        </is>
+      </c>
+      <c r="E504" s="28" t="inlineStr">
+        <is>
+          <t>Newcastle Upon Tyne, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F504" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G504" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H504" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I504" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J504" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K504" s="31" t="inlineStr"/>
+      <c r="L504" s="31" t="inlineStr"/>
+      <c r="M504" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N504" s="32" t="inlineStr"/>
+      <c r="O504" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -30737,6 +30855,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J500" r:id="rId231"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J501" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J502" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J503" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J504" r:id="rId235"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O504"/>
+  <dimension ref="A1:O505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -30608,6 +30608,65 @@
       </c>
       <c r="N504" s="32" t="inlineStr"/>
       <c r="O504" s="31" t="inlineStr"/>
+    </row>
+    <row r="505" ht="16" customHeight="1">
+      <c r="A505" s="33" t="inlineStr">
+        <is>
+          <t>da2627f3f4a7</t>
+        </is>
+      </c>
+      <c r="B505" s="33" t="inlineStr">
+        <is>
+          <t>16/07/2026</t>
+        </is>
+      </c>
+      <c r="C505" s="33" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller - UK Water / Wastewater</t>
+        </is>
+      </c>
+      <c r="D505" s="33" t="inlineStr">
+        <is>
+          <t>Egis</t>
+        </is>
+      </c>
+      <c r="E505" s="33" t="inlineStr">
+        <is>
+          <t>Manchester, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F505" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G505" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H505" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I505" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="J505" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K505" s="35" t="inlineStr"/>
+      <c r="L505" s="35" t="inlineStr"/>
+      <c r="M505" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N505" s="36" t="inlineStr"/>
+      <c r="O505" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -30857,6 +30916,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J502" r:id="rId233"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J503" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J504" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J505" r:id="rId236"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O505"/>
+  <dimension ref="A1:O506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -30667,6 +30667,65 @@
       </c>
       <c r="N505" s="36" t="inlineStr"/>
       <c r="O505" s="35" t="inlineStr"/>
+    </row>
+    <row r="506" ht="16" customHeight="1">
+      <c r="A506" s="28" t="inlineStr">
+        <is>
+          <t>2a04cd87ddd4</t>
+        </is>
+      </c>
+      <c r="B506" s="28" t="inlineStr">
+        <is>
+          <t>18/07/2026</t>
+        </is>
+      </c>
+      <c r="C506" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D506" s="28" t="inlineStr">
+        <is>
+          <t>AtkinsRéalis</t>
+        </is>
+      </c>
+      <c r="E506" s="28" t="inlineStr">
+        <is>
+          <t>Bristol, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F506" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G506" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H506" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I506" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J506" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K506" s="31" t="inlineStr"/>
+      <c r="L506" s="31" t="inlineStr"/>
+      <c r="M506" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N506" s="32" t="inlineStr"/>
+      <c r="O506" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -30917,6 +30976,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J503" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J504" r:id="rId235"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J505" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J506" r:id="rId237"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O506"/>
+  <dimension ref="A1:O508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -30726,6 +30726,124 @@
       </c>
       <c r="N506" s="32" t="inlineStr"/>
       <c r="O506" s="31" t="inlineStr"/>
+    </row>
+    <row r="507" ht="16" customHeight="1">
+      <c r="A507" s="33" t="inlineStr">
+        <is>
+          <t>897f2563c016</t>
+        </is>
+      </c>
+      <c r="B507" s="33" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="C507" s="33" t="inlineStr">
+        <is>
+          <t>Clean Water (Hydraulic) Modeller</t>
+        </is>
+      </c>
+      <c r="D507" s="33" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E507" s="33" t="inlineStr">
+        <is>
+          <t>Derby, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F507" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G507" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H507" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I507" s="33" t="n">
+        <v>65</v>
+      </c>
+      <c r="J507" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K507" s="35" t="inlineStr"/>
+      <c r="L507" s="35" t="inlineStr"/>
+      <c r="M507" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N507" s="36" t="inlineStr"/>
+      <c r="O507" s="35" t="inlineStr"/>
+    </row>
+    <row r="508" ht="16" customHeight="1">
+      <c r="A508" s="28" t="inlineStr">
+        <is>
+          <t>a0bcaba9737a</t>
+        </is>
+      </c>
+      <c r="B508" s="28" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="C508" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D508" s="28" t="inlineStr">
+        <is>
+          <t>Mott MacDonald</t>
+        </is>
+      </c>
+      <c r="E508" s="28" t="inlineStr">
+        <is>
+          <t>Leeds, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F508" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G508" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H508" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I508" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J508" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K508" s="31" t="inlineStr"/>
+      <c r="L508" s="31" t="inlineStr"/>
+      <c r="M508" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N508" s="32" t="inlineStr"/>
+      <c r="O508" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -30977,6 +31095,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J504" r:id="rId235"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J505" r:id="rId236"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J506" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J507" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J508" r:id="rId239"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O508"/>
+  <dimension ref="A1:O510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -30844,6 +30844,124 @@
       </c>
       <c r="N508" s="32" t="inlineStr"/>
       <c r="O508" s="31" t="inlineStr"/>
+    </row>
+    <row r="509" ht="16" customHeight="1">
+      <c r="A509" s="33" t="inlineStr">
+        <is>
+          <t>89ff0644d75f</t>
+        </is>
+      </c>
+      <c r="B509" s="33" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="C509" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Sector AMP8</t>
+        </is>
+      </c>
+      <c r="D509" s="33" t="inlineStr">
+        <is>
+          <t>Arcadis</t>
+        </is>
+      </c>
+      <c r="E509" s="33" t="inlineStr">
+        <is>
+          <t>Leeds, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F509" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G509" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H509" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I509" s="33" t="n">
+        <v>75</v>
+      </c>
+      <c r="J509" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K509" s="35" t="inlineStr"/>
+      <c r="L509" s="35" t="inlineStr"/>
+      <c r="M509" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N509" s="36" t="inlineStr"/>
+      <c r="O509" s="35" t="inlineStr"/>
+    </row>
+    <row r="510" ht="16" customHeight="1">
+      <c r="A510" s="28" t="inlineStr">
+        <is>
+          <t>88d6d0bc26a7</t>
+        </is>
+      </c>
+      <c r="B510" s="28" t="inlineStr">
+        <is>
+          <t>26/07/2026</t>
+        </is>
+      </c>
+      <c r="C510" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D510" s="28" t="inlineStr">
+        <is>
+          <t>WSP</t>
+        </is>
+      </c>
+      <c r="E510" s="28" t="inlineStr">
+        <is>
+          <t>Aldwych, Central London</t>
+        </is>
+      </c>
+      <c r="F510" s="28" t="inlineStr">
+        <is>
+          <t>£46,441 – £46,441</t>
+        </is>
+      </c>
+      <c r="G510" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H510" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I510" s="28" t="n">
+        <v>70</v>
+      </c>
+      <c r="J510" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K510" s="31" t="inlineStr"/>
+      <c r="L510" s="31" t="inlineStr"/>
+      <c r="M510" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N510" s="32" t="inlineStr"/>
+      <c r="O510" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -31097,6 +31215,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J506" r:id="rId237"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J507" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J508" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J509" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J510" r:id="rId241"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O510"/>
+  <dimension ref="A1:O511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -30962,6 +30962,65 @@
       </c>
       <c r="N510" s="32" t="inlineStr"/>
       <c r="O510" s="31" t="inlineStr"/>
+    </row>
+    <row r="511" ht="16" customHeight="1">
+      <c r="A511" s="33" t="inlineStr">
+        <is>
+          <t>f791bb862832</t>
+        </is>
+      </c>
+      <c r="B511" s="33" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C511" s="33" t="inlineStr">
+        <is>
+          <t>Flood Risk &amp; Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D511" s="33" t="inlineStr">
+        <is>
+          <t>Hays</t>
+        </is>
+      </c>
+      <c r="E511" s="33" t="inlineStr">
+        <is>
+          <t>Lincolnshire, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F511" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G511" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H511" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I511" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="J511" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K511" s="35" t="inlineStr"/>
+      <c r="L511" s="35" t="inlineStr"/>
+      <c r="M511" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N511" s="36" t="inlineStr"/>
+      <c r="O511" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -31217,6 +31276,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J508" r:id="rId239"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J509" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J510" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J511" r:id="rId242"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O511"/>
+  <dimension ref="A1:O512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -31021,6 +31021,65 @@
       </c>
       <c r="N511" s="36" t="inlineStr"/>
       <c r="O511" s="35" t="inlineStr"/>
+    </row>
+    <row r="512" ht="16" customHeight="1">
+      <c r="A512" s="28" t="inlineStr">
+        <is>
+          <t>6e6b31db3d1e</t>
+        </is>
+      </c>
+      <c r="B512" s="28" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="C512" s="28" t="inlineStr">
+        <is>
+          <t>Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D512" s="28" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E512" s="28" t="inlineStr">
+        <is>
+          <t>High Wycombe, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F512" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G512" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H512" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I512" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J512" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K512" s="31" t="inlineStr"/>
+      <c r="L512" s="31" t="inlineStr"/>
+      <c r="M512" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N512" s="32" t="inlineStr"/>
+      <c r="O512" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -31277,6 +31336,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J509" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J510" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J511" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J512" r:id="rId243"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O512"/>
+  <dimension ref="A1:O513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -31080,6 +31080,65 @@
       </c>
       <c r="N512" s="32" t="inlineStr"/>
       <c r="O512" s="31" t="inlineStr"/>
+    </row>
+    <row r="513" ht="16" customHeight="1">
+      <c r="A513" s="33" t="inlineStr">
+        <is>
+          <t>748095b40beb</t>
+        </is>
+      </c>
+      <c r="B513" s="33" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="C513" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater (Hydraulic) Modeller</t>
+        </is>
+      </c>
+      <c r="D513" s="33" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E513" s="33" t="inlineStr">
+        <is>
+          <t>Leeds, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F513" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G513" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H513" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I513" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J513" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K513" s="35" t="inlineStr"/>
+      <c r="L513" s="35" t="inlineStr"/>
+      <c r="M513" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N513" s="36" t="inlineStr"/>
+      <c r="O513" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -31337,6 +31396,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J510" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J511" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J512" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J513" r:id="rId244"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O513"/>
+  <dimension ref="A1:O514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -31139,6 +31139,65 @@
       </c>
       <c r="N513" s="36" t="inlineStr"/>
       <c r="O513" s="35" t="inlineStr"/>
+    </row>
+    <row r="514" ht="16" customHeight="1">
+      <c r="A514" s="28" t="inlineStr">
+        <is>
+          <t>15018702a1c1</t>
+        </is>
+      </c>
+      <c r="B514" s="28" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="C514" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer (Water/Wastewater)</t>
+        </is>
+      </c>
+      <c r="D514" s="28" t="inlineStr">
+        <is>
+          <t>COWI</t>
+        </is>
+      </c>
+      <c r="E514" s="28" t="inlineStr">
+        <is>
+          <t>Derby, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F514" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G514" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H514" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I514" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J514" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K514" s="31" t="inlineStr"/>
+      <c r="L514" s="31" t="inlineStr"/>
+      <c r="M514" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N514" s="32" t="inlineStr"/>
+      <c r="O514" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -31397,6 +31456,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J511" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J512" r:id="rId243"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J513" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J514" r:id="rId245"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O514"/>
+  <dimension ref="A1:O515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -31198,6 +31198,65 @@
       </c>
       <c r="N514" s="32" t="inlineStr"/>
       <c r="O514" s="31" t="inlineStr"/>
+    </row>
+    <row r="515" ht="16" customHeight="1">
+      <c r="A515" s="33" t="inlineStr">
+        <is>
+          <t>d02efaa21a49</t>
+        </is>
+      </c>
+      <c r="B515" s="33" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="C515" s="33" t="inlineStr">
+        <is>
+          <t>Water Networks Modeller</t>
+        </is>
+      </c>
+      <c r="D515" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E515" s="33" t="inlineStr">
+        <is>
+          <t>Worcestershire, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F515" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G515" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H515" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I515" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J515" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K515" s="35" t="inlineStr"/>
+      <c r="L515" s="35" t="inlineStr"/>
+      <c r="M515" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N515" s="36" t="inlineStr"/>
+      <c r="O515" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -31457,6 +31516,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J512" r:id="rId243"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J513" r:id="rId244"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J514" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J515" r:id="rId246"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O515"/>
+  <dimension ref="A1:O516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -31257,6 +31257,65 @@
       </c>
       <c r="N515" s="36" t="inlineStr"/>
       <c r="O515" s="35" t="inlineStr"/>
+    </row>
+    <row r="516" ht="16" customHeight="1">
+      <c r="A516" s="28" t="inlineStr">
+        <is>
+          <t>b453b9ec8edd</t>
+        </is>
+      </c>
+      <c r="B516" s="28" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="C516" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineering Manager (Water Services)</t>
+        </is>
+      </c>
+      <c r="D516" s="28" t="inlineStr">
+        <is>
+          <t>Binnies</t>
+        </is>
+      </c>
+      <c r="E516" s="28" t="inlineStr">
+        <is>
+          <t>West Midlands, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F516" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G516" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H516" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I516" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J516" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K516" s="31" t="inlineStr"/>
+      <c r="L516" s="31" t="inlineStr"/>
+      <c r="M516" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N516" s="32" t="inlineStr"/>
+      <c r="O516" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -31517,6 +31576,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J513" r:id="rId244"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J514" r:id="rId245"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J515" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J516" r:id="rId247"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O516"/>
+  <dimension ref="A1:O517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -31316,6 +31316,65 @@
       </c>
       <c r="N516" s="32" t="inlineStr"/>
       <c r="O516" s="31" t="inlineStr"/>
+    </row>
+    <row r="517" ht="16" customHeight="1">
+      <c r="A517" s="33" t="inlineStr">
+        <is>
+          <t>d5559706391a</t>
+        </is>
+      </c>
+      <c r="B517" s="33" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="C517" s="33" t="inlineStr">
+        <is>
+          <t>Expression of Interest - Design Manager - Water Sector</t>
+        </is>
+      </c>
+      <c r="D517" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E517" s="33" t="inlineStr">
+        <is>
+          <t>Reading, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F517" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G517" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H517" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I517" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J517" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K517" s="35" t="inlineStr"/>
+      <c r="L517" s="35" t="inlineStr"/>
+      <c r="M517" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N517" s="36" t="inlineStr"/>
+      <c r="O517" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -31577,6 +31636,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J514" r:id="rId245"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J515" r:id="rId246"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J516" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J517" r:id="rId248"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O517"/>
+  <dimension ref="A1:O518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -31375,6 +31375,65 @@
       </c>
       <c r="N517" s="36" t="inlineStr"/>
       <c r="O517" s="35" t="inlineStr"/>
+    </row>
+    <row r="518" ht="16" customHeight="1">
+      <c r="A518" s="28" t="inlineStr">
+        <is>
+          <t>a2bdd8ef43c7</t>
+        </is>
+      </c>
+      <c r="B518" s="28" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C518" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulic Modellers (Flood Risk Management)</t>
+        </is>
+      </c>
+      <c r="D518" s="28" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E518" s="28" t="inlineStr">
+        <is>
+          <t>Belfast, Northern Ireland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F518" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G518" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H518" s="37" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="I518" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J518" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K518" s="31" t="inlineStr"/>
+      <c r="L518" s="31" t="inlineStr"/>
+      <c r="M518" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N518" s="32" t="inlineStr"/>
+      <c r="O518" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -31637,6 +31696,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J515" r:id="rId246"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J516" r:id="rId247"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J517" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J518" r:id="rId249"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O518"/>
+  <dimension ref="A1:O519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -31434,6 +31434,65 @@
       </c>
       <c r="N518" s="32" t="inlineStr"/>
       <c r="O518" s="31" t="inlineStr"/>
+    </row>
+    <row r="519" ht="16" customHeight="1">
+      <c r="A519" s="33" t="inlineStr">
+        <is>
+          <t>beee967d823c</t>
+        </is>
+      </c>
+      <c r="B519" s="33" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="C519" s="33" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller – Water &amp; Wastewater</t>
+        </is>
+      </c>
+      <c r="D519" s="33" t="inlineStr">
+        <is>
+          <t>Arup</t>
+        </is>
+      </c>
+      <c r="E519" s="33" t="inlineStr">
+        <is>
+          <t>Cardiff, Wales, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F519" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G519" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H519" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I519" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="J519" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K519" s="35" t="inlineStr"/>
+      <c r="L519" s="35" t="inlineStr"/>
+      <c r="M519" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N519" s="36" t="inlineStr"/>
+      <c r="O519" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -31697,6 +31756,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J516" r:id="rId247"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J517" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J518" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J519" r:id="rId250"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O519"/>
+  <dimension ref="A1:O521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -31493,6 +31493,124 @@
       </c>
       <c r="N519" s="36" t="inlineStr"/>
       <c r="O519" s="35" t="inlineStr"/>
+    </row>
+    <row r="520" ht="16" customHeight="1">
+      <c r="A520" s="28" t="inlineStr">
+        <is>
+          <t>ed2752395740</t>
+        </is>
+      </c>
+      <c r="B520" s="28" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="C520" s="28" t="inlineStr">
+        <is>
+          <t>Hydrologist | Flood Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D520" s="28" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E520" s="28" t="inlineStr">
+        <is>
+          <t>Leeds, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F520" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G520" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H520" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I520" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J520" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K520" s="31" t="inlineStr"/>
+      <c r="L520" s="31" t="inlineStr"/>
+      <c r="M520" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N520" s="32" t="inlineStr"/>
+      <c r="O520" s="31" t="inlineStr"/>
+    </row>
+    <row r="521" ht="16" customHeight="1">
+      <c r="A521" s="33" t="inlineStr">
+        <is>
+          <t>0b9c666f727c</t>
+        </is>
+      </c>
+      <c r="B521" s="33" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
+      <c r="C521" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Industry</t>
+        </is>
+      </c>
+      <c r="D521" s="33" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E521" s="33" t="inlineStr">
+        <is>
+          <t>Sheffield, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F521" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G521" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H521" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I521" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J521" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K521" s="35" t="inlineStr"/>
+      <c r="L521" s="35" t="inlineStr"/>
+      <c r="M521" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N521" s="36" t="inlineStr"/>
+      <c r="O521" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -31757,6 +31875,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J517" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J518" r:id="rId249"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J519" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J520" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J521" r:id="rId252"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O521"/>
+  <dimension ref="A1:O524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -31611,6 +31611,183 @@
       </c>
       <c r="N521" s="36" t="inlineStr"/>
       <c r="O521" s="35" t="inlineStr"/>
+    </row>
+    <row r="522" ht="16" customHeight="1">
+      <c r="A522" s="28" t="inlineStr">
+        <is>
+          <t>bee36f5b776f</t>
+        </is>
+      </c>
+      <c r="B522" s="28" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="C522" s="28" t="inlineStr">
+        <is>
+          <t>Clean Water (Hydraulic) Modeller</t>
+        </is>
+      </c>
+      <c r="D522" s="28" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E522" s="28" t="inlineStr">
+        <is>
+          <t>Sheffield, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F522" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G522" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H522" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I522" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="J522" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K522" s="31" t="inlineStr"/>
+      <c r="L522" s="31" t="inlineStr"/>
+      <c r="M522" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N522" s="32" t="inlineStr"/>
+      <c r="O522" s="31" t="inlineStr"/>
+    </row>
+    <row r="523" ht="16" customHeight="1">
+      <c r="A523" s="33" t="inlineStr">
+        <is>
+          <t>59369621a2b3</t>
+        </is>
+      </c>
+      <c r="B523" s="33" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="C523" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Industry</t>
+        </is>
+      </c>
+      <c r="D523" s="33" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E523" s="33" t="inlineStr">
+        <is>
+          <t>Derby, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F523" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G523" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H523" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I523" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J523" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K523" s="35" t="inlineStr"/>
+      <c r="L523" s="35" t="inlineStr"/>
+      <c r="M523" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N523" s="36" t="inlineStr"/>
+      <c r="O523" s="35" t="inlineStr"/>
+    </row>
+    <row r="524" ht="16" customHeight="1">
+      <c r="A524" s="28" t="inlineStr">
+        <is>
+          <t>fe2cfe9600ab</t>
+        </is>
+      </c>
+      <c r="B524" s="28" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="C524" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D524" s="28" t="inlineStr">
+        <is>
+          <t>WSP in the UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="E524" s="28" t="inlineStr">
+        <is>
+          <t>Leeds, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F524" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G524" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H524" s="37" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="I524" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J524" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K524" s="31" t="inlineStr"/>
+      <c r="L524" s="31" t="inlineStr"/>
+      <c r="M524" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N524" s="32" t="inlineStr"/>
+      <c r="O524" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -31877,6 +32054,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J519" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J520" r:id="rId251"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J521" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J522" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J523" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J524" r:id="rId255"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O524"/>
+  <dimension ref="A1:O528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -31788,6 +31788,242 @@
       </c>
       <c r="N524" s="32" t="inlineStr"/>
       <c r="O524" s="31" t="inlineStr"/>
+    </row>
+    <row r="525" ht="16" customHeight="1">
+      <c r="A525" s="33" t="inlineStr">
+        <is>
+          <t>76b6268967ad</t>
+        </is>
+      </c>
+      <c r="B525" s="33" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="C525" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer – Water &amp; Utilities (ID: LEE0000P9)</t>
+        </is>
+      </c>
+      <c r="D525" s="33" t="inlineStr">
+        <is>
+          <t>Arup</t>
+        </is>
+      </c>
+      <c r="E525" s="33" t="inlineStr">
+        <is>
+          <t>Leeds, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F525" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G525" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H525" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I525" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J525" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K525" s="35" t="inlineStr"/>
+      <c r="L525" s="35" t="inlineStr"/>
+      <c r="M525" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N525" s="36" t="inlineStr"/>
+      <c r="O525" s="35" t="inlineStr"/>
+    </row>
+    <row r="526" ht="16" customHeight="1">
+      <c r="A526" s="28" t="inlineStr">
+        <is>
+          <t>2e259b12f489</t>
+        </is>
+      </c>
+      <c r="B526" s="28" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="C526" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer – Water &amp; Utilities</t>
+        </is>
+      </c>
+      <c r="D526" s="28" t="inlineStr">
+        <is>
+          <t>Arup</t>
+        </is>
+      </c>
+      <c r="E526" s="28" t="inlineStr">
+        <is>
+          <t>Leeds, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F526" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G526" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H526" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I526" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J526" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K526" s="31" t="inlineStr"/>
+      <c r="L526" s="31" t="inlineStr"/>
+      <c r="M526" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N526" s="32" t="inlineStr"/>
+      <c r="O526" s="31" t="inlineStr"/>
+    </row>
+    <row r="527" ht="16" customHeight="1">
+      <c r="A527" s="33" t="inlineStr">
+        <is>
+          <t>3f3d46de5c70</t>
+        </is>
+      </c>
+      <c r="B527" s="33" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="C527" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Industry</t>
+        </is>
+      </c>
+      <c r="D527" s="33" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E527" s="33" t="inlineStr">
+        <is>
+          <t>Leeds, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F527" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G527" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H527" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I527" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J527" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K527" s="35" t="inlineStr"/>
+      <c r="L527" s="35" t="inlineStr"/>
+      <c r="M527" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N527" s="36" t="inlineStr"/>
+      <c r="O527" s="35" t="inlineStr"/>
+    </row>
+    <row r="528" ht="16" customHeight="1">
+      <c r="A528" s="28" t="inlineStr">
+        <is>
+          <t>f6cd68b257c9</t>
+        </is>
+      </c>
+      <c r="B528" s="28" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="C528" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D528" s="28" t="inlineStr">
+        <is>
+          <t>WSP in the UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="E528" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F528" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G528" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H528" s="37" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="I528" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J528" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K528" s="31" t="inlineStr"/>
+      <c r="L528" s="31" t="inlineStr"/>
+      <c r="M528" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N528" s="32" t="inlineStr"/>
+      <c r="O528" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -32057,6 +32293,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J522" r:id="rId253"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J523" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J524" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J525" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J526" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J527" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J528" r:id="rId259"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O528"/>
+  <dimension ref="A1:O530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -32024,6 +32024,124 @@
       </c>
       <c r="N528" s="32" t="inlineStr"/>
       <c r="O528" s="31" t="inlineStr"/>
+    </row>
+    <row r="529" ht="16" customHeight="1">
+      <c r="A529" s="33" t="inlineStr">
+        <is>
+          <t>1c809d406efa</t>
+        </is>
+      </c>
+      <c r="B529" s="33" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="C529" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Sector AMP8</t>
+        </is>
+      </c>
+      <c r="D529" s="33" t="inlineStr">
+        <is>
+          <t>Arcadis</t>
+        </is>
+      </c>
+      <c r="E529" s="33" t="inlineStr">
+        <is>
+          <t>Manchester, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F529" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G529" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H529" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I529" s="33" t="n">
+        <v>75</v>
+      </c>
+      <c r="J529" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K529" s="35" t="inlineStr"/>
+      <c r="L529" s="35" t="inlineStr"/>
+      <c r="M529" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N529" s="36" t="inlineStr"/>
+      <c r="O529" s="35" t="inlineStr"/>
+    </row>
+    <row r="530" ht="16" customHeight="1">
+      <c r="A530" s="28" t="inlineStr">
+        <is>
+          <t>60cd2634e204</t>
+        </is>
+      </c>
+      <c r="B530" s="28" t="inlineStr">
+        <is>
+          <t>16/08/2026</t>
+        </is>
+      </c>
+      <c r="C530" s="28" t="inlineStr">
+        <is>
+          <t>Design Manager - Water Sector</t>
+        </is>
+      </c>
+      <c r="D530" s="28" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E530" s="28" t="inlineStr">
+        <is>
+          <t>Brighton, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F530" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G530" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H530" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I530" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J530" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K530" s="31" t="inlineStr"/>
+      <c r="L530" s="31" t="inlineStr"/>
+      <c r="M530" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N530" s="32" t="inlineStr"/>
+      <c r="O530" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -32297,6 +32415,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J526" r:id="rId257"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J527" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J528" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J529" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J530" r:id="rId261"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O530"/>
+  <dimension ref="A1:O531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -32142,6 +32142,65 @@
       </c>
       <c r="N530" s="32" t="inlineStr"/>
       <c r="O530" s="31" t="inlineStr"/>
+    </row>
+    <row r="531" ht="16" customHeight="1">
+      <c r="A531" s="33" t="inlineStr">
+        <is>
+          <t>a2717522cd0c</t>
+        </is>
+      </c>
+      <c r="B531" s="33" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="C531" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Sector AMP8</t>
+        </is>
+      </c>
+      <c r="D531" s="33" t="inlineStr">
+        <is>
+          <t>Arcadis</t>
+        </is>
+      </c>
+      <c r="E531" s="33" t="inlineStr">
+        <is>
+          <t>Cambridge, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F531" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G531" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H531" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I531" s="33" t="n">
+        <v>75</v>
+      </c>
+      <c r="J531" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K531" s="35" t="inlineStr"/>
+      <c r="L531" s="35" t="inlineStr"/>
+      <c r="M531" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N531" s="36" t="inlineStr"/>
+      <c r="O531" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -32417,6 +32476,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J528" r:id="rId259"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J529" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J530" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J531" r:id="rId262"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O531"/>
+  <dimension ref="A1:O532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -32201,6 +32201,65 @@
       </c>
       <c r="N531" s="36" t="inlineStr"/>
       <c r="O531" s="35" t="inlineStr"/>
+    </row>
+    <row r="532" ht="16" customHeight="1">
+      <c r="A532" s="28" t="inlineStr">
+        <is>
+          <t>36337a032691</t>
+        </is>
+      </c>
+      <c r="B532" s="28" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="C532" s="28" t="inlineStr">
+        <is>
+          <t>Design Engineer (Water)</t>
+        </is>
+      </c>
+      <c r="D532" s="28" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E532" s="28" t="inlineStr">
+        <is>
+          <t>Birmingham, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F532" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G532" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H532" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I532" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J532" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K532" s="31" t="inlineStr"/>
+      <c r="L532" s="31" t="inlineStr"/>
+      <c r="M532" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N532" s="32" t="inlineStr"/>
+      <c r="O532" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -32477,6 +32536,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J529" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J530" r:id="rId261"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J531" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J532" r:id="rId263"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O532"/>
+  <dimension ref="A1:O533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -32260,6 +32260,65 @@
       </c>
       <c r="N532" s="32" t="inlineStr"/>
       <c r="O532" s="31" t="inlineStr"/>
+    </row>
+    <row r="533" ht="16" customHeight="1">
+      <c r="A533" s="33" t="inlineStr">
+        <is>
+          <t>c79b6f4cab84</t>
+        </is>
+      </c>
+      <c r="B533" s="33" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="C533" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater (Hydraulic) Modeller</t>
+        </is>
+      </c>
+      <c r="D533" s="33" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E533" s="33" t="inlineStr">
+        <is>
+          <t>Sheffield, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F533" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G533" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H533" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I533" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J533" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K533" s="35" t="inlineStr"/>
+      <c r="L533" s="35" t="inlineStr"/>
+      <c r="M533" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N533" s="36" t="inlineStr"/>
+      <c r="O533" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -32537,6 +32596,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J530" r:id="rId261"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J531" r:id="rId262"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J532" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J533" r:id="rId264"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O533"/>
+  <dimension ref="A1:O537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -32319,6 +32319,242 @@
       </c>
       <c r="N533" s="36" t="inlineStr"/>
       <c r="O533" s="35" t="inlineStr"/>
+    </row>
+    <row r="534" ht="16" customHeight="1">
+      <c r="A534" s="28" t="inlineStr">
+        <is>
+          <t>ced89a3f9210</t>
+        </is>
+      </c>
+      <c r="B534" s="28" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="C534" s="28" t="inlineStr">
+        <is>
+          <t>Flood Risk &amp; Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D534" s="28" t="inlineStr">
+        <is>
+          <t>Hays</t>
+        </is>
+      </c>
+      <c r="E534" s="28" t="inlineStr">
+        <is>
+          <t>Lincolnshire, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F534" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G534" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H534" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I534" s="28" t="n">
+        <v>90</v>
+      </c>
+      <c r="J534" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K534" s="31" t="inlineStr"/>
+      <c r="L534" s="31" t="inlineStr"/>
+      <c r="M534" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N534" s="32" t="inlineStr"/>
+      <c r="O534" s="31" t="inlineStr"/>
+    </row>
+    <row r="535" ht="16" customHeight="1">
+      <c r="A535" s="33" t="inlineStr">
+        <is>
+          <t>a39fd6c12de7</t>
+        </is>
+      </c>
+      <c r="B535" s="33" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="C535" s="33" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Wastewater Infrastructure</t>
+        </is>
+      </c>
+      <c r="D535" s="33" t="inlineStr">
+        <is>
+          <t>Advance TRS</t>
+        </is>
+      </c>
+      <c r="E535" s="33" t="inlineStr">
+        <is>
+          <t>Chalvey, Slough</t>
+        </is>
+      </c>
+      <c r="F535" s="33" t="inlineStr">
+        <is>
+          <t>£40,000 – £55,000</t>
+        </is>
+      </c>
+      <c r="G535" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H535" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I535" s="33" t="n">
+        <v>85</v>
+      </c>
+      <c r="J535" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K535" s="35" t="inlineStr"/>
+      <c r="L535" s="35" t="inlineStr"/>
+      <c r="M535" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N535" s="36" t="inlineStr"/>
+      <c r="O535" s="35" t="inlineStr"/>
+    </row>
+    <row r="536" ht="16" customHeight="1">
+      <c r="A536" s="28" t="inlineStr">
+        <is>
+          <t>0eecaf8df3eb</t>
+        </is>
+      </c>
+      <c r="B536" s="28" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="C536" s="28" t="inlineStr">
+        <is>
+          <t>Design Engineer (Water)</t>
+        </is>
+      </c>
+      <c r="D536" s="28" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E536" s="28" t="inlineStr">
+        <is>
+          <t>Birmingham, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F536" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G536" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H536" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I536" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J536" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K536" s="31" t="inlineStr"/>
+      <c r="L536" s="31" t="inlineStr"/>
+      <c r="M536" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N536" s="32" t="inlineStr"/>
+      <c r="O536" s="31" t="inlineStr"/>
+    </row>
+    <row r="537" ht="16" customHeight="1">
+      <c r="A537" s="33" t="inlineStr">
+        <is>
+          <t>581cd4c03261</t>
+        </is>
+      </c>
+      <c r="B537" s="33" t="inlineStr">
+        <is>
+          <t>22/08/2026</t>
+        </is>
+      </c>
+      <c r="C537" s="33" t="inlineStr">
+        <is>
+          <t>NavCom Field Service Engineer</t>
+        </is>
+      </c>
+      <c r="D537" s="33" t="inlineStr">
+        <is>
+          <t>Elvis Eckardt Recruitment</t>
+        </is>
+      </c>
+      <c r="E537" s="33" t="inlineStr">
+        <is>
+          <t>Portsmouth, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F537" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G537" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H537" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I537" s="33" t="n">
+        <v>80</v>
+      </c>
+      <c r="J537" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K537" s="35" t="inlineStr"/>
+      <c r="L537" s="35" t="inlineStr"/>
+      <c r="M537" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N537" s="36" t="inlineStr"/>
+      <c r="O537" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -32597,6 +32833,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J531" r:id="rId262"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J532" r:id="rId263"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J533" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J534" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J535" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J536" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J537" r:id="rId268"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O537"/>
+  <dimension ref="A1:O538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -32555,6 +32555,65 @@
       </c>
       <c r="N537" s="36" t="inlineStr"/>
       <c r="O537" s="35" t="inlineStr"/>
+    </row>
+    <row r="538" ht="16" customHeight="1">
+      <c r="A538" s="28" t="inlineStr">
+        <is>
+          <t>386a5a4f6f74</t>
+        </is>
+      </c>
+      <c r="B538" s="28" t="inlineStr">
+        <is>
+          <t>23/08/2026</t>
+        </is>
+      </c>
+      <c r="C538" s="28" t="inlineStr">
+        <is>
+          <t>Engineering Supervisor (Pumps / Water Infrastructure)</t>
+        </is>
+      </c>
+      <c r="D538" s="28" t="inlineStr">
+        <is>
+          <t>Ernest Gordon Recruitment</t>
+        </is>
+      </c>
+      <c r="E538" s="28" t="inlineStr">
+        <is>
+          <t>Edinburgh, Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F538" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G538" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H538" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I538" s="28" t="n">
+        <v>65</v>
+      </c>
+      <c r="J538" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K538" s="31" t="inlineStr"/>
+      <c r="L538" s="31" t="inlineStr"/>
+      <c r="M538" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N538" s="32" t="inlineStr"/>
+      <c r="O538" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -32837,6 +32896,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J535" r:id="rId266"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J536" r:id="rId267"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J537" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J538" r:id="rId269"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O538"/>
+  <dimension ref="A1:O540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -32614,6 +32614,124 @@
       </c>
       <c r="N538" s="32" t="inlineStr"/>
       <c r="O538" s="31" t="inlineStr"/>
+    </row>
+    <row r="539" ht="16" customHeight="1">
+      <c r="A539" s="33" t="inlineStr">
+        <is>
+          <t>88f8298ef3f4</t>
+        </is>
+      </c>
+      <c r="B539" s="33" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="C539" s="33" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller - UK Water / Wastewater</t>
+        </is>
+      </c>
+      <c r="D539" s="33" t="inlineStr">
+        <is>
+          <t>Egis</t>
+        </is>
+      </c>
+      <c r="E539" s="33" t="inlineStr">
+        <is>
+          <t>Manchester, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F539" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G539" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H539" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I539" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="J539" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K539" s="35" t="inlineStr"/>
+      <c r="L539" s="35" t="inlineStr"/>
+      <c r="M539" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N539" s="36" t="inlineStr"/>
+      <c r="O539" s="35" t="inlineStr"/>
+    </row>
+    <row r="540" ht="16" customHeight="1">
+      <c r="A540" s="28" t="inlineStr">
+        <is>
+          <t>edbcda21f3dd</t>
+        </is>
+      </c>
+      <c r="B540" s="28" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
+      </c>
+      <c r="C540" s="28" t="inlineStr">
+        <is>
+          <t>Civil Designer - Water</t>
+        </is>
+      </c>
+      <c r="D540" s="28" t="inlineStr">
+        <is>
+          <t>Jacobs</t>
+        </is>
+      </c>
+      <c r="E540" s="28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F540" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G540" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H540" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I540" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J540" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K540" s="31" t="inlineStr"/>
+      <c r="L540" s="31" t="inlineStr"/>
+      <c r="M540" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N540" s="32" t="inlineStr"/>
+      <c r="O540" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -32897,6 +33015,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J536" r:id="rId267"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J537" r:id="rId268"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J538" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J539" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J540" r:id="rId271"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O540"/>
+  <dimension ref="A1:O542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -32732,6 +32732,124 @@
       </c>
       <c r="N540" s="32" t="inlineStr"/>
       <c r="O540" s="31" t="inlineStr"/>
+    </row>
+    <row r="541" ht="16" customHeight="1">
+      <c r="A541" s="33" t="inlineStr">
+        <is>
+          <t>b74854844894</t>
+        </is>
+      </c>
+      <c r="B541" s="33" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="C541" s="33" t="inlineStr">
+        <is>
+          <t>Design Manager - Water Sector</t>
+        </is>
+      </c>
+      <c r="D541" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E541" s="33" t="inlineStr">
+        <is>
+          <t>Reading, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F541" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G541" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H541" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I541" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J541" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K541" s="35" t="inlineStr"/>
+      <c r="L541" s="35" t="inlineStr"/>
+      <c r="M541" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N541" s="36" t="inlineStr"/>
+      <c r="O541" s="35" t="inlineStr"/>
+    </row>
+    <row r="542" ht="16" customHeight="1">
+      <c r="A542" s="28" t="inlineStr">
+        <is>
+          <t>9b168736da61</t>
+        </is>
+      </c>
+      <c r="B542" s="28" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="C542" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Design Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D542" s="28" t="inlineStr">
+        <is>
+          <t>Finlay Jude Recruitment Ltd</t>
+        </is>
+      </c>
+      <c r="E542" s="28" t="inlineStr">
+        <is>
+          <t>Batley, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F542" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G542" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H542" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I542" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J542" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K542" s="31" t="inlineStr"/>
+      <c r="L542" s="31" t="inlineStr"/>
+      <c r="M542" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N542" s="32" t="inlineStr"/>
+      <c r="O542" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -33017,6 +33135,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J538" r:id="rId269"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J539" r:id="rId270"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J540" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J541" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J542" r:id="rId273"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O542"/>
+  <dimension ref="A1:O543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -32850,6 +32850,65 @@
       </c>
       <c r="N542" s="32" t="inlineStr"/>
       <c r="O542" s="31" t="inlineStr"/>
+    </row>
+    <row r="543" ht="16" customHeight="1">
+      <c r="A543" s="33" t="inlineStr">
+        <is>
+          <t>6efe1e8e0e02</t>
+        </is>
+      </c>
+      <c r="B543" s="33" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="C543" s="33" t="inlineStr">
+        <is>
+          <t>Expression of Interest - Design Manager - Water Sector</t>
+        </is>
+      </c>
+      <c r="D543" s="33" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E543" s="33" t="inlineStr">
+        <is>
+          <t>Brighton, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F543" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G543" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H543" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I543" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J543" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K543" s="35" t="inlineStr"/>
+      <c r="L543" s="35" t="inlineStr"/>
+      <c r="M543" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N543" s="36" t="inlineStr"/>
+      <c r="O543" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -33137,6 +33196,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J540" r:id="rId271"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J541" r:id="rId272"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J542" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J543" r:id="rId274"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O543"/>
+  <dimension ref="A1:O544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -32909,6 +32909,65 @@
       </c>
       <c r="N543" s="36" t="inlineStr"/>
       <c r="O543" s="35" t="inlineStr"/>
+    </row>
+    <row r="544" ht="16" customHeight="1">
+      <c r="A544" s="28" t="inlineStr">
+        <is>
+          <t>e5b5335346e5</t>
+        </is>
+      </c>
+      <c r="B544" s="28" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="C544" s="28" t="inlineStr">
+        <is>
+          <t>Expression of Interest - Design Manager - Water Sector</t>
+        </is>
+      </c>
+      <c r="D544" s="28" t="inlineStr">
+        <is>
+          <t>Stantec</t>
+        </is>
+      </c>
+      <c r="E544" s="28" t="inlineStr">
+        <is>
+          <t>Cambridge, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F544" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G544" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H544" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I544" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J544" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K544" s="31" t="inlineStr"/>
+      <c r="L544" s="31" t="inlineStr"/>
+      <c r="M544" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N544" s="32" t="inlineStr"/>
+      <c r="O544" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -33197,6 +33256,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J541" r:id="rId272"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J542" r:id="rId273"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J543" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J544" r:id="rId275"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O544"/>
+  <dimension ref="A1:O545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -32968,6 +32968,65 @@
       </c>
       <c r="N544" s="32" t="inlineStr"/>
       <c r="O544" s="31" t="inlineStr"/>
+    </row>
+    <row r="545" ht="16" customHeight="1">
+      <c r="A545" s="33" t="inlineStr">
+        <is>
+          <t>ea06c15702be</t>
+        </is>
+      </c>
+      <c r="B545" s="33" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="C545" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D545" s="33" t="inlineStr">
+        <is>
+          <t>Mott MacDonald</t>
+        </is>
+      </c>
+      <c r="E545" s="33" t="inlineStr">
+        <is>
+          <t>Leeds, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F545" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G545" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H545" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I545" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J545" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K545" s="35" t="inlineStr"/>
+      <c r="L545" s="35" t="inlineStr"/>
+      <c r="M545" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N545" s="36" t="inlineStr"/>
+      <c r="O545" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -33257,6 +33316,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J542" r:id="rId273"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J543" r:id="rId274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J544" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J545" r:id="rId276"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O545"/>
+  <dimension ref="A1:O547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -33027,6 +33027,124 @@
       </c>
       <c r="N545" s="36" t="inlineStr"/>
       <c r="O545" s="35" t="inlineStr"/>
+    </row>
+    <row r="546" ht="16" customHeight="1">
+      <c r="A546" s="28" t="inlineStr">
+        <is>
+          <t>537082c150a4</t>
+        </is>
+      </c>
+      <c r="B546" s="28" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C546" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Industry</t>
+        </is>
+      </c>
+      <c r="D546" s="28" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E546" s="28" t="inlineStr">
+        <is>
+          <t>Exeter, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F546" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G546" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H546" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I546" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J546" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K546" s="31" t="inlineStr"/>
+      <c r="L546" s="31" t="inlineStr"/>
+      <c r="M546" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N546" s="32" t="inlineStr"/>
+      <c r="O546" s="31" t="inlineStr"/>
+    </row>
+    <row r="547" ht="16" customHeight="1">
+      <c r="A547" s="33" t="inlineStr">
+        <is>
+          <t>ac118ce7168e</t>
+        </is>
+      </c>
+      <c r="B547" s="33" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C547" s="33" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D547" s="33" t="inlineStr">
+        <is>
+          <t>WSP in the UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="E547" s="33" t="inlineStr">
+        <is>
+          <t>Newcastle Upon Tyne, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F547" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G547" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H547" s="37" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="I547" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J547" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K547" s="35" t="inlineStr"/>
+      <c r="L547" s="35" t="inlineStr"/>
+      <c r="M547" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N547" s="36" t="inlineStr"/>
+      <c r="O547" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -33317,6 +33435,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J543" r:id="rId274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J544" r:id="rId275"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J545" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J546" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J547" r:id="rId278"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O547"/>
+  <dimension ref="A1:O552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -33145,6 +33145,301 @@
       </c>
       <c r="N547" s="36" t="inlineStr"/>
       <c r="O547" s="35" t="inlineStr"/>
+    </row>
+    <row r="548" ht="16" customHeight="1">
+      <c r="A548" s="28" t="inlineStr">
+        <is>
+          <t>ce85463f0e98</t>
+        </is>
+      </c>
+      <c r="B548" s="28" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="C548" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Industry</t>
+        </is>
+      </c>
+      <c r="D548" s="28" t="inlineStr">
+        <is>
+          <t>Tetra Tech Europe</t>
+        </is>
+      </c>
+      <c r="E548" s="28" t="inlineStr">
+        <is>
+          <t>Brighton, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F548" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G548" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H548" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I548" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J548" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K548" s="31" t="inlineStr"/>
+      <c r="L548" s="31" t="inlineStr"/>
+      <c r="M548" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N548" s="32" t="inlineStr"/>
+      <c r="O548" s="31" t="inlineStr"/>
+    </row>
+    <row r="549" ht="16" customHeight="1">
+      <c r="A549" s="33" t="inlineStr">
+        <is>
+          <t>96d681082328</t>
+        </is>
+      </c>
+      <c r="B549" s="33" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="C549" s="33" t="inlineStr">
+        <is>
+          <t>Hydraulic Project / Design Engineer</t>
+        </is>
+      </c>
+      <c r="D549" s="33" t="inlineStr">
+        <is>
+          <t>Maritime Developments Limited</t>
+        </is>
+      </c>
+      <c r="E549" s="33" t="inlineStr">
+        <is>
+          <t>Aberdeen, Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F549" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G549" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H549" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I549" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J549" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K549" s="35" t="inlineStr"/>
+      <c r="L549" s="35" t="inlineStr"/>
+      <c r="M549" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N549" s="36" t="inlineStr"/>
+      <c r="O549" s="35" t="inlineStr"/>
+    </row>
+    <row r="550" ht="16" customHeight="1">
+      <c r="A550" s="28" t="inlineStr">
+        <is>
+          <t>812faa0bca71</t>
+        </is>
+      </c>
+      <c r="B550" s="28" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="C550" s="28" t="inlineStr">
+        <is>
+          <t>Water Network Analyst</t>
+        </is>
+      </c>
+      <c r="D550" s="28" t="inlineStr">
+        <is>
+          <t>NWG (Northumbrian Water Group)</t>
+        </is>
+      </c>
+      <c r="E550" s="28" t="inlineStr">
+        <is>
+          <t>Chelmsford, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F550" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G550" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H550" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I550" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J550" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K550" s="31" t="inlineStr"/>
+      <c r="L550" s="31" t="inlineStr"/>
+      <c r="M550" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N550" s="32" t="inlineStr"/>
+      <c r="O550" s="31" t="inlineStr"/>
+    </row>
+    <row r="551" ht="16" customHeight="1">
+      <c r="A551" s="33" t="inlineStr">
+        <is>
+          <t>e5b24f5cddea</t>
+        </is>
+      </c>
+      <c r="B551" s="33" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="C551" s="33" t="inlineStr">
+        <is>
+          <t>Water Network Controller</t>
+        </is>
+      </c>
+      <c r="D551" s="33" t="inlineStr">
+        <is>
+          <t>South Staffs Water</t>
+        </is>
+      </c>
+      <c r="E551" s="33" t="inlineStr">
+        <is>
+          <t>Cambridge, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F551" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G551" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H551" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I551" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J551" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K551" s="35" t="inlineStr"/>
+      <c r="L551" s="35" t="inlineStr"/>
+      <c r="M551" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N551" s="36" t="inlineStr"/>
+      <c r="O551" s="35" t="inlineStr"/>
+    </row>
+    <row r="552" ht="16" customHeight="1">
+      <c r="A552" s="28" t="inlineStr">
+        <is>
+          <t>807096552ae4</t>
+        </is>
+      </c>
+      <c r="B552" s="28" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="C552" s="28" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer – Water &amp; Infrastructure Projects – 20310</t>
+        </is>
+      </c>
+      <c r="D552" s="28" t="inlineStr">
+        <is>
+          <t>RR</t>
+        </is>
+      </c>
+      <c r="E552" s="28" t="inlineStr">
+        <is>
+          <t>Sheffield, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F552" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G552" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H552" s="38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I552" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J552" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K552" s="31" t="inlineStr"/>
+      <c r="L552" s="31" t="inlineStr"/>
+      <c r="M552" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N552" s="32" t="inlineStr"/>
+      <c r="O552" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -33437,6 +33732,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J545" r:id="rId276"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J546" r:id="rId277"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J547" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J548" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J549" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J550" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J551" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J552" r:id="rId283"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O552"/>
+  <dimension ref="A1:O554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -33440,6 +33440,124 @@
       </c>
       <c r="N552" s="32" t="inlineStr"/>
       <c r="O552" s="31" t="inlineStr"/>
+    </row>
+    <row r="553" ht="16" customHeight="1">
+      <c r="A553" s="33" t="inlineStr">
+        <is>
+          <t>20d61c8370f9</t>
+        </is>
+      </c>
+      <c r="B553" s="33" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="C553" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water Sector AMP8</t>
+        </is>
+      </c>
+      <c r="D553" s="33" t="inlineStr">
+        <is>
+          <t>Arcadis</t>
+        </is>
+      </c>
+      <c r="E553" s="33" t="inlineStr">
+        <is>
+          <t>Plymouth, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F553" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G553" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H553" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I553" s="33" t="n">
+        <v>75</v>
+      </c>
+      <c r="J553" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K553" s="35" t="inlineStr"/>
+      <c r="L553" s="35" t="inlineStr"/>
+      <c r="M553" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N553" s="36" t="inlineStr"/>
+      <c r="O553" s="35" t="inlineStr"/>
+    </row>
+    <row r="554" ht="16" customHeight="1">
+      <c r="A554" s="28" t="inlineStr">
+        <is>
+          <t>70be2541759e</t>
+        </is>
+      </c>
+      <c r="B554" s="28" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="C554" s="28" t="inlineStr">
+        <is>
+          <t>Wastewater Network Modeller</t>
+        </is>
+      </c>
+      <c r="D554" s="28" t="inlineStr">
+        <is>
+          <t>WSP in the UK &amp; Ireland</t>
+        </is>
+      </c>
+      <c r="E554" s="28" t="inlineStr">
+        <is>
+          <t>England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F554" s="28" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G554" s="28" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H554" s="37" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="I554" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="J554" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K554" s="31" t="inlineStr"/>
+      <c r="L554" s="31" t="inlineStr"/>
+      <c r="M554" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N554" s="32" t="inlineStr"/>
+      <c r="O554" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -33737,6 +33855,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J550" r:id="rId281"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J551" r:id="rId282"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J552" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J553" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J554" r:id="rId285"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O554"/>
+  <dimension ref="A1:O555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -33558,6 +33558,65 @@
       </c>
       <c r="N554" s="32" t="inlineStr"/>
       <c r="O554" s="31" t="inlineStr"/>
+    </row>
+    <row r="555" ht="16" customHeight="1">
+      <c r="A555" s="33" t="inlineStr">
+        <is>
+          <t>55212327de67</t>
+        </is>
+      </c>
+      <c r="B555" s="33" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="C555" s="33" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D555" s="33" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment</t>
+        </is>
+      </c>
+      <c r="E555" s="33" t="inlineStr">
+        <is>
+          <t>The City, Central London</t>
+        </is>
+      </c>
+      <c r="F555" s="33" t="inlineStr">
+        <is>
+          <t>£40,000 – £50,000</t>
+        </is>
+      </c>
+      <c r="G555" s="33" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H555" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I555" s="33" t="n">
+        <v>160</v>
+      </c>
+      <c r="J555" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K555" s="35" t="inlineStr"/>
+      <c r="L555" s="35" t="inlineStr"/>
+      <c r="M555" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N555" s="36" t="inlineStr"/>
+      <c r="O555" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -33857,6 +33916,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J552" r:id="rId283"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J553" r:id="rId284"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J554" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J555" r:id="rId286"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O555"/>
+  <dimension ref="A1:O557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -33617,6 +33617,124 @@
       </c>
       <c r="N555" s="36" t="inlineStr"/>
       <c r="O555" s="35" t="inlineStr"/>
+    </row>
+    <row r="556" ht="16" customHeight="1">
+      <c r="A556" s="28" t="inlineStr">
+        <is>
+          <t>79f319cd94ae</t>
+        </is>
+      </c>
+      <c r="B556" s="28" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C556" s="28" t="inlineStr">
+        <is>
+          <t>Hydraulic Modeller</t>
+        </is>
+      </c>
+      <c r="D556" s="28" t="inlineStr">
+        <is>
+          <t>Penguin Recruitment Ltd</t>
+        </is>
+      </c>
+      <c r="E556" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F556" s="28" t="inlineStr">
+        <is>
+          <t>£43,496 – £43,496</t>
+        </is>
+      </c>
+      <c r="G556" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H556" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I556" s="28" t="n">
+        <v>160</v>
+      </c>
+      <c r="J556" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K556" s="31" t="inlineStr"/>
+      <c r="L556" s="31" t="inlineStr"/>
+      <c r="M556" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N556" s="32" t="inlineStr"/>
+      <c r="O556" s="31" t="inlineStr"/>
+    </row>
+    <row r="557" ht="16" customHeight="1">
+      <c r="A557" s="33" t="inlineStr">
+        <is>
+          <t>2b663d4deedf</t>
+        </is>
+      </c>
+      <c r="B557" s="33" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="C557" s="33" t="inlineStr">
+        <is>
+          <t>Civil Design Engineer - Water &amp; Infrastructure Projects</t>
+        </is>
+      </c>
+      <c r="D557" s="33" t="inlineStr">
+        <is>
+          <t>CHG Electrical</t>
+        </is>
+      </c>
+      <c r="E557" s="33" t="inlineStr">
+        <is>
+          <t>Sheffield, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="F557" s="33" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="G557" s="33" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="H557" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I557" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J557" s="34" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K557" s="35" t="inlineStr"/>
+      <c r="L557" s="35" t="inlineStr"/>
+      <c r="M557" s="35" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N557" s="36" t="inlineStr"/>
+      <c r="O557" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -33917,6 +34035,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J553" r:id="rId284"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J554" r:id="rId285"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J555" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J556" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J557" r:id="rId288"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/job_tracker.xlsx
+++ b/job_tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O557"/>
+  <dimension ref="A1:O558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="14" customWidth="1" min="1" max="1"/>
@@ -33735,6 +33735,65 @@
       </c>
       <c r="N557" s="36" t="inlineStr"/>
       <c r="O557" s="35" t="inlineStr"/>
+    </row>
+    <row r="558" ht="16" customHeight="1">
+      <c r="A558" s="28" t="inlineStr">
+        <is>
+          <t>9b85a37955d7</t>
+        </is>
+      </c>
+      <c r="B558" s="28" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="C558" s="28" t="inlineStr">
+        <is>
+          <t>Hydrologist- Flood Risk and Hydraulic Modelling Consultant</t>
+        </is>
+      </c>
+      <c r="D558" s="28" t="inlineStr">
+        <is>
+          <t>Ramboll</t>
+        </is>
+      </c>
+      <c r="E558" s="28" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="F558" s="28" t="inlineStr">
+        <is>
+          <t>£43,813 – £43,813</t>
+        </is>
+      </c>
+      <c r="G558" s="28" t="inlineStr">
+        <is>
+          <t>Adzuna UK</t>
+        </is>
+      </c>
+      <c r="H558" s="29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="I558" s="28" t="n">
+        <v>110</v>
+      </c>
+      <c r="J558" s="30" t="inlineStr">
+        <is>
+          <t>Apply Here</t>
+        </is>
+      </c>
+      <c r="K558" s="31" t="inlineStr"/>
+      <c r="L558" s="31" t="inlineStr"/>
+      <c r="M558" s="31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="N558" s="32" t="inlineStr"/>
+      <c r="O558" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -34037,6 +34096,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J555" r:id="rId286"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J556" r:id="rId287"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J557" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J558" r:id="rId289"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
